--- a/inventaire_mobilier.xlsx
+++ b/inventaire_mobilier.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobilier" sheetId="1" r:id="Rbde5f9b8555c4929"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Photos" sheetId="2" r:id="R982bfabc9a784e9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="3" r:id="R59765c6a848b4eff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobilier" sheetId="1" r:id="R32424bbe41ee467f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Photos" sheetId="2" r:id="R88269b8810ff47a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="3" r:id="R5fab186910124d85"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2113,10 +2113,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="165" formatCode="0\ &quot;€&quot;"/>
+    <x:numFmt numFmtId="200" formatCode="#,##0 &quot;€&quot;"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -2144,8 +2145,19 @@
       <x:color rgb="FF2E2A26"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF243238"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF20343A"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -2172,8 +2184,18 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF3F6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE7EC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="4">
     <x:border/>
     <x:border>
       <x:bottom style="medium">
@@ -2185,11 +2207,16 @@
         <x:color rgb="FFE8E1D5"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFAEBFC7"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -2230,6 +2257,36 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -4969,6 +5026,2073 @@
         <x:v>https://ultimheat.info/search_pdf/1912%20Azurea%20Paris%20export.pdf</x:v>
       </x:c>
     </x:row>
+    <x:row r="49" ht="66" customHeight="1">
+      <x:c r="A49" s="28" t="str">
+        <x:v>MOB-046</x:v>
+      </x:c>
+      <x:c r="B49" s="20" t="str">
+        <x:v>Encoignure à une porte</x:v>
+      </x:c>
+      <x:c r="C49" s="20" t="str">
+        <x:v>Meuble de rangement</x:v>
+      </x:c>
+      <x:c r="D49" s="20" t="str">
+        <x:v>Fin XVIIIe–début XIXe siècle</x:v>
+      </x:c>
+      <x:c r="E49" s="20" t="str">
+        <x:v>Europe occidentale, probablement Italie ou France</x:v>
+      </x:c>
+      <x:c r="F49" s="20" t="str">
+        <x:v>Bois massif teinté, ferrures métalliques</x:v>
+      </x:c>
+      <x:c r="G49" s="20" t="str">
+        <x:v>Encoignure haute à façade coupée, une porte moulurée et deux niveaux intérieurs triangulaires. Corniche et plinthe saillantes; construction rustique ancienne.</x:v>
+      </x:c>
+      <x:c r="H49" s="20" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I49" s="20" t="str">
+        <x:v>État d'usage ancien; usures, chocs et reprises visibles; serrure et stabilité à contrôler</x:v>
+      </x:c>
+      <x:c r="J49" s="21" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K49" s="21" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L49" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M49" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N49" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O49" s="20" t="str">
+        <x:v>encoignure; meuble d'angle; bois; XVIIIe; XIXe</x:v>
+      </x:c>
+      <x:c r="P49" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q49" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="66" customHeight="1">
+      <x:c r="A50" s="29" t="str">
+        <x:v>MOB-047</x:v>
+      </x:c>
+      <x:c r="B50" s="26" t="str">
+        <x:v>Suspension à grand abat-jour textile fleuri</x:v>
+      </x:c>
+      <x:c r="C50" s="26" t="str">
+        <x:v>Luminaire</x:v>
+      </x:c>
+      <x:c r="D50" s="26" t="str">
+        <x:v>Vers 1930–1950</x:v>
+      </x:c>
+      <x:c r="E50" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F50" s="26" t="str">
+        <x:v>Structure métallique, textile imprimé, passementerie</x:v>
+      </x:c>
+      <x:c r="G50" s="26" t="str">
+        <x:v>Grande suspension en forme de dôme segmenté, garnie d'un tissu à décor floral et bordée de franges. Électrification ancienne.</x:v>
+      </x:c>
+      <x:c r="H50" s="26" t="str">
+        <x:v>À relever (diamètre × H)</x:v>
+      </x:c>
+      <x:c r="I50" s="26" t="str">
+        <x:v>Textile passé, taché et fragilisé; franges incomplètes; électrification à réviser</x:v>
+      </x:c>
+      <x:c r="J50" s="27" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K50" s="27" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="L50" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M50" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N50" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O50" s="26" t="str">
+        <x:v>suspension; abat-jour; textile; fleurs; passementerie</x:v>
+      </x:c>
+      <x:c r="P50" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q50" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="66" customHeight="1">
+      <x:c r="A51" s="28" t="str">
+        <x:v>MOB-048</x:v>
+      </x:c>
+      <x:c r="B51" s="20" t="str">
+        <x:v>Suspension à vasque en verre opalin bleu pâle</x:v>
+      </x:c>
+      <x:c r="C51" s="20" t="str">
+        <x:v>Luminaire</x:v>
+      </x:c>
+      <x:c r="D51" s="20" t="str">
+        <x:v>Vers 1930–1950</x:v>
+      </x:c>
+      <x:c r="E51" s="20" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F51" s="20" t="str">
+        <x:v>Verre opalin moulé, métal</x:v>
+      </x:c>
+      <x:c r="G51" s="20" t="str">
+        <x:v>Suspension composée d'une vasque festonnée en verre opalin bleu très pâle, à profil ondulé.</x:v>
+      </x:c>
+      <x:c r="H51" s="20" t="str">
+        <x:v>À relever (diamètre × H)</x:v>
+      </x:c>
+      <x:c r="I51" s="20" t="str">
+        <x:v>Bon état apparent du verre; montage et électrification à contrôler</x:v>
+      </x:c>
+      <x:c r="J51" s="21" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K51" s="21" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="L51" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M51" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N51" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O51" s="20" t="str">
+        <x:v>suspension; opaline; verre moulé; Art déco</x:v>
+      </x:c>
+      <x:c r="P51" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q51" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="66" customHeight="1">
+      <x:c r="A52" s="29" t="str">
+        <x:v>MOB-049</x:v>
+      </x:c>
+      <x:c r="B52" s="26" t="str">
+        <x:v>Applique à deux lumières aux feuilles d'acanthe</x:v>
+      </x:c>
+      <x:c r="C52" s="26" t="str">
+        <x:v>Luminaire</x:v>
+      </x:c>
+      <x:c r="D52" s="26" t="str">
+        <x:v>Vers 1900–1930</x:v>
+      </x:c>
+      <x:c r="E52" s="26" t="str">
+        <x:v>Europe, style historiciste</x:v>
+      </x:c>
+      <x:c r="F52" s="26" t="str">
+        <x:v>Métal repoussé ou fonte d'art dorée, textile</x:v>
+      </x:c>
+      <x:c r="G52" s="26" t="str">
+        <x:v>Applique murale symétrique à deux bras, abondant décor de feuilles d'acanthe et fleurons, avec petits abat-jour demi-lune.</x:v>
+      </x:c>
+      <x:c r="H52" s="26" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I52" s="26" t="str">
+        <x:v>Patine, oxydation et salissures; abat-jour usés; électrification à réviser</x:v>
+      </x:c>
+      <x:c r="J52" s="27" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K52" s="27" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="L52" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M52" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N52" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O52" s="26" t="str">
+        <x:v>applique; deux lumières; acanthe; métal doré; historicisme</x:v>
+      </x:c>
+      <x:c r="P52" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q52" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="66" customHeight="1">
+      <x:c r="A53" s="28" t="str">
+        <x:v>MOB-050</x:v>
+      </x:c>
+      <x:c r="B53" s="20" t="str">
+        <x:v>Lustre à pendeloques de verre</x:v>
+      </x:c>
+      <x:c r="C53" s="20" t="str">
+        <x:v>Luminaire</x:v>
+      </x:c>
+      <x:c r="D53" s="20" t="str">
+        <x:v>Vers 1940–1960</x:v>
+      </x:c>
+      <x:c r="E53" s="20" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F53" s="20" t="str">
+        <x:v>Métal, verre moulé et taillé</x:v>
+      </x:c>
+      <x:c r="G53" s="20" t="str">
+        <x:v>Lustre à plusieurs bras courbes, coupelles et guirlandes de pendeloques en verre, terminé par une boule facettée.</x:v>
+      </x:c>
+      <x:c r="H53" s="20" t="str">
+        <x:v>À relever (H × diamètre)</x:v>
+      </x:c>
+      <x:c r="I53" s="20" t="str">
+        <x:v>Empoussiéré; pendeloques possiblement manquantes; électrification à réviser</x:v>
+      </x:c>
+      <x:c r="J53" s="21" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K53" s="21" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="L53" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M53" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N53" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O53" s="20" t="str">
+        <x:v>lustre; verre; pendeloques; cristal; plusieurs bras</x:v>
+      </x:c>
+      <x:c r="P53" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q53" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="66" customHeight="1">
+      <x:c r="A54" s="29" t="str">
+        <x:v>MOB-051</x:v>
+      </x:c>
+      <x:c r="B54" s="26" t="str">
+        <x:v>Applique à deux lumières au motif de fleur de lys</x:v>
+      </x:c>
+      <x:c r="C54" s="26" t="str">
+        <x:v>Luminaire</x:v>
+      </x:c>
+      <x:c r="D54" s="26" t="str">
+        <x:v>Vers 1940–1960</x:v>
+      </x:c>
+      <x:c r="E54" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F54" s="26" t="str">
+        <x:v>Fer forgé ou tôle dorée</x:v>
+      </x:c>
+      <x:c r="G54" s="26" t="str">
+        <x:v>Applique à deux bras en volutes sur une platine découpée en fleur de lys.</x:v>
+      </x:c>
+      <x:c r="H54" s="26" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I54" s="26" t="str">
+        <x:v>Usures et oxydation; douilles et câblage à contrôler</x:v>
+      </x:c>
+      <x:c r="J54" s="27" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K54" s="27" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="L54" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M54" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N54" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O54" s="26" t="str">
+        <x:v>applique; fleur de lys; fer doré; deux lumières</x:v>
+      </x:c>
+      <x:c r="P54" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q54" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="66" customHeight="1">
+      <x:c r="A55" s="28" t="str">
+        <x:v>MOB-052</x:v>
+      </x:c>
+      <x:c r="B55" s="20" t="str">
+        <x:v>Suspension à vasque festonnée jaune pâle</x:v>
+      </x:c>
+      <x:c r="C55" s="20" t="str">
+        <x:v>Luminaire</x:v>
+      </x:c>
+      <x:c r="D55" s="20" t="str">
+        <x:v>Vers 1930–1950</x:v>
+      </x:c>
+      <x:c r="E55" s="20" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F55" s="20" t="str">
+        <x:v>Verre opalin teinté, métal</x:v>
+      </x:c>
+      <x:c r="G55" s="20" t="str">
+        <x:v>Suspension à large vasque côtelée et festonnée en verre opalin jaune pâle.</x:v>
+      </x:c>
+      <x:c r="H55" s="20" t="str">
+        <x:v>À relever (diamètre × H)</x:v>
+      </x:c>
+      <x:c r="I55" s="20" t="str">
+        <x:v>Salissures et petites usures; verre apparemment intact; électrification à revoir</x:v>
+      </x:c>
+      <x:c r="J55" s="21" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="K55" s="21" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="L55" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M55" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N55" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O55" s="20" t="str">
+        <x:v>suspension; opaline; verre jaune; vasque festonnée</x:v>
+      </x:c>
+      <x:c r="P55" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q55" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="66" customHeight="1">
+      <x:c r="A56" s="29" t="str">
+        <x:v>MOB-053</x:v>
+      </x:c>
+      <x:c r="B56" s="26" t="str">
+        <x:v>Coffre en bois à façade panneautée</x:v>
+      </x:c>
+      <x:c r="C56" s="26" t="str">
+        <x:v>Meuble de rangement</x:v>
+      </x:c>
+      <x:c r="D56" s="26" t="str">
+        <x:v>XIXe siècle</x:v>
+      </x:c>
+      <x:c r="E56" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F56" s="26" t="str">
+        <x:v>Bois massif, ferrures métalliques</x:v>
+      </x:c>
+      <x:c r="G56" s="26" t="str">
+        <x:v>Coffre rectangulaire à couvercle légèrement débordant, façade composée de larges panneaux horizontaux et petits pieds.</x:v>
+      </x:c>
+      <x:c r="H56" s="26" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I56" s="26" t="str">
+        <x:v>Usures, rayures et trous d'insectes possibles; intérieur et serrure non examinés</x:v>
+      </x:c>
+      <x:c r="J56" s="27" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K56" s="27" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="L56" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M56" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N56" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O56" s="26" t="str">
+        <x:v>coffre; bois massif; rangement; XIXe</x:v>
+      </x:c>
+      <x:c r="P56" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q56" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="66" customHeight="1">
+      <x:c r="A57" s="28" t="str">
+        <x:v>MOB-054</x:v>
+      </x:c>
+      <x:c r="B57" s="20" t="str">
+        <x:v>Meuble de toilette à dessus de marbre et miroir triptyque</x:v>
+      </x:c>
+      <x:c r="C57" s="20" t="str">
+        <x:v>Mobilier de toilette</x:v>
+      </x:c>
+      <x:c r="D57" s="20" t="str">
+        <x:v>Vers 1900–1930</x:v>
+      </x:c>
+      <x:c r="E57" s="20" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F57" s="20" t="str">
+        <x:v>Marbre veiné, laiton ou bronze, bois, miroir</x:v>
+      </x:c>
+      <x:c r="G57" s="20" t="str">
+        <x:v>Meuble de toilette à deux plateaux de marbre, montants métalliques et miroir triptyque orientable; supports latéraux et anneau porte-cuvette.</x:v>
+      </x:c>
+      <x:c r="H57" s="20" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I57" s="20" t="str">
+        <x:v>Miroirs absents ou déposés sur les volets photographiés; piqûres et oxydation; marbre à contrôler</x:v>
+      </x:c>
+      <x:c r="J57" s="21" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="K57" s="21" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L57" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M57" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N57" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O57" s="20" t="str">
+        <x:v>toilette; coiffeuse; marbre; laiton; miroir triptyque</x:v>
+      </x:c>
+      <x:c r="P57" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q57" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="66" customHeight="1">
+      <x:c r="A58" s="29" t="str">
+        <x:v>MOB-055</x:v>
+      </x:c>
+      <x:c r="B58" s="26" t="str">
+        <x:v>Petite table noire à piètement cannelé</x:v>
+      </x:c>
+      <x:c r="C58" s="26" t="str">
+        <x:v>Table d'appoint</x:v>
+      </x:c>
+      <x:c r="D58" s="26" t="str">
+        <x:v>Fin XIXe–début XXe siècle</x:v>
+      </x:c>
+      <x:c r="E58" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F58" s="26" t="str">
+        <x:v>Bois noirci</x:v>
+      </x:c>
+      <x:c r="G58" s="26" t="str">
+        <x:v>Petite table rectangulaire en bois noirci, pieds jumelés cannelés réunis par des traverses basses.</x:v>
+      </x:c>
+      <x:c r="H58" s="26" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I58" s="26" t="str">
+        <x:v>Plateau rayé et usé; petits éclats; stabilité à contrôler</x:v>
+      </x:c>
+      <x:c r="J58" s="27" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K58" s="27" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="L58" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M58" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N58" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O58" s="26" t="str">
+        <x:v>table d'appoint; bois noirci; pieds cannelés</x:v>
+      </x:c>
+      <x:c r="P58" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q58" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="66" customHeight="1">
+      <x:c r="A59" s="28" t="str">
+        <x:v>MOB-056</x:v>
+      </x:c>
+      <x:c r="B59" s="20" t="str">
+        <x:v>Chaise en bois courbé et cannage</x:v>
+      </x:c>
+      <x:c r="C59" s="20" t="str">
+        <x:v>Siège</x:v>
+      </x:c>
+      <x:c r="D59" s="20" t="str">
+        <x:v>Vers 1900–1930</x:v>
+      </x:c>
+      <x:c r="E59" s="20" t="str">
+        <x:v>Europe centrale, dans le goût de Thonet</x:v>
+      </x:c>
+      <x:c r="F59" s="20" t="str">
+        <x:v>Hêtre courbé teinté, cannage</x:v>
+      </x:c>
+      <x:c r="G59" s="20" t="str">
+        <x:v>Chaise à haut dossier ovale canné, assise cannée et montants en bois courbé; marquages au revers peu lisibles.</x:v>
+      </x:c>
+      <x:c r="H59" s="20" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I59" s="20" t="str">
+        <x:v>Cannage refait ou restauré, avec quelques défauts; structure à contrôler</x:v>
+      </x:c>
+      <x:c r="J59" s="21" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K59" s="21" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="L59" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M59" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N59" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O59" s="20" t="str">
+        <x:v>chaise; bois courbé; cannage; Thonet; bistrot</x:v>
+      </x:c>
+      <x:c r="P59" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q59" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="66" customHeight="1">
+      <x:c r="A60" s="29" t="str">
+        <x:v>MOB-057</x:v>
+      </x:c>
+      <x:c r="B60" s="26" t="str">
+        <x:v>Tabouret de piano pivotant</x:v>
+      </x:c>
+      <x:c r="C60" s="26" t="str">
+        <x:v>Siège</x:v>
+      </x:c>
+      <x:c r="D60" s="26" t="str">
+        <x:v>Vers 1890–1920</x:v>
+      </x:c>
+      <x:c r="E60" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F60" s="26" t="str">
+        <x:v>Bois noirci, cuir, clous métalliques</x:v>
+      </x:c>
+      <x:c r="G60" s="26" t="str">
+        <x:v>Tabouret de piano à assise circulaire pivotante garnie de cuir, porté par un fût central et quatre pieds courbes.</x:v>
+      </x:c>
+      <x:c r="H60" s="26" t="str">
+        <x:v>À relever (H × diamètre)</x:v>
+      </x:c>
+      <x:c r="I60" s="26" t="str">
+        <x:v>Cuir très usé et taché; bois éraflé; mécanisme à contrôler</x:v>
+      </x:c>
+      <x:c r="J60" s="27" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K60" s="27" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="L60" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M60" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N60" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O60" s="26" t="str">
+        <x:v>tabouret de piano; pivotant; cuir; bois courbé</x:v>
+      </x:c>
+      <x:c r="P60" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q60" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="66" customHeight="1">
+      <x:c r="A61" s="28" t="str">
+        <x:v>MOB-058</x:v>
+      </x:c>
+      <x:c r="B61" s="20" t="str">
+        <x:v>Chaise à dossier sculpté et garniture jaune</x:v>
+      </x:c>
+      <x:c r="C61" s="20" t="str">
+        <x:v>Siège</x:v>
+      </x:c>
+      <x:c r="D61" s="20" t="str">
+        <x:v>Vers 1910–1930</x:v>
+      </x:c>
+      <x:c r="E61" s="20" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F61" s="20" t="str">
+        <x:v>Bois teinté sculpté, textile</x:v>
+      </x:c>
+      <x:c r="G61" s="20" t="str">
+        <x:v>Chaise à haut dossier ajouré orné d'une frise de fruits sculptés, assise et médaillon central garnis d'un textile jaune.</x:v>
+      </x:c>
+      <x:c r="H61" s="20" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I61" s="20" t="str">
+        <x:v>Textile usé et effiloché; structure à contrôler</x:v>
+      </x:c>
+      <x:c r="J61" s="21" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K61" s="21" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="L61" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M61" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N61" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O61" s="20" t="str">
+        <x:v>chaise; bois sculpté; fruits; Art nouveau; Art déco</x:v>
+      </x:c>
+      <x:c r="P61" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q61" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="66" customHeight="1">
+      <x:c r="A62" s="29" t="str">
+        <x:v>MOB-059</x:v>
+      </x:c>
+      <x:c r="B62" s="26" t="str">
+        <x:v>Petit meuble haut à deux portes et un tiroir</x:v>
+      </x:c>
+      <x:c r="C62" s="26" t="str">
+        <x:v>Meuble de rangement</x:v>
+      </x:c>
+      <x:c r="D62" s="26" t="str">
+        <x:v>Début XXe siècle</x:v>
+      </x:c>
+      <x:c r="E62" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F62" s="26" t="str">
+        <x:v>Bois massif et placage, métal</x:v>
+      </x:c>
+      <x:c r="G62" s="26" t="str">
+        <x:v>Petit meuble étroit sur pieds hauts, un tiroir supérieur et deux portes panneautées à anneaux de tirage.</x:v>
+      </x:c>
+      <x:c r="H62" s="26" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I62" s="26" t="str">
+        <x:v>État d'usage, rayures et taches; quincaillerie à contrôler</x:v>
+      </x:c>
+      <x:c r="J62" s="27" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K62" s="27" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="L62" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M62" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N62" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O62" s="26" t="str">
+        <x:v>meuble haut; chevet; deux portes; tiroir</x:v>
+      </x:c>
+      <x:c r="P62" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q62" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="66" customHeight="1">
+      <x:c r="A63" s="28" t="str">
+        <x:v>MOB-060</x:v>
+      </x:c>
+      <x:c r="B63" s="20" t="str">
+        <x:v>Table rectangulaire à quatre pieds tournés</x:v>
+      </x:c>
+      <x:c r="C63" s="20" t="str">
+        <x:v>Table</x:v>
+      </x:c>
+      <x:c r="D63" s="20" t="str">
+        <x:v>Fin XIXe–début XXe siècle</x:v>
+      </x:c>
+      <x:c r="E63" s="20" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F63" s="20" t="str">
+        <x:v>Bois massif, bouton en métal</x:v>
+      </x:c>
+      <x:c r="G63" s="20" t="str">
+        <x:v>Table ou console rectangulaire à un tiroir en ceinture et quatre pieds tournés fuselés.</x:v>
+      </x:c>
+      <x:c r="H63" s="20" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I63" s="20" t="str">
+        <x:v>Plateau fortement marqué; usures et rayures; stabilité à contrôler</x:v>
+      </x:c>
+      <x:c r="J63" s="21" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="K63" s="21" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="L63" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M63" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N63" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O63" s="20" t="str">
+        <x:v>table; console; pieds tournés; tiroir</x:v>
+      </x:c>
+      <x:c r="P63" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q63" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="66" customHeight="1">
+      <x:c r="A64" s="29" t="str">
+        <x:v>MOB-061</x:v>
+      </x:c>
+      <x:c r="B64" s="26" t="str">
+        <x:v>Machine à expresso à levier Riviera Espresso</x:v>
+      </x:c>
+      <x:c r="C64" s="26" t="str">
+        <x:v>Objet technique</x:v>
+      </x:c>
+      <x:c r="D64" s="26" t="str">
+        <x:v>Vers 1970–1990</x:v>
+      </x:c>
+      <x:c r="E64" s="26" t="str">
+        <x:v>Italie, attribution à confirmer</x:v>
+      </x:c>
+      <x:c r="F64" s="26" t="str">
+        <x:v>Laiton, cuivre ou métal doré, acier, plastique, composants électriques</x:v>
+      </x:c>
+      <x:c r="G64" s="26" t="str">
+        <x:v>Machine à expresso domestique à levier, manomètre et buse vapeur, décorée d'un aigle; plaque Riviera Espresso.</x:v>
+      </x:c>
+      <x:c r="H64" s="26" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I64" s="26" t="str">
+        <x:v>Oxydation et dépôts; fonctionnement, étanchéité et sécurité électrique non testés</x:v>
+      </x:c>
+      <x:c r="J64" s="27" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K64" s="27" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="L64" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M64" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N64" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O64" s="26" t="str">
+        <x:v>machine expresso; Riviera Espresso; levier; café; Italie</x:v>
+      </x:c>
+      <x:c r="P64" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q64" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="66" customHeight="1">
+      <x:c r="A65" s="28" t="str">
+        <x:v>MOB-062</x:v>
+      </x:c>
+      <x:c r="B65" s="20" t="str">
+        <x:v>Lampe de bureau Art déco avec pendulette</x:v>
+      </x:c>
+      <x:c r="C65" s="20" t="str">
+        <x:v>Luminaire et horlogerie</x:v>
+      </x:c>
+      <x:c r="D65" s="20" t="str">
+        <x:v>Vers 1930–1940</x:v>
+      </x:c>
+      <x:c r="E65" s="20" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F65" s="20" t="str">
+        <x:v>Bois noirci, métal chromé ou nickelé, mécanisme d'horloge</x:v>
+      </x:c>
+      <x:c r="G65" s="20" t="str">
+        <x:v>Lampe de bureau sur base ovale, réflecteur hémisphérique et pendulette trapézoïdale à chiffres géométriques.</x:v>
+      </x:c>
+      <x:c r="H65" s="20" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I65" s="20" t="str">
+        <x:v>Usures, piqûres et manques de peinture; lampe et horloge non testées</x:v>
+      </x:c>
+      <x:c r="J65" s="21" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K65" s="21" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="L65" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M65" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N65" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O65" s="20" t="str">
+        <x:v>lampe de bureau; pendulette; Art déco; chrome</x:v>
+      </x:c>
+      <x:c r="P65" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q65" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="66" customHeight="1">
+      <x:c r="A66" s="29" t="str">
+        <x:v>MOB-063</x:v>
+      </x:c>
+      <x:c r="B66" s="26" t="str">
+        <x:v>Suspension en verre moulé plissé</x:v>
+      </x:c>
+      <x:c r="C66" s="26" t="str">
+        <x:v>Luminaire</x:v>
+      </x:c>
+      <x:c r="D66" s="26" t="str">
+        <x:v>Vers 1920–1940</x:v>
+      </x:c>
+      <x:c r="E66" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F66" s="26" t="str">
+        <x:v>Verre moulé transparent, métal</x:v>
+      </x:c>
+      <x:c r="G66" s="26" t="str">
+        <x:v>Petite suspension à tulipe conique en verre moulé à côtes verticales et bord volanté.</x:v>
+      </x:c>
+      <x:c r="H66" s="26" t="str">
+        <x:v>À relever (H × diamètre)</x:v>
+      </x:c>
+      <x:c r="I66" s="26" t="str">
+        <x:v>Bon état apparent; fixation et électrification à contrôler</x:v>
+      </x:c>
+      <x:c r="J66" s="27" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K66" s="27" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="L66" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M66" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N66" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O66" s="26" t="str">
+        <x:v>suspension; verre moulé; tulipe; plissé</x:v>
+      </x:c>
+      <x:c r="P66" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q66" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="66" customHeight="1">
+      <x:c r="A67" s="28" t="str">
+        <x:v>MOB-064</x:v>
+      </x:c>
+      <x:c r="B67" s="20" t="str">
+        <x:v>Suspension en verre opalin à décor floral orangé</x:v>
+      </x:c>
+      <x:c r="C67" s="20" t="str">
+        <x:v>Luminaire</x:v>
+      </x:c>
+      <x:c r="D67" s="20" t="str">
+        <x:v>Vers 1930–1950</x:v>
+      </x:c>
+      <x:c r="E67" s="20" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F67" s="20" t="str">
+        <x:v>Verre opalin peint, métal</x:v>
+      </x:c>
+      <x:c r="G67" s="20" t="str">
+        <x:v>Suspension à vasque polygonale en verre opalin crème, décor au pochoir de fleurs et feuillages orangés.</x:v>
+      </x:c>
+      <x:c r="H67" s="20" t="str">
+        <x:v>À relever (H × diamètre)</x:v>
+      </x:c>
+      <x:c r="I67" s="20" t="str">
+        <x:v>Salissures et usures du décor; électrification à revoir</x:v>
+      </x:c>
+      <x:c r="J67" s="21" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="K67" s="21" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="L67" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M67" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N67" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O67" s="20" t="str">
+        <x:v>suspension; opaline; décor floral; verre peint</x:v>
+      </x:c>
+      <x:c r="P67" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q67" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="66" customHeight="1">
+      <x:c r="A68" s="29" t="str">
+        <x:v>MOB-065</x:v>
+      </x:c>
+      <x:c r="B68" s="26" t="str">
+        <x:v>Porte-manteau mural à deux crochets grotesques</x:v>
+      </x:c>
+      <x:c r="C68" s="26" t="str">
+        <x:v>Accessoire de maison</x:v>
+      </x:c>
+      <x:c r="D68" s="26" t="str">
+        <x:v>Début XXe siècle</x:v>
+      </x:c>
+      <x:c r="E68" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F68" s="26" t="str">
+        <x:v>Bois tourné, métal patiné</x:v>
+      </x:c>
+      <x:c r="G68" s="26" t="str">
+        <x:v>Porte-manteau mural composé d'un fût de bois tourné et de deux longs crochets métalliques fixés sur des mascarons grotesques.</x:v>
+      </x:c>
+      <x:c r="H68" s="26" t="str">
+        <x:v>À relever (L × H × P)</x:v>
+      </x:c>
+      <x:c r="I68" s="26" t="str">
+        <x:v>Patine, oxydation et fixation remaniée; état d'usage</x:v>
+      </x:c>
+      <x:c r="J68" s="27" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K68" s="27" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="L68" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M68" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N68" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O68" s="26" t="str">
+        <x:v>porte-manteau; crochets; mascarons; bois tourné</x:v>
+      </x:c>
+      <x:c r="P68" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q68" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="66" customHeight="1">
+      <x:c r="A69" s="28" t="str">
+        <x:v>MOB-066</x:v>
+      </x:c>
+      <x:c r="B69" s="20" t="str">
+        <x:v>Lustre floral en métal peint à deux lumières</x:v>
+      </x:c>
+      <x:c r="C69" s="20" t="str">
+        <x:v>Luminaire</x:v>
+      </x:c>
+      <x:c r="D69" s="20" t="str">
+        <x:v>Vers 1950–1970</x:v>
+      </x:c>
+      <x:c r="E69" s="20" t="str">
+        <x:v>Italie ou France</x:v>
+      </x:c>
+      <x:c r="F69" s="20" t="str">
+        <x:v>Tôle peinte polychrome et dorée</x:v>
+      </x:c>
+      <x:c r="G69" s="20" t="str">
+        <x:v>Lustre à deux bras composé d'un bouquet de fleurs, épis et feuilles en tôle peinte.</x:v>
+      </x:c>
+      <x:c r="H69" s="20" t="str">
+        <x:v>À relever (H × diamètre)</x:v>
+      </x:c>
+      <x:c r="I69" s="20" t="str">
+        <x:v>Peinture usée, oxydation et déformations légères; électrification à réviser</x:v>
+      </x:c>
+      <x:c r="J69" s="21" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K69" s="21" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="L69" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M69" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N69" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O69" s="20" t="str">
+        <x:v>lustre floral; tôle peinte; deux lumières; Italie</x:v>
+      </x:c>
+      <x:c r="P69" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q69" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="66" customHeight="1">
+      <x:c r="A70" s="29" t="str">
+        <x:v>MOB-067</x:v>
+      </x:c>
+      <x:c r="B70" s="26" t="str">
+        <x:v>Petit meuble mural à porte vitrée verte</x:v>
+      </x:c>
+      <x:c r="C70" s="26" t="str">
+        <x:v>Meuble de rangement</x:v>
+      </x:c>
+      <x:c r="D70" s="26" t="str">
+        <x:v>Vers 1900–1930</x:v>
+      </x:c>
+      <x:c r="E70" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F70" s="26" t="str">
+        <x:v>Bois peint ou verni, verre cathédrale vert, métal</x:v>
+      </x:c>
+      <x:c r="G70" s="26" t="str">
+        <x:v>Petit meuble mural à une porte vitrée de verre texturé vert et tablettes réglables, couronnement ajouré.</x:v>
+      </x:c>
+      <x:c r="H70" s="26" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I70" s="26" t="str">
+        <x:v>Usures et repeints; verre apparemment intact; serrure à contrôler</x:v>
+      </x:c>
+      <x:c r="J70" s="27" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K70" s="27" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="L70" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M70" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N70" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O70" s="26" t="str">
+        <x:v>meuble mural; pharmacie; verre vert; rangement</x:v>
+      </x:c>
+      <x:c r="P70" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q70" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="66" customHeight="1">
+      <x:c r="A71" s="28" t="str">
+        <x:v>MOB-068</x:v>
+      </x:c>
+      <x:c r="B71" s="20" t="str">
+        <x:v>Meuble bas à huit tiroirs</x:v>
+      </x:c>
+      <x:c r="C71" s="20" t="str">
+        <x:v>Meuble de rangement</x:v>
+      </x:c>
+      <x:c r="D71" s="20" t="str">
+        <x:v>Milieu XXe siècle</x:v>
+      </x:c>
+      <x:c r="E71" s="20" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F71" s="20" t="str">
+        <x:v>Bois massif et contreplaqué</x:v>
+      </x:c>
+      <x:c r="G71" s="20" t="str">
+        <x:v>Meuble bas de rangement à huit tiroirs de deux largeurs, façades moulurées et boutons en bois.</x:v>
+      </x:c>
+      <x:c r="H71" s="20" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I71" s="20" t="str">
+        <x:v>Usures, taches et rayures; un bouton semble remplacé ou manquant</x:v>
+      </x:c>
+      <x:c r="J71" s="21" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K71" s="21" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="L71" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M71" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N71" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O71" s="20" t="str">
+        <x:v>meuble à tiroirs; rangement; huit tiroirs</x:v>
+      </x:c>
+      <x:c r="P71" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q71" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="66" customHeight="1">
+      <x:c r="A72" s="29" t="str">
+        <x:v>MOB-069</x:v>
+      </x:c>
+      <x:c r="B72" s="26" t="str">
+        <x:v>Horloge-calendrier avec thermomètre et sonnerie</x:v>
+      </x:c>
+      <x:c r="C72" s="26" t="str">
+        <x:v>Horlogerie</x:v>
+      </x:c>
+      <x:c r="D72" s="26" t="str">
+        <x:v>Vers 1930–1950</x:v>
+      </x:c>
+      <x:c r="E72" s="26" t="str">
+        <x:v>Italie</x:v>
+      </x:c>
+      <x:c r="F72" s="26" t="str">
+        <x:v>Bois, métal, verre, papier imprimé, mécanisme d'horloge</x:v>
+      </x:c>
+      <x:c r="G72" s="26" t="str">
+        <x:v>Appareil mural multifonction à cadran d'horloge, double timbre, thermomètre, calendrier et disque indicateur; cadran marqué Made in Italy.</x:v>
+      </x:c>
+      <x:c r="H72" s="26" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I72" s="26" t="str">
+        <x:v>Papier très altéré, oxydation et salissures; fonctionnement non testé; éléments possiblement incomplets</x:v>
+      </x:c>
+      <x:c r="J72" s="27" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="K72" s="27" t="n">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="L72" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M72" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N72" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O72" s="26" t="str">
+        <x:v>horloge; calendrier; thermomètre; sonnerie; Italie</x:v>
+      </x:c>
+      <x:c r="P72" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q72" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="66" customHeight="1">
+      <x:c r="A73" s="28" t="str">
+        <x:v>MOB-070</x:v>
+      </x:c>
+      <x:c r="B73" s="20" t="str">
+        <x:v>Lustre feuillagé en métal doré</x:v>
+      </x:c>
+      <x:c r="C73" s="20" t="str">
+        <x:v>Luminaire</x:v>
+      </x:c>
+      <x:c r="D73" s="20" t="str">
+        <x:v>Vers 1950–1970</x:v>
+      </x:c>
+      <x:c r="E73" s="20" t="str">
+        <x:v>Italie ou France</x:v>
+      </x:c>
+      <x:c r="F73" s="20" t="str">
+        <x:v>Métal doré</x:v>
+      </x:c>
+      <x:c r="G73" s="20" t="str">
+        <x:v>Lustre décoratif en forme de bouquet de branches et feuilles, à plusieurs lumières.</x:v>
+      </x:c>
+      <x:c r="H73" s="20" t="str">
+        <x:v>À relever (H × diamètre)</x:v>
+      </x:c>
+      <x:c r="I73" s="20" t="str">
+        <x:v>Patine et oxydation; photographie peu détaillée; électrification à réviser</x:v>
+      </x:c>
+      <x:c r="J73" s="21" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K73" s="21" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="L73" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M73" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N73" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O73" s="20" t="str">
+        <x:v>lustre; feuillage; métal doré; bouquet</x:v>
+      </x:c>
+      <x:c r="P73" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q73" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="66" customHeight="1">
+      <x:c r="A74" s="29" t="str">
+        <x:v>MOB-071</x:v>
+      </x:c>
+      <x:c r="B74" s="26" t="str">
+        <x:v>Étagère de salle de bains en verre et métal</x:v>
+      </x:c>
+      <x:c r="C74" s="26" t="str">
+        <x:v>Accessoire de maison</x:v>
+      </x:c>
+      <x:c r="D74" s="26" t="str">
+        <x:v>Vers 1940–1960</x:v>
+      </x:c>
+      <x:c r="E74" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F74" s="26" t="str">
+        <x:v>Verre, laiton ou métal nickelé</x:v>
+      </x:c>
+      <x:c r="G74" s="26" t="str">
+        <x:v>Étagère étroite de salle de bains à plusieurs niveaux, tablettes de verre et garde-corps métalliques.</x:v>
+      </x:c>
+      <x:c r="H74" s="26" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I74" s="26" t="str">
+        <x:v>Oxydation et salissures; fixation et complétude à contrôler</x:v>
+      </x:c>
+      <x:c r="J74" s="27" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K74" s="27" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="L74" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M74" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N74" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O74" s="26" t="str">
+        <x:v>étagère; salle de bains; verre; laiton</x:v>
+      </x:c>
+      <x:c r="P74" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q74" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="66" customHeight="1">
+      <x:c r="A75" s="28" t="str">
+        <x:v>MOB-072</x:v>
+      </x:c>
+      <x:c r="B75" s="20" t="str">
+        <x:v>Harmonium à deux claviers Ph. J. Trayser &amp; Cie</x:v>
+      </x:c>
+      <x:c r="C75" s="20" t="str">
+        <x:v>Instrument de musique</x:v>
+      </x:c>
+      <x:c r="D75" s="20" t="str">
+        <x:v>Vers 1880–1910</x:v>
+      </x:c>
+      <x:c r="E75" s="20" t="str">
+        <x:v>Stuttgart, Allemagne</x:v>
+      </x:c>
+      <x:c r="F75" s="20" t="str">
+        <x:v>Bois plaqué et sculpté, ivoirine, ébène, métal, mécanisme d'anches</x:v>
+      </x:c>
+      <x:c r="G75" s="20" t="str">
+        <x:v>Harmonium domestique à deux claviers, registres et pédales, portant l'étiquette Ph. J. Trayser &amp; Cie, Stuttgart, et la mention de dépôts suisses.</x:v>
+      </x:c>
+      <x:c r="H75" s="20" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I75" s="20" t="str">
+        <x:v>Instrument très empoussiéré; touches jaunies; fonctionnement, soufflerie et complétude non testés</x:v>
+      </x:c>
+      <x:c r="J75" s="21" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="K75" s="21" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="L75" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M75" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N75" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O75" s="20" t="str">
+        <x:v>harmonium; orgue; Trayser; Stuttgart; instrument</x:v>
+      </x:c>
+      <x:c r="P75" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q75" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="66" customHeight="1">
+      <x:c r="A76" s="29" t="str">
+        <x:v>MOB-073</x:v>
+      </x:c>
+      <x:c r="B76" s="26" t="str">
+        <x:v>Commode sombre à quatre tiroirs</x:v>
+      </x:c>
+      <x:c r="C76" s="26" t="str">
+        <x:v>Meuble de rangement</x:v>
+      </x:c>
+      <x:c r="D76" s="26" t="str">
+        <x:v>XIXe siècle, remaniements possibles</x:v>
+      </x:c>
+      <x:c r="E76" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F76" s="26" t="str">
+        <x:v>Bois massif, peinture ou teinte sombre, métal</x:v>
+      </x:c>
+      <x:c r="G76" s="26" t="str">
+        <x:v>Commode à quatre grands tiroirs, montants tournés et petits pieds boule; finition sombre.</x:v>
+      </x:c>
+      <x:c r="H76" s="26" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I76" s="26" t="str">
+        <x:v>Usures et éclats de finition; boutons hétérogènes ou remplacés; structure à contrôler</x:v>
+      </x:c>
+      <x:c r="J76" s="27" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="K76" s="27" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="L76" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M76" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N76" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O76" s="26" t="str">
+        <x:v>commode; quatre tiroirs; bois peint; XIXe</x:v>
+      </x:c>
+      <x:c r="P76" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q76" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="66" customHeight="1">
+      <x:c r="A77" s="28" t="str">
+        <x:v>MOB-074</x:v>
+      </x:c>
+      <x:c r="B77" s="20" t="str">
+        <x:v>Meuble haut à une porte et un tiroir</x:v>
+      </x:c>
+      <x:c r="C77" s="20" t="str">
+        <x:v>Meuble de rangement</x:v>
+      </x:c>
+      <x:c r="D77" s="20" t="str">
+        <x:v>Fin XIXe–début XXe siècle</x:v>
+      </x:c>
+      <x:c r="E77" s="20" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F77" s="20" t="str">
+        <x:v>Bois massif, métal</x:v>
+      </x:c>
+      <x:c r="G77" s="20" t="str">
+        <x:v>Meuble haut et étroit à un tiroir supérieur et une grande porte panneautée, sur pieds courts tournés.</x:v>
+      </x:c>
+      <x:c r="H77" s="20" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I77" s="20" t="str">
+        <x:v>Usures et rayures; serrure, intérieur et stabilité à contrôler</x:v>
+      </x:c>
+      <x:c r="J77" s="21" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K77" s="21" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="L77" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M77" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N77" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O77" s="20" t="str">
+        <x:v>meuble haut; bonnetière; une porte; tiroir</x:v>
+      </x:c>
+      <x:c r="P77" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q77" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="66" customHeight="1">
+      <x:c r="A78" s="29" t="str">
+        <x:v>MOB-075</x:v>
+      </x:c>
+      <x:c r="B78" s="26" t="str">
+        <x:v>Armoire à deux portes panneautées</x:v>
+      </x:c>
+      <x:c r="C78" s="26" t="str">
+        <x:v>Meuble de rangement</x:v>
+      </x:c>
+      <x:c r="D78" s="26" t="str">
+        <x:v>XIXe siècle</x:v>
+      </x:c>
+      <x:c r="E78" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F78" s="26" t="str">
+        <x:v>Bois massif, métal</x:v>
+      </x:c>
+      <x:c r="G78" s="26" t="str">
+        <x:v>Grande armoire à deux portes composées de trois panneaux chacune, corniche saillante et frise de denticules simplifiés.</x:v>
+      </x:c>
+      <x:c r="H78" s="26" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I78" s="26" t="str">
+        <x:v>Patine et usures importantes; poignées probablement remplacées; intérieur non documenté</x:v>
+      </x:c>
+      <x:c r="J78" s="27" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="K78" s="27" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="L78" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M78" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N78" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O78" s="26" t="str">
+        <x:v>armoire; deux portes; bois massif; XIXe</x:v>
+      </x:c>
+      <x:c r="P78" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q78" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="66" customHeight="1">
+      <x:c r="A79" s="28" t="str">
+        <x:v>MOB-076</x:v>
+      </x:c>
+      <x:c r="B79" s="20" t="str">
+        <x:v>Lit double en métal à médaillons ovales</x:v>
+      </x:c>
+      <x:c r="C79" s="20" t="str">
+        <x:v>Lit</x:v>
+      </x:c>
+      <x:c r="D79" s="20" t="str">
+        <x:v>Fin XIXe–début XXe siècle</x:v>
+      </x:c>
+      <x:c r="E79" s="20" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F79" s="20" t="str">
+        <x:v>Métal peint, panneaux décoratifs</x:v>
+      </x:c>
+      <x:c r="G79" s="20" t="str">
+        <x:v>Lit double en métal noir, tête et pied ornés de grands médaillons ovales peints à décor floral.</x:v>
+      </x:c>
+      <x:c r="H79" s="20" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I79" s="20" t="str">
+        <x:v>Usures, oxydation et éléments à contrôler; literie exclue de l'estimation</x:v>
+      </x:c>
+      <x:c r="J79" s="21" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="K79" s="21" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L79" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M79" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N79" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O79" s="20" t="str">
+        <x:v>lit; métal; médaillons; décor floral; Napoléon III</x:v>
+      </x:c>
+      <x:c r="P79" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q79" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="66" customHeight="1">
+      <x:c r="A80" s="29" t="str">
+        <x:v>MOB-077</x:v>
+      </x:c>
+      <x:c r="B80" s="26" t="str">
+        <x:v>Table de chevet à trois tiroirs</x:v>
+      </x:c>
+      <x:c r="C80" s="26" t="str">
+        <x:v>Meuble de rangement</x:v>
+      </x:c>
+      <x:c r="D80" s="26" t="str">
+        <x:v>Vers 1960–1980</x:v>
+      </x:c>
+      <x:c r="E80" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F80" s="26" t="str">
+        <x:v>Bois et placage, métal</x:v>
+      </x:c>
+      <x:c r="G80" s="26" t="str">
+        <x:v>Table de chevet rectangulaire à trois tiroirs moulurés et petits boutons ronds.</x:v>
+      </x:c>
+      <x:c r="H80" s="26" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I80" s="26" t="str">
+        <x:v>État d'usage, rayures et décoloration; intérieur non examiné</x:v>
+      </x:c>
+      <x:c r="J80" s="27" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K80" s="27" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="L80" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M80" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N80" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O80" s="26" t="str">
+        <x:v>chevet; trois tiroirs; chambre</x:v>
+      </x:c>
+      <x:c r="P80" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q80" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="66" customHeight="1">
+      <x:c r="A81" s="28" t="str">
+        <x:v>MOB-078</x:v>
+      </x:c>
+      <x:c r="B81" s="20" t="str">
+        <x:v>Buffet bas à deux portes et deux tiroirs</x:v>
+      </x:c>
+      <x:c r="C81" s="20" t="str">
+        <x:v>Meuble de rangement</x:v>
+      </x:c>
+      <x:c r="D81" s="20" t="str">
+        <x:v>XXe siècle</x:v>
+      </x:c>
+      <x:c r="E81" s="20" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F81" s="20" t="str">
+        <x:v>Bois résineux, métal</x:v>
+      </x:c>
+      <x:c r="G81" s="20" t="str">
+        <x:v>Buffet bas rustique à deux tiroirs en ceinture et deux portes panneautées.</x:v>
+      </x:c>
+      <x:c r="H81" s="20" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I81" s="20" t="str">
+        <x:v>Photographie sombre; usures et rayures; intérieur non examiné</x:v>
+      </x:c>
+      <x:c r="J81" s="21" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K81" s="21" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="L81" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M81" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N81" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O81" s="20" t="str">
+        <x:v>buffet; deux portes; deux tiroirs; pin</x:v>
+      </x:c>
+      <x:c r="P81" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q81" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="66" customHeight="1">
+      <x:c r="A82" s="29" t="str">
+        <x:v>MOB-079</x:v>
+      </x:c>
+      <x:c r="B82" s="26" t="str">
+        <x:v>Meuble de toilette à miroir et plateau de marbre</x:v>
+      </x:c>
+      <x:c r="C82" s="26" t="str">
+        <x:v>Mobilier de toilette</x:v>
+      </x:c>
+      <x:c r="D82" s="26" t="str">
+        <x:v>Fin XIXe–début XXe siècle</x:v>
+      </x:c>
+      <x:c r="E82" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F82" s="26" t="str">
+        <x:v>Bois, marbre, miroir, métal</x:v>
+      </x:c>
+      <x:c r="G82" s="26" t="str">
+        <x:v>Meuble de toilette à plateau de marbre, tiroir, pieds tournés et haut miroir rectangulaire surmonté d'une balustrade.</x:v>
+      </x:c>
+      <x:c r="H82" s="26" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I82" s="26" t="str">
+        <x:v>Encombré sur la photographie; miroir et marbre à contrôler; usures d'usage</x:v>
+      </x:c>
+      <x:c r="J82" s="27" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K82" s="27" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="L82" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M82" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N82" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O82" s="26" t="str">
+        <x:v>toilette; lavabo; miroir; marbre; salle de bains</x:v>
+      </x:c>
+      <x:c r="P82" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q82" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="66" customHeight="1">
+      <x:c r="A83" s="28" t="str">
+        <x:v>MOB-080</x:v>
+      </x:c>
+      <x:c r="B83" s="20" t="str">
+        <x:v>Grand miroir doré de style rocaille</x:v>
+      </x:c>
+      <x:c r="C83" s="20" t="str">
+        <x:v>Miroir</x:v>
+      </x:c>
+      <x:c r="D83" s="20" t="str">
+        <x:v>XXe siècle, style Louis XV</x:v>
+      </x:c>
+      <x:c r="E83" s="20" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F83" s="20" t="str">
+        <x:v>Bois ou composition moulée dorée, miroir</x:v>
+      </x:c>
+      <x:c r="G83" s="20" t="str">
+        <x:v>Grand miroir mural ovale à riche encadrement rocaille, coquilles, rinceaux et mascaron sommital.</x:v>
+      </x:c>
+      <x:c r="H83" s="20" t="str">
+        <x:v>À relever (H × L)</x:v>
+      </x:c>
+      <x:c r="I83" s="20" t="str">
+        <x:v>Dorure usée et encrassée; miroir à contrôler pour piqûres; fixation non examinée</x:v>
+      </x:c>
+      <x:c r="J83" s="21" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K83" s="21" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="L83" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M83" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N83" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O83" s="20" t="str">
+        <x:v>miroir; rocaille; doré; style Louis XV</x:v>
+      </x:c>
+      <x:c r="P83" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q83" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="66" customHeight="1">
+      <x:c r="A84" s="29" t="str">
+        <x:v>MOB-081</x:v>
+      </x:c>
+      <x:c r="B84" s="26" t="str">
+        <x:v>Fauteuil à dossier cintré et garniture noire</x:v>
+      </x:c>
+      <x:c r="C84" s="26" t="str">
+        <x:v>Siège</x:v>
+      </x:c>
+      <x:c r="D84" s="26" t="str">
+        <x:v>Vers 1920–1940, restauration postérieure possible</x:v>
+      </x:c>
+      <x:c r="E84" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F84" s="26" t="str">
+        <x:v>Bois courbé, garniture synthétique ou cuir, clous</x:v>
+      </x:c>
+      <x:c r="G84" s="26" t="str">
+        <x:v>Fauteuil enveloppant à dossier cintré continu, assise et dossier garnis de noir et soulignés de clous.</x:v>
+      </x:c>
+      <x:c r="H84" s="26" t="str">
+        <x:v>À relever (H × L × P)</x:v>
+      </x:c>
+      <x:c r="I84" s="26" t="str">
+        <x:v>Garniture probablement récente, rayures au bois; structure à contrôler</x:v>
+      </x:c>
+      <x:c r="J84" s="27" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="K84" s="27" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="L84" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M84" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N84" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O84" s="26" t="str">
+        <x:v>fauteuil; Art déco; bois courbé; garniture noire</x:v>
+      </x:c>
+      <x:c r="P84" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q84" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="66" customHeight="1">
+      <x:c r="A85" s="28" t="str">
+        <x:v>MOB-082</x:v>
+      </x:c>
+      <x:c r="B85" s="20" t="str">
+        <x:v>Lampe de table en métal patiné</x:v>
+      </x:c>
+      <x:c r="C85" s="20" t="str">
+        <x:v>Luminaire</x:v>
+      </x:c>
+      <x:c r="D85" s="20" t="str">
+        <x:v>Première moitié du XXe siècle, style historiciste</x:v>
+      </x:c>
+      <x:c r="E85" s="20" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F85" s="20" t="str">
+        <x:v>Métal patiné, textile, passementerie</x:v>
+      </x:c>
+      <x:c r="G85" s="20" t="str">
+        <x:v>Lampe de table à fût balustre en métal patiné et base circulaire ornée, munie d'un abat-jour cylindrique en textile.</x:v>
+      </x:c>
+      <x:c r="H85" s="20" t="str">
+        <x:v>À relever (H × diamètre)</x:v>
+      </x:c>
+      <x:c r="I85" s="20" t="str">
+        <x:v>Patine, poussière et usures du textile; électrification à réviser</x:v>
+      </x:c>
+      <x:c r="J85" s="21" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="K85" s="21" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="L85" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M85" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N85" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O85" s="20" t="str">
+        <x:v>lampe de table; métal patiné; abat-jour; historicisme</x:v>
+      </x:c>
+      <x:c r="P85" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q85" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="66" customHeight="1">
+      <x:c r="A86" s="29" t="str">
+        <x:v>MOB-083</x:v>
+      </x:c>
+      <x:c r="B86" s="26" t="str">
+        <x:v>Grand plateau de service vitré</x:v>
+      </x:c>
+      <x:c r="C86" s="26" t="str">
+        <x:v>Arts de la table</x:v>
+      </x:c>
+      <x:c r="D86" s="26" t="str">
+        <x:v>Fin XIXe–début XXe siècle</x:v>
+      </x:c>
+      <x:c r="E86" s="26" t="str">
+        <x:v>Europe</x:v>
+      </x:c>
+      <x:c r="F86" s="26" t="str">
+        <x:v>Bois teinté, verre, laiton</x:v>
+      </x:c>
+      <x:c r="G86" s="26" t="str">
+        <x:v>Grand plateau rectangulaire à angles arrondis, fond vitré, encadrement en bois et deux poignées ajourées en laiton.</x:v>
+      </x:c>
+      <x:c r="H86" s="26" t="str">
+        <x:v>À relever (L × l × H)</x:v>
+      </x:c>
+      <x:c r="I86" s="26" t="str">
+        <x:v>Rayures et petits trous; verre à vérifier sur les chants; poignées patinées</x:v>
+      </x:c>
+      <x:c r="J86" s="27" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K86" s="27" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="L86" s="26" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M86" s="26" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N86" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O86" s="26" t="str">
+        <x:v>plateau; service; bois; verre; laiton</x:v>
+      </x:c>
+      <x:c r="P86" s="26" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q86" s="26" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="66" customHeight="1">
+      <x:c r="A87" s="28" t="str">
+        <x:v>MOB-084</x:v>
+      </x:c>
+      <x:c r="B87" s="20" t="str">
+        <x:v>Ménagère de couverts à manches clairs en coffret</x:v>
+      </x:c>
+      <x:c r="C87" s="20" t="str">
+        <x:v>Arts de la table</x:v>
+      </x:c>
+      <x:c r="D87" s="20" t="str">
+        <x:v>Vers 1890–1920</x:v>
+      </x:c>
+      <x:c r="E87" s="20" t="str">
+        <x:v>Royaume-Uni, attribution d'après les poinçons à confirmer</x:v>
+      </x:c>
+      <x:c r="F87" s="20" t="str">
+        <x:v>Métal argenté ou argent, manches en os ou ivoirine, bois, velours</x:v>
+      </x:c>
+      <x:c r="G87" s="20" t="str">
+        <x:v>Ensemble dépareillé ou incomplet de couteaux, fourchettes et pièces de service, lames gravées et manches clairs, présenté dans un coffret garni. Poinçons britanniques visibles mais non déchiffrés avec certitude.</x:v>
+      </x:c>
+      <x:c r="H87" s="20" t="str">
+        <x:v>Coffret à relever; 15 pièces visibles environ</x:v>
+      </x:c>
+      <x:c r="I87" s="20" t="str">
+        <x:v>Métal terni et piqué; manches tachés; coffret usé; inventaire et lecture des poinçons à compléter</x:v>
+      </x:c>
+      <x:c r="J87" s="21" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K87" s="21" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="L87" s="20" t="str">
+        <x:v>À préciser</x:v>
+      </x:c>
+      <x:c r="M87" s="20" t="str">
+        <x:v>À documenter</x:v>
+      </x:c>
+      <x:c r="N87" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+      <x:c r="O87" s="20" t="str">
+        <x:v>ménagère; couverts; poinçons britanniques; os; ivoirine; coffret</x:v>
+      </x:c>
+      <x:c r="P87" s="20" t="str">
+        <x:v>https://www.proantic.com/</x:v>
+      </x:c>
+      <x:c r="Q87" s="20" t="str">
+        <x:v>https://www.interencheres.com/</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:Q1"/>
@@ -4984,7 +7108,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a13151452ec4841"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4994c526569b4818"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6752,6 +8876,1366 @@
         <x:v>500</x:v>
       </x:c>
     </x:row>
+    <x:row r="105" ht="24" customHeight="1">
+      <x:c r="A105" s="20" t="str">
+        <x:v>MOB-046</x:v>
+      </x:c>
+      <x:c r="B105" s="20" t="str">
+        <x:v>MOB-046-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C105" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D105" s="20" t="str">
+        <x:v>Encoignure à une porte — vue 1</x:v>
+      </x:c>
+      <x:c r="E105" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="24" customHeight="1">
+      <x:c r="A106" s="26" t="str">
+        <x:v>MOB-046</x:v>
+      </x:c>
+      <x:c r="B106" s="26" t="str">
+        <x:v>MOB-046-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C106" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D106" s="26" t="str">
+        <x:v>Encoignure à une porte — vue 2</x:v>
+      </x:c>
+      <x:c r="E106" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="24" customHeight="1">
+      <x:c r="A107" s="20" t="str">
+        <x:v>MOB-047</x:v>
+      </x:c>
+      <x:c r="B107" s="20" t="str">
+        <x:v>MOB-047-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C107" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D107" s="20" t="str">
+        <x:v>Suspension à grand abat-jour textile fleuri — vue 1</x:v>
+      </x:c>
+      <x:c r="E107" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="24" customHeight="1">
+      <x:c r="A108" s="26" t="str">
+        <x:v>MOB-047</x:v>
+      </x:c>
+      <x:c r="B108" s="26" t="str">
+        <x:v>MOB-047-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C108" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D108" s="26" t="str">
+        <x:v>Suspension à grand abat-jour textile fleuri — vue 2</x:v>
+      </x:c>
+      <x:c r="E108" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="24" customHeight="1">
+      <x:c r="A109" s="20" t="str">
+        <x:v>MOB-048</x:v>
+      </x:c>
+      <x:c r="B109" s="20" t="str">
+        <x:v>MOB-048-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C109" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D109" s="20" t="str">
+        <x:v>Suspension à vasque en verre opalin bleu pâle — vue 1</x:v>
+      </x:c>
+      <x:c r="E109" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="24" customHeight="1">
+      <x:c r="A110" s="26" t="str">
+        <x:v>MOB-049</x:v>
+      </x:c>
+      <x:c r="B110" s="26" t="str">
+        <x:v>MOB-049-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C110" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D110" s="26" t="str">
+        <x:v>Applique à deux lumières aux feuilles d'acanthe — vue 1</x:v>
+      </x:c>
+      <x:c r="E110" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="24" customHeight="1">
+      <x:c r="A111" s="20" t="str">
+        <x:v>MOB-049</x:v>
+      </x:c>
+      <x:c r="B111" s="20" t="str">
+        <x:v>MOB-049-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C111" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D111" s="20" t="str">
+        <x:v>Applique à deux lumières aux feuilles d'acanthe — vue 2</x:v>
+      </x:c>
+      <x:c r="E111" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="24" customHeight="1">
+      <x:c r="A112" s="26" t="str">
+        <x:v>MOB-049</x:v>
+      </x:c>
+      <x:c r="B112" s="26" t="str">
+        <x:v>MOB-049-03.jpeg</x:v>
+      </x:c>
+      <x:c r="C112" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D112" s="26" t="str">
+        <x:v>Applique à deux lumières aux feuilles d'acanthe — vue 3</x:v>
+      </x:c>
+      <x:c r="E112" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="24" customHeight="1">
+      <x:c r="A113" s="20" t="str">
+        <x:v>MOB-049</x:v>
+      </x:c>
+      <x:c r="B113" s="20" t="str">
+        <x:v>MOB-049-04.jpeg</x:v>
+      </x:c>
+      <x:c r="C113" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D113" s="20" t="str">
+        <x:v>Applique à deux lumières aux feuilles d'acanthe — vue 4</x:v>
+      </x:c>
+      <x:c r="E113" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="24" customHeight="1">
+      <x:c r="A114" s="26" t="str">
+        <x:v>MOB-049</x:v>
+      </x:c>
+      <x:c r="B114" s="26" t="str">
+        <x:v>MOB-049-05.jpeg</x:v>
+      </x:c>
+      <x:c r="C114" s="26" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D114" s="26" t="str">
+        <x:v>Applique à deux lumières aux feuilles d'acanthe — vue 5</x:v>
+      </x:c>
+      <x:c r="E114" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="24" customHeight="1">
+      <x:c r="A115" s="20" t="str">
+        <x:v>MOB-050</x:v>
+      </x:c>
+      <x:c r="B115" s="20" t="str">
+        <x:v>MOB-050-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C115" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D115" s="20" t="str">
+        <x:v>Lustre à pendeloques de verre — vue 1</x:v>
+      </x:c>
+      <x:c r="E115" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="24" customHeight="1">
+      <x:c r="A116" s="26" t="str">
+        <x:v>MOB-050</x:v>
+      </x:c>
+      <x:c r="B116" s="26" t="str">
+        <x:v>MOB-050-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C116" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D116" s="26" t="str">
+        <x:v>Lustre à pendeloques de verre — vue 2</x:v>
+      </x:c>
+      <x:c r="E116" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="24" customHeight="1">
+      <x:c r="A117" s="20" t="str">
+        <x:v>MOB-051</x:v>
+      </x:c>
+      <x:c r="B117" s="20" t="str">
+        <x:v>MOB-051-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C117" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D117" s="20" t="str">
+        <x:v>Applique à deux lumières au motif de fleur de lys — vue 1</x:v>
+      </x:c>
+      <x:c r="E117" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="24" customHeight="1">
+      <x:c r="A118" s="26" t="str">
+        <x:v>MOB-052</x:v>
+      </x:c>
+      <x:c r="B118" s="26" t="str">
+        <x:v>MOB-052-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C118" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D118" s="26" t="str">
+        <x:v>Suspension à vasque festonnée jaune pâle — vue 1</x:v>
+      </x:c>
+      <x:c r="E118" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="24" customHeight="1">
+      <x:c r="A119" s="20" t="str">
+        <x:v>MOB-052</x:v>
+      </x:c>
+      <x:c r="B119" s="20" t="str">
+        <x:v>MOB-052-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C119" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D119" s="20" t="str">
+        <x:v>Suspension à vasque festonnée jaune pâle — vue 2</x:v>
+      </x:c>
+      <x:c r="E119" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="24" customHeight="1">
+      <x:c r="A120" s="26" t="str">
+        <x:v>MOB-053</x:v>
+      </x:c>
+      <x:c r="B120" s="26" t="str">
+        <x:v>MOB-053-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C120" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D120" s="26" t="str">
+        <x:v>Coffre en bois à façade panneautée — vue 1</x:v>
+      </x:c>
+      <x:c r="E120" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="24" customHeight="1">
+      <x:c r="A121" s="20" t="str">
+        <x:v>MOB-053</x:v>
+      </x:c>
+      <x:c r="B121" s="20" t="str">
+        <x:v>MOB-053-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C121" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D121" s="20" t="str">
+        <x:v>Coffre en bois à façade panneautée — vue 2</x:v>
+      </x:c>
+      <x:c r="E121" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="24" customHeight="1">
+      <x:c r="A122" s="26" t="str">
+        <x:v>MOB-054</x:v>
+      </x:c>
+      <x:c r="B122" s="26" t="str">
+        <x:v>MOB-054-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C122" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D122" s="26" t="str">
+        <x:v>Meuble de toilette à dessus de marbre et miroir triptyque — vue 1</x:v>
+      </x:c>
+      <x:c r="E122" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="24" customHeight="1">
+      <x:c r="A123" s="20" t="str">
+        <x:v>MOB-054</x:v>
+      </x:c>
+      <x:c r="B123" s="20" t="str">
+        <x:v>MOB-054-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C123" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D123" s="20" t="str">
+        <x:v>Meuble de toilette à dessus de marbre et miroir triptyque — vue 2</x:v>
+      </x:c>
+      <x:c r="E123" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="24" customHeight="1">
+      <x:c r="A124" s="26" t="str">
+        <x:v>MOB-054</x:v>
+      </x:c>
+      <x:c r="B124" s="26" t="str">
+        <x:v>MOB-054-03.jpeg</x:v>
+      </x:c>
+      <x:c r="C124" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D124" s="26" t="str">
+        <x:v>Meuble de toilette à dessus de marbre et miroir triptyque — vue 3</x:v>
+      </x:c>
+      <x:c r="E124" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="24" customHeight="1">
+      <x:c r="A125" s="20" t="str">
+        <x:v>MOB-055</x:v>
+      </x:c>
+      <x:c r="B125" s="20" t="str">
+        <x:v>MOB-055-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C125" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D125" s="20" t="str">
+        <x:v>Petite table noire à piètement cannelé — vue 1</x:v>
+      </x:c>
+      <x:c r="E125" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="24" customHeight="1">
+      <x:c r="A126" s="26" t="str">
+        <x:v>MOB-055</x:v>
+      </x:c>
+      <x:c r="B126" s="26" t="str">
+        <x:v>MOB-055-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C126" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D126" s="26" t="str">
+        <x:v>Petite table noire à piètement cannelé — vue 2</x:v>
+      </x:c>
+      <x:c r="E126" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="24" customHeight="1">
+      <x:c r="A127" s="20" t="str">
+        <x:v>MOB-056</x:v>
+      </x:c>
+      <x:c r="B127" s="20" t="str">
+        <x:v>MOB-056-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C127" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D127" s="20" t="str">
+        <x:v>Chaise en bois courbé et cannage — vue 1</x:v>
+      </x:c>
+      <x:c r="E127" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="24" customHeight="1">
+      <x:c r="A128" s="26" t="str">
+        <x:v>MOB-056</x:v>
+      </x:c>
+      <x:c r="B128" s="26" t="str">
+        <x:v>MOB-056-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C128" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D128" s="26" t="str">
+        <x:v>Chaise en bois courbé et cannage — vue 2</x:v>
+      </x:c>
+      <x:c r="E128" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="24" customHeight="1">
+      <x:c r="A129" s="20" t="str">
+        <x:v>MOB-056</x:v>
+      </x:c>
+      <x:c r="B129" s="20" t="str">
+        <x:v>MOB-056-03.jpeg</x:v>
+      </x:c>
+      <x:c r="C129" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D129" s="20" t="str">
+        <x:v>Chaise en bois courbé et cannage — vue 3</x:v>
+      </x:c>
+      <x:c r="E129" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="24" customHeight="1">
+      <x:c r="A130" s="26" t="str">
+        <x:v>MOB-056</x:v>
+      </x:c>
+      <x:c r="B130" s="26" t="str">
+        <x:v>MOB-056-04.jpeg</x:v>
+      </x:c>
+      <x:c r="C130" s="26" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D130" s="26" t="str">
+        <x:v>Chaise en bois courbé et cannage — vue 4</x:v>
+      </x:c>
+      <x:c r="E130" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="24" customHeight="1">
+      <x:c r="A131" s="20" t="str">
+        <x:v>MOB-057</x:v>
+      </x:c>
+      <x:c r="B131" s="20" t="str">
+        <x:v>MOB-057-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C131" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D131" s="20" t="str">
+        <x:v>Tabouret de piano pivotant — vue 1</x:v>
+      </x:c>
+      <x:c r="E131" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="24" customHeight="1">
+      <x:c r="A132" s="26" t="str">
+        <x:v>MOB-057</x:v>
+      </x:c>
+      <x:c r="B132" s="26" t="str">
+        <x:v>MOB-057-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C132" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D132" s="26" t="str">
+        <x:v>Tabouret de piano pivotant — vue 2</x:v>
+      </x:c>
+      <x:c r="E132" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="24" customHeight="1">
+      <x:c r="A133" s="20" t="str">
+        <x:v>MOB-058</x:v>
+      </x:c>
+      <x:c r="B133" s="20" t="str">
+        <x:v>MOB-058-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C133" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D133" s="20" t="str">
+        <x:v>Chaise à dossier sculpté et garniture jaune — vue 1</x:v>
+      </x:c>
+      <x:c r="E133" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="24" customHeight="1">
+      <x:c r="A134" s="26" t="str">
+        <x:v>MOB-058</x:v>
+      </x:c>
+      <x:c r="B134" s="26" t="str">
+        <x:v>MOB-058-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C134" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D134" s="26" t="str">
+        <x:v>Chaise à dossier sculpté et garniture jaune — vue 2</x:v>
+      </x:c>
+      <x:c r="E134" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="24" customHeight="1">
+      <x:c r="A135" s="20" t="str">
+        <x:v>MOB-059</x:v>
+      </x:c>
+      <x:c r="B135" s="20" t="str">
+        <x:v>MOB-059-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C135" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D135" s="20" t="str">
+        <x:v>Petit meuble haut à deux portes et un tiroir — vue 1</x:v>
+      </x:c>
+      <x:c r="E135" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="24" customHeight="1">
+      <x:c r="A136" s="26" t="str">
+        <x:v>MOB-059</x:v>
+      </x:c>
+      <x:c r="B136" s="26" t="str">
+        <x:v>MOB-059-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C136" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D136" s="26" t="str">
+        <x:v>Petit meuble haut à deux portes et un tiroir — vue 2</x:v>
+      </x:c>
+      <x:c r="E136" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="24" customHeight="1">
+      <x:c r="A137" s="20" t="str">
+        <x:v>MOB-060</x:v>
+      </x:c>
+      <x:c r="B137" s="20" t="str">
+        <x:v>MOB-060-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C137" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D137" s="20" t="str">
+        <x:v>Table rectangulaire à quatre pieds tournés — vue 1</x:v>
+      </x:c>
+      <x:c r="E137" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="24" customHeight="1">
+      <x:c r="A138" s="26" t="str">
+        <x:v>MOB-060</x:v>
+      </x:c>
+      <x:c r="B138" s="26" t="str">
+        <x:v>MOB-060-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C138" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D138" s="26" t="str">
+        <x:v>Table rectangulaire à quatre pieds tournés — vue 2</x:v>
+      </x:c>
+      <x:c r="E138" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="24" customHeight="1">
+      <x:c r="A139" s="20" t="str">
+        <x:v>MOB-060</x:v>
+      </x:c>
+      <x:c r="B139" s="20" t="str">
+        <x:v>MOB-060-03.jpeg</x:v>
+      </x:c>
+      <x:c r="C139" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D139" s="20" t="str">
+        <x:v>Table rectangulaire à quatre pieds tournés — vue 3</x:v>
+      </x:c>
+      <x:c r="E139" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="24" customHeight="1">
+      <x:c r="A140" s="26" t="str">
+        <x:v>MOB-061</x:v>
+      </x:c>
+      <x:c r="B140" s="26" t="str">
+        <x:v>MOB-061-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C140" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D140" s="26" t="str">
+        <x:v>Machine à expresso à levier Riviera Espresso — vue 1</x:v>
+      </x:c>
+      <x:c r="E140" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="24" customHeight="1">
+      <x:c r="A141" s="20" t="str">
+        <x:v>MOB-061</x:v>
+      </x:c>
+      <x:c r="B141" s="20" t="str">
+        <x:v>MOB-061-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C141" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D141" s="20" t="str">
+        <x:v>Machine à expresso à levier Riviera Espresso — vue 2</x:v>
+      </x:c>
+      <x:c r="E141" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="24" customHeight="1">
+      <x:c r="A142" s="26" t="str">
+        <x:v>MOB-061</x:v>
+      </x:c>
+      <x:c r="B142" s="26" t="str">
+        <x:v>MOB-061-03.jpeg</x:v>
+      </x:c>
+      <x:c r="C142" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D142" s="26" t="str">
+        <x:v>Machine à expresso à levier Riviera Espresso — vue 3</x:v>
+      </x:c>
+      <x:c r="E142" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="24" customHeight="1">
+      <x:c r="A143" s="20" t="str">
+        <x:v>MOB-061</x:v>
+      </x:c>
+      <x:c r="B143" s="20" t="str">
+        <x:v>MOB-061-04.jpeg</x:v>
+      </x:c>
+      <x:c r="C143" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D143" s="20" t="str">
+        <x:v>Machine à expresso à levier Riviera Espresso — vue 4</x:v>
+      </x:c>
+      <x:c r="E143" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="24" customHeight="1">
+      <x:c r="A144" s="26" t="str">
+        <x:v>MOB-062</x:v>
+      </x:c>
+      <x:c r="B144" s="26" t="str">
+        <x:v>MOB-062-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C144" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D144" s="26" t="str">
+        <x:v>Lampe de bureau Art déco avec pendulette — vue 1</x:v>
+      </x:c>
+      <x:c r="E144" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="24" customHeight="1">
+      <x:c r="A145" s="20" t="str">
+        <x:v>MOB-062</x:v>
+      </x:c>
+      <x:c r="B145" s="20" t="str">
+        <x:v>MOB-062-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C145" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D145" s="20" t="str">
+        <x:v>Lampe de bureau Art déco avec pendulette — vue 2</x:v>
+      </x:c>
+      <x:c r="E145" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="24" customHeight="1">
+      <x:c r="A146" s="26" t="str">
+        <x:v>MOB-062</x:v>
+      </x:c>
+      <x:c r="B146" s="26" t="str">
+        <x:v>MOB-062-03.jpeg</x:v>
+      </x:c>
+      <x:c r="C146" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D146" s="26" t="str">
+        <x:v>Lampe de bureau Art déco avec pendulette — vue 3</x:v>
+      </x:c>
+      <x:c r="E146" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="24" customHeight="1">
+      <x:c r="A147" s="20" t="str">
+        <x:v>MOB-063</x:v>
+      </x:c>
+      <x:c r="B147" s="20" t="str">
+        <x:v>MOB-063-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C147" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D147" s="20" t="str">
+        <x:v>Suspension en verre moulé plissé — vue 1</x:v>
+      </x:c>
+      <x:c r="E147" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="24" customHeight="1">
+      <x:c r="A148" s="26" t="str">
+        <x:v>MOB-064</x:v>
+      </x:c>
+      <x:c r="B148" s="26" t="str">
+        <x:v>MOB-064-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C148" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D148" s="26" t="str">
+        <x:v>Suspension en verre opalin à décor floral orangé — vue 1</x:v>
+      </x:c>
+      <x:c r="E148" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="24" customHeight="1">
+      <x:c r="A149" s="20" t="str">
+        <x:v>MOB-064</x:v>
+      </x:c>
+      <x:c r="B149" s="20" t="str">
+        <x:v>MOB-064-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C149" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D149" s="20" t="str">
+        <x:v>Suspension en verre opalin à décor floral orangé — vue 2</x:v>
+      </x:c>
+      <x:c r="E149" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="24" customHeight="1">
+      <x:c r="A150" s="26" t="str">
+        <x:v>MOB-065</x:v>
+      </x:c>
+      <x:c r="B150" s="26" t="str">
+        <x:v>MOB-065-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C150" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D150" s="26" t="str">
+        <x:v>Porte-manteau mural à deux crochets grotesques — vue 1</x:v>
+      </x:c>
+      <x:c r="E150" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="24" customHeight="1">
+      <x:c r="A151" s="20" t="str">
+        <x:v>MOB-065</x:v>
+      </x:c>
+      <x:c r="B151" s="20" t="str">
+        <x:v>MOB-065-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C151" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D151" s="20" t="str">
+        <x:v>Porte-manteau mural à deux crochets grotesques — vue 2</x:v>
+      </x:c>
+      <x:c r="E151" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="24" customHeight="1">
+      <x:c r="A152" s="26" t="str">
+        <x:v>MOB-066</x:v>
+      </x:c>
+      <x:c r="B152" s="26" t="str">
+        <x:v>MOB-066-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C152" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D152" s="26" t="str">
+        <x:v>Lustre floral en métal peint à deux lumières — vue 1</x:v>
+      </x:c>
+      <x:c r="E152" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="24" customHeight="1">
+      <x:c r="A153" s="20" t="str">
+        <x:v>MOB-066</x:v>
+      </x:c>
+      <x:c r="B153" s="20" t="str">
+        <x:v>MOB-066-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C153" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D153" s="20" t="str">
+        <x:v>Lustre floral en métal peint à deux lumières — vue 2</x:v>
+      </x:c>
+      <x:c r="E153" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="24" customHeight="1">
+      <x:c r="A154" s="26" t="str">
+        <x:v>MOB-067</x:v>
+      </x:c>
+      <x:c r="B154" s="26" t="str">
+        <x:v>MOB-067-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C154" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D154" s="26" t="str">
+        <x:v>Petit meuble mural à porte vitrée verte — vue 1</x:v>
+      </x:c>
+      <x:c r="E154" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="24" customHeight="1">
+      <x:c r="A155" s="20" t="str">
+        <x:v>MOB-067</x:v>
+      </x:c>
+      <x:c r="B155" s="20" t="str">
+        <x:v>MOB-067-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C155" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D155" s="20" t="str">
+        <x:v>Petit meuble mural à porte vitrée verte — vue 2</x:v>
+      </x:c>
+      <x:c r="E155" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="24" customHeight="1">
+      <x:c r="A156" s="26" t="str">
+        <x:v>MOB-068</x:v>
+      </x:c>
+      <x:c r="B156" s="26" t="str">
+        <x:v>MOB-068-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C156" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D156" s="26" t="str">
+        <x:v>Meuble bas à huit tiroirs — vue 1</x:v>
+      </x:c>
+      <x:c r="E156" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="24" customHeight="1">
+      <x:c r="A157" s="20" t="str">
+        <x:v>MOB-068</x:v>
+      </x:c>
+      <x:c r="B157" s="20" t="str">
+        <x:v>MOB-068-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C157" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D157" s="20" t="str">
+        <x:v>Meuble bas à huit tiroirs — vue 2</x:v>
+      </x:c>
+      <x:c r="E157" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="24" customHeight="1">
+      <x:c r="A158" s="26" t="str">
+        <x:v>MOB-069</x:v>
+      </x:c>
+      <x:c r="B158" s="26" t="str">
+        <x:v>MOB-069-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C158" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D158" s="26" t="str">
+        <x:v>Horloge-calendrier avec thermomètre et sonnerie — vue 1</x:v>
+      </x:c>
+      <x:c r="E158" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="24" customHeight="1">
+      <x:c r="A159" s="20" t="str">
+        <x:v>MOB-069</x:v>
+      </x:c>
+      <x:c r="B159" s="20" t="str">
+        <x:v>MOB-069-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C159" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D159" s="20" t="str">
+        <x:v>Horloge-calendrier avec thermomètre et sonnerie — vue 2</x:v>
+      </x:c>
+      <x:c r="E159" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="24" customHeight="1">
+      <x:c r="A160" s="26" t="str">
+        <x:v>MOB-069</x:v>
+      </x:c>
+      <x:c r="B160" s="26" t="str">
+        <x:v>MOB-069-03.jpeg</x:v>
+      </x:c>
+      <x:c r="C160" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D160" s="26" t="str">
+        <x:v>Horloge-calendrier avec thermomètre et sonnerie — vue 3</x:v>
+      </x:c>
+      <x:c r="E160" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="24" customHeight="1">
+      <x:c r="A161" s="20" t="str">
+        <x:v>MOB-069</x:v>
+      </x:c>
+      <x:c r="B161" s="20" t="str">
+        <x:v>MOB-069-04.jpeg</x:v>
+      </x:c>
+      <x:c r="C161" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D161" s="20" t="str">
+        <x:v>Horloge-calendrier avec thermomètre et sonnerie — vue 4</x:v>
+      </x:c>
+      <x:c r="E161" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="24" customHeight="1">
+      <x:c r="A162" s="26" t="str">
+        <x:v>MOB-070</x:v>
+      </x:c>
+      <x:c r="B162" s="26" t="str">
+        <x:v>MOB-070-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C162" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D162" s="26" t="str">
+        <x:v>Lustre feuillagé en métal doré — vue 1</x:v>
+      </x:c>
+      <x:c r="E162" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="24" customHeight="1">
+      <x:c r="A163" s="20" t="str">
+        <x:v>MOB-071</x:v>
+      </x:c>
+      <x:c r="B163" s="20" t="str">
+        <x:v>MOB-071-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C163" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D163" s="20" t="str">
+        <x:v>Étagère de salle de bains en verre et métal — vue 1</x:v>
+      </x:c>
+      <x:c r="E163" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="24" customHeight="1">
+      <x:c r="A164" s="26" t="str">
+        <x:v>MOB-072</x:v>
+      </x:c>
+      <x:c r="B164" s="26" t="str">
+        <x:v>MOB-072-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C164" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D164" s="26" t="str">
+        <x:v>Harmonium à deux claviers Ph. J. Trayser &amp; Cie — vue 1</x:v>
+      </x:c>
+      <x:c r="E164" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="24" customHeight="1">
+      <x:c r="A165" s="20" t="str">
+        <x:v>MOB-072</x:v>
+      </x:c>
+      <x:c r="B165" s="20" t="str">
+        <x:v>MOB-072-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C165" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D165" s="20" t="str">
+        <x:v>Harmonium à deux claviers Ph. J. Trayser &amp; Cie — vue 2</x:v>
+      </x:c>
+      <x:c r="E165" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="24" customHeight="1">
+      <x:c r="A166" s="26" t="str">
+        <x:v>MOB-072</x:v>
+      </x:c>
+      <x:c r="B166" s="26" t="str">
+        <x:v>MOB-072-03.jpeg</x:v>
+      </x:c>
+      <x:c r="C166" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D166" s="26" t="str">
+        <x:v>Harmonium à deux claviers Ph. J. Trayser &amp; Cie — vue 3</x:v>
+      </x:c>
+      <x:c r="E166" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="24" customHeight="1">
+      <x:c r="A167" s="20" t="str">
+        <x:v>MOB-072</x:v>
+      </x:c>
+      <x:c r="B167" s="20" t="str">
+        <x:v>MOB-072-04.jpeg</x:v>
+      </x:c>
+      <x:c r="C167" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D167" s="20" t="str">
+        <x:v>Harmonium à deux claviers Ph. J. Trayser &amp; Cie — vue 4</x:v>
+      </x:c>
+      <x:c r="E167" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="24" customHeight="1">
+      <x:c r="A168" s="26" t="str">
+        <x:v>MOB-072</x:v>
+      </x:c>
+      <x:c r="B168" s="26" t="str">
+        <x:v>MOB-072-05.jpeg</x:v>
+      </x:c>
+      <x:c r="C168" s="26" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D168" s="26" t="str">
+        <x:v>Harmonium à deux claviers Ph. J. Trayser &amp; Cie — vue 5</x:v>
+      </x:c>
+      <x:c r="E168" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="24" customHeight="1">
+      <x:c r="A169" s="20" t="str">
+        <x:v>MOB-073</x:v>
+      </x:c>
+      <x:c r="B169" s="20" t="str">
+        <x:v>MOB-073-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C169" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D169" s="20" t="str">
+        <x:v>Commode sombre à quatre tiroirs — vue 1</x:v>
+      </x:c>
+      <x:c r="E169" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="24" customHeight="1">
+      <x:c r="A170" s="26" t="str">
+        <x:v>MOB-074</x:v>
+      </x:c>
+      <x:c r="B170" s="26" t="str">
+        <x:v>MOB-074-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C170" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D170" s="26" t="str">
+        <x:v>Meuble haut à une porte et un tiroir — vue 1</x:v>
+      </x:c>
+      <x:c r="E170" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="24" customHeight="1">
+      <x:c r="A171" s="20" t="str">
+        <x:v>MOB-075</x:v>
+      </x:c>
+      <x:c r="B171" s="20" t="str">
+        <x:v>MOB-075-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C171" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D171" s="20" t="str">
+        <x:v>Armoire à deux portes panneautées — vue 1</x:v>
+      </x:c>
+      <x:c r="E171" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="24" customHeight="1">
+      <x:c r="A172" s="26" t="str">
+        <x:v>MOB-076</x:v>
+      </x:c>
+      <x:c r="B172" s="26" t="str">
+        <x:v>MOB-076-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C172" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D172" s="26" t="str">
+        <x:v>Lit double en métal à médaillons ovales — vue 1</x:v>
+      </x:c>
+      <x:c r="E172" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" ht="24" customHeight="1">
+      <x:c r="A173" s="20" t="str">
+        <x:v>MOB-077</x:v>
+      </x:c>
+      <x:c r="B173" s="20" t="str">
+        <x:v>MOB-077-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C173" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D173" s="20" t="str">
+        <x:v>Table de chevet à trois tiroirs — vue 1</x:v>
+      </x:c>
+      <x:c r="E173" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" ht="24" customHeight="1">
+      <x:c r="A174" s="26" t="str">
+        <x:v>MOB-078</x:v>
+      </x:c>
+      <x:c r="B174" s="26" t="str">
+        <x:v>MOB-078-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C174" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D174" s="26" t="str">
+        <x:v>Buffet bas à deux portes et deux tiroirs — vue 1</x:v>
+      </x:c>
+      <x:c r="E174" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" ht="24" customHeight="1">
+      <x:c r="A175" s="20" t="str">
+        <x:v>MOB-079</x:v>
+      </x:c>
+      <x:c r="B175" s="20" t="str">
+        <x:v>MOB-079-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C175" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D175" s="20" t="str">
+        <x:v>Meuble de toilette à miroir et plateau de marbre — vue 1</x:v>
+      </x:c>
+      <x:c r="E175" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" ht="24" customHeight="1">
+      <x:c r="A176" s="26" t="str">
+        <x:v>MOB-080</x:v>
+      </x:c>
+      <x:c r="B176" s="26" t="str">
+        <x:v>MOB-080-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C176" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D176" s="26" t="str">
+        <x:v>Grand miroir doré de style rocaille — vue 1</x:v>
+      </x:c>
+      <x:c r="E176" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" ht="24" customHeight="1">
+      <x:c r="A177" s="20" t="str">
+        <x:v>MOB-081</x:v>
+      </x:c>
+      <x:c r="B177" s="20" t="str">
+        <x:v>MOB-081-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C177" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D177" s="20" t="str">
+        <x:v>Fauteuil à dossier cintré et garniture noire — vue 1</x:v>
+      </x:c>
+      <x:c r="E177" s="20" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" ht="24" customHeight="1">
+      <x:c r="A178" s="26" t="str">
+        <x:v>MOB-082</x:v>
+      </x:c>
+      <x:c r="B178" s="26" t="str">
+        <x:v>MOB-082-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C178" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D178" s="26" t="str">
+        <x:v>Lampe de table en métal patiné — vue 1</x:v>
+      </x:c>
+      <x:c r="E178" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" ht="24" customHeight="1">
+      <x:c r="A179" s="20" t="str">
+        <x:v>MOB-082</x:v>
+      </x:c>
+      <x:c r="B179" s="20" t="str">
+        <x:v>MOB-082-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C179" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D179" s="20" t="str">
+        <x:v>Lampe de table en métal patiné — vue 2</x:v>
+      </x:c>
+      <x:c r="E179" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" ht="24" customHeight="1">
+      <x:c r="A180" s="26" t="str">
+        <x:v>MOB-083</x:v>
+      </x:c>
+      <x:c r="B180" s="26" t="str">
+        <x:v>MOB-083-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C180" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D180" s="26" t="str">
+        <x:v>Grand plateau de service vitré — vue 1</x:v>
+      </x:c>
+      <x:c r="E180" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" ht="24" customHeight="1">
+      <x:c r="A181" s="20" t="str">
+        <x:v>MOB-083</x:v>
+      </x:c>
+      <x:c r="B181" s="20" t="str">
+        <x:v>MOB-083-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C181" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D181" s="20" t="str">
+        <x:v>Grand plateau de service vitré — vue 2</x:v>
+      </x:c>
+      <x:c r="E181" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" ht="24" customHeight="1">
+      <x:c r="A182" s="26" t="str">
+        <x:v>MOB-084</x:v>
+      </x:c>
+      <x:c r="B182" s="26" t="str">
+        <x:v>MOB-084-01.jpeg</x:v>
+      </x:c>
+      <x:c r="C182" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D182" s="26" t="str">
+        <x:v>Ménagère de couverts à manches clairs en coffret — vue 1</x:v>
+      </x:c>
+      <x:c r="E182" s="26" t="str">
+        <x:v>Oui</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" ht="24" customHeight="1">
+      <x:c r="A183" s="20" t="str">
+        <x:v>MOB-084</x:v>
+      </x:c>
+      <x:c r="B183" s="20" t="str">
+        <x:v>MOB-084-02.jpeg</x:v>
+      </x:c>
+      <x:c r="C183" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D183" s="20" t="str">
+        <x:v>Ménagère de couverts à manches clairs en coffret — vue 2</x:v>
+      </x:c>
+      <x:c r="E183" s="20" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" ht="24" customHeight="1">
+      <x:c r="A184" s="26" t="str">
+        <x:v>MOB-084</x:v>
+      </x:c>
+      <x:c r="B184" s="26" t="str">
+        <x:v>MOB-084-03.jpeg</x:v>
+      </x:c>
+      <x:c r="C184" s="26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D184" s="26" t="str">
+        <x:v>Ménagère de couverts à manches clairs en coffret — vue 3</x:v>
+      </x:c>
+      <x:c r="E184" s="26" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
@@ -6768,7 +10252,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28c07101958344f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c22940558304462"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/inventaire_mobilier.xlsx
+++ b/inventaire_mobilier.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolas.coquet/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FF339A-228B-2844-BD4F-C73E44B98385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC75BDCA-2CD1-3C48-A084-A2BCE1037243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mobilier" sheetId="1" r:id="rId1"/>
@@ -2109,9 +2109,6 @@
     <t>État ancien non nettoyé ; poussière, oxydation et usures de peinture. Réflecteur présent, mais brûleur, lampe ou réservoir, vitrage et accessoires à inventorier ; fonctionnement non testé. Ne pas remettre en service sans contrôle professionnel.</t>
   </si>
   <si>
-    <t>Cheminée</t>
-  </si>
-  <si>
     <t>calorifère; pétrole; chauffage; réflecteur; tôle peinte; fonte; vers 1900</t>
   </si>
   <si>
@@ -3514,6 +3511,9 @@
   </si>
   <si>
     <t>Salle de bain 1</t>
+  </si>
+  <si>
+    <t>À conserver</t>
   </si>
 </sst>
 </file>
@@ -3710,6 +3710,15 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3720,15 +3729,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4045,54 +4045,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="34" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
     </row>
     <row r="2" spans="1:21" ht="28" customHeight="1">
-      <c r="A2" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
+      <c r="A2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
     </row>
     <row r="3" spans="1:21" ht="38" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -4232,7 +4232,7 @@
         <v>32</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>33</v>
@@ -4259,7 +4259,7 @@
         <v>250</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>224</v>
@@ -4324,7 +4324,7 @@
         <v>60</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>224</v>
@@ -4389,7 +4389,7 @@
         <v>100</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>224</v>
@@ -4427,7 +4427,7 @@
         <v>66</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>67</v>
@@ -4454,7 +4454,7 @@
         <v>70</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>224</v>
@@ -4519,7 +4519,7 @@
         <v>180</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>224</v>
@@ -4584,7 +4584,7 @@
         <v>650</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>224</v>
@@ -4649,7 +4649,7 @@
         <v>450</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>224</v>
@@ -4714,7 +4714,7 @@
         <v>400</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>224</v>
@@ -4779,7 +4779,7 @@
         <v>700</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>224</v>
@@ -4816,7 +4816,7 @@
       <c r="B14" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="19" t="s">
         <v>86</v>
       </c>
       <c r="D14" s="9" t="s">
@@ -4844,7 +4844,7 @@
         <v>600</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>224</v>
@@ -4909,7 +4909,7 @@
         <v>650</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>224</v>
@@ -4949,7 +4949,7 @@
         <v>148</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>149</v>
@@ -4976,7 +4976,7 @@
         <v>80</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>224</v>
@@ -5041,7 +5041,7 @@
         <v>160</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>224</v>
@@ -5106,7 +5106,7 @@
         <v>200</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>224</v>
@@ -5144,7 +5144,7 @@
         <v>179</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>180</v>
@@ -5171,7 +5171,7 @@
         <v>80</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>224</v>
@@ -5209,7 +5209,7 @@
         <v>189</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>107</v>
@@ -5236,7 +5236,7 @@
         <v>350</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>224</v>
@@ -5273,7 +5273,7 @@
       <c r="B21" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="19" t="s">
         <v>86</v>
       </c>
       <c r="D21" s="9" t="s">
@@ -5301,7 +5301,7 @@
         <v>140</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>224</v>
@@ -5338,7 +5338,7 @@
       <c r="B22" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="19" t="s">
         <v>86</v>
       </c>
       <c r="D22" s="9" t="s">
@@ -5366,7 +5366,7 @@
         <v>90</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>224</v>
@@ -5404,7 +5404,7 @@
         <v>217</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>218</v>
@@ -5431,7 +5431,7 @@
         <v>100</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>224</v>
@@ -5469,7 +5469,7 @@
         <v>229</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>107</v>
@@ -5496,10 +5496,10 @@
         <v>500</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>224</v>
+        <v>1159</v>
       </c>
       <c r="N24" s="9" t="s">
         <v>27</v>
@@ -5534,7 +5534,7 @@
         <v>238</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>160</v>
@@ -5561,10 +5561,10 @@
         <v>2200</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>224</v>
+        <v>1159</v>
       </c>
       <c r="N25" s="9" t="s">
         <v>27</v>
@@ -5626,7 +5626,7 @@
         <v>100</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>224</v>
@@ -5691,7 +5691,7 @@
         <v>180</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>224</v>
@@ -5729,7 +5729,7 @@
         <v>268</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>269</v>
@@ -5756,7 +5756,7 @@
         <v>220</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>224</v>
@@ -5821,7 +5821,7 @@
         <v>150</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>224</v>
@@ -5951,7 +5951,7 @@
         <v>100</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>224</v>
@@ -5989,7 +5989,7 @@
         <v>310</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>311</v>
@@ -6016,7 +6016,7 @@
         <v>180</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>224</v>
@@ -6054,7 +6054,7 @@
         <v>321</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>322</v>
@@ -6276,7 +6276,7 @@
         <v>600</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="M36" s="3" t="s">
         <v>224</v>
@@ -6314,7 +6314,7 @@
         <v>363</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>107</v>
@@ -6341,10 +6341,10 @@
         <v>700</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>224</v>
+        <v>1159</v>
       </c>
       <c r="N37" s="9" t="s">
         <v>27</v>
@@ -6379,7 +6379,7 @@
         <v>372</v>
       </c>
       <c r="C38" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D38" t="s">
         <v>373</v>
@@ -6406,7 +6406,7 @@
         <v>600</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M38" s="3" t="s">
         <v>224</v>
@@ -6471,7 +6471,7 @@
         <v>250</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>224</v>
@@ -6536,7 +6536,7 @@
         <v>150</v>
       </c>
       <c r="L40" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>224</v>
@@ -6601,7 +6601,7 @@
         <v>180</v>
       </c>
       <c r="L41" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>224</v>
@@ -6639,7 +6639,7 @@
         <v>412</v>
       </c>
       <c r="C42" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D42" t="s">
         <v>149</v>
@@ -6666,7 +6666,7 @@
         <v>100</v>
       </c>
       <c r="L42" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>224</v>
@@ -6704,7 +6704,7 @@
         <v>422</v>
       </c>
       <c r="C43" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D43" t="s">
         <v>119</v>
@@ -6731,7 +6731,7 @@
         <v>2200</v>
       </c>
       <c r="L43" s="9" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>224</v>
@@ -6771,7 +6771,7 @@
         <v>431</v>
       </c>
       <c r="C44" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D44" t="s">
         <v>160</v>
@@ -6798,10 +6798,10 @@
         <v>600</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>224</v>
+        <v>1159</v>
       </c>
       <c r="N44" t="s">
         <v>27</v>
@@ -6836,7 +6836,7 @@
         <v>440</v>
       </c>
       <c r="C45" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D45" t="s">
         <v>160</v>
@@ -6863,7 +6863,7 @@
         <v>700</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>224</v>
@@ -6903,7 +6903,7 @@
         <v>449</v>
       </c>
       <c r="C46" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D46" t="s">
         <v>160</v>
@@ -6930,7 +6930,7 @@
         <v>350</v>
       </c>
       <c r="L46" s="9" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>224</v>
@@ -6970,7 +6970,7 @@
         <v>456</v>
       </c>
       <c r="C47" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D47" t="s">
         <v>457</v>
@@ -6997,7 +6997,7 @@
         <v>120</v>
       </c>
       <c r="L47" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>224</v>
@@ -7061,8 +7061,8 @@
       <c r="K48" s="9">
         <v>120</v>
       </c>
-      <c r="L48" t="s">
-        <v>691</v>
+      <c r="L48" s="11" t="s">
+        <v>1150</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>224</v>
@@ -7071,13 +7071,13 @@
         <v>27</v>
       </c>
       <c r="O48" t="s">
+        <v>691</v>
+      </c>
+      <c r="P48" t="s">
         <v>692</v>
       </c>
-      <c r="P48" t="s">
+      <c r="Q48" t="s">
         <v>693</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>694</v>
       </c>
       <c r="R48" s="17">
         <v>1</v>
@@ -7094,31 +7094,31 @@
     </row>
     <row r="49" spans="1:21" ht="66" customHeight="1">
       <c r="A49" s="15" t="s">
+        <v>694</v>
+      </c>
+      <c r="B49" s="11" t="s">
         <v>695</v>
       </c>
-      <c r="B49" s="11" t="s">
-        <v>696</v>
-      </c>
       <c r="C49" s="11" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D49" s="11" t="s">
+        <v>697</v>
+      </c>
+      <c r="E49" s="11" t="s">
         <v>698</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="F49" s="11" t="s">
         <v>699</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="G49" s="11" t="s">
         <v>700</v>
       </c>
-      <c r="G49" s="11" t="s">
+      <c r="H49" s="11" t="s">
         <v>701</v>
       </c>
-      <c r="H49" s="11" t="s">
+      <c r="I49" s="11" t="s">
         <v>702</v>
-      </c>
-      <c r="I49" s="11" t="s">
-        <v>703</v>
       </c>
       <c r="J49" s="12">
         <v>150</v>
@@ -7127,7 +7127,7 @@
         <v>300</v>
       </c>
       <c r="L49" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>224</v>
@@ -7136,13 +7136,13 @@
         <v>27</v>
       </c>
       <c r="O49" s="11" t="s">
+        <v>703</v>
+      </c>
+      <c r="P49" s="11" t="s">
         <v>704</v>
       </c>
-      <c r="P49" s="11" t="s">
+      <c r="Q49" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q49" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R49" s="17">
         <v>1</v>
@@ -7159,31 +7159,31 @@
     </row>
     <row r="50" spans="1:21" ht="66" customHeight="1">
       <c r="A50" s="16" t="s">
+        <v>706</v>
+      </c>
+      <c r="B50" s="13" t="s">
         <v>707</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>708</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>86</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E50" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F50" s="13" t="s">
+        <v>709</v>
+      </c>
+      <c r="G50" s="13" t="s">
         <v>710</v>
       </c>
-      <c r="G50" s="13" t="s">
+      <c r="H50" s="13" t="s">
         <v>711</v>
       </c>
-      <c r="H50" s="13" t="s">
+      <c r="I50" s="13" t="s">
         <v>712</v>
-      </c>
-      <c r="I50" s="13" t="s">
-        <v>713</v>
       </c>
       <c r="J50" s="14">
         <v>40</v>
@@ -7201,13 +7201,13 @@
         <v>27</v>
       </c>
       <c r="O50" s="13" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="P50" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q50" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q50" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R50" s="17">
         <v>1</v>
@@ -7224,31 +7224,31 @@
     </row>
     <row r="51" spans="1:21" ht="66" customHeight="1">
       <c r="A51" s="15" t="s">
+        <v>714</v>
+      </c>
+      <c r="B51" s="11" t="s">
         <v>715</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>716</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>86</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>345</v>
       </c>
       <c r="F51" s="11" t="s">
+        <v>716</v>
+      </c>
+      <c r="G51" s="11" t="s">
         <v>717</v>
       </c>
-      <c r="G51" s="11" t="s">
+      <c r="H51" s="11" t="s">
+        <v>711</v>
+      </c>
+      <c r="I51" s="11" t="s">
         <v>718</v>
-      </c>
-      <c r="H51" s="11" t="s">
-        <v>712</v>
-      </c>
-      <c r="I51" s="11" t="s">
-        <v>719</v>
       </c>
       <c r="J51" s="12">
         <v>40</v>
@@ -7266,13 +7266,13 @@
         <v>27</v>
       </c>
       <c r="O51" s="11" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="P51" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q51" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q51" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R51" s="17">
         <v>1</v>
@@ -7289,31 +7289,31 @@
     </row>
     <row r="52" spans="1:21" ht="66" customHeight="1">
       <c r="A52" s="16" t="s">
+        <v>720</v>
+      </c>
+      <c r="B52" s="13" t="s">
         <v>721</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>722</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>86</v>
       </c>
       <c r="D52" s="13" t="s">
+        <v>722</v>
+      </c>
+      <c r="E52" s="13" t="s">
         <v>723</v>
       </c>
-      <c r="E52" s="13" t="s">
+      <c r="F52" s="13" t="s">
         <v>724</v>
       </c>
-      <c r="F52" s="13" t="s">
+      <c r="G52" s="13" t="s">
         <v>725</v>
       </c>
-      <c r="G52" s="13" t="s">
+      <c r="H52" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="I52" s="13" t="s">
         <v>726</v>
-      </c>
-      <c r="H52" s="13" t="s">
-        <v>702</v>
-      </c>
-      <c r="I52" s="13" t="s">
-        <v>727</v>
       </c>
       <c r="J52" s="14">
         <v>80</v>
@@ -7322,7 +7322,7 @@
         <v>180</v>
       </c>
       <c r="L52" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>224</v>
@@ -7331,13 +7331,13 @@
         <v>27</v>
       </c>
       <c r="O52" s="13" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="P52" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q52" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q52" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R52" s="17">
         <v>1</v>
@@ -7354,31 +7354,31 @@
     </row>
     <row r="53" spans="1:21" ht="66" customHeight="1">
       <c r="A53" s="15" t="s">
+        <v>728</v>
+      </c>
+      <c r="B53" s="11" t="s">
         <v>729</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>730</v>
       </c>
       <c r="C53" s="11" t="s">
         <v>86</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>345</v>
       </c>
       <c r="F53" s="11" t="s">
+        <v>731</v>
+      </c>
+      <c r="G53" s="11" t="s">
         <v>732</v>
       </c>
-      <c r="G53" s="11" t="s">
+      <c r="H53" s="11" t="s">
         <v>733</v>
       </c>
-      <c r="H53" s="11" t="s">
+      <c r="I53" s="11" t="s">
         <v>734</v>
-      </c>
-      <c r="I53" s="11" t="s">
-        <v>735</v>
       </c>
       <c r="J53" s="12">
         <v>150</v>
@@ -7387,7 +7387,7 @@
         <v>350</v>
       </c>
       <c r="L53" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M53" s="3" t="s">
         <v>224</v>
@@ -7396,13 +7396,13 @@
         <v>27</v>
       </c>
       <c r="O53" s="11" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="P53" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q53" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q53" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R53" s="17">
         <v>1</v>
@@ -7419,31 +7419,31 @@
     </row>
     <row r="54" spans="1:21" ht="66" customHeight="1">
       <c r="A54" s="16" t="s">
+        <v>736</v>
+      </c>
+      <c r="B54" s="13" t="s">
         <v>737</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>738</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>86</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E54" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F54" s="13" t="s">
+        <v>738</v>
+      </c>
+      <c r="G54" s="13" t="s">
         <v>739</v>
       </c>
-      <c r="G54" s="13" t="s">
+      <c r="H54" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="I54" s="13" t="s">
         <v>740</v>
-      </c>
-      <c r="H54" s="13" t="s">
-        <v>702</v>
-      </c>
-      <c r="I54" s="13" t="s">
-        <v>741</v>
       </c>
       <c r="J54" s="14">
         <v>40</v>
@@ -7461,13 +7461,13 @@
         <v>27</v>
       </c>
       <c r="O54" s="13" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="P54" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q54" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q54" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R54" s="17">
         <v>1</v>
@@ -7484,31 +7484,31 @@
     </row>
     <row r="55" spans="1:21" ht="66" customHeight="1">
       <c r="A55" s="15" t="s">
+        <v>742</v>
+      </c>
+      <c r="B55" s="11" t="s">
         <v>743</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>744</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>86</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>345</v>
       </c>
       <c r="F55" s="11" t="s">
+        <v>744</v>
+      </c>
+      <c r="G55" s="11" t="s">
         <v>745</v>
       </c>
-      <c r="G55" s="11" t="s">
+      <c r="H55" s="11" t="s">
+        <v>711</v>
+      </c>
+      <c r="I55" s="11" t="s">
         <v>746</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>712</v>
-      </c>
-      <c r="I55" s="11" t="s">
-        <v>747</v>
       </c>
       <c r="J55" s="12">
         <v>50</v>
@@ -7526,13 +7526,13 @@
         <v>27</v>
       </c>
       <c r="O55" s="11" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="P55" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q55" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q55" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R55" s="17">
         <v>1</v>
@@ -7549,31 +7549,31 @@
     </row>
     <row r="56" spans="1:21" ht="66" customHeight="1">
       <c r="A56" s="16" t="s">
+        <v>748</v>
+      </c>
+      <c r="B56" s="13" t="s">
         <v>749</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="C56" s="13" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D56" s="13" t="s">
         <v>750</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>1148</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>751</v>
       </c>
       <c r="E56" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F56" s="13" t="s">
+        <v>751</v>
+      </c>
+      <c r="G56" s="13" t="s">
         <v>752</v>
       </c>
-      <c r="G56" s="13" t="s">
+      <c r="H56" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="I56" s="13" t="s">
         <v>753</v>
-      </c>
-      <c r="H56" s="13" t="s">
-        <v>702</v>
-      </c>
-      <c r="I56" s="13" t="s">
-        <v>754</v>
       </c>
       <c r="J56" s="14">
         <v>100</v>
@@ -7582,22 +7582,22 @@
         <v>250</v>
       </c>
       <c r="L56" s="13" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>224</v>
+        <v>1159</v>
       </c>
       <c r="N56" s="13" t="s">
         <v>27</v>
       </c>
       <c r="O56" s="13" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="P56" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q56" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q56" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R56" s="17">
         <v>1</v>
@@ -7614,31 +7614,31 @@
     </row>
     <row r="57" spans="1:21" ht="66" customHeight="1">
       <c r="A57" s="15" t="s">
+        <v>755</v>
+      </c>
+      <c r="B57" s="11" t="s">
         <v>756</v>
       </c>
-      <c r="B57" s="11" t="s">
-        <v>757</v>
-      </c>
       <c r="C57" s="11" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>345</v>
       </c>
       <c r="F57" s="11" t="s">
+        <v>757</v>
+      </c>
+      <c r="G57" s="11" t="s">
         <v>758</v>
       </c>
-      <c r="G57" s="11" t="s">
+      <c r="H57" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="I57" s="11" t="s">
         <v>759</v>
-      </c>
-      <c r="H57" s="11" t="s">
-        <v>702</v>
-      </c>
-      <c r="I57" s="11" t="s">
-        <v>760</v>
       </c>
       <c r="J57" s="12">
         <v>200</v>
@@ -7647,7 +7647,7 @@
         <v>450</v>
       </c>
       <c r="L57" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>224</v>
@@ -7656,13 +7656,13 @@
         <v>27</v>
       </c>
       <c r="O57" s="11" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="P57" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q57" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q57" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R57" s="17">
         <v>1</v>
@@ -7679,31 +7679,31 @@
     </row>
     <row r="58" spans="1:21" ht="66" customHeight="1">
       <c r="A58" s="16" t="s">
+        <v>761</v>
+      </c>
+      <c r="B58" s="13" t="s">
         <v>762</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>763</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>118</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E58" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F58" s="13" t="s">
+        <v>764</v>
+      </c>
+      <c r="G58" s="13" t="s">
         <v>765</v>
       </c>
-      <c r="G58" s="13" t="s">
+      <c r="H58" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="I58" s="13" t="s">
         <v>766</v>
-      </c>
-      <c r="H58" s="13" t="s">
-        <v>702</v>
-      </c>
-      <c r="I58" s="13" t="s">
-        <v>767</v>
       </c>
       <c r="J58" s="14">
         <v>80</v>
@@ -7712,7 +7712,7 @@
         <v>180</v>
       </c>
       <c r="L58" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>224</v>
@@ -7721,13 +7721,13 @@
         <v>27</v>
       </c>
       <c r="O58" s="13" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="P58" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q58" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q58" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R58" s="17">
         <v>1</v>
@@ -7744,31 +7744,31 @@
     </row>
     <row r="59" spans="1:21" ht="66" customHeight="1">
       <c r="A59" s="15" t="s">
+        <v>768</v>
+      </c>
+      <c r="B59" s="11" t="s">
         <v>769</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="C59" s="11" t="s">
         <v>770</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="D59" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="E59" s="11" t="s">
         <v>771</v>
       </c>
-      <c r="D59" s="11" t="s">
-        <v>723</v>
-      </c>
-      <c r="E59" s="11" t="s">
+      <c r="F59" s="11" t="s">
         <v>772</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="G59" s="11" t="s">
         <v>773</v>
       </c>
-      <c r="G59" s="11" t="s">
+      <c r="H59" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="I59" s="11" t="s">
         <v>774</v>
-      </c>
-      <c r="H59" s="11" t="s">
-        <v>702</v>
-      </c>
-      <c r="I59" s="11" t="s">
-        <v>775</v>
       </c>
       <c r="J59" s="12">
         <v>80</v>
@@ -7777,7 +7777,7 @@
         <v>160</v>
       </c>
       <c r="L59" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>224</v>
@@ -7786,13 +7786,13 @@
         <v>27</v>
       </c>
       <c r="O59" s="11" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="P59" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q59" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q59" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R59" s="17">
         <v>1</v>
@@ -7809,31 +7809,31 @@
     </row>
     <row r="60" spans="1:21" ht="66" customHeight="1">
       <c r="A60" s="16" t="s">
+        <v>776</v>
+      </c>
+      <c r="B60" s="13" t="s">
         <v>777</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="C60" s="13" t="s">
+        <v>770</v>
+      </c>
+      <c r="D60" s="13" t="s">
         <v>778</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>771</v>
-      </c>
-      <c r="D60" s="13" t="s">
-        <v>779</v>
       </c>
       <c r="E60" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F60" s="13" t="s">
+        <v>779</v>
+      </c>
+      <c r="G60" s="13" t="s">
         <v>780</v>
       </c>
-      <c r="G60" s="13" t="s">
+      <c r="H60" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="I60" s="13" t="s">
         <v>781</v>
-      </c>
-      <c r="H60" s="13" t="s">
-        <v>734</v>
-      </c>
-      <c r="I60" s="13" t="s">
-        <v>782</v>
       </c>
       <c r="J60" s="14">
         <v>60</v>
@@ -7842,22 +7842,22 @@
         <v>140</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>224</v>
+        <v>1159</v>
       </c>
       <c r="N60" s="13" t="s">
         <v>27</v>
       </c>
       <c r="O60" s="13" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="P60" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q60" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q60" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R60" s="17">
         <v>1</v>
@@ -7874,31 +7874,31 @@
     </row>
     <row r="61" spans="1:21" ht="66" customHeight="1">
       <c r="A61" s="15" t="s">
+        <v>783</v>
+      </c>
+      <c r="B61" s="11" t="s">
         <v>784</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="C61" s="11" t="s">
+        <v>770</v>
+      </c>
+      <c r="D61" s="11" t="s">
         <v>785</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>771</v>
-      </c>
-      <c r="D61" s="11" t="s">
-        <v>786</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>345</v>
       </c>
       <c r="F61" s="11" t="s">
+        <v>786</v>
+      </c>
+      <c r="G61" s="11" t="s">
         <v>787</v>
       </c>
-      <c r="G61" s="11" t="s">
+      <c r="H61" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="I61" s="11" t="s">
         <v>788</v>
-      </c>
-      <c r="H61" s="11" t="s">
-        <v>702</v>
-      </c>
-      <c r="I61" s="11" t="s">
-        <v>789</v>
       </c>
       <c r="J61" s="12">
         <v>80</v>
@@ -7907,7 +7907,7 @@
         <v>160</v>
       </c>
       <c r="L61" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M61" s="3" t="s">
         <v>224</v>
@@ -7916,13 +7916,13 @@
         <v>27</v>
       </c>
       <c r="O61" s="11" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="P61" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q61" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q61" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R61" s="17">
         <v>1</v>
@@ -7939,31 +7939,31 @@
     </row>
     <row r="62" spans="1:21" ht="66" customHeight="1">
       <c r="A62" s="16" t="s">
+        <v>790</v>
+      </c>
+      <c r="B62" s="13" t="s">
         <v>791</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="C62" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="D62" s="13" t="s">
         <v>792</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>697</v>
-      </c>
-      <c r="D62" s="13" t="s">
-        <v>793</v>
       </c>
       <c r="E62" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F62" s="13" t="s">
+        <v>793</v>
+      </c>
+      <c r="G62" s="13" t="s">
         <v>794</v>
       </c>
-      <c r="G62" s="13" t="s">
+      <c r="H62" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="I62" s="13" t="s">
         <v>795</v>
-      </c>
-      <c r="H62" s="13" t="s">
-        <v>702</v>
-      </c>
-      <c r="I62" s="13" t="s">
-        <v>796</v>
       </c>
       <c r="J62" s="14">
         <v>80</v>
@@ -7972,7 +7972,7 @@
         <v>180</v>
       </c>
       <c r="L62" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>224</v>
@@ -7981,13 +7981,13 @@
         <v>27</v>
       </c>
       <c r="O62" s="13" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="P62" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q62" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q62" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R62" s="17">
         <v>1</v>
@@ -8004,31 +8004,31 @@
     </row>
     <row r="63" spans="1:21" ht="66" customHeight="1">
       <c r="A63" s="15" t="s">
+        <v>797</v>
+      </c>
+      <c r="B63" s="11" t="s">
         <v>798</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>799</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>118</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>345</v>
       </c>
       <c r="F63" s="11" t="s">
+        <v>799</v>
+      </c>
+      <c r="G63" s="11" t="s">
         <v>800</v>
       </c>
-      <c r="G63" s="11" t="s">
+      <c r="H63" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="I63" s="11" t="s">
         <v>801</v>
-      </c>
-      <c r="H63" s="11" t="s">
-        <v>702</v>
-      </c>
-      <c r="I63" s="11" t="s">
-        <v>802</v>
       </c>
       <c r="J63" s="12">
         <v>120</v>
@@ -8037,7 +8037,7 @@
         <v>250</v>
       </c>
       <c r="L63" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M63" s="3" t="s">
         <v>224</v>
@@ -8046,13 +8046,13 @@
         <v>27</v>
       </c>
       <c r="O63" s="11" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="P63" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q63" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q63" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R63" s="17">
         <v>1</v>
@@ -8069,31 +8069,31 @@
     </row>
     <row r="64" spans="1:21" ht="66" customHeight="1">
       <c r="A64" s="16" t="s">
+        <v>803</v>
+      </c>
+      <c r="B64" s="13" t="s">
         <v>804</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="C64" s="13" t="s">
         <v>805</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="D64" s="13" t="s">
         <v>806</v>
       </c>
-      <c r="D64" s="13" t="s">
+      <c r="E64" s="13" t="s">
         <v>807</v>
       </c>
-      <c r="E64" s="13" t="s">
+      <c r="F64" s="13" t="s">
         <v>808</v>
       </c>
-      <c r="F64" s="13" t="s">
+      <c r="G64" s="13" t="s">
         <v>809</v>
       </c>
-      <c r="G64" s="13" t="s">
+      <c r="H64" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="I64" s="13" t="s">
         <v>810</v>
-      </c>
-      <c r="H64" s="13" t="s">
-        <v>702</v>
-      </c>
-      <c r="I64" s="13" t="s">
-        <v>811</v>
       </c>
       <c r="J64" s="14">
         <v>80</v>
@@ -8102,7 +8102,7 @@
         <v>180</v>
       </c>
       <c r="L64" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M64" s="3" t="s">
         <v>224</v>
@@ -8111,13 +8111,13 @@
         <v>27</v>
       </c>
       <c r="O64" s="13" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="P64" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q64" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q64" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R64" s="17">
         <v>1</v>
@@ -8134,31 +8134,31 @@
     </row>
     <row r="65" spans="1:21" ht="66" customHeight="1">
       <c r="A65" s="15" t="s">
+        <v>812</v>
+      </c>
+      <c r="B65" s="11" t="s">
         <v>813</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="C65" s="11" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D65" s="11" t="s">
         <v>814</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>815</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>345</v>
       </c>
       <c r="F65" s="11" t="s">
+        <v>815</v>
+      </c>
+      <c r="G65" s="11" t="s">
         <v>816</v>
       </c>
-      <c r="G65" s="11" t="s">
+      <c r="H65" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="I65" s="11" t="s">
         <v>817</v>
-      </c>
-      <c r="H65" s="11" t="s">
-        <v>702</v>
-      </c>
-      <c r="I65" s="11" t="s">
-        <v>818</v>
       </c>
       <c r="J65" s="12">
         <v>100</v>
@@ -8167,7 +8167,7 @@
         <v>250</v>
       </c>
       <c r="L65" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M65" s="3" t="s">
         <v>224</v>
@@ -8176,13 +8176,13 @@
         <v>27</v>
       </c>
       <c r="O65" s="11" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="P65" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q65" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q65" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R65" s="17">
         <v>1</v>
@@ -8199,31 +8199,31 @@
     </row>
     <row r="66" spans="1:21" ht="66" customHeight="1">
       <c r="A66" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="B66" s="13" t="s">
         <v>820</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>821</v>
       </c>
       <c r="C66" s="13" t="s">
         <v>86</v>
       </c>
       <c r="D66" s="13" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E66" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F66" s="13" t="s">
+        <v>822</v>
+      </c>
+      <c r="G66" s="13" t="s">
         <v>823</v>
       </c>
-      <c r="G66" s="13" t="s">
+      <c r="H66" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="I66" s="13" t="s">
         <v>824</v>
-      </c>
-      <c r="H66" s="13" t="s">
-        <v>734</v>
-      </c>
-      <c r="I66" s="13" t="s">
-        <v>825</v>
       </c>
       <c r="J66" s="14">
         <v>30</v>
@@ -8241,13 +8241,13 @@
         <v>27</v>
       </c>
       <c r="O66" s="13" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="P66" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q66" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q66" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R66" s="17">
         <v>1</v>
@@ -8264,31 +8264,31 @@
     </row>
     <row r="67" spans="1:21" ht="66" customHeight="1">
       <c r="A67" s="15" t="s">
+        <v>826</v>
+      </c>
+      <c r="B67" s="11" t="s">
         <v>827</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>828</v>
       </c>
       <c r="C67" s="11" t="s">
         <v>86</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E67" s="11" t="s">
         <v>345</v>
       </c>
       <c r="F67" s="11" t="s">
+        <v>828</v>
+      </c>
+      <c r="G67" s="11" t="s">
         <v>829</v>
       </c>
-      <c r="G67" s="11" t="s">
+      <c r="H67" s="11" t="s">
+        <v>733</v>
+      </c>
+      <c r="I67" s="11" t="s">
         <v>830</v>
-      </c>
-      <c r="H67" s="11" t="s">
-        <v>734</v>
-      </c>
-      <c r="I67" s="11" t="s">
-        <v>831</v>
       </c>
       <c r="J67" s="12">
         <v>50</v>
@@ -8306,13 +8306,13 @@
         <v>27</v>
       </c>
       <c r="O67" s="11" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="P67" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q67" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q67" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R67" s="17">
         <v>1</v>
@@ -8329,31 +8329,31 @@
     </row>
     <row r="68" spans="1:21" ht="66" customHeight="1">
       <c r="A68" s="16" t="s">
+        <v>832</v>
+      </c>
+      <c r="B68" s="13" t="s">
         <v>833</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="C68" s="13" t="s">
         <v>834</v>
       </c>
-      <c r="C68" s="13" t="s">
-        <v>835</v>
-      </c>
       <c r="D68" s="13" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E68" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F68" s="13" t="s">
+        <v>835</v>
+      </c>
+      <c r="G68" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="G68" s="13" t="s">
+      <c r="H68" s="13" t="s">
         <v>837</v>
       </c>
-      <c r="H68" s="13" t="s">
+      <c r="I68" s="13" t="s">
         <v>838</v>
-      </c>
-      <c r="I68" s="13" t="s">
-        <v>839</v>
       </c>
       <c r="J68" s="14">
         <v>30</v>
@@ -8362,7 +8362,7 @@
         <v>70</v>
       </c>
       <c r="L68" s="11" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="M68" s="3" t="s">
         <v>224</v>
@@ -8371,19 +8371,19 @@
         <v>27</v>
       </c>
       <c r="O68" s="13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="P68" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q68" s="13" t="s">
         <v>705</v>
       </c>
-      <c r="Q68" s="13" t="s">
-        <v>706</v>
-      </c>
       <c r="R68" s="17">
         <v>1</v>
       </c>
       <c r="S68" s="18">
-        <f t="shared" ref="S68:S99" si="4">IF(OR(J68="",R68=""),"",J68*R68)</f>
+        <f t="shared" ref="S68:S87" si="4">IF(OR(J68="",R68=""),"",J68*R68)</f>
         <v>30</v>
       </c>
       <c r="T68" s="18">
@@ -8394,31 +8394,31 @@
     </row>
     <row r="69" spans="1:21" ht="66" customHeight="1">
       <c r="A69" s="15" t="s">
+        <v>840</v>
+      </c>
+      <c r="B69" s="11" t="s">
         <v>841</v>
-      </c>
-      <c r="B69" s="11" t="s">
-        <v>842</v>
       </c>
       <c r="C69" s="11" t="s">
         <v>86</v>
       </c>
       <c r="D69" s="11" t="s">
+        <v>842</v>
+      </c>
+      <c r="E69" s="11" t="s">
         <v>843</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="F69" s="11" t="s">
         <v>844</v>
       </c>
-      <c r="F69" s="11" t="s">
+      <c r="G69" s="11" t="s">
         <v>845</v>
       </c>
-      <c r="G69" s="11" t="s">
+      <c r="H69" s="11" t="s">
+        <v>733</v>
+      </c>
+      <c r="I69" s="11" t="s">
         <v>846</v>
-      </c>
-      <c r="H69" s="11" t="s">
-        <v>734</v>
-      </c>
-      <c r="I69" s="11" t="s">
-        <v>847</v>
       </c>
       <c r="J69" s="12">
         <v>80</v>
@@ -8427,7 +8427,7 @@
         <v>180</v>
       </c>
       <c r="L69" s="11" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="M69" s="3" t="s">
         <v>224</v>
@@ -8436,13 +8436,13 @@
         <v>27</v>
       </c>
       <c r="O69" s="11" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="P69" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q69" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q69" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R69" s="17">
         <v>1</v>
@@ -8459,31 +8459,31 @@
     </row>
     <row r="70" spans="1:21" ht="66" customHeight="1">
       <c r="A70" s="16" t="s">
+        <v>848</v>
+      </c>
+      <c r="B70" s="13" t="s">
         <v>849</v>
       </c>
-      <c r="B70" s="13" t="s">
-        <v>850</v>
-      </c>
       <c r="C70" s="13" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E70" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F70" s="13" t="s">
+        <v>850</v>
+      </c>
+      <c r="G70" s="13" t="s">
         <v>851</v>
       </c>
-      <c r="G70" s="13" t="s">
+      <c r="H70" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="I70" s="13" t="s">
         <v>852</v>
-      </c>
-      <c r="H70" s="13" t="s">
-        <v>702</v>
-      </c>
-      <c r="I70" s="13" t="s">
-        <v>853</v>
       </c>
       <c r="J70" s="14">
         <v>80</v>
@@ -8492,7 +8492,7 @@
         <v>160</v>
       </c>
       <c r="L70" s="11" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="M70" s="3" t="s">
         <v>224</v>
@@ -8501,13 +8501,13 @@
         <v>27</v>
       </c>
       <c r="O70" s="13" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="P70" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q70" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q70" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R70" s="17">
         <v>1</v>
@@ -8524,31 +8524,31 @@
     </row>
     <row r="71" spans="1:21" ht="66" customHeight="1">
       <c r="A71" s="15" t="s">
+        <v>854</v>
+      </c>
+      <c r="B71" s="11" t="s">
         <v>855</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="C71" s="11" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D71" s="11" t="s">
         <v>856</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>1148</v>
-      </c>
-      <c r="D71" s="11" t="s">
-        <v>857</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>345</v>
       </c>
       <c r="F71" s="11" t="s">
+        <v>857</v>
+      </c>
+      <c r="G71" s="11" t="s">
         <v>858</v>
       </c>
-      <c r="G71" s="11" t="s">
+      <c r="H71" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="I71" s="11" t="s">
         <v>859</v>
-      </c>
-      <c r="H71" s="11" t="s">
-        <v>702</v>
-      </c>
-      <c r="I71" s="11" t="s">
-        <v>860</v>
       </c>
       <c r="J71" s="12">
         <v>80</v>
@@ -8557,7 +8557,7 @@
         <v>180</v>
       </c>
       <c r="L71" s="11" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="M71" s="3" t="s">
         <v>224</v>
@@ -8566,13 +8566,13 @@
         <v>27</v>
       </c>
       <c r="O71" s="11" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="P71" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q71" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q71" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R71" s="17">
         <v>1</v>
@@ -8589,31 +8589,31 @@
     </row>
     <row r="72" spans="1:21" ht="66" customHeight="1">
       <c r="A72" s="16" t="s">
+        <v>861</v>
+      </c>
+      <c r="B72" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="B72" s="13" t="s">
+      <c r="C72" s="13" t="s">
         <v>863</v>
       </c>
-      <c r="C72" s="13" t="s">
+      <c r="D72" s="13" t="s">
+        <v>708</v>
+      </c>
+      <c r="E72" s="13" t="s">
         <v>864</v>
       </c>
-      <c r="D72" s="13" t="s">
-        <v>709</v>
-      </c>
-      <c r="E72" s="13" t="s">
+      <c r="F72" s="13" t="s">
         <v>865</v>
       </c>
-      <c r="F72" s="13" t="s">
+      <c r="G72" s="13" t="s">
         <v>866</v>
       </c>
-      <c r="G72" s="13" t="s">
+      <c r="H72" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="I72" s="13" t="s">
         <v>867</v>
-      </c>
-      <c r="H72" s="13" t="s">
-        <v>702</v>
-      </c>
-      <c r="I72" s="13" t="s">
-        <v>868</v>
       </c>
       <c r="J72" s="14">
         <v>150</v>
@@ -8622,7 +8622,7 @@
         <v>350</v>
       </c>
       <c r="L72" s="13" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>224</v>
@@ -8631,13 +8631,13 @@
         <v>27</v>
       </c>
       <c r="O72" s="13" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="P72" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q72" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q72" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R72" s="17">
         <v>1</v>
@@ -8654,31 +8654,31 @@
     </row>
     <row r="73" spans="1:21" ht="66" customHeight="1">
       <c r="A73" s="15" t="s">
+        <v>869</v>
+      </c>
+      <c r="B73" s="11" t="s">
         <v>870</v>
-      </c>
-      <c r="B73" s="11" t="s">
-        <v>871</v>
       </c>
       <c r="C73" s="11" t="s">
         <v>86</v>
       </c>
       <c r="D73" s="11" t="s">
+        <v>842</v>
+      </c>
+      <c r="E73" s="11" t="s">
         <v>843</v>
       </c>
-      <c r="E73" s="11" t="s">
-        <v>844</v>
-      </c>
       <c r="F73" s="11" t="s">
+        <v>871</v>
+      </c>
+      <c r="G73" s="11" t="s">
         <v>872</v>
       </c>
-      <c r="G73" s="11" t="s">
+      <c r="H73" s="11" t="s">
+        <v>733</v>
+      </c>
+      <c r="I73" s="11" t="s">
         <v>873</v>
-      </c>
-      <c r="H73" s="11" t="s">
-        <v>734</v>
-      </c>
-      <c r="I73" s="11" t="s">
-        <v>874</v>
       </c>
       <c r="J73" s="12">
         <v>80</v>
@@ -8687,7 +8687,7 @@
         <v>180</v>
       </c>
       <c r="L73" s="11" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="M73" s="3" t="s">
         <v>224</v>
@@ -8696,13 +8696,13 @@
         <v>27</v>
       </c>
       <c r="O73" s="11" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="P73" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q73" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q73" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R73" s="17">
         <v>1</v>
@@ -8719,31 +8719,31 @@
     </row>
     <row r="74" spans="1:21" ht="66" customHeight="1">
       <c r="A74" s="16" t="s">
+        <v>875</v>
+      </c>
+      <c r="B74" s="13" t="s">
         <v>876</v>
       </c>
-      <c r="B74" s="13" t="s">
-        <v>877</v>
-      </c>
       <c r="C74" s="13" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D74" s="13" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E74" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F74" s="13" t="s">
+        <v>877</v>
+      </c>
+      <c r="G74" s="13" t="s">
         <v>878</v>
       </c>
-      <c r="G74" s="13" t="s">
+      <c r="H74" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="I74" s="13" t="s">
         <v>879</v>
-      </c>
-      <c r="H74" s="13" t="s">
-        <v>702</v>
-      </c>
-      <c r="I74" s="13" t="s">
-        <v>880</v>
       </c>
       <c r="J74" s="14">
         <v>30</v>
@@ -8752,7 +8752,7 @@
         <v>70</v>
       </c>
       <c r="L74" s="13" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="M74" s="3" t="s">
         <v>224</v>
@@ -8761,13 +8761,13 @@
         <v>27</v>
       </c>
       <c r="O74" s="13" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="P74" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q74" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q74" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R74" s="17">
         <v>1</v>
@@ -8784,31 +8784,31 @@
     </row>
     <row r="75" spans="1:21" ht="66" customHeight="1">
       <c r="A75" s="15" t="s">
+        <v>881</v>
+      </c>
+      <c r="B75" s="11" t="s">
         <v>882</v>
       </c>
-      <c r="B75" s="11" t="s">
+      <c r="C75" s="11" t="s">
         <v>883</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="D75" s="11" t="s">
         <v>884</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="E75" s="11" t="s">
         <v>885</v>
       </c>
-      <c r="E75" s="11" t="s">
+      <c r="F75" s="11" t="s">
         <v>886</v>
       </c>
-      <c r="F75" s="11" t="s">
+      <c r="G75" s="11" t="s">
         <v>887</v>
       </c>
-      <c r="G75" s="11" t="s">
+      <c r="H75" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="I75" s="11" t="s">
         <v>888</v>
-      </c>
-      <c r="H75" s="11" t="s">
-        <v>702</v>
-      </c>
-      <c r="I75" s="11" t="s">
-        <v>889</v>
       </c>
       <c r="J75" s="12">
         <v>250</v>
@@ -8817,7 +8817,7 @@
         <v>700</v>
       </c>
       <c r="L75" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M75" s="3" t="s">
         <v>224</v>
@@ -8826,13 +8826,13 @@
         <v>27</v>
       </c>
       <c r="O75" s="11" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="P75" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q75" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q75" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R75" s="17">
         <v>1</v>
@@ -8849,31 +8849,31 @@
     </row>
     <row r="76" spans="1:21" ht="66" customHeight="1">
       <c r="A76" s="16" t="s">
+        <v>890</v>
+      </c>
+      <c r="B76" s="13" t="s">
         <v>891</v>
       </c>
-      <c r="B76" s="13" t="s">
+      <c r="C76" s="13" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D76" s="13" t="s">
         <v>892</v>
-      </c>
-      <c r="C76" s="13" t="s">
-        <v>1148</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>893</v>
       </c>
       <c r="E76" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F76" s="13" t="s">
+        <v>893</v>
+      </c>
+      <c r="G76" s="13" t="s">
         <v>894</v>
       </c>
-      <c r="G76" s="13" t="s">
+      <c r="H76" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="I76" s="13" t="s">
         <v>895</v>
-      </c>
-      <c r="H76" s="13" t="s">
-        <v>702</v>
-      </c>
-      <c r="I76" s="13" t="s">
-        <v>896</v>
       </c>
       <c r="J76" s="14">
         <v>120</v>
@@ -8891,13 +8891,13 @@
         <v>27</v>
       </c>
       <c r="O76" s="13" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="P76" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q76" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q76" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R76" s="17">
         <v>1</v>
@@ -8914,31 +8914,31 @@
     </row>
     <row r="77" spans="1:21" ht="66" customHeight="1">
       <c r="A77" s="15" t="s">
+        <v>897</v>
+      </c>
+      <c r="B77" s="11" t="s">
         <v>898</v>
       </c>
-      <c r="B77" s="11" t="s">
-        <v>899</v>
-      </c>
       <c r="C77" s="11" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E77" s="11" t="s">
         <v>345</v>
       </c>
       <c r="F77" s="11" t="s">
+        <v>899</v>
+      </c>
+      <c r="G77" s="11" t="s">
         <v>900</v>
       </c>
-      <c r="G77" s="11" t="s">
+      <c r="H77" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="I77" s="11" t="s">
         <v>901</v>
-      </c>
-      <c r="H77" s="11" t="s">
-        <v>702</v>
-      </c>
-      <c r="I77" s="11" t="s">
-        <v>902</v>
       </c>
       <c r="J77" s="12">
         <v>100</v>
@@ -8956,13 +8956,13 @@
         <v>27</v>
       </c>
       <c r="O77" s="11" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="P77" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q77" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q77" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R77" s="17">
         <v>1</v>
@@ -8979,31 +8979,31 @@
     </row>
     <row r="78" spans="1:21" ht="66" customHeight="1">
       <c r="A78" s="16" t="s">
+        <v>903</v>
+      </c>
+      <c r="B78" s="13" t="s">
         <v>904</v>
       </c>
-      <c r="B78" s="13" t="s">
-        <v>905</v>
-      </c>
       <c r="C78" s="13" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E78" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G78" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="H78" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="I78" s="13" t="s">
         <v>906</v>
-      </c>
-      <c r="H78" s="13" t="s">
-        <v>702</v>
-      </c>
-      <c r="I78" s="13" t="s">
-        <v>907</v>
       </c>
       <c r="J78" s="14">
         <v>200</v>
@@ -9021,13 +9021,13 @@
         <v>27</v>
       </c>
       <c r="O78" s="13" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="P78" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q78" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q78" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R78" s="17">
         <v>1</v>
@@ -9041,36 +9041,36 @@
         <v>450</v>
       </c>
       <c r="U78" s="9" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="79" spans="1:21" ht="66" customHeight="1">
       <c r="A79" s="15" t="s">
+        <v>909</v>
+      </c>
+      <c r="B79" s="11" t="s">
         <v>910</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>911</v>
       </c>
       <c r="C79" s="11" t="s">
         <v>19</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E79" s="11" t="s">
         <v>345</v>
       </c>
       <c r="F79" s="11" t="s">
+        <v>911</v>
+      </c>
+      <c r="G79" s="11" t="s">
         <v>912</v>
       </c>
-      <c r="G79" s="11" t="s">
+      <c r="H79" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="I79" s="11" t="s">
         <v>913</v>
-      </c>
-      <c r="H79" s="11" t="s">
-        <v>702</v>
-      </c>
-      <c r="I79" s="11" t="s">
-        <v>914</v>
       </c>
       <c r="J79" s="12">
         <v>200</v>
@@ -9088,13 +9088,13 @@
         <v>27</v>
       </c>
       <c r="O79" s="11" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="P79" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q79" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q79" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R79" s="17">
         <v>1</v>
@@ -9108,36 +9108,36 @@
         <v>500</v>
       </c>
       <c r="U79" s="9" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="80" spans="1:21" ht="66" customHeight="1">
       <c r="A80" s="16" t="s">
+        <v>916</v>
+      </c>
+      <c r="B80" s="13" t="s">
         <v>917</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="C80" s="13" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D80" s="13" t="s">
         <v>918</v>
-      </c>
-      <c r="C80" s="13" t="s">
-        <v>1148</v>
-      </c>
-      <c r="D80" s="13" t="s">
-        <v>919</v>
       </c>
       <c r="E80" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F80" s="13" t="s">
+        <v>919</v>
+      </c>
+      <c r="G80" s="13" t="s">
         <v>920</v>
       </c>
-      <c r="G80" s="13" t="s">
+      <c r="H80" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="I80" s="13" t="s">
         <v>921</v>
-      </c>
-      <c r="H80" s="13" t="s">
-        <v>702</v>
-      </c>
-      <c r="I80" s="13" t="s">
-        <v>922</v>
       </c>
       <c r="J80" s="14">
         <v>40</v>
@@ -9155,13 +9155,13 @@
         <v>27</v>
       </c>
       <c r="O80" s="13" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="P80" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q80" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q80" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R80" s="17">
         <v>1</v>
@@ -9175,36 +9175,36 @@
         <v>80</v>
       </c>
       <c r="U80" s="9" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="81" spans="1:21" ht="66" customHeight="1">
       <c r="A81" s="15" t="s">
+        <v>924</v>
+      </c>
+      <c r="B81" s="11" t="s">
         <v>925</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="C81" s="11" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D81" s="11" t="s">
         <v>926</v>
-      </c>
-      <c r="C81" s="11" t="s">
-        <v>1148</v>
-      </c>
-      <c r="D81" s="11" t="s">
-        <v>927</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>345</v>
       </c>
       <c r="F81" s="11" t="s">
+        <v>927</v>
+      </c>
+      <c r="G81" s="11" t="s">
         <v>928</v>
       </c>
-      <c r="G81" s="11" t="s">
+      <c r="H81" s="11" t="s">
+        <v>701</v>
+      </c>
+      <c r="I81" s="11" t="s">
         <v>929</v>
-      </c>
-      <c r="H81" s="11" t="s">
-        <v>702</v>
-      </c>
-      <c r="I81" s="11" t="s">
-        <v>930</v>
       </c>
       <c r="J81" s="12">
         <v>80</v>
@@ -9222,13 +9222,13 @@
         <v>27</v>
       </c>
       <c r="O81" s="11" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="P81" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q81" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q81" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R81" s="17">
         <v>1</v>
@@ -9245,31 +9245,31 @@
     </row>
     <row r="82" spans="1:21" ht="66" customHeight="1">
       <c r="A82" s="16" t="s">
+        <v>931</v>
+      </c>
+      <c r="B82" s="13" t="s">
         <v>932</v>
       </c>
-      <c r="B82" s="13" t="s">
-        <v>933</v>
-      </c>
       <c r="C82" s="13" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D82" s="13" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E82" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F82" s="13" t="s">
+        <v>933</v>
+      </c>
+      <c r="G82" s="13" t="s">
         <v>934</v>
       </c>
-      <c r="G82" s="13" t="s">
+      <c r="H82" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="I82" s="13" t="s">
         <v>935</v>
-      </c>
-      <c r="H82" s="13" t="s">
-        <v>702</v>
-      </c>
-      <c r="I82" s="13" t="s">
-        <v>936</v>
       </c>
       <c r="J82" s="14">
         <v>100</v>
@@ -9278,7 +9278,7 @@
         <v>250</v>
       </c>
       <c r="L82" s="13" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="M82" s="3" t="s">
         <v>224</v>
@@ -9287,13 +9287,13 @@
         <v>27</v>
       </c>
       <c r="O82" s="13" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="P82" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q82" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q82" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R82" s="17">
         <v>1</v>
@@ -9310,31 +9310,31 @@
     </row>
     <row r="83" spans="1:21" ht="66" customHeight="1">
       <c r="A83" s="15" t="s">
+        <v>937</v>
+      </c>
+      <c r="B83" s="11" t="s">
         <v>938</v>
-      </c>
-      <c r="B83" s="11" t="s">
-        <v>939</v>
       </c>
       <c r="C83" s="11" t="s">
         <v>301</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E83" s="11" t="s">
         <v>345</v>
       </c>
       <c r="F83" s="11" t="s">
+        <v>940</v>
+      </c>
+      <c r="G83" s="11" t="s">
         <v>941</v>
       </c>
-      <c r="G83" s="11" t="s">
+      <c r="H83" s="11" t="s">
         <v>942</v>
       </c>
-      <c r="H83" s="11" t="s">
+      <c r="I83" s="11" t="s">
         <v>943</v>
-      </c>
-      <c r="I83" s="11" t="s">
-        <v>944</v>
       </c>
       <c r="J83" s="12">
         <v>100</v>
@@ -9343,22 +9343,22 @@
         <v>250</v>
       </c>
       <c r="L83" s="11" t="s">
+        <v>1158</v>
+      </c>
+      <c r="M83" s="3" t="s">
         <v>1159</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>224</v>
-      </c>
       <c r="N83" s="11" t="s">
         <v>27</v>
       </c>
       <c r="O83" s="11" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="P83" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q83" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q83" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R83" s="17">
         <v>1</v>
@@ -9375,31 +9375,31 @@
     </row>
     <row r="84" spans="1:21" ht="66" customHeight="1">
       <c r="A84" s="16" t="s">
+        <v>945</v>
+      </c>
+      <c r="B84" s="13" t="s">
         <v>946</v>
       </c>
-      <c r="B84" s="13" t="s">
+      <c r="C84" s="13" t="s">
+        <v>770</v>
+      </c>
+      <c r="D84" s="13" t="s">
         <v>947</v>
-      </c>
-      <c r="C84" s="13" t="s">
-        <v>771</v>
-      </c>
-      <c r="D84" s="13" t="s">
-        <v>948</v>
       </c>
       <c r="E84" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F84" s="13" t="s">
+        <v>948</v>
+      </c>
+      <c r="G84" s="13" t="s">
         <v>949</v>
       </c>
-      <c r="G84" s="13" t="s">
+      <c r="H84" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="I84" s="13" t="s">
         <v>950</v>
-      </c>
-      <c r="H84" s="13" t="s">
-        <v>702</v>
-      </c>
-      <c r="I84" s="13" t="s">
-        <v>951</v>
       </c>
       <c r="J84" s="14">
         <v>100</v>
@@ -9408,22 +9408,22 @@
         <v>250</v>
       </c>
       <c r="L84" s="13" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>224</v>
+        <v>1159</v>
       </c>
       <c r="N84" s="13" t="s">
         <v>27</v>
       </c>
       <c r="O84" s="13" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="P84" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q84" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q84" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R84" s="17">
         <v>1</v>
@@ -9440,31 +9440,31 @@
     </row>
     <row r="85" spans="1:21" ht="66" customHeight="1">
       <c r="A85" s="15" t="s">
+        <v>952</v>
+      </c>
+      <c r="B85" s="11" t="s">
         <v>953</v>
-      </c>
-      <c r="B85" s="11" t="s">
-        <v>954</v>
       </c>
       <c r="C85" s="11" t="s">
         <v>86</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E85" s="11" t="s">
         <v>345</v>
       </c>
       <c r="F85" s="11" t="s">
+        <v>955</v>
+      </c>
+      <c r="G85" s="11" t="s">
         <v>956</v>
       </c>
-      <c r="G85" s="11" t="s">
+      <c r="H85" s="11" t="s">
+        <v>733</v>
+      </c>
+      <c r="I85" s="11" t="s">
         <v>957</v>
-      </c>
-      <c r="H85" s="11" t="s">
-        <v>734</v>
-      </c>
-      <c r="I85" s="11" t="s">
-        <v>958</v>
       </c>
       <c r="J85" s="12">
         <v>50</v>
@@ -9473,7 +9473,7 @@
         <v>120</v>
       </c>
       <c r="L85" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M85" s="3" t="s">
         <v>224</v>
@@ -9482,13 +9482,13 @@
         <v>27</v>
       </c>
       <c r="O85" s="11" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="P85" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q85" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q85" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R85" s="17">
         <v>1</v>
@@ -9505,31 +9505,31 @@
     </row>
     <row r="86" spans="1:21" ht="66" customHeight="1">
       <c r="A86" s="16" t="s">
+        <v>959</v>
+      </c>
+      <c r="B86" s="13" t="s">
         <v>960</v>
       </c>
-      <c r="B86" s="13" t="s">
+      <c r="C86" s="13" t="s">
         <v>961</v>
       </c>
-      <c r="C86" s="13" t="s">
-        <v>962</v>
-      </c>
       <c r="D86" s="13" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E86" s="13" t="s">
         <v>345</v>
       </c>
       <c r="F86" s="13" t="s">
+        <v>962</v>
+      </c>
+      <c r="G86" s="13" t="s">
         <v>963</v>
       </c>
-      <c r="G86" s="13" t="s">
+      <c r="H86" s="13" t="s">
         <v>964</v>
       </c>
-      <c r="H86" s="13" t="s">
+      <c r="I86" s="13" t="s">
         <v>965</v>
-      </c>
-      <c r="I86" s="13" t="s">
-        <v>966</v>
       </c>
       <c r="J86" s="14">
         <v>60</v>
@@ -9538,7 +9538,7 @@
         <v>140</v>
       </c>
       <c r="L86" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M86" s="3" t="s">
         <v>224</v>
@@ -9547,13 +9547,13 @@
         <v>27</v>
       </c>
       <c r="O86" s="13" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="P86" s="13" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q86" s="13" t="s">
         <v>705</v>
-      </c>
-      <c r="Q86" s="13" t="s">
-        <v>706</v>
       </c>
       <c r="R86" s="17">
         <v>1</v>
@@ -9570,31 +9570,31 @@
     </row>
     <row r="87" spans="1:21" ht="66" customHeight="1">
       <c r="A87" s="15" t="s">
+        <v>967</v>
+      </c>
+      <c r="B87" s="11" t="s">
         <v>968</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="C87" s="11" t="s">
+        <v>961</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>778</v>
+      </c>
+      <c r="E87" s="11" t="s">
         <v>969</v>
       </c>
-      <c r="C87" s="11" t="s">
-        <v>962</v>
-      </c>
-      <c r="D87" s="11" t="s">
-        <v>779</v>
-      </c>
-      <c r="E87" s="11" t="s">
+      <c r="F87" s="11" t="s">
         <v>970</v>
       </c>
-      <c r="F87" s="11" t="s">
+      <c r="G87" s="11" t="s">
         <v>971</v>
       </c>
-      <c r="G87" s="11" t="s">
+      <c r="H87" s="11" t="s">
         <v>972</v>
       </c>
-      <c r="H87" s="11" t="s">
+      <c r="I87" s="11" t="s">
         <v>973</v>
-      </c>
-      <c r="I87" s="11" t="s">
-        <v>974</v>
       </c>
       <c r="J87" s="12">
         <v>80</v>
@@ -9603,7 +9603,7 @@
         <v>180</v>
       </c>
       <c r="L87" s="11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="M87" s="3" t="s">
         <v>224</v>
@@ -9612,13 +9612,13 @@
         <v>27</v>
       </c>
       <c r="O87" s="11" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="P87" s="11" t="s">
+        <v>704</v>
+      </c>
+      <c r="Q87" s="11" t="s">
         <v>705</v>
-      </c>
-      <c r="Q87" s="11" t="s">
-        <v>706</v>
       </c>
       <c r="R87" s="17">
         <v>1</v>
@@ -9634,139 +9634,139 @@
       <c r="U87" s="9"/>
     </row>
     <row r="168" spans="3:3">
-      <c r="C168" s="26"/>
+      <c r="C168" s="20"/>
     </row>
     <row r="169" spans="3:3">
-      <c r="C169" s="26"/>
+      <c r="C169" s="20"/>
     </row>
     <row r="170" spans="3:3">
-      <c r="C170" s="26"/>
+      <c r="C170" s="20"/>
     </row>
     <row r="171" spans="3:3">
-      <c r="C171" s="26"/>
+      <c r="C171" s="20"/>
     </row>
     <row r="172" spans="3:3">
-      <c r="C172" s="26"/>
+      <c r="C172" s="20"/>
     </row>
     <row r="173" spans="3:3">
-      <c r="C173" s="26"/>
+      <c r="C173" s="20"/>
     </row>
     <row r="174" spans="3:3">
-      <c r="C174" s="26"/>
+      <c r="C174" s="20"/>
     </row>
     <row r="175" spans="3:3">
-      <c r="C175" s="26"/>
+      <c r="C175" s="20"/>
     </row>
     <row r="176" spans="3:3">
-      <c r="C176" s="26"/>
+      <c r="C176" s="20"/>
     </row>
     <row r="177" spans="3:3">
-      <c r="C177" s="26"/>
+      <c r="C177" s="20"/>
     </row>
     <row r="178" spans="3:3">
-      <c r="C178" s="26"/>
+      <c r="C178" s="20"/>
     </row>
     <row r="179" spans="3:3">
-      <c r="C179" s="26"/>
+      <c r="C179" s="20"/>
     </row>
     <row r="180" spans="3:3">
-      <c r="C180" s="26"/>
+      <c r="C180" s="20"/>
     </row>
     <row r="181" spans="3:3">
-      <c r="C181" s="26"/>
+      <c r="C181" s="20"/>
     </row>
     <row r="182" spans="3:3">
-      <c r="C182" s="26"/>
+      <c r="C182" s="20"/>
     </row>
     <row r="183" spans="3:3">
-      <c r="C183" s="26"/>
+      <c r="C183" s="20"/>
     </row>
     <row r="184" spans="3:3">
-      <c r="C184" s="26"/>
+      <c r="C184" s="20"/>
     </row>
     <row r="185" spans="3:3">
-      <c r="C185" s="26"/>
+      <c r="C185" s="20"/>
     </row>
     <row r="186" spans="3:3">
-      <c r="C186" s="26"/>
+      <c r="C186" s="20"/>
     </row>
     <row r="187" spans="3:3">
-      <c r="C187" s="26"/>
+      <c r="C187" s="20"/>
     </row>
     <row r="188" spans="3:3">
-      <c r="C188" s="26"/>
+      <c r="C188" s="20"/>
     </row>
     <row r="189" spans="3:3">
-      <c r="C189" s="26"/>
+      <c r="C189" s="20"/>
     </row>
     <row r="190" spans="3:3">
-      <c r="C190" s="26"/>
+      <c r="C190" s="20"/>
     </row>
     <row r="191" spans="3:3">
-      <c r="C191" s="26"/>
+      <c r="C191" s="20"/>
     </row>
     <row r="192" spans="3:3">
-      <c r="C192" s="26"/>
+      <c r="C192" s="20"/>
     </row>
     <row r="193" spans="3:3">
-      <c r="C193" s="26"/>
+      <c r="C193" s="20"/>
     </row>
     <row r="194" spans="3:3">
-      <c r="C194" s="26"/>
+      <c r="C194" s="20"/>
     </row>
     <row r="195" spans="3:3">
-      <c r="C195" s="26"/>
+      <c r="C195" s="20"/>
     </row>
     <row r="196" spans="3:3">
-      <c r="C196" s="26"/>
+      <c r="C196" s="20"/>
     </row>
     <row r="197" spans="3:3">
-      <c r="C197" s="26"/>
+      <c r="C197" s="20"/>
     </row>
     <row r="198" spans="3:3">
-      <c r="C198" s="26"/>
+      <c r="C198" s="20"/>
     </row>
     <row r="199" spans="3:3">
-      <c r="C199" s="26"/>
+      <c r="C199" s="20"/>
     </row>
     <row r="200" spans="3:3">
-      <c r="C200" s="26"/>
+      <c r="C200" s="20"/>
     </row>
     <row r="201" spans="3:3">
-      <c r="C201" s="26"/>
+      <c r="C201" s="20"/>
     </row>
     <row r="202" spans="3:3">
-      <c r="C202" s="26"/>
+      <c r="C202" s="20"/>
     </row>
     <row r="203" spans="3:3">
-      <c r="C203" s="26"/>
+      <c r="C203" s="20"/>
     </row>
     <row r="204" spans="3:3">
-      <c r="C204" s="26"/>
+      <c r="C204" s="20"/>
     </row>
     <row r="205" spans="3:3">
-      <c r="C205" s="26"/>
+      <c r="C205" s="20"/>
     </row>
     <row r="206" spans="3:3">
-      <c r="C206" s="26"/>
+      <c r="C206" s="20"/>
     </row>
     <row r="207" spans="3:3">
-      <c r="C207" s="26"/>
+      <c r="C207" s="20"/>
     </row>
     <row r="208" spans="3:3">
-      <c r="C208" s="26"/>
+      <c r="C208" s="20"/>
     </row>
     <row r="209" spans="3:3">
-      <c r="C209" s="26"/>
+      <c r="C209" s="20"/>
     </row>
     <row r="210" spans="3:3">
-      <c r="C210" s="26"/>
+      <c r="C210" s="20"/>
     </row>
     <row r="211" spans="3:3">
-      <c r="C211" s="26"/>
+      <c r="C211" s="20"/>
     </row>
     <row r="212" spans="3:3">
-      <c r="C212" s="27"/>
+      <c r="C212" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9801,22 +9801,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="34" customHeight="1">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="25" t="s">
         <v>465</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="2" spans="1:5" ht="15">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="24" t="s">
         <v>466</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
     </row>
     <row r="3" spans="1:5" ht="16">
       <c r="A3" s="4" t="s">
@@ -10061,13 +10061,13 @@
         <v>685</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>975</v>
+      </c>
+      <c r="C17" s="9">
+        <v>1</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>976</v>
-      </c>
-      <c r="C17" s="9">
-        <v>1</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>977</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>27</v>
@@ -10078,13 +10078,13 @@
         <v>685</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C18" s="9">
         <v>2</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>476</v>
@@ -10095,13 +10095,13 @@
         <v>76</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>979</v>
+      </c>
+      <c r="C19" s="9">
+        <v>1</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>980</v>
-      </c>
-      <c r="C19" s="9">
-        <v>1</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>981</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>27</v>
@@ -10112,13 +10112,13 @@
         <v>76</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C20" s="9">
         <v>2</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>476</v>
@@ -11554,50 +11554,50 @@
     </row>
     <row r="105" spans="1:5" ht="24" customHeight="1">
       <c r="A105" s="11" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C105" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>27</v>
+        <v>476</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="24" customHeight="1">
       <c r="A106" s="13" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C106" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>476</v>
+        <v>27</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="24" customHeight="1">
       <c r="A107" s="11" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B107" s="11" t="s">
+        <v>987</v>
+      </c>
+      <c r="C107" s="11">
+        <v>1</v>
+      </c>
+      <c r="D107" s="11" t="s">
         <v>988</v>
-      </c>
-      <c r="C107" s="11">
-        <v>1</v>
-      </c>
-      <c r="D107" s="11" t="s">
-        <v>989</v>
       </c>
       <c r="E107" s="11" t="s">
         <v>27</v>
@@ -11605,16 +11605,16 @@
     </row>
     <row r="108" spans="1:5" ht="24" customHeight="1">
       <c r="A108" s="13" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C108" s="13">
         <v>2</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E108" s="13" t="s">
         <v>476</v>
@@ -11622,16 +11622,16 @@
     </row>
     <row r="109" spans="1:5" ht="24" customHeight="1">
       <c r="A109" s="11" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B109" s="11" t="s">
+        <v>991</v>
+      </c>
+      <c r="C109" s="11">
+        <v>1</v>
+      </c>
+      <c r="D109" s="11" t="s">
         <v>992</v>
-      </c>
-      <c r="C109" s="11">
-        <v>1</v>
-      </c>
-      <c r="D109" s="11" t="s">
-        <v>993</v>
       </c>
       <c r="E109" s="11" t="s">
         <v>27</v>
@@ -11639,16 +11639,16 @@
     </row>
     <row r="110" spans="1:5" ht="24" customHeight="1">
       <c r="A110" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B110" s="13" t="s">
+        <v>993</v>
+      </c>
+      <c r="C110" s="13">
+        <v>1</v>
+      </c>
+      <c r="D110" s="13" t="s">
         <v>994</v>
-      </c>
-      <c r="C110" s="13">
-        <v>1</v>
-      </c>
-      <c r="D110" s="13" t="s">
-        <v>995</v>
       </c>
       <c r="E110" s="13" t="s">
         <v>27</v>
@@ -11656,16 +11656,16 @@
     </row>
     <row r="111" spans="1:5" ht="24" customHeight="1">
       <c r="A111" s="11" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C111" s="11">
         <v>2</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E111" s="11" t="s">
         <v>476</v>
@@ -11673,16 +11673,16 @@
     </row>
     <row r="112" spans="1:5" ht="24" customHeight="1">
       <c r="A112" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="C112" s="13">
         <v>3</v>
       </c>
       <c r="D112" s="13" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E112" s="13" t="s">
         <v>476</v>
@@ -11690,16 +11690,16 @@
     </row>
     <row r="113" spans="1:5" ht="24" customHeight="1">
       <c r="A113" s="11" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C113" s="11">
         <v>4</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E113" s="11" t="s">
         <v>476</v>
@@ -11707,16 +11707,16 @@
     </row>
     <row r="114" spans="1:5" ht="24" customHeight="1">
       <c r="A114" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C114" s="13">
         <v>5</v>
       </c>
       <c r="D114" s="13" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E114" s="13" t="s">
         <v>476</v>
@@ -11724,16 +11724,16 @@
     </row>
     <row r="115" spans="1:5" ht="24" customHeight="1">
       <c r="A115" s="11" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B115" s="11" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C115" s="11">
+        <v>1</v>
+      </c>
+      <c r="D115" s="11" t="s">
         <v>1004</v>
-      </c>
-      <c r="C115" s="11">
-        <v>1</v>
-      </c>
-      <c r="D115" s="11" t="s">
-        <v>1005</v>
       </c>
       <c r="E115" s="11" t="s">
         <v>27</v>
@@ -11741,16 +11741,16 @@
     </row>
     <row r="116" spans="1:5" ht="24" customHeight="1">
       <c r="A116" s="13" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C116" s="13">
         <v>2</v>
       </c>
       <c r="D116" s="13" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E116" s="13" t="s">
         <v>476</v>
@@ -11758,16 +11758,16 @@
     </row>
     <row r="117" spans="1:5" ht="24" customHeight="1">
       <c r="A117" s="11" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B117" s="11" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C117" s="11">
+        <v>1</v>
+      </c>
+      <c r="D117" s="11" t="s">
         <v>1008</v>
-      </c>
-      <c r="C117" s="11">
-        <v>1</v>
-      </c>
-      <c r="D117" s="11" t="s">
-        <v>1009</v>
       </c>
       <c r="E117" s="11" t="s">
         <v>27</v>
@@ -11775,16 +11775,16 @@
     </row>
     <row r="118" spans="1:5" ht="24" customHeight="1">
       <c r="A118" s="13" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B118" s="13" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C118" s="13">
+        <v>1</v>
+      </c>
+      <c r="D118" s="13" t="s">
         <v>1010</v>
-      </c>
-      <c r="C118" s="13">
-        <v>1</v>
-      </c>
-      <c r="D118" s="13" t="s">
-        <v>1011</v>
       </c>
       <c r="E118" s="13" t="s">
         <v>27</v>
@@ -11792,16 +11792,16 @@
     </row>
     <row r="119" spans="1:5" ht="24" customHeight="1">
       <c r="A119" s="11" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C119" s="11">
         <v>2</v>
       </c>
       <c r="D119" s="11" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E119" s="11" t="s">
         <v>476</v>
@@ -11809,16 +11809,16 @@
     </row>
     <row r="120" spans="1:5" ht="24" customHeight="1">
       <c r="A120" s="13" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B120" s="13" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C120" s="13">
+        <v>1</v>
+      </c>
+      <c r="D120" s="13" t="s">
         <v>1014</v>
-      </c>
-      <c r="C120" s="13">
-        <v>1</v>
-      </c>
-      <c r="D120" s="13" t="s">
-        <v>1015</v>
       </c>
       <c r="E120" s="13" t="s">
         <v>27</v>
@@ -11826,16 +11826,16 @@
     </row>
     <row r="121" spans="1:5" ht="24" customHeight="1">
       <c r="A121" s="11" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C121" s="11">
         <v>2</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E121" s="11" t="s">
         <v>476</v>
@@ -11843,16 +11843,16 @@
     </row>
     <row r="122" spans="1:5" ht="24" customHeight="1">
       <c r="A122" s="13" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B122" s="13" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C122" s="13">
+        <v>1</v>
+      </c>
+      <c r="D122" s="13" t="s">
         <v>1018</v>
-      </c>
-      <c r="C122" s="13">
-        <v>1</v>
-      </c>
-      <c r="D122" s="13" t="s">
-        <v>1019</v>
       </c>
       <c r="E122" s="13" t="s">
         <v>27</v>
@@ -11860,16 +11860,16 @@
     </row>
     <row r="123" spans="1:5" ht="24" customHeight="1">
       <c r="A123" s="11" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C123" s="11">
         <v>2</v>
       </c>
       <c r="D123" s="11" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E123" s="11" t="s">
         <v>476</v>
@@ -11877,16 +11877,16 @@
     </row>
     <row r="124" spans="1:5" ht="24" customHeight="1">
       <c r="A124" s="13" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C124" s="13">
         <v>3</v>
       </c>
       <c r="D124" s="13" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E124" s="13" t="s">
         <v>476</v>
@@ -11894,16 +11894,16 @@
     </row>
     <row r="125" spans="1:5" ht="24" customHeight="1">
       <c r="A125" s="11" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B125" s="11" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C125" s="11">
+        <v>1</v>
+      </c>
+      <c r="D125" s="11" t="s">
         <v>1024</v>
-      </c>
-      <c r="C125" s="11">
-        <v>1</v>
-      </c>
-      <c r="D125" s="11" t="s">
-        <v>1025</v>
       </c>
       <c r="E125" s="11" t="s">
         <v>27</v>
@@ -11911,16 +11911,16 @@
     </row>
     <row r="126" spans="1:5" ht="24" customHeight="1">
       <c r="A126" s="13" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C126" s="13">
         <v>2</v>
       </c>
       <c r="D126" s="13" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E126" s="13" t="s">
         <v>476</v>
@@ -11928,16 +11928,16 @@
     </row>
     <row r="127" spans="1:5" ht="24" customHeight="1">
       <c r="A127" s="11" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B127" s="11" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C127" s="11">
+        <v>1</v>
+      </c>
+      <c r="D127" s="11" t="s">
         <v>1028</v>
-      </c>
-      <c r="C127" s="11">
-        <v>1</v>
-      </c>
-      <c r="D127" s="11" t="s">
-        <v>1029</v>
       </c>
       <c r="E127" s="11" t="s">
         <v>27</v>
@@ -11945,16 +11945,16 @@
     </row>
     <row r="128" spans="1:5" ht="24" customHeight="1">
       <c r="A128" s="13" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C128" s="13">
         <v>2</v>
       </c>
       <c r="D128" s="13" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E128" s="13" t="s">
         <v>476</v>
@@ -11962,16 +11962,16 @@
     </row>
     <row r="129" spans="1:5" ht="24" customHeight="1">
       <c r="A129" s="11" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C129" s="11">
         <v>3</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E129" s="11" t="s">
         <v>476</v>
@@ -11979,16 +11979,16 @@
     </row>
     <row r="130" spans="1:5" ht="24" customHeight="1">
       <c r="A130" s="13" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="C130" s="13">
         <v>4</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E130" s="13" t="s">
         <v>476</v>
@@ -11996,16 +11996,16 @@
     </row>
     <row r="131" spans="1:5" ht="24" customHeight="1">
       <c r="A131" s="11" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B131" s="11" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C131" s="11">
+        <v>1</v>
+      </c>
+      <c r="D131" s="11" t="s">
         <v>1036</v>
-      </c>
-      <c r="C131" s="11">
-        <v>1</v>
-      </c>
-      <c r="D131" s="11" t="s">
-        <v>1037</v>
       </c>
       <c r="E131" s="11" t="s">
         <v>27</v>
@@ -12013,16 +12013,16 @@
     </row>
     <row r="132" spans="1:5" ht="24" customHeight="1">
       <c r="A132" s="13" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C132" s="13">
         <v>2</v>
       </c>
       <c r="D132" s="13" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E132" s="13" t="s">
         <v>476</v>
@@ -12030,16 +12030,16 @@
     </row>
     <row r="133" spans="1:5" ht="24" customHeight="1">
       <c r="A133" s="11" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B133" s="11" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C133" s="11">
+        <v>1</v>
+      </c>
+      <c r="D133" s="11" t="s">
         <v>1040</v>
-      </c>
-      <c r="C133" s="11">
-        <v>1</v>
-      </c>
-      <c r="D133" s="11" t="s">
-        <v>1041</v>
       </c>
       <c r="E133" s="11" t="s">
         <v>27</v>
@@ -12047,16 +12047,16 @@
     </row>
     <row r="134" spans="1:5" ht="24" customHeight="1">
       <c r="A134" s="13" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C134" s="13">
         <v>2</v>
       </c>
       <c r="D134" s="13" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E134" s="13" t="s">
         <v>476</v>
@@ -12064,16 +12064,16 @@
     </row>
     <row r="135" spans="1:5" ht="24" customHeight="1">
       <c r="A135" s="11" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B135" s="11" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C135" s="11">
+        <v>1</v>
+      </c>
+      <c r="D135" s="11" t="s">
         <v>1044</v>
-      </c>
-      <c r="C135" s="11">
-        <v>1</v>
-      </c>
-      <c r="D135" s="11" t="s">
-        <v>1045</v>
       </c>
       <c r="E135" s="11" t="s">
         <v>27</v>
@@ -12081,16 +12081,16 @@
     </row>
     <row r="136" spans="1:5" ht="24" customHeight="1">
       <c r="A136" s="13" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C136" s="13">
         <v>2</v>
       </c>
       <c r="D136" s="13" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E136" s="13" t="s">
         <v>476</v>
@@ -12098,16 +12098,16 @@
     </row>
     <row r="137" spans="1:5" ht="24" customHeight="1">
       <c r="A137" s="11" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B137" s="11" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C137" s="11">
+        <v>1</v>
+      </c>
+      <c r="D137" s="11" t="s">
         <v>1048</v>
-      </c>
-      <c r="C137" s="11">
-        <v>1</v>
-      </c>
-      <c r="D137" s="11" t="s">
-        <v>1049</v>
       </c>
       <c r="E137" s="11" t="s">
         <v>27</v>
@@ -12115,16 +12115,16 @@
     </row>
     <row r="138" spans="1:5" ht="24" customHeight="1">
       <c r="A138" s="13" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="C138" s="13">
         <v>2</v>
       </c>
       <c r="D138" s="13" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="E138" s="13" t="s">
         <v>476</v>
@@ -12132,16 +12132,16 @@
     </row>
     <row r="139" spans="1:5" ht="24" customHeight="1">
       <c r="A139" s="11" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C139" s="11">
         <v>3</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E139" s="11" t="s">
         <v>476</v>
@@ -12149,16 +12149,16 @@
     </row>
     <row r="140" spans="1:5" ht="24" customHeight="1">
       <c r="A140" s="13" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B140" s="13" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C140" s="13">
+        <v>1</v>
+      </c>
+      <c r="D140" s="13" t="s">
         <v>1054</v>
-      </c>
-      <c r="C140" s="13">
-        <v>1</v>
-      </c>
-      <c r="D140" s="13" t="s">
-        <v>1055</v>
       </c>
       <c r="E140" s="13" t="s">
         <v>27</v>
@@ -12166,16 +12166,16 @@
     </row>
     <row r="141" spans="1:5" ht="24" customHeight="1">
       <c r="A141" s="11" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C141" s="11">
         <v>2</v>
       </c>
       <c r="D141" s="11" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E141" s="11" t="s">
         <v>476</v>
@@ -12183,16 +12183,16 @@
     </row>
     <row r="142" spans="1:5" ht="24" customHeight="1">
       <c r="A142" s="13" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C142" s="13">
         <v>3</v>
       </c>
       <c r="D142" s="13" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E142" s="13" t="s">
         <v>476</v>
@@ -12200,16 +12200,16 @@
     </row>
     <row r="143" spans="1:5" ht="24" customHeight="1">
       <c r="A143" s="11" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C143" s="11">
         <v>4</v>
       </c>
       <c r="D143" s="11" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="E143" s="11" t="s">
         <v>476</v>
@@ -12217,16 +12217,16 @@
     </row>
     <row r="144" spans="1:5" ht="24" customHeight="1">
       <c r="A144" s="13" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B144" s="13" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C144" s="13">
+        <v>1</v>
+      </c>
+      <c r="D144" s="13" t="s">
         <v>1062</v>
-      </c>
-      <c r="C144" s="13">
-        <v>1</v>
-      </c>
-      <c r="D144" s="13" t="s">
-        <v>1063</v>
       </c>
       <c r="E144" s="13" t="s">
         <v>27</v>
@@ -12234,16 +12234,16 @@
     </row>
     <row r="145" spans="1:5" ht="24" customHeight="1">
       <c r="A145" s="11" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C145" s="11">
         <v>2</v>
       </c>
       <c r="D145" s="11" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="E145" s="11" t="s">
         <v>476</v>
@@ -12251,16 +12251,16 @@
     </row>
     <row r="146" spans="1:5" ht="24" customHeight="1">
       <c r="A146" s="13" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C146" s="13">
         <v>3</v>
       </c>
       <c r="D146" s="13" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E146" s="13" t="s">
         <v>476</v>
@@ -12268,16 +12268,16 @@
     </row>
     <row r="147" spans="1:5" ht="24" customHeight="1">
       <c r="A147" s="11" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B147" s="11" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C147" s="11">
+        <v>1</v>
+      </c>
+      <c r="D147" s="11" t="s">
         <v>1068</v>
-      </c>
-      <c r="C147" s="11">
-        <v>1</v>
-      </c>
-      <c r="D147" s="11" t="s">
-        <v>1069</v>
       </c>
       <c r="E147" s="11" t="s">
         <v>27</v>
@@ -12285,16 +12285,16 @@
     </row>
     <row r="148" spans="1:5" ht="24" customHeight="1">
       <c r="A148" s="13" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B148" s="13" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C148" s="13">
+        <v>1</v>
+      </c>
+      <c r="D148" s="13" t="s">
         <v>1070</v>
-      </c>
-      <c r="C148" s="13">
-        <v>1</v>
-      </c>
-      <c r="D148" s="13" t="s">
-        <v>1071</v>
       </c>
       <c r="E148" s="13" t="s">
         <v>27</v>
@@ -12302,16 +12302,16 @@
     </row>
     <row r="149" spans="1:5" ht="24" customHeight="1">
       <c r="A149" s="11" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B149" s="11" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C149" s="11">
         <v>2</v>
       </c>
       <c r="D149" s="11" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="E149" s="11" t="s">
         <v>476</v>
@@ -12319,16 +12319,16 @@
     </row>
     <row r="150" spans="1:5" ht="24" customHeight="1">
       <c r="A150" s="13" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B150" s="13" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C150" s="13">
+        <v>1</v>
+      </c>
+      <c r="D150" s="13" t="s">
         <v>1074</v>
-      </c>
-      <c r="C150" s="13">
-        <v>1</v>
-      </c>
-      <c r="D150" s="13" t="s">
-        <v>1075</v>
       </c>
       <c r="E150" s="13" t="s">
         <v>27</v>
@@ -12336,16 +12336,16 @@
     </row>
     <row r="151" spans="1:5" ht="24" customHeight="1">
       <c r="A151" s="11" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B151" s="11" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C151" s="11">
         <v>2</v>
       </c>
       <c r="D151" s="11" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E151" s="11" t="s">
         <v>476</v>
@@ -12353,16 +12353,16 @@
     </row>
     <row r="152" spans="1:5" ht="24" customHeight="1">
       <c r="A152" s="13" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B152" s="13" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C152" s="13">
+        <v>1</v>
+      </c>
+      <c r="D152" s="13" t="s">
         <v>1078</v>
-      </c>
-      <c r="C152" s="13">
-        <v>1</v>
-      </c>
-      <c r="D152" s="13" t="s">
-        <v>1079</v>
       </c>
       <c r="E152" s="13" t="s">
         <v>27</v>
@@ -12370,16 +12370,16 @@
     </row>
     <row r="153" spans="1:5" ht="24" customHeight="1">
       <c r="A153" s="11" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B153" s="11" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C153" s="11">
         <v>2</v>
       </c>
       <c r="D153" s="11" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="E153" s="11" t="s">
         <v>476</v>
@@ -12387,16 +12387,16 @@
     </row>
     <row r="154" spans="1:5" ht="24" customHeight="1">
       <c r="A154" s="13" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B154" s="13" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C154" s="13">
+        <v>1</v>
+      </c>
+      <c r="D154" s="13" t="s">
         <v>1082</v>
-      </c>
-      <c r="C154" s="13">
-        <v>1</v>
-      </c>
-      <c r="D154" s="13" t="s">
-        <v>1083</v>
       </c>
       <c r="E154" s="13" t="s">
         <v>27</v>
@@ -12404,16 +12404,16 @@
     </row>
     <row r="155" spans="1:5" ht="24" customHeight="1">
       <c r="A155" s="11" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C155" s="11">
         <v>2</v>
       </c>
       <c r="D155" s="11" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E155" s="11" t="s">
         <v>476</v>
@@ -12421,16 +12421,16 @@
     </row>
     <row r="156" spans="1:5" ht="24" customHeight="1">
       <c r="A156" s="13" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B156" s="13" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C156" s="13">
+        <v>1</v>
+      </c>
+      <c r="D156" s="13" t="s">
         <v>1086</v>
-      </c>
-      <c r="C156" s="13">
-        <v>1</v>
-      </c>
-      <c r="D156" s="13" t="s">
-        <v>1087</v>
       </c>
       <c r="E156" s="13" t="s">
         <v>27</v>
@@ -12438,16 +12438,16 @@
     </row>
     <row r="157" spans="1:5" ht="24" customHeight="1">
       <c r="A157" s="11" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C157" s="11">
         <v>2</v>
       </c>
       <c r="D157" s="11" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E157" s="11" t="s">
         <v>476</v>
@@ -12455,16 +12455,16 @@
     </row>
     <row r="158" spans="1:5" ht="24" customHeight="1">
       <c r="A158" s="13" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B158" s="13" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C158" s="13">
+        <v>1</v>
+      </c>
+      <c r="D158" s="13" t="s">
         <v>1090</v>
-      </c>
-      <c r="C158" s="13">
-        <v>1</v>
-      </c>
-      <c r="D158" s="13" t="s">
-        <v>1091</v>
       </c>
       <c r="E158" s="13" t="s">
         <v>27</v>
@@ -12472,16 +12472,16 @@
     </row>
     <row r="159" spans="1:5" ht="24" customHeight="1">
       <c r="A159" s="11" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C159" s="11">
         <v>2</v>
       </c>
       <c r="D159" s="11" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E159" s="11" t="s">
         <v>476</v>
@@ -12489,16 +12489,16 @@
     </row>
     <row r="160" spans="1:5" ht="24" customHeight="1">
       <c r="A160" s="13" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C160" s="13">
         <v>3</v>
       </c>
       <c r="D160" s="13" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="E160" s="13" t="s">
         <v>476</v>
@@ -12506,16 +12506,16 @@
     </row>
     <row r="161" spans="1:5" ht="24" customHeight="1">
       <c r="A161" s="11" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C161" s="11">
         <v>4</v>
       </c>
       <c r="D161" s="11" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E161" s="11" t="s">
         <v>476</v>
@@ -12523,16 +12523,16 @@
     </row>
     <row r="162" spans="1:5" ht="24" customHeight="1">
       <c r="A162" s="13" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B162" s="13" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C162" s="13">
+        <v>1</v>
+      </c>
+      <c r="D162" s="13" t="s">
         <v>1098</v>
-      </c>
-      <c r="C162" s="13">
-        <v>1</v>
-      </c>
-      <c r="D162" s="13" t="s">
-        <v>1099</v>
       </c>
       <c r="E162" s="13" t="s">
         <v>27</v>
@@ -12540,16 +12540,16 @@
     </row>
     <row r="163" spans="1:5" ht="24" customHeight="1">
       <c r="A163" s="11" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B163" s="11" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C163" s="11">
+        <v>1</v>
+      </c>
+      <c r="D163" s="11" t="s">
         <v>1100</v>
-      </c>
-      <c r="C163" s="11">
-        <v>1</v>
-      </c>
-      <c r="D163" s="11" t="s">
-        <v>1101</v>
       </c>
       <c r="E163" s="11" t="s">
         <v>27</v>
@@ -12557,16 +12557,16 @@
     </row>
     <row r="164" spans="1:5" ht="24" customHeight="1">
       <c r="A164" s="13" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B164" s="13" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C164" s="13">
+        <v>1</v>
+      </c>
+      <c r="D164" s="13" t="s">
         <v>1102</v>
-      </c>
-      <c r="C164" s="13">
-        <v>1</v>
-      </c>
-      <c r="D164" s="13" t="s">
-        <v>1103</v>
       </c>
       <c r="E164" s="13" t="s">
         <v>27</v>
@@ -12574,16 +12574,16 @@
     </row>
     <row r="165" spans="1:5" ht="24" customHeight="1">
       <c r="A165" s="11" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B165" s="11" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C165" s="11">
         <v>2</v>
       </c>
       <c r="D165" s="11" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="E165" s="11" t="s">
         <v>476</v>
@@ -12591,16 +12591,16 @@
     </row>
     <row r="166" spans="1:5" ht="24" customHeight="1">
       <c r="A166" s="13" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C166" s="13">
         <v>3</v>
       </c>
       <c r="D166" s="13" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E166" s="13" t="s">
         <v>476</v>
@@ -12608,16 +12608,16 @@
     </row>
     <row r="167" spans="1:5" ht="24" customHeight="1">
       <c r="A167" s="11" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B167" s="11" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C167" s="11">
         <v>4</v>
       </c>
       <c r="D167" s="11" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="E167" s="11" t="s">
         <v>476</v>
@@ -12625,16 +12625,16 @@
     </row>
     <row r="168" spans="1:5" ht="24" customHeight="1">
       <c r="A168" s="13" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C168" s="13">
         <v>5</v>
       </c>
       <c r="D168" s="13" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="E168" s="13" t="s">
         <v>476</v>
@@ -12642,16 +12642,16 @@
     </row>
     <row r="169" spans="1:5" ht="24" customHeight="1">
       <c r="A169" s="11" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B169" s="11" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C169" s="11">
+        <v>1</v>
+      </c>
+      <c r="D169" s="11" t="s">
         <v>1112</v>
-      </c>
-      <c r="C169" s="11">
-        <v>1</v>
-      </c>
-      <c r="D169" s="11" t="s">
-        <v>1113</v>
       </c>
       <c r="E169" s="11" t="s">
         <v>27</v>
@@ -12659,16 +12659,16 @@
     </row>
     <row r="170" spans="1:5" ht="24" customHeight="1">
       <c r="A170" s="13" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B170" s="13" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C170" s="13">
+        <v>1</v>
+      </c>
+      <c r="D170" s="13" t="s">
         <v>1114</v>
-      </c>
-      <c r="C170" s="13">
-        <v>1</v>
-      </c>
-      <c r="D170" s="13" t="s">
-        <v>1115</v>
       </c>
       <c r="E170" s="13" t="s">
         <v>27</v>
@@ -12676,16 +12676,16 @@
     </row>
     <row r="171" spans="1:5" ht="24" customHeight="1">
       <c r="A171" s="11" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B171" s="11" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C171" s="11">
+        <v>1</v>
+      </c>
+      <c r="D171" s="11" t="s">
         <v>1116</v>
-      </c>
-      <c r="C171" s="11">
-        <v>1</v>
-      </c>
-      <c r="D171" s="11" t="s">
-        <v>1117</v>
       </c>
       <c r="E171" s="11" t="s">
         <v>27</v>
@@ -12693,16 +12693,16 @@
     </row>
     <row r="172" spans="1:5" ht="24" customHeight="1">
       <c r="A172" s="13" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B172" s="13" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C172" s="13">
+        <v>1</v>
+      </c>
+      <c r="D172" s="13" t="s">
         <v>1118</v>
-      </c>
-      <c r="C172" s="13">
-        <v>1</v>
-      </c>
-      <c r="D172" s="13" t="s">
-        <v>1119</v>
       </c>
       <c r="E172" s="13" t="s">
         <v>27</v>
@@ -12710,16 +12710,16 @@
     </row>
     <row r="173" spans="1:5" ht="24" customHeight="1">
       <c r="A173" s="11" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B173" s="11" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C173" s="11">
+        <v>1</v>
+      </c>
+      <c r="D173" s="11" t="s">
         <v>1120</v>
-      </c>
-      <c r="C173" s="11">
-        <v>1</v>
-      </c>
-      <c r="D173" s="11" t="s">
-        <v>1121</v>
       </c>
       <c r="E173" s="11" t="s">
         <v>27</v>
@@ -12727,16 +12727,16 @@
     </row>
     <row r="174" spans="1:5" ht="24" customHeight="1">
       <c r="A174" s="13" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B174" s="13" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C174" s="13">
+        <v>1</v>
+      </c>
+      <c r="D174" s="13" t="s">
         <v>1122</v>
-      </c>
-      <c r="C174" s="13">
-        <v>1</v>
-      </c>
-      <c r="D174" s="13" t="s">
-        <v>1123</v>
       </c>
       <c r="E174" s="13" t="s">
         <v>27</v>
@@ -12744,16 +12744,16 @@
     </row>
     <row r="175" spans="1:5" ht="24" customHeight="1">
       <c r="A175" s="11" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B175" s="11" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C175" s="11">
+        <v>1</v>
+      </c>
+      <c r="D175" s="11" t="s">
         <v>1124</v>
-      </c>
-      <c r="C175" s="11">
-        <v>1</v>
-      </c>
-      <c r="D175" s="11" t="s">
-        <v>1125</v>
       </c>
       <c r="E175" s="11" t="s">
         <v>27</v>
@@ -12761,16 +12761,16 @@
     </row>
     <row r="176" spans="1:5" ht="24" customHeight="1">
       <c r="A176" s="13" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B176" s="13" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C176" s="13">
+        <v>1</v>
+      </c>
+      <c r="D176" s="13" t="s">
         <v>1126</v>
-      </c>
-      <c r="C176" s="13">
-        <v>1</v>
-      </c>
-      <c r="D176" s="13" t="s">
-        <v>1127</v>
       </c>
       <c r="E176" s="13" t="s">
         <v>27</v>
@@ -12778,16 +12778,16 @@
     </row>
     <row r="177" spans="1:5" ht="24" customHeight="1">
       <c r="A177" s="11" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B177" s="11" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C177" s="11">
+        <v>1</v>
+      </c>
+      <c r="D177" s="11" t="s">
         <v>1128</v>
-      </c>
-      <c r="C177" s="11">
-        <v>1</v>
-      </c>
-      <c r="D177" s="11" t="s">
-        <v>1129</v>
       </c>
       <c r="E177" s="11" t="s">
         <v>27</v>
@@ -12795,16 +12795,16 @@
     </row>
     <row r="178" spans="1:5" ht="24" customHeight="1">
       <c r="A178" s="13" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B178" s="13" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C178" s="13">
+        <v>1</v>
+      </c>
+      <c r="D178" s="13" t="s">
         <v>1130</v>
-      </c>
-      <c r="C178" s="13">
-        <v>1</v>
-      </c>
-      <c r="D178" s="13" t="s">
-        <v>1131</v>
       </c>
       <c r="E178" s="13" t="s">
         <v>27</v>
@@ -12812,16 +12812,16 @@
     </row>
     <row r="179" spans="1:5" ht="24" customHeight="1">
       <c r="A179" s="11" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B179" s="11" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C179" s="11">
         <v>2</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="E179" s="11" t="s">
         <v>476</v>
@@ -12829,16 +12829,16 @@
     </row>
     <row r="180" spans="1:5" ht="24" customHeight="1">
       <c r="A180" s="13" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B180" s="13" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C180" s="13">
+        <v>1</v>
+      </c>
+      <c r="D180" s="13" t="s">
         <v>1134</v>
-      </c>
-      <c r="C180" s="13">
-        <v>1</v>
-      </c>
-      <c r="D180" s="13" t="s">
-        <v>1135</v>
       </c>
       <c r="E180" s="13" t="s">
         <v>27</v>
@@ -12846,16 +12846,16 @@
     </row>
     <row r="181" spans="1:5" ht="24" customHeight="1">
       <c r="A181" s="11" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B181" s="11" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C181" s="11">
         <v>2</v>
       </c>
       <c r="D181" s="11" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E181" s="11" t="s">
         <v>476</v>
@@ -12863,16 +12863,16 @@
     </row>
     <row r="182" spans="1:5" ht="24" customHeight="1">
       <c r="A182" s="13" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B182" s="13" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C182" s="13">
+        <v>1</v>
+      </c>
+      <c r="D182" s="13" t="s">
         <v>1138</v>
-      </c>
-      <c r="C182" s="13">
-        <v>1</v>
-      </c>
-      <c r="D182" s="13" t="s">
-        <v>1139</v>
       </c>
       <c r="E182" s="13" t="s">
         <v>27</v>
@@ -12880,16 +12880,16 @@
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1">
       <c r="A183" s="11" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B183" s="11" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C183" s="11">
         <v>2</v>
       </c>
       <c r="D183" s="11" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E183" s="11" t="s">
         <v>476</v>
@@ -12897,16 +12897,16 @@
     </row>
     <row r="184" spans="1:5" ht="24" customHeight="1">
       <c r="A184" s="13" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C184" s="13">
         <v>3</v>
       </c>
       <c r="D184" s="13" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E184" s="13" t="s">
         <v>476</v>
@@ -12942,108 +12942,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="25" t="s">
         <v>666</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
     </row>
     <row r="3" spans="1:6" ht="15">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="26" t="s">
         <v>667</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
     </row>
     <row r="4" spans="1:6" ht="46" customHeight="1">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="27" t="s">
         <v>668</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="6" spans="1:6" ht="15">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="26" t="s">
         <v>669</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
     </row>
     <row r="7" spans="1:6" ht="54" customHeight="1">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="27" t="s">
         <v>670</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="9" spans="1:6" ht="15">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="26" t="s">
         <v>671</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
     </row>
     <row r="10" spans="1:6" ht="46" customHeight="1">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="27" t="s">
         <v>672</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="12" spans="1:6" ht="15">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="26" t="s">
         <v>673</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
     </row>
     <row r="13" spans="1:6" ht="54" customHeight="1">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="27" t="s">
         <v>674</v>
       </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" spans="1:6" ht="32" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="32" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="32" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
   </sheetData>

--- a/inventaire_mobilier.xlsx
+++ b/inventaire_mobilier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolas.coquet/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC75BDCA-2CD1-3C48-A084-A2BCE1037243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4F87AC-BFE5-5E4F-BA15-97E9837C60E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10098,13 +10098,13 @@
         <v>979</v>
       </c>
       <c r="C19" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>980</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>27</v>
+        <v>476</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15">
@@ -10115,13 +10115,13 @@
         <v>981</v>
       </c>
       <c r="C20" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>982</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>476</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15">

--- a/inventaire_mobilier.xlsx
+++ b/inventaire_mobilier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolas.coquet/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDA566E-6573-D645-8E67-5F5610E31364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FBB1A8-A821-C849-BC26-E90F6F2BAE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2366" uniqueCount="1350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2440" uniqueCount="1350">
   <si>
     <t>Inventaire du mobilier</t>
   </si>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="U87" s="9"/>
     </row>
-    <row r="88" spans="1:21">
+    <row r="88" spans="1:21" ht="15">
       <c r="A88" t="s">
         <v>779</v>
       </c>
@@ -10230,6 +10230,15 @@
       <c r="L88" t="s">
         <v>316</v>
       </c>
+      <c r="M88" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N88" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R88" s="17">
+        <v>1</v>
+      </c>
       <c r="S88">
         <v>80</v>
       </c>
@@ -10237,7 +10246,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="89" spans="1:21">
+    <row r="89" spans="1:21" ht="15">
       <c r="A89" t="s">
         <v>786</v>
       </c>
@@ -10271,6 +10280,15 @@
       <c r="L89" t="s">
         <v>316</v>
       </c>
+      <c r="M89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N89" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R89" s="17">
+        <v>1</v>
+      </c>
       <c r="S89">
         <v>20</v>
       </c>
@@ -10278,7 +10296,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="90" spans="1:21">
+    <row r="90" spans="1:21" ht="15">
       <c r="A90" t="s">
         <v>791</v>
       </c>
@@ -10312,6 +10330,15 @@
       <c r="L90" t="s">
         <v>316</v>
       </c>
+      <c r="M90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N90" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R90" s="17">
+        <v>1</v>
+      </c>
       <c r="S90">
         <v>700</v>
       </c>
@@ -10319,7 +10346,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="91" spans="1:21">
+    <row r="91" spans="1:21" ht="15">
       <c r="A91" t="s">
         <v>799</v>
       </c>
@@ -10353,6 +10380,15 @@
       <c r="L91" t="s">
         <v>316</v>
       </c>
+      <c r="M91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N91" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R91" s="17">
+        <v>1</v>
+      </c>
       <c r="S91">
         <v>250</v>
       </c>
@@ -10360,7 +10396,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="92" spans="1:21">
+    <row r="92" spans="1:21" ht="15">
       <c r="A92" t="s">
         <v>806</v>
       </c>
@@ -10394,6 +10430,15 @@
       <c r="L92" t="s">
         <v>316</v>
       </c>
+      <c r="M92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N92" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R92" s="17">
+        <v>1</v>
+      </c>
       <c r="S92">
         <v>20</v>
       </c>
@@ -10401,7 +10446,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="93" spans="1:21">
+    <row r="93" spans="1:21" ht="15">
       <c r="A93" t="s">
         <v>812</v>
       </c>
@@ -10435,6 +10480,15 @@
       <c r="L93" t="s">
         <v>316</v>
       </c>
+      <c r="M93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N93" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R93" s="17">
+        <v>1</v>
+      </c>
       <c r="S93">
         <v>30</v>
       </c>
@@ -10442,7 +10496,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="94" spans="1:21">
+    <row r="94" spans="1:21" ht="15">
       <c r="A94" t="s">
         <v>818</v>
       </c>
@@ -10476,6 +10530,15 @@
       <c r="L94" t="s">
         <v>316</v>
       </c>
+      <c r="M94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N94" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R94" s="17">
+        <v>1</v>
+      </c>
       <c r="S94">
         <v>30</v>
       </c>
@@ -10483,7 +10546,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="95" spans="1:21">
+    <row r="95" spans="1:21" ht="15">
       <c r="A95" t="s">
         <v>823</v>
       </c>
@@ -10517,6 +10580,15 @@
       <c r="L95" t="s">
         <v>316</v>
       </c>
+      <c r="M95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N95" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R95" s="17">
+        <v>1</v>
+      </c>
       <c r="S95">
         <v>30</v>
       </c>
@@ -10524,7 +10596,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="96" spans="1:21">
+    <row r="96" spans="1:21" ht="15">
       <c r="A96" t="s">
         <v>827</v>
       </c>
@@ -10558,6 +10630,15 @@
       <c r="L96" t="s">
         <v>316</v>
       </c>
+      <c r="M96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N96" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R96" s="17">
+        <v>1</v>
+      </c>
       <c r="S96">
         <v>30</v>
       </c>
@@ -10565,7 +10646,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="97" spans="1:20">
+    <row r="97" spans="1:20" ht="15">
       <c r="A97" t="s">
         <v>831</v>
       </c>
@@ -10599,6 +10680,15 @@
       <c r="L97" t="s">
         <v>316</v>
       </c>
+      <c r="M97" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N97" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R97" s="17">
+        <v>1</v>
+      </c>
       <c r="S97">
         <v>40</v>
       </c>
@@ -10606,7 +10696,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="98" spans="1:20">
+    <row r="98" spans="1:20" ht="15">
       <c r="A98" t="s">
         <v>836</v>
       </c>
@@ -10640,6 +10730,15 @@
       <c r="L98" t="s">
         <v>316</v>
       </c>
+      <c r="M98" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N98" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R98" s="17">
+        <v>1</v>
+      </c>
       <c r="S98">
         <v>20</v>
       </c>
@@ -10647,7 +10746,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="99" spans="1:20">
+    <row r="99" spans="1:20" ht="15">
       <c r="A99" t="s">
         <v>841</v>
       </c>
@@ -10681,6 +10780,15 @@
       <c r="L99" t="s">
         <v>316</v>
       </c>
+      <c r="M99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N99" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R99" s="17">
+        <v>1</v>
+      </c>
       <c r="S99">
         <v>40</v>
       </c>
@@ -10688,7 +10796,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="100" spans="1:20">
+    <row r="100" spans="1:20" ht="15">
       <c r="A100" t="s">
         <v>847</v>
       </c>
@@ -10722,6 +10830,15 @@
       <c r="L100" t="s">
         <v>316</v>
       </c>
+      <c r="M100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N100" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R100" s="17">
+        <v>1</v>
+      </c>
       <c r="S100">
         <v>60</v>
       </c>
@@ -10729,7 +10846,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="101" spans="1:20">
+    <row r="101" spans="1:20" ht="15">
       <c r="A101" t="s">
         <v>852</v>
       </c>
@@ -10763,6 +10880,15 @@
       <c r="L101" t="s">
         <v>316</v>
       </c>
+      <c r="M101" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N101" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R101" s="17">
+        <v>1</v>
+      </c>
       <c r="S101">
         <v>40</v>
       </c>
@@ -10770,7 +10896,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="102" spans="1:20">
+    <row r="102" spans="1:20" ht="15">
       <c r="A102" t="s">
         <v>856</v>
       </c>
@@ -10804,6 +10930,15 @@
       <c r="L102" t="s">
         <v>316</v>
       </c>
+      <c r="M102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N102" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R102" s="17">
+        <v>1</v>
+      </c>
       <c r="S102">
         <v>40</v>
       </c>
@@ -10811,7 +10946,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="103" spans="1:20">
+    <row r="103" spans="1:20" ht="15">
       <c r="A103" t="s">
         <v>859</v>
       </c>
@@ -10845,6 +10980,15 @@
       <c r="L103" t="s">
         <v>316</v>
       </c>
+      <c r="M103" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N103" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R103" s="17">
+        <v>1</v>
+      </c>
       <c r="S103">
         <v>70</v>
       </c>
@@ -10852,7 +10996,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="104" spans="1:20">
+    <row r="104" spans="1:20" ht="15">
       <c r="A104" t="s">
         <v>862</v>
       </c>
@@ -10886,6 +11030,15 @@
       <c r="L104" t="s">
         <v>316</v>
       </c>
+      <c r="M104" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N104" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R104" s="17">
+        <v>1</v>
+      </c>
       <c r="S104">
         <v>150</v>
       </c>
@@ -10893,7 +11046,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="105" spans="1:20">
+    <row r="105" spans="1:20" ht="15">
       <c r="A105" t="s">
         <v>869</v>
       </c>
@@ -10927,6 +11080,15 @@
       <c r="L105" t="s">
         <v>316</v>
       </c>
+      <c r="M105" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N105" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R105" s="17">
+        <v>1</v>
+      </c>
       <c r="S105">
         <v>120</v>
       </c>
@@ -10934,7 +11096,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="106" spans="1:20">
+    <row r="106" spans="1:20" ht="15">
       <c r="A106" t="s">
         <v>874</v>
       </c>
@@ -10968,6 +11130,15 @@
       <c r="L106" t="s">
         <v>316</v>
       </c>
+      <c r="M106" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N106" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R106" s="17">
+        <v>1</v>
+      </c>
       <c r="S106">
         <v>20</v>
       </c>
@@ -10975,7 +11146,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:20">
+    <row r="107" spans="1:20" ht="15">
       <c r="A107" t="s">
         <v>879</v>
       </c>
@@ -11009,6 +11180,15 @@
       <c r="L107" t="s">
         <v>316</v>
       </c>
+      <c r="M107" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N107" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R107" s="17">
+        <v>1</v>
+      </c>
       <c r="S107">
         <v>20</v>
       </c>
@@ -11016,7 +11196,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:20">
+    <row r="108" spans="1:20" ht="15">
       <c r="A108" t="s">
         <v>883</v>
       </c>
@@ -11050,6 +11230,15 @@
       <c r="L108" t="s">
         <v>316</v>
       </c>
+      <c r="M108" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N108" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R108" s="17">
+        <v>1</v>
+      </c>
       <c r="S108">
         <v>30</v>
       </c>
@@ -11057,7 +11246,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="109" spans="1:20">
+    <row r="109" spans="1:20" ht="15">
       <c r="A109" t="s">
         <v>889</v>
       </c>
@@ -11091,6 +11280,15 @@
       <c r="L109" t="s">
         <v>316</v>
       </c>
+      <c r="M109" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N109" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R109" s="17">
+        <v>1</v>
+      </c>
       <c r="S109">
         <v>80</v>
       </c>
@@ -11098,7 +11296,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="110" spans="1:20">
+    <row r="110" spans="1:20" ht="15">
       <c r="A110" t="s">
         <v>895</v>
       </c>
@@ -11132,6 +11330,15 @@
       <c r="L110" t="s">
         <v>316</v>
       </c>
+      <c r="M110" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N110" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R110" s="17">
+        <v>1</v>
+      </c>
       <c r="S110">
         <v>100</v>
       </c>
@@ -11139,7 +11346,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="111" spans="1:20">
+    <row r="111" spans="1:20" ht="15">
       <c r="A111" t="s">
         <v>900</v>
       </c>
@@ -11173,6 +11380,15 @@
       <c r="L111" t="s">
         <v>316</v>
       </c>
+      <c r="M111" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N111" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R111" s="17">
+        <v>1</v>
+      </c>
       <c r="S111">
         <v>80</v>
       </c>
@@ -11180,7 +11396,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="112" spans="1:20">
+    <row r="112" spans="1:20" ht="15">
       <c r="A112" t="s">
         <v>905</v>
       </c>
@@ -11214,6 +11430,15 @@
       <c r="L112" t="s">
         <v>316</v>
       </c>
+      <c r="M112" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N112" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R112" s="17">
+        <v>1</v>
+      </c>
       <c r="S112">
         <v>80</v>
       </c>
@@ -11221,7 +11446,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="113" spans="1:20">
+    <row r="113" spans="1:20" ht="15">
       <c r="A113" t="s">
         <v>910</v>
       </c>
@@ -11255,6 +11480,15 @@
       <c r="L113" t="s">
         <v>316</v>
       </c>
+      <c r="M113" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N113" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R113" s="17">
+        <v>1</v>
+      </c>
       <c r="S113">
         <v>80</v>
       </c>
@@ -11262,7 +11496,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="114" spans="1:20">
+    <row r="114" spans="1:20" ht="15">
       <c r="A114" t="s">
         <v>915</v>
       </c>
@@ -11295,6 +11529,15 @@
       </c>
       <c r="L114" t="s">
         <v>316</v>
+      </c>
+      <c r="M114" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N114" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R114" s="17">
+        <v>1</v>
       </c>
       <c r="S114">
         <v>40</v>
@@ -11337,6 +11580,15 @@
       <c r="L115" t="s">
         <v>316</v>
       </c>
+      <c r="M115" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N115" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R115" s="17">
+        <v>1</v>
+      </c>
       <c r="S115">
         <v>250</v>
       </c>
@@ -11344,7 +11596,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="116" spans="1:20">
+    <row r="116" spans="1:20" ht="15">
       <c r="A116" t="s">
         <v>926</v>
       </c>
@@ -11378,6 +11630,15 @@
       <c r="L116" t="s">
         <v>316</v>
       </c>
+      <c r="M116" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N116" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R116" s="17">
+        <v>1</v>
+      </c>
       <c r="S116">
         <v>100</v>
       </c>
@@ -11385,7 +11646,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="117" spans="1:20">
+    <row r="117" spans="1:20" ht="15">
       <c r="A117" t="s">
         <v>930</v>
       </c>
@@ -11419,6 +11680,15 @@
       <c r="L117" t="s">
         <v>316</v>
       </c>
+      <c r="M117" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N117" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R117" s="17">
+        <v>1</v>
+      </c>
       <c r="S117">
         <v>80</v>
       </c>
@@ -11426,7 +11696,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="118" spans="1:20">
+    <row r="118" spans="1:20" ht="15">
       <c r="A118" t="s">
         <v>936</v>
       </c>
@@ -11460,6 +11730,15 @@
       <c r="L118" t="s">
         <v>316</v>
       </c>
+      <c r="M118" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N118" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R118" s="17">
+        <v>1</v>
+      </c>
       <c r="S118">
         <v>150</v>
       </c>
@@ -11467,7 +11746,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="119" spans="1:20">
+    <row r="119" spans="1:20" ht="15">
       <c r="A119" t="s">
         <v>939</v>
       </c>
@@ -11501,6 +11780,15 @@
       <c r="L119" t="s">
         <v>316</v>
       </c>
+      <c r="M119" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N119" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R119" s="17">
+        <v>1</v>
+      </c>
       <c r="S119">
         <v>200</v>
       </c>
@@ -11508,7 +11796,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="120" spans="1:20">
+    <row r="120" spans="1:20" ht="15">
       <c r="A120" t="s">
         <v>945</v>
       </c>
@@ -11542,6 +11830,15 @@
       <c r="L120" t="s">
         <v>316</v>
       </c>
+      <c r="M120" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N120" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R120" s="17">
+        <v>1</v>
+      </c>
       <c r="S120">
         <v>40</v>
       </c>
@@ -11549,7 +11846,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="121" spans="1:20">
+    <row r="121" spans="1:20" ht="15">
       <c r="A121" t="s">
         <v>949</v>
       </c>
@@ -11583,6 +11880,15 @@
       <c r="L121" t="s">
         <v>316</v>
       </c>
+      <c r="M121" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N121" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R121" s="17">
+        <v>1</v>
+      </c>
       <c r="S121">
         <v>120</v>
       </c>
@@ -11590,7 +11896,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="122" spans="1:20">
+    <row r="122" spans="1:20" ht="15">
       <c r="A122" t="s">
         <v>953</v>
       </c>
@@ -11624,6 +11930,15 @@
       <c r="L122" t="s">
         <v>316</v>
       </c>
+      <c r="M122" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N122" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R122" s="17">
+        <v>1</v>
+      </c>
       <c r="S122">
         <v>150</v>
       </c>
@@ -11631,7 +11946,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="123" spans="1:20">
+    <row r="123" spans="1:20" ht="15">
       <c r="A123" t="s">
         <v>958</v>
       </c>
@@ -11665,6 +11980,15 @@
       <c r="L123" t="s">
         <v>316</v>
       </c>
+      <c r="M123" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N123" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R123" s="17">
+        <v>1</v>
+      </c>
       <c r="S123">
         <v>100</v>
       </c>
@@ -11672,7 +11996,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="124" spans="1:20">
+    <row r="124" spans="1:20" ht="15">
       <c r="A124" t="s">
         <v>964</v>
       </c>
@@ -11705,6 +12029,15 @@
       </c>
       <c r="L124" t="s">
         <v>316</v>
+      </c>
+      <c r="M124" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N124" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R124" s="17">
+        <v>1</v>
       </c>
       <c r="S124">
         <v>80</v>
@@ -11719,7 +12052,7 @@
     <mergeCell ref="A2:U2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="M4:M87" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="M4:M124" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"À documenter,À restaurer,À conserver,À vendre,Vendu"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="N4" xr:uid="{00000000-0002-0000-0000-000001000000}">

--- a/inventaire_mobilier.xlsx
+++ b/inventaire_mobilier.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolas.coquet/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45907D68-B534-A54B-988D-2084C5D170A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B18DCD8-908C-B046-B76C-F6C7B8540899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="1281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="1281">
   <si>
     <t>Inventaire du mobilier</t>
   </si>
@@ -2268,9 +2268,6 @@
     <t>Ensemble dépareillé ou incomplet de couteaux, fourchettes et pièces de service, lames gravées et manches clairs, présenté dans un coffret garni. Poinçons britanniques visibles mais non déchiffrés avec certitude.</t>
   </si>
   <si>
-    <t>Coffret à relever; 15 pièces visibles environ</t>
-  </si>
-  <si>
     <t>Métal terni et piqué; manches tachés; coffret usé; inventaire et lecture des poinçons à compléter</t>
   </si>
   <si>
@@ -3702,123 +3699,6 @@
     <t>tabouret; pianot; bois noirci; pieds cannelés</t>
   </si>
   <si>
-    <t>MOB-085-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-086-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-087-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-088-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-089-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-090-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-091-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-092-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-093-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-094-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-095-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-096-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-097-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-098-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-100-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-101-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-102-01.webp</t>
-  </si>
-  <si>
-    <t>MOB-085-02.webp</t>
-  </si>
-  <si>
-    <t>MOB-085-03.webp</t>
-  </si>
-  <si>
-    <t>MOB-085-04.webp</t>
-  </si>
-  <si>
-    <t>MOB-086-02.webp</t>
-  </si>
-  <si>
-    <t>MOB-086-03.webp</t>
-  </si>
-  <si>
-    <t>MOB-087-02.webp</t>
-  </si>
-  <si>
-    <t>MOB-087-03.webp</t>
-  </si>
-  <si>
-    <t>MOB-087-04.webp</t>
-  </si>
-  <si>
-    <t>MOB-087-05.webp</t>
-  </si>
-  <si>
-    <t>MOB-087-06.webp</t>
-  </si>
-  <si>
-    <t>MOB-087-07.webp</t>
-  </si>
-  <si>
-    <t>MOB-088-02.webp</t>
-  </si>
-  <si>
-    <t>MOB-088-03.webp</t>
-  </si>
-  <si>
-    <t>MOB-090-02.webp</t>
-  </si>
-  <si>
-    <t>MOB-091-02.webp</t>
-  </si>
-  <si>
-    <t>MOB-092-03.webp</t>
-  </si>
-  <si>
-    <t>MOB-092-02.webp</t>
-  </si>
-  <si>
-    <t>MOB-093-02.webp</t>
-  </si>
-  <si>
-    <t>MOB-101-02.webp</t>
-  </si>
-  <si>
-    <t>MOB-101-03.webp</t>
-  </si>
-  <si>
-    <t>MOB-101-04.webp</t>
-  </si>
-  <si>
-    <t>MOB-098-02.webp</t>
-  </si>
-  <si>
     <t>Chambre Aura</t>
   </si>
   <si>
@@ -3877,6 +3757,126 @@
   </si>
   <si>
     <t>France ou Italie</t>
+  </si>
+  <si>
+    <t>MOB-085-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-085-02.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-085-03.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-085-04.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-086-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-086-02.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-086-03.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-087-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-087-02.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-087-03.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-087-04.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-087-05.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-087-06.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-087-07.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-088-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-088-02.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-088-03.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-089-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-090-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-090-02.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-091-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-091-02.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-092-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-092-02.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-092-03.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-093-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-093-02.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-094-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-095-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-096-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-097-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-098-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-098-02.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-100-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-101-01.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-101-02.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-101-03.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-101-04.jpeg</t>
+  </si>
+  <si>
+    <t>MOB-102-01.jpeg</t>
+  </si>
+  <si>
+    <t>/</t>
   </si>
 </sst>
 </file>
@@ -5028,7 +5028,7 @@
         <v>38</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1274</v>
+        <v>1234</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>39</v>
@@ -5291,7 +5291,7 @@
         <v>86</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>87</v>
@@ -5353,7 +5353,7 @@
         <v>96</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>1275</v>
+        <v>1235</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>52</v>
@@ -5418,7 +5418,7 @@
         <v>106</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1276</v>
+        <v>1236</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>52</v>
@@ -5548,7 +5548,7 @@
         <v>126</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1273</v>
+        <v>1233</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>198</v>
@@ -5678,7 +5678,7 @@
         <v>146</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1272</v>
+        <v>1232</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>198</v>
@@ -5813,7 +5813,7 @@
         <v>167</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>168</v>
@@ -6398,7 +6398,7 @@
         <v>256</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>257</v>
@@ -6463,7 +6463,7 @@
         <v>267</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>268</v>
@@ -6593,13 +6593,13 @@
         <v>289</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>127</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>1280</v>
+        <v>1240</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>290</v>
@@ -6785,7 +6785,7 @@
         <v>318</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>319</v>
@@ -7370,7 +7370,7 @@
         <v>410</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>1270</v>
+        <v>1230</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>309</v>
@@ -7500,7 +7500,7 @@
         <v>155</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>1271</v>
+        <v>1231</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>198</v>
@@ -8088,7 +8088,7 @@
         <v>503</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>1279</v>
+        <v>1239</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>504</v>
@@ -8445,7 +8445,7 @@
         <v>542</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>319</v>
@@ -8460,7 +8460,7 @@
         <v>544</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="H58" s="12" t="s">
         <v>484</v>
@@ -8484,7 +8484,7 @@
         <v>34</v>
       </c>
       <c r="O58" s="12" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="P58" s="12"/>
       <c r="Q58" s="12"/>
@@ -8515,7 +8515,7 @@
         <v>503</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>1278</v>
+        <v>1238</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>548</v>
@@ -8814,7 +8814,7 @@
         <v>580</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D64" s="12" t="s">
         <v>581</v>
@@ -8872,7 +8872,7 @@
         <v>586</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>1269</v>
+        <v>1229</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>587</v>
@@ -9058,7 +9058,7 @@
         <v>607</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>568</v>
@@ -9424,7 +9424,7 @@
         <v>648</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D74" s="12" t="s">
         <v>510</v>
@@ -9634,7 +9634,7 @@
         <v>220</v>
       </c>
       <c r="L77" s="12" t="s">
-        <v>1261</v>
+        <v>1221</v>
       </c>
       <c r="M77" s="5" t="s">
         <v>33</v>
@@ -9695,7 +9695,7 @@
         <v>450</v>
       </c>
       <c r="L78" s="12" t="s">
-        <v>1261</v>
+        <v>1221</v>
       </c>
       <c r="M78" s="5" t="s">
         <v>33</v>
@@ -9758,7 +9758,7 @@
         <v>500</v>
       </c>
       <c r="L79" s="12" t="s">
-        <v>1261</v>
+        <v>1221</v>
       </c>
       <c r="M79" s="5" t="s">
         <v>33</v>
@@ -10229,7 +10229,7 @@
         <v>554</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>1277</v>
+        <v>1237</v>
       </c>
       <c r="F87" s="12" t="s">
         <v>742</v>
@@ -10237,11 +10237,11 @@
       <c r="G87" s="12" t="s">
         <v>743</v>
       </c>
-      <c r="H87" s="12" t="s">
+      <c r="H87" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I87" s="12" t="s">
         <v>744</v>
-      </c>
-      <c r="I87" s="12" t="s">
-        <v>745</v>
       </c>
       <c r="J87" s="16">
         <v>80</v>
@@ -10259,7 +10259,7 @@
         <v>34</v>
       </c>
       <c r="O87" s="12" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="P87" s="12"/>
       <c r="Q87" s="12"/>
@@ -10278,29 +10278,31 @@
     </row>
     <row r="88" spans="1:21">
       <c r="A88" s="13" t="s">
+        <v>746</v>
+      </c>
+      <c r="B88" s="14" t="s">
         <v>747</v>
-      </c>
-      <c r="B88" s="14" t="s">
-        <v>748</v>
       </c>
       <c r="C88" s="12" t="s">
         <v>52</v>
       </c>
       <c r="D88" s="14" t="s">
+        <v>748</v>
+      </c>
+      <c r="E88" s="14" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F88" s="14" t="s">
         <v>749</v>
       </c>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14" t="s">
+      <c r="G88" s="14" t="s">
         <v>750</v>
       </c>
-      <c r="G88" s="14" t="s">
+      <c r="H88" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I88" s="14" t="s">
         <v>751</v>
-      </c>
-      <c r="H88" s="14" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I88" s="14" t="s">
-        <v>752</v>
       </c>
       <c r="J88" s="27">
         <v>80</v>
@@ -10333,10 +10335,10 @@
     </row>
     <row r="89" spans="1:21">
       <c r="A89" s="13" t="s">
+        <v>752</v>
+      </c>
+      <c r="B89" s="14" t="s">
         <v>753</v>
-      </c>
-      <c r="B89" s="14" t="s">
-        <v>754</v>
       </c>
       <c r="C89" s="12" t="s">
         <v>734</v>
@@ -10348,16 +10350,16 @@
         <v>636</v>
       </c>
       <c r="F89" s="14" t="s">
+        <v>754</v>
+      </c>
+      <c r="G89" s="14" t="s">
         <v>755</v>
       </c>
-      <c r="G89" s="14" t="s">
+      <c r="H89" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I89" s="14" t="s">
         <v>756</v>
-      </c>
-      <c r="H89" s="14" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I89" s="14" t="s">
-        <v>757</v>
       </c>
       <c r="J89" s="27">
         <v>20</v>
@@ -10390,29 +10392,31 @@
     </row>
     <row r="90" spans="1:21">
       <c r="A90" s="13" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>1267</v>
+        <v>1227</v>
       </c>
       <c r="C90" s="9" t="s">
         <v>198</v>
       </c>
       <c r="D90" s="14" t="s">
+        <v>758</v>
+      </c>
+      <c r="E90" s="14" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F90" s="14" t="s">
         <v>759</v>
       </c>
-      <c r="E90" s="14"/>
-      <c r="F90" s="14" t="s">
+      <c r="G90" s="14" t="s">
         <v>760</v>
       </c>
-      <c r="G90" s="14" t="s">
+      <c r="H90" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I90" s="14" t="s">
         <v>761</v>
-      </c>
-      <c r="H90" s="14" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I90" s="14" t="s">
-        <v>762</v>
       </c>
       <c r="J90" s="27">
         <v>700</v>
@@ -10445,29 +10449,31 @@
     </row>
     <row r="91" spans="1:21">
       <c r="A91" s="13" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>1266</v>
+        <v>1226</v>
       </c>
       <c r="C91" s="9" t="s">
         <v>198</v>
       </c>
       <c r="D91" s="14" t="s">
+        <v>763</v>
+      </c>
+      <c r="E91" s="14" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F91" s="14" t="s">
         <v>764</v>
       </c>
-      <c r="E91" s="14"/>
-      <c r="F91" s="14" t="s">
+      <c r="G91" s="14" t="s">
         <v>765</v>
       </c>
-      <c r="G91" s="14" t="s">
+      <c r="H91" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I91" s="14" t="s">
         <v>766</v>
-      </c>
-      <c r="H91" s="14" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I91" s="14" t="s">
-        <v>767</v>
       </c>
       <c r="J91" s="27">
         <v>250</v>
@@ -10500,13 +10506,13 @@
     </row>
     <row r="92" spans="1:21">
       <c r="A92" s="13" t="s">
+        <v>767</v>
+      </c>
+      <c r="B92" s="14" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C92" s="12" t="s">
         <v>768</v>
-      </c>
-      <c r="B92" s="14" t="s">
-        <v>1265</v>
-      </c>
-      <c r="C92" s="12" t="s">
-        <v>769</v>
       </c>
       <c r="D92" s="14" t="s">
         <v>615</v>
@@ -10515,16 +10521,16 @@
         <v>636</v>
       </c>
       <c r="F92" s="14" t="s">
+        <v>769</v>
+      </c>
+      <c r="G92" s="14" t="s">
         <v>770</v>
       </c>
-      <c r="G92" s="14" t="s">
+      <c r="H92" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I92" s="14" t="s">
         <v>771</v>
-      </c>
-      <c r="H92" s="14" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I92" s="14" t="s">
-        <v>772</v>
       </c>
       <c r="J92" s="27">
         <v>20</v>
@@ -10557,13 +10563,13 @@
     </row>
     <row r="93" spans="1:21">
       <c r="A93" s="13" t="s">
+        <v>772</v>
+      </c>
+      <c r="B93" s="14" t="s">
         <v>773</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="C93" s="12" t="s">
         <v>774</v>
-      </c>
-      <c r="C93" s="12" t="s">
-        <v>775</v>
       </c>
       <c r="D93" s="14" t="s">
         <v>158</v>
@@ -10572,16 +10578,16 @@
         <v>354</v>
       </c>
       <c r="F93" s="14" t="s">
+        <v>775</v>
+      </c>
+      <c r="G93" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="G93" s="14" t="s">
+      <c r="H93" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I93" s="14" t="s">
         <v>777</v>
-      </c>
-      <c r="H93" s="14" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I93" s="14" t="s">
-        <v>778</v>
       </c>
       <c r="J93" s="27">
         <v>30</v>
@@ -10614,13 +10620,13 @@
     </row>
     <row r="94" spans="1:21">
       <c r="A94" s="13" t="s">
+        <v>778</v>
+      </c>
+      <c r="B94" s="14" t="s">
         <v>779</v>
       </c>
-      <c r="B94" s="14" t="s">
-        <v>780</v>
-      </c>
       <c r="C94" s="12" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D94" s="14" t="s">
         <v>53</v>
@@ -10629,16 +10635,16 @@
         <v>354</v>
       </c>
       <c r="F94" s="14" t="s">
+        <v>780</v>
+      </c>
+      <c r="G94" s="14" t="s">
         <v>781</v>
       </c>
-      <c r="G94" s="14" t="s">
+      <c r="H94" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I94" s="14" t="s">
         <v>782</v>
-      </c>
-      <c r="H94" s="14" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I94" s="14" t="s">
-        <v>783</v>
       </c>
       <c r="J94" s="27">
         <v>30</v>
@@ -10671,13 +10677,13 @@
     </row>
     <row r="95" spans="1:21">
       <c r="A95" s="13" t="s">
+        <v>783</v>
+      </c>
+      <c r="B95" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="B95" s="14" t="s">
-        <v>785</v>
-      </c>
       <c r="C95" s="12" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D95" s="14" t="s">
         <v>158</v>
@@ -10686,16 +10692,16 @@
         <v>354</v>
       </c>
       <c r="F95" s="14" t="s">
+        <v>785</v>
+      </c>
+      <c r="G95" s="14" t="s">
         <v>786</v>
       </c>
-      <c r="G95" s="14" t="s">
-        <v>787</v>
-      </c>
       <c r="H95" s="14" t="s">
-        <v>1264</v>
+        <v>1224</v>
       </c>
       <c r="I95" s="14" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="J95" s="27">
         <v>30</v>
@@ -10728,13 +10734,13 @@
     </row>
     <row r="96" spans="1:21">
       <c r="A96" s="13" t="s">
+        <v>787</v>
+      </c>
+      <c r="B96" s="14" t="s">
         <v>788</v>
       </c>
-      <c r="B96" s="14" t="s">
-        <v>789</v>
-      </c>
       <c r="C96" s="12" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D96" s="14" t="s">
         <v>158</v>
@@ -10743,16 +10749,16 @@
         <v>354</v>
       </c>
       <c r="F96" s="14" t="s">
+        <v>789</v>
+      </c>
+      <c r="G96" s="14" t="s">
         <v>790</v>
       </c>
-      <c r="G96" s="14" t="s">
-        <v>791</v>
-      </c>
       <c r="H96" s="14" t="s">
-        <v>1264</v>
+        <v>1224</v>
       </c>
       <c r="I96" s="14" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="J96" s="27">
         <v>30</v>
@@ -10785,10 +10791,10 @@
     </row>
     <row r="97" spans="1:21">
       <c r="A97" s="13" t="s">
+        <v>791</v>
+      </c>
+      <c r="B97" s="14" t="s">
         <v>792</v>
-      </c>
-      <c r="B97" s="14" t="s">
-        <v>793</v>
       </c>
       <c r="C97" s="12" t="s">
         <v>75</v>
@@ -10800,16 +10806,16 @@
         <v>354</v>
       </c>
       <c r="F97" s="14" t="s">
+        <v>793</v>
+      </c>
+      <c r="G97" s="14" t="s">
         <v>794</v>
       </c>
-      <c r="G97" s="14" t="s">
+      <c r="H97" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I97" s="14" t="s">
         <v>795</v>
-      </c>
-      <c r="H97" s="14" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I97" s="14" t="s">
-        <v>796</v>
       </c>
       <c r="J97" s="27">
         <v>40</v>
@@ -10842,10 +10848,10 @@
     </row>
     <row r="98" spans="1:21">
       <c r="A98" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="B98" s="14" t="s">
         <v>797</v>
-      </c>
-      <c r="B98" s="14" t="s">
-        <v>798</v>
       </c>
       <c r="C98" s="12" t="s">
         <v>734</v>
@@ -10857,16 +10863,16 @@
         <v>354</v>
       </c>
       <c r="F98" s="14" t="s">
+        <v>798</v>
+      </c>
+      <c r="G98" s="14" t="s">
         <v>799</v>
       </c>
-      <c r="G98" s="14" t="s">
+      <c r="H98" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I98" s="14" t="s">
         <v>800</v>
-      </c>
-      <c r="H98" s="14" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I98" s="14" t="s">
-        <v>801</v>
       </c>
       <c r="J98" s="27">
         <v>20</v>
@@ -10899,31 +10905,31 @@
     </row>
     <row r="99" spans="1:21">
       <c r="A99" s="13" t="s">
+        <v>801</v>
+      </c>
+      <c r="B99" s="14" t="s">
         <v>802</v>
       </c>
-      <c r="B99" s="14" t="s">
+      <c r="C99" s="12" t="s">
         <v>803</v>
-      </c>
-      <c r="C99" s="12" t="s">
-        <v>804</v>
       </c>
       <c r="D99" s="14" t="s">
         <v>188</v>
       </c>
       <c r="E99" s="14" t="s">
-        <v>1262</v>
+        <v>1222</v>
       </c>
       <c r="F99" s="14" t="s">
+        <v>804</v>
+      </c>
+      <c r="G99" s="14" t="s">
         <v>805</v>
       </c>
-      <c r="G99" s="14" t="s">
-        <v>806</v>
-      </c>
       <c r="H99" s="14" t="s">
-        <v>1264</v>
+        <v>1224</v>
       </c>
       <c r="I99" s="14" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="J99" s="27">
         <v>40</v>
@@ -10956,31 +10962,31 @@
     </row>
     <row r="100" spans="1:21">
       <c r="A100" s="13" t="s">
+        <v>806</v>
+      </c>
+      <c r="B100" s="14" t="s">
         <v>807</v>
       </c>
-      <c r="B100" s="14" t="s">
-        <v>808</v>
-      </c>
       <c r="C100" s="12" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D100" s="14" t="s">
         <v>188</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>1262</v>
+        <v>1222</v>
       </c>
       <c r="F100" s="14" t="s">
+        <v>808</v>
+      </c>
+      <c r="G100" s="14" t="s">
         <v>809</v>
       </c>
-      <c r="G100" s="14" t="s">
+      <c r="H100" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I100" s="14" t="s">
         <v>810</v>
-      </c>
-      <c r="H100" s="14" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I100" s="14" t="s">
-        <v>811</v>
       </c>
       <c r="J100" s="27">
         <v>60</v>
@@ -11013,31 +11019,31 @@
     </row>
     <row r="101" spans="1:21">
       <c r="A101" s="13" t="s">
+        <v>811</v>
+      </c>
+      <c r="B101" s="14" t="s">
         <v>812</v>
       </c>
-      <c r="B101" s="14" t="s">
-        <v>813</v>
-      </c>
       <c r="C101" s="12" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D101" s="14" t="s">
         <v>188</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>1262</v>
+        <v>1222</v>
       </c>
       <c r="F101" s="14" t="s">
+        <v>813</v>
+      </c>
+      <c r="G101" s="14" t="s">
         <v>814</v>
       </c>
-      <c r="G101" s="14" t="s">
-        <v>815</v>
-      </c>
       <c r="H101" s="14" t="s">
-        <v>1264</v>
+        <v>1224</v>
       </c>
       <c r="I101" s="14" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="J101" s="27">
         <v>40</v>
@@ -11070,31 +11076,31 @@
     </row>
     <row r="102" spans="1:21">
       <c r="A102" s="13" t="s">
+        <v>815</v>
+      </c>
+      <c r="B102" s="14" t="s">
         <v>816</v>
       </c>
-      <c r="B102" s="14" t="s">
-        <v>817</v>
-      </c>
       <c r="C102" s="12" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D102" s="14" t="s">
         <v>188</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>1262</v>
+        <v>1222</v>
       </c>
       <c r="F102" s="14" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G102" s="14" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H102" s="14" t="s">
-        <v>1264</v>
+        <v>1224</v>
       </c>
       <c r="I102" s="14" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="J102" s="27">
         <v>40</v>
@@ -11127,31 +11133,31 @@
     </row>
     <row r="103" spans="1:21">
       <c r="A103" s="13" t="s">
+        <v>818</v>
+      </c>
+      <c r="B103" s="14" t="s">
         <v>819</v>
       </c>
-      <c r="B103" s="14" t="s">
-        <v>820</v>
-      </c>
       <c r="C103" s="12" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D103" s="14" t="s">
         <v>188</v>
       </c>
       <c r="E103" s="14" t="s">
-        <v>1262</v>
+        <v>1222</v>
       </c>
       <c r="F103" s="14" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G103" s="14" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H103" s="14" t="s">
-        <v>1264</v>
+        <v>1224</v>
       </c>
       <c r="I103" s="14" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="J103" s="27">
         <v>70</v>
@@ -11184,31 +11190,31 @@
     </row>
     <row r="104" spans="1:21">
       <c r="A104" s="13" t="s">
+        <v>821</v>
+      </c>
+      <c r="B104" s="14" t="s">
         <v>822</v>
       </c>
-      <c r="B104" s="14" t="s">
+      <c r="C104" s="12" t="s">
+        <v>803</v>
+      </c>
+      <c r="D104" s="14" t="s">
         <v>823</v>
       </c>
-      <c r="C104" s="12" t="s">
-        <v>804</v>
-      </c>
-      <c r="D104" s="14" t="s">
+      <c r="E104" s="14" t="s">
         <v>824</v>
       </c>
-      <c r="E104" s="14" t="s">
+      <c r="F104" s="14" t="s">
         <v>825</v>
       </c>
-      <c r="F104" s="14" t="s">
+      <c r="G104" s="14" t="s">
         <v>826</v>
       </c>
-      <c r="G104" s="14" t="s">
+      <c r="H104" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I104" s="14" t="s">
         <v>827</v>
-      </c>
-      <c r="H104" s="14" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I104" s="14" t="s">
-        <v>828</v>
       </c>
       <c r="J104" s="27">
         <v>150</v>
@@ -11241,10 +11247,10 @@
     </row>
     <row r="105" spans="1:21">
       <c r="A105" s="13" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>1268</v>
+        <v>1228</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>52</v>
@@ -11252,18 +11258,20 @@
       <c r="D105" s="14" t="s">
         <v>489</v>
       </c>
-      <c r="E105" s="14"/>
+      <c r="E105" s="14" t="s">
+        <v>1280</v>
+      </c>
       <c r="F105" s="14" t="s">
+        <v>829</v>
+      </c>
+      <c r="G105" s="14" t="s">
         <v>830</v>
       </c>
-      <c r="G105" s="14" t="s">
+      <c r="H105" s="14" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I105" s="14" t="s">
         <v>831</v>
-      </c>
-      <c r="H105" s="14" t="s">
-        <v>1264</v>
-      </c>
-      <c r="I105" s="14" t="s">
-        <v>832</v>
       </c>
       <c r="J105" s="27">
         <v>120</v>
@@ -11328,7 +11336,7 @@
   <sheetData>
     <row r="1" spans="1:5" s="3" customFormat="1" ht="34" customHeight="1">
       <c r="A1" s="28" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -11337,7 +11345,7 @@
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
       <c r="A2" s="31" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
@@ -11346,19 +11354,19 @@
     </row>
     <row r="3" spans="1:5" s="21" customFormat="1" ht="16" customHeight="1">
       <c r="A3" s="20" t="s">
+        <v>834</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>835</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="C3" s="20" t="s">
         <v>836</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="D3" s="20" t="s">
         <v>837</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="E3" s="20" t="s">
         <v>838</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
@@ -11366,13 +11374,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="22" t="s">
+        <v>839</v>
+      </c>
+      <c r="C4" s="23">
+        <v>1</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>840</v>
-      </c>
-      <c r="C4" s="23">
-        <v>1</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>841</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>34</v>
@@ -11383,16 +11391,16 @@
         <v>23</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C5" s="23">
         <v>2</v>
       </c>
       <c r="D5" s="22" t="s">
+        <v>842</v>
+      </c>
+      <c r="E5" s="22" t="s">
         <v>843</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
@@ -11400,16 +11408,16 @@
         <v>23</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C6" s="25">
         <v>3</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
@@ -11417,13 +11425,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="26" t="s">
+        <v>846</v>
+      </c>
+      <c r="C7" s="26">
+        <v>1</v>
+      </c>
+      <c r="D7" s="26" t="s">
         <v>847</v>
-      </c>
-      <c r="C7" s="26">
-        <v>1</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>848</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>34</v>
@@ -11434,16 +11442,16 @@
         <v>38</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C8" s="26">
         <v>2</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
@@ -11451,16 +11459,16 @@
         <v>38</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C9" s="26">
         <v>3</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
@@ -11468,13 +11476,13 @@
         <v>50</v>
       </c>
       <c r="B10" s="26" t="s">
+        <v>852</v>
+      </c>
+      <c r="C10" s="26">
+        <v>1</v>
+      </c>
+      <c r="D10" s="26" t="s">
         <v>853</v>
-      </c>
-      <c r="C10" s="26">
-        <v>1</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>854</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>34</v>
@@ -11485,13 +11493,13 @@
         <v>62</v>
       </c>
       <c r="B11" s="26" t="s">
+        <v>854</v>
+      </c>
+      <c r="C11" s="26">
+        <v>1</v>
+      </c>
+      <c r="D11" s="26" t="s">
         <v>855</v>
-      </c>
-      <c r="C11" s="26">
-        <v>1</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>856</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>34</v>
@@ -11502,16 +11510,16 @@
         <v>62</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C12" s="26">
         <v>2</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1">
@@ -11519,16 +11527,16 @@
         <v>62</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C13" s="26">
         <v>3</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
@@ -11536,13 +11544,13 @@
         <v>73</v>
       </c>
       <c r="B14" s="26" t="s">
+        <v>860</v>
+      </c>
+      <c r="C14" s="26">
+        <v>1</v>
+      </c>
+      <c r="D14" s="26" t="s">
         <v>861</v>
-      </c>
-      <c r="C14" s="26">
-        <v>1</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>862</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>34</v>
@@ -11553,16 +11561,16 @@
         <v>73</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C15" s="26">
         <v>2</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1">
@@ -11570,16 +11578,16 @@
         <v>73</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C16" s="26">
         <v>3</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1">
@@ -11587,13 +11595,13 @@
         <v>470</v>
       </c>
       <c r="B17" s="26" t="s">
+        <v>866</v>
+      </c>
+      <c r="C17" s="26">
+        <v>1</v>
+      </c>
+      <c r="D17" s="26" t="s">
         <v>867</v>
-      </c>
-      <c r="C17" s="26">
-        <v>1</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>868</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>34</v>
@@ -11604,16 +11612,16 @@
         <v>470</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C18" s="26">
         <v>2</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1">
@@ -11621,16 +11629,16 @@
         <v>85</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C19" s="26">
         <v>2</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1">
@@ -11638,13 +11646,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="26" t="s">
+        <v>872</v>
+      </c>
+      <c r="C20" s="26">
+        <v>1</v>
+      </c>
+      <c r="D20" s="26" t="s">
         <v>873</v>
-      </c>
-      <c r="C20" s="26">
-        <v>1</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>874</v>
       </c>
       <c r="E20" s="26" t="s">
         <v>34</v>
@@ -11655,16 +11663,16 @@
         <v>96</v>
       </c>
       <c r="B21" s="26" t="s">
+        <v>874</v>
+      </c>
+      <c r="C21" s="26">
+        <v>1</v>
+      </c>
+      <c r="D21" s="26" t="s">
         <v>875</v>
       </c>
-      <c r="C21" s="26">
-        <v>1</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>876</v>
-      </c>
       <c r="E21" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1">
@@ -11672,13 +11680,13 @@
         <v>96</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C22" s="26">
         <v>2</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E22" s="26" t="s">
         <v>34</v>
@@ -11689,16 +11697,16 @@
         <v>96</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C23" s="26">
         <v>3</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1">
@@ -11706,16 +11714,16 @@
         <v>96</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C24" s="26">
         <v>4</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1">
@@ -11723,13 +11731,13 @@
         <v>106</v>
       </c>
       <c r="B25" s="26" t="s">
+        <v>882</v>
+      </c>
+      <c r="C25" s="26">
+        <v>1</v>
+      </c>
+      <c r="D25" s="26" t="s">
         <v>883</v>
-      </c>
-      <c r="C25" s="26">
-        <v>1</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>884</v>
       </c>
       <c r="E25" s="26" t="s">
         <v>34</v>
@@ -11740,16 +11748,16 @@
         <v>114</v>
       </c>
       <c r="B26" s="26" t="s">
+        <v>884</v>
+      </c>
+      <c r="C26" s="26">
+        <v>1</v>
+      </c>
+      <c r="D26" s="26" t="s">
         <v>885</v>
       </c>
-      <c r="C26" s="26">
-        <v>1</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>886</v>
-      </c>
       <c r="E26" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1">
@@ -11757,16 +11765,16 @@
         <v>114</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C27" s="26">
         <v>2</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1">
@@ -11774,13 +11782,13 @@
         <v>114</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C28" s="26">
         <v>3</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E28" s="26" t="s">
         <v>34</v>
@@ -11791,16 +11799,16 @@
         <v>114</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C29" s="26">
         <v>4</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1">
@@ -11808,16 +11816,16 @@
         <v>126</v>
       </c>
       <c r="B30" s="26" t="s">
+        <v>891</v>
+      </c>
+      <c r="C30" s="26">
+        <v>1</v>
+      </c>
+      <c r="D30" s="26" t="s">
         <v>892</v>
       </c>
-      <c r="C30" s="26">
-        <v>1</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>893</v>
-      </c>
       <c r="E30" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1">
@@ -11825,13 +11833,13 @@
         <v>126</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C31" s="26">
         <v>2</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E31" s="26" t="s">
         <v>34</v>
@@ -11842,16 +11850,16 @@
         <v>126</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C32" s="26">
         <v>3</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1">
@@ -11859,13 +11867,13 @@
         <v>136</v>
       </c>
       <c r="B33" s="26" t="s">
+        <v>897</v>
+      </c>
+      <c r="C33" s="26">
+        <v>1</v>
+      </c>
+      <c r="D33" s="26" t="s">
         <v>898</v>
-      </c>
-      <c r="C33" s="26">
-        <v>1</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>899</v>
       </c>
       <c r="E33" s="26" t="s">
         <v>34</v>
@@ -11876,16 +11884,16 @@
         <v>136</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C34" s="26">
         <v>2</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1">
@@ -11893,16 +11901,16 @@
         <v>136</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C35" s="26">
         <v>3</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1">
@@ -11910,13 +11918,13 @@
         <v>146</v>
       </c>
       <c r="B36" s="26" t="s">
+        <v>903</v>
+      </c>
+      <c r="C36" s="26">
+        <v>1</v>
+      </c>
+      <c r="D36" s="26" t="s">
         <v>904</v>
-      </c>
-      <c r="C36" s="26">
-        <v>1</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>905</v>
       </c>
       <c r="E36" s="26" t="s">
         <v>34</v>
@@ -11927,16 +11935,16 @@
         <v>146</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C37" s="26">
         <v>2</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1">
@@ -11944,16 +11952,16 @@
         <v>146</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C38" s="26">
         <v>3</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1">
@@ -11961,16 +11969,16 @@
         <v>146</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C39" s="26">
         <v>4</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1">
@@ -11978,16 +11986,16 @@
         <v>146</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C40" s="26">
         <v>5</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1">
@@ -11995,16 +12003,16 @@
         <v>146</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C41" s="26">
         <v>6</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15" customHeight="1">
@@ -12012,13 +12020,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="26" t="s">
+        <v>915</v>
+      </c>
+      <c r="C42" s="26">
+        <v>1</v>
+      </c>
+      <c r="D42" s="26" t="s">
         <v>916</v>
-      </c>
-      <c r="C42" s="26">
-        <v>1</v>
-      </c>
-      <c r="D42" s="26" t="s">
-        <v>917</v>
       </c>
       <c r="E42" s="26" t="s">
         <v>34</v>
@@ -12029,13 +12037,13 @@
         <v>166</v>
       </c>
       <c r="B43" s="26" t="s">
+        <v>917</v>
+      </c>
+      <c r="C43" s="26">
+        <v>1</v>
+      </c>
+      <c r="D43" s="26" t="s">
         <v>918</v>
-      </c>
-      <c r="C43" s="26">
-        <v>1</v>
-      </c>
-      <c r="D43" s="26" t="s">
-        <v>919</v>
       </c>
       <c r="E43" s="26" t="s">
         <v>34</v>
@@ -12046,13 +12054,13 @@
         <v>176</v>
       </c>
       <c r="B44" s="26" t="s">
+        <v>919</v>
+      </c>
+      <c r="C44" s="26">
+        <v>1</v>
+      </c>
+      <c r="D44" s="26" t="s">
         <v>920</v>
-      </c>
-      <c r="C44" s="26">
-        <v>1</v>
-      </c>
-      <c r="D44" s="26" t="s">
-        <v>921</v>
       </c>
       <c r="E44" s="26" t="s">
         <v>34</v>
@@ -12063,13 +12071,13 @@
         <v>186</v>
       </c>
       <c r="B45" s="26" t="s">
+        <v>921</v>
+      </c>
+      <c r="C45" s="26">
+        <v>1</v>
+      </c>
+      <c r="D45" s="26" t="s">
         <v>922</v>
-      </c>
-      <c r="C45" s="26">
-        <v>1</v>
-      </c>
-      <c r="D45" s="26" t="s">
-        <v>923</v>
       </c>
       <c r="E45" s="26" t="s">
         <v>34</v>
@@ -12080,13 +12088,13 @@
         <v>196</v>
       </c>
       <c r="B46" s="26" t="s">
+        <v>923</v>
+      </c>
+      <c r="C46" s="26">
+        <v>1</v>
+      </c>
+      <c r="D46" s="26" t="s">
         <v>924</v>
-      </c>
-      <c r="C46" s="26">
-        <v>1</v>
-      </c>
-      <c r="D46" s="26" t="s">
-        <v>925</v>
       </c>
       <c r="E46" s="26" t="s">
         <v>34</v>
@@ -12097,16 +12105,16 @@
         <v>196</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C47" s="26">
         <v>2</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" customHeight="1">
@@ -12114,16 +12122,16 @@
         <v>207</v>
       </c>
       <c r="B48" s="26" t="s">
+        <v>927</v>
+      </c>
+      <c r="C48" s="26">
+        <v>1</v>
+      </c>
+      <c r="D48" s="26" t="s">
         <v>928</v>
       </c>
-      <c r="C48" s="26">
-        <v>1</v>
-      </c>
-      <c r="D48" s="26" t="s">
-        <v>929</v>
-      </c>
       <c r="E48" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1">
@@ -12131,16 +12139,16 @@
         <v>207</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C49" s="26">
         <v>2</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1">
@@ -12148,16 +12156,16 @@
         <v>207</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C50" s="26">
         <v>3</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E50" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15" customHeight="1">
@@ -12165,13 +12173,13 @@
         <v>207</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C51" s="26">
         <v>4</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="E51" s="26" t="s">
         <v>34</v>
@@ -12182,13 +12190,13 @@
         <v>216</v>
       </c>
       <c r="B52" s="26" t="s">
+        <v>935</v>
+      </c>
+      <c r="C52" s="26">
+        <v>1</v>
+      </c>
+      <c r="D52" s="26" t="s">
         <v>936</v>
-      </c>
-      <c r="C52" s="26">
-        <v>1</v>
-      </c>
-      <c r="D52" s="26" t="s">
-        <v>937</v>
       </c>
       <c r="E52" s="26" t="s">
         <v>34</v>
@@ -12199,16 +12207,16 @@
         <v>216</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C53" s="26">
         <v>2</v>
       </c>
       <c r="D53" s="26" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15" customHeight="1">
@@ -12216,16 +12224,16 @@
         <v>216</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C54" s="26">
         <v>3</v>
       </c>
       <c r="D54" s="26" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="E54" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15" customHeight="1">
@@ -12233,13 +12241,13 @@
         <v>226</v>
       </c>
       <c r="B55" s="26" t="s">
+        <v>941</v>
+      </c>
+      <c r="C55" s="26">
+        <v>1</v>
+      </c>
+      <c r="D55" s="26" t="s">
         <v>942</v>
-      </c>
-      <c r="C55" s="26">
-        <v>1</v>
-      </c>
-      <c r="D55" s="26" t="s">
-        <v>943</v>
       </c>
       <c r="E55" s="26" t="s">
         <v>34</v>
@@ -12250,16 +12258,16 @@
         <v>226</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C56" s="26">
         <v>2</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="E56" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15" customHeight="1">
@@ -12267,13 +12275,13 @@
         <v>237</v>
       </c>
       <c r="B57" s="26" t="s">
+        <v>945</v>
+      </c>
+      <c r="C57" s="26">
+        <v>1</v>
+      </c>
+      <c r="D57" s="26" t="s">
         <v>946</v>
-      </c>
-      <c r="C57" s="26">
-        <v>1</v>
-      </c>
-      <c r="D57" s="26" t="s">
-        <v>947</v>
       </c>
       <c r="E57" s="26" t="s">
         <v>34</v>
@@ -12284,13 +12292,13 @@
         <v>247</v>
       </c>
       <c r="B58" s="26" t="s">
+        <v>947</v>
+      </c>
+      <c r="C58" s="26">
+        <v>1</v>
+      </c>
+      <c r="D58" s="26" t="s">
         <v>948</v>
-      </c>
-      <c r="C58" s="26">
-        <v>1</v>
-      </c>
-      <c r="D58" s="26" t="s">
-        <v>949</v>
       </c>
       <c r="E58" s="26" t="s">
         <v>34</v>
@@ -12301,13 +12309,13 @@
         <v>255</v>
       </c>
       <c r="B59" s="26" t="s">
+        <v>949</v>
+      </c>
+      <c r="C59" s="26">
+        <v>1</v>
+      </c>
+      <c r="D59" s="26" t="s">
         <v>950</v>
-      </c>
-      <c r="C59" s="26">
-        <v>1</v>
-      </c>
-      <c r="D59" s="26" t="s">
-        <v>951</v>
       </c>
       <c r="E59" s="26" t="s">
         <v>34</v>
@@ -12318,16 +12326,16 @@
         <v>255</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C60" s="26">
         <v>2</v>
       </c>
       <c r="D60" s="26" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15" customHeight="1">
@@ -12335,13 +12343,13 @@
         <v>266</v>
       </c>
       <c r="B61" s="26" t="s">
+        <v>953</v>
+      </c>
+      <c r="C61" s="26">
+        <v>1</v>
+      </c>
+      <c r="D61" s="26" t="s">
         <v>954</v>
-      </c>
-      <c r="C61" s="26">
-        <v>1</v>
-      </c>
-      <c r="D61" s="26" t="s">
-        <v>955</v>
       </c>
       <c r="E61" s="26" t="s">
         <v>34</v>
@@ -12352,16 +12360,16 @@
         <v>106</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="C62" s="26">
         <v>5</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E62" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15" customHeight="1">
@@ -12369,16 +12377,16 @@
         <v>106</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="C63" s="26">
         <v>6</v>
       </c>
       <c r="D63" s="26" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E63" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15" customHeight="1">
@@ -12386,16 +12394,16 @@
         <v>106</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C64" s="26">
         <v>7</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E64" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15" customHeight="1">
@@ -12403,13 +12411,13 @@
         <v>276</v>
       </c>
       <c r="B65" s="26" t="s">
+        <v>961</v>
+      </c>
+      <c r="C65" s="26">
+        <v>1</v>
+      </c>
+      <c r="D65" s="26" t="s">
         <v>962</v>
-      </c>
-      <c r="C65" s="26">
-        <v>1</v>
-      </c>
-      <c r="D65" s="26" t="s">
-        <v>963</v>
       </c>
       <c r="E65" s="26" t="s">
         <v>34</v>
@@ -12420,13 +12428,13 @@
         <v>288</v>
       </c>
       <c r="B66" s="26" t="s">
+        <v>963</v>
+      </c>
+      <c r="C66" s="26">
+        <v>1</v>
+      </c>
+      <c r="D66" s="26" t="s">
         <v>964</v>
-      </c>
-      <c r="C66" s="26">
-        <v>1</v>
-      </c>
-      <c r="D66" s="26" t="s">
-        <v>965</v>
       </c>
       <c r="E66" s="26" t="s">
         <v>34</v>
@@ -12437,16 +12445,16 @@
         <v>288</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C67" s="26">
         <v>2</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15" customHeight="1">
@@ -12454,16 +12462,16 @@
         <v>297</v>
       </c>
       <c r="B68" s="26" t="s">
+        <v>967</v>
+      </c>
+      <c r="C68" s="26">
+        <v>1</v>
+      </c>
+      <c r="D68" s="26" t="s">
         <v>968</v>
       </c>
-      <c r="C68" s="26">
-        <v>1</v>
-      </c>
-      <c r="D68" s="26" t="s">
-        <v>969</v>
-      </c>
       <c r="E68" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15" customHeight="1">
@@ -12471,13 +12479,13 @@
         <v>297</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C69" s="26">
         <v>2</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E69" s="26" t="s">
         <v>34</v>
@@ -12488,13 +12496,13 @@
         <v>307</v>
       </c>
       <c r="B70" s="26" t="s">
+        <v>971</v>
+      </c>
+      <c r="C70" s="26">
+        <v>1</v>
+      </c>
+      <c r="D70" s="26" t="s">
         <v>972</v>
-      </c>
-      <c r="C70" s="26">
-        <v>1</v>
-      </c>
-      <c r="D70" s="26" t="s">
-        <v>973</v>
       </c>
       <c r="E70" s="26" t="s">
         <v>34</v>
@@ -12505,13 +12513,13 @@
         <v>318</v>
       </c>
       <c r="B71" s="26" t="s">
+        <v>973</v>
+      </c>
+      <c r="C71" s="26">
+        <v>1</v>
+      </c>
+      <c r="D71" s="26" t="s">
         <v>974</v>
-      </c>
-      <c r="C71" s="26">
-        <v>1</v>
-      </c>
-      <c r="D71" s="26" t="s">
-        <v>975</v>
       </c>
       <c r="E71" s="26" t="s">
         <v>34</v>
@@ -12522,16 +12530,16 @@
         <v>318</v>
       </c>
       <c r="B72" s="26" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C72" s="26">
         <v>2</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E72" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15" customHeight="1">
@@ -12539,16 +12547,16 @@
         <v>329</v>
       </c>
       <c r="B73" s="26" t="s">
+        <v>977</v>
+      </c>
+      <c r="C73" s="26">
+        <v>1</v>
+      </c>
+      <c r="D73" s="26" t="s">
         <v>978</v>
       </c>
-      <c r="C73" s="26">
-        <v>1</v>
-      </c>
-      <c r="D73" s="26" t="s">
-        <v>979</v>
-      </c>
       <c r="E73" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15" customHeight="1">
@@ -12556,13 +12564,13 @@
         <v>329</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C74" s="26">
         <v>2</v>
       </c>
       <c r="D74" s="26" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E74" s="26" t="s">
         <v>34</v>
@@ -12573,13 +12581,13 @@
         <v>339</v>
       </c>
       <c r="B75" s="26" t="s">
+        <v>981</v>
+      </c>
+      <c r="C75" s="26">
+        <v>1</v>
+      </c>
+      <c r="D75" s="26" t="s">
         <v>982</v>
-      </c>
-      <c r="C75" s="26">
-        <v>1</v>
-      </c>
-      <c r="D75" s="26" t="s">
-        <v>983</v>
       </c>
       <c r="E75" s="26" t="s">
         <v>34</v>
@@ -12590,13 +12598,13 @@
         <v>350</v>
       </c>
       <c r="B76" s="26" t="s">
+        <v>983</v>
+      </c>
+      <c r="C76" s="26">
+        <v>1</v>
+      </c>
+      <c r="D76" s="26" t="s">
         <v>984</v>
-      </c>
-      <c r="C76" s="26">
-        <v>1</v>
-      </c>
-      <c r="D76" s="26" t="s">
-        <v>985</v>
       </c>
       <c r="E76" s="26" t="s">
         <v>34</v>
@@ -12607,16 +12615,16 @@
         <v>350</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C77" s="26">
         <v>2</v>
       </c>
       <c r="D77" s="26" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15" customHeight="1">
@@ -12624,16 +12632,16 @@
         <v>362</v>
       </c>
       <c r="B78" s="26" t="s">
+        <v>987</v>
+      </c>
+      <c r="C78" s="26">
+        <v>1</v>
+      </c>
+      <c r="D78" s="26" t="s">
         <v>988</v>
       </c>
-      <c r="C78" s="26">
-        <v>1</v>
-      </c>
-      <c r="D78" s="26" t="s">
-        <v>989</v>
-      </c>
       <c r="E78" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="15" customHeight="1">
@@ -12641,13 +12649,13 @@
         <v>362</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C79" s="26">
         <v>2</v>
       </c>
       <c r="D79" s="26" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E79" s="26" t="s">
         <v>34</v>
@@ -12658,13 +12666,13 @@
         <v>371</v>
       </c>
       <c r="B80" s="26" t="s">
+        <v>991</v>
+      </c>
+      <c r="C80" s="26">
+        <v>1</v>
+      </c>
+      <c r="D80" s="26" t="s">
         <v>992</v>
-      </c>
-      <c r="C80" s="26">
-        <v>1</v>
-      </c>
-      <c r="D80" s="26" t="s">
-        <v>993</v>
       </c>
       <c r="E80" s="26" t="s">
         <v>34</v>
@@ -12675,13 +12683,13 @@
         <v>380</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="C81" s="3">
+        <v>1</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>994</v>
-      </c>
-      <c r="C81" s="3">
-        <v>1</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>995</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>34</v>
@@ -12692,16 +12700,16 @@
         <v>380</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C82" s="3">
         <v>2</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -12709,16 +12717,16 @@
         <v>391</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="C83" s="3">
+        <v>1</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>998</v>
       </c>
-      <c r="C83" s="3">
-        <v>1</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>999</v>
-      </c>
       <c r="E83" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -12726,13 +12734,13 @@
         <v>391</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C84" s="3">
         <v>2</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>34</v>
@@ -12743,16 +12751,16 @@
         <v>391</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C85" s="3">
         <v>3</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -12760,13 +12768,13 @@
         <v>400</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C86" s="3">
+        <v>1</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>1004</v>
-      </c>
-      <c r="C86" s="3">
-        <v>1</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>1005</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>34</v>
@@ -12777,16 +12785,16 @@
         <v>400</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="C87" s="3">
         <v>2</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -12794,13 +12802,13 @@
         <v>410</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C88" s="3">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>1008</v>
-      </c>
-      <c r="C88" s="3">
-        <v>1</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>1009</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>34</v>
@@ -12811,16 +12819,16 @@
         <v>410</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C89" s="3">
         <v>2</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -12828,13 +12836,13 @@
         <v>419</v>
       </c>
       <c r="B90" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C90" s="3">
+        <v>1</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>1012</v>
-      </c>
-      <c r="C90" s="3">
-        <v>1</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>1013</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>34</v>
@@ -12845,16 +12853,16 @@
         <v>155</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C91" s="3">
+        <v>1</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>1014</v>
       </c>
-      <c r="C91" s="3">
-        <v>1</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>1015</v>
-      </c>
       <c r="E91" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -12862,16 +12870,16 @@
         <v>155</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C92" s="3">
         <v>2</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -12879,16 +12887,16 @@
         <v>155</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C93" s="3">
         <v>3</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -12896,13 +12904,13 @@
         <v>155</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C94" s="3">
         <v>4</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>34</v>
@@ -12913,13 +12921,13 @@
         <v>435</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C95" s="3">
+        <v>1</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>1022</v>
-      </c>
-      <c r="C95" s="3">
-        <v>1</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>1023</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>34</v>
@@ -12930,16 +12938,16 @@
         <v>435</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C96" s="3">
         <v>2</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -12947,16 +12955,16 @@
         <v>435</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C97" s="3">
         <v>3</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -12964,13 +12972,13 @@
         <v>444</v>
       </c>
       <c r="B98" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C98" s="3">
+        <v>1</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>1028</v>
-      </c>
-      <c r="C98" s="3">
-        <v>1</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>1029</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>34</v>
@@ -12981,16 +12989,16 @@
         <v>444</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C99" s="3">
         <v>2</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -12998,16 +13006,16 @@
         <v>444</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C100" s="3">
         <v>3</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -13015,13 +13023,13 @@
         <v>453</v>
       </c>
       <c r="B101" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C101" s="3">
+        <v>1</v>
+      </c>
+      <c r="D101" s="3" t="s">
         <v>1034</v>
-      </c>
-      <c r="C101" s="3">
-        <v>1</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>1035</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>34</v>
@@ -13032,13 +13040,13 @@
         <v>460</v>
       </c>
       <c r="B102" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C102" s="3">
+        <v>1</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>1036</v>
-      </c>
-      <c r="C102" s="3">
-        <v>1</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>1037</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>34</v>
@@ -13049,16 +13057,16 @@
         <v>460</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C103" s="3">
         <v>2</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -13066,16 +13074,16 @@
         <v>460</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="C104" s="3">
         <v>3</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="24" customHeight="1">
@@ -13083,16 +13091,16 @@
         <v>479</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C105" s="2">
         <v>2</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="24" customHeight="1">
@@ -13100,13 +13108,13 @@
         <v>479</v>
       </c>
       <c r="B106" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C106" s="2">
+        <v>1</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>1044</v>
-      </c>
-      <c r="C106" s="2">
-        <v>1</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>1045</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>34</v>
@@ -13117,13 +13125,13 @@
         <v>487</v>
       </c>
       <c r="B107" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C107" s="2">
+        <v>1</v>
+      </c>
+      <c r="D107" s="2" t="s">
         <v>1046</v>
-      </c>
-      <c r="C107" s="2">
-        <v>1</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>1047</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>34</v>
@@ -13134,16 +13142,16 @@
         <v>487</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C108" s="2">
         <v>2</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="24" customHeight="1">
@@ -13151,13 +13159,13 @@
         <v>495</v>
       </c>
       <c r="B109" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C109" s="2">
+        <v>1</v>
+      </c>
+      <c r="D109" s="2" t="s">
         <v>1050</v>
-      </c>
-      <c r="C109" s="2">
-        <v>1</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>1051</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>34</v>
@@ -13168,13 +13176,13 @@
         <v>501</v>
       </c>
       <c r="B110" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C110" s="2">
+        <v>1</v>
+      </c>
+      <c r="D110" s="2" t="s">
         <v>1052</v>
-      </c>
-      <c r="C110" s="2">
-        <v>1</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>1053</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>34</v>
@@ -13185,16 +13193,16 @@
         <v>501</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="C111" s="2">
         <v>2</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="24" customHeight="1">
@@ -13202,16 +13210,16 @@
         <v>501</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C112" s="2">
         <v>3</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="24" customHeight="1">
@@ -13219,16 +13227,16 @@
         <v>501</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C113" s="2">
         <v>4</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="24" customHeight="1">
@@ -13236,16 +13244,16 @@
         <v>501</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C114" s="2">
         <v>5</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="24" customHeight="1">
@@ -13253,13 +13261,13 @@
         <v>508</v>
       </c>
       <c r="B115" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C115" s="2">
+        <v>1</v>
+      </c>
+      <c r="D115" s="2" t="s">
         <v>1062</v>
-      </c>
-      <c r="C115" s="2">
-        <v>1</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>1063</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>34</v>
@@ -13270,16 +13278,16 @@
         <v>508</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C116" s="2">
         <v>2</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="24" customHeight="1">
@@ -13287,13 +13295,13 @@
         <v>516</v>
       </c>
       <c r="B117" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C117" s="2">
+        <v>1</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>1066</v>
-      </c>
-      <c r="C117" s="2">
-        <v>1</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>1067</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>34</v>
@@ -13304,13 +13312,13 @@
         <v>522</v>
       </c>
       <c r="B118" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C118" s="2">
+        <v>1</v>
+      </c>
+      <c r="D118" s="2" t="s">
         <v>1068</v>
-      </c>
-      <c r="C118" s="2">
-        <v>1</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>1069</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>34</v>
@@ -13321,16 +13329,16 @@
         <v>522</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C119" s="2">
         <v>2</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="24" customHeight="1">
@@ -13338,13 +13346,13 @@
         <v>528</v>
       </c>
       <c r="B120" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C120" s="2">
+        <v>1</v>
+      </c>
+      <c r="D120" s="2" t="s">
         <v>1072</v>
-      </c>
-      <c r="C120" s="2">
-        <v>1</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>1073</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>34</v>
@@ -13355,16 +13363,16 @@
         <v>528</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C121" s="2">
         <v>2</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="24" customHeight="1">
@@ -13372,13 +13380,13 @@
         <v>536</v>
       </c>
       <c r="B122" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C122" s="2">
+        <v>1</v>
+      </c>
+      <c r="D122" s="2" t="s">
         <v>1076</v>
-      </c>
-      <c r="C122" s="2">
-        <v>1</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>1077</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>34</v>
@@ -13389,16 +13397,16 @@
         <v>536</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C123" s="2">
         <v>2</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="24" customHeight="1">
@@ -13406,16 +13414,16 @@
         <v>536</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C124" s="2">
         <v>3</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="24" customHeight="1">
@@ -13423,13 +13431,13 @@
         <v>542</v>
       </c>
       <c r="B125" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C125" s="2">
+        <v>1</v>
+      </c>
+      <c r="D125" s="2" t="s">
         <v>1082</v>
-      </c>
-      <c r="C125" s="2">
-        <v>1</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>1083</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>34</v>
@@ -13440,16 +13448,16 @@
         <v>542</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C126" s="2">
         <v>2</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="24" customHeight="1">
@@ -13457,13 +13465,13 @@
         <v>546</v>
       </c>
       <c r="B127" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C127" s="2">
+        <v>1</v>
+      </c>
+      <c r="D127" s="2" t="s">
         <v>1086</v>
-      </c>
-      <c r="C127" s="2">
-        <v>1</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>1087</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>34</v>
@@ -13474,16 +13482,16 @@
         <v>546</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C128" s="2">
         <v>2</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="24" customHeight="1">
@@ -13491,16 +13499,16 @@
         <v>546</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C129" s="2">
         <v>3</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="24" customHeight="1">
@@ -13508,16 +13516,16 @@
         <v>546</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C130" s="2">
         <v>4</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="24" customHeight="1">
@@ -13525,13 +13533,13 @@
         <v>552</v>
       </c>
       <c r="B131" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C131" s="2">
+        <v>1</v>
+      </c>
+      <c r="D131" s="2" t="s">
         <v>1094</v>
-      </c>
-      <c r="C131" s="2">
-        <v>1</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>1095</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>34</v>
@@ -13542,16 +13550,16 @@
         <v>552</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C132" s="2">
         <v>2</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="24" customHeight="1">
@@ -13559,13 +13567,13 @@
         <v>559</v>
       </c>
       <c r="B133" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C133" s="2">
+        <v>1</v>
+      </c>
+      <c r="D133" s="2" t="s">
         <v>1098</v>
-      </c>
-      <c r="C133" s="2">
-        <v>1</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>1099</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>34</v>
@@ -13576,16 +13584,16 @@
         <v>559</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C134" s="2">
         <v>2</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="24" customHeight="1">
@@ -13593,13 +13601,13 @@
         <v>566</v>
       </c>
       <c r="B135" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C135" s="2">
+        <v>1</v>
+      </c>
+      <c r="D135" s="2" t="s">
         <v>1102</v>
-      </c>
-      <c r="C135" s="2">
-        <v>1</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>1103</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>34</v>
@@ -13610,16 +13618,16 @@
         <v>566</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C136" s="2">
         <v>2</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="24" customHeight="1">
@@ -13627,13 +13635,13 @@
         <v>573</v>
       </c>
       <c r="B137" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C137" s="2">
+        <v>1</v>
+      </c>
+      <c r="D137" s="2" t="s">
         <v>1106</v>
-      </c>
-      <c r="C137" s="2">
-        <v>1</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>1107</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>34</v>
@@ -13644,16 +13652,16 @@
         <v>573</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C138" s="2">
         <v>2</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="24" customHeight="1">
@@ -13661,16 +13669,16 @@
         <v>573</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C139" s="2">
         <v>3</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="24" customHeight="1">
@@ -13678,13 +13686,13 @@
         <v>579</v>
       </c>
       <c r="B140" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C140" s="2">
+        <v>1</v>
+      </c>
+      <c r="D140" s="2" t="s">
         <v>1112</v>
-      </c>
-      <c r="C140" s="2">
-        <v>1</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>1113</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>34</v>
@@ -13695,16 +13703,16 @@
         <v>579</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C141" s="2">
         <v>2</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="24" customHeight="1">
@@ -13712,16 +13720,16 @@
         <v>579</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C142" s="2">
         <v>3</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="24" customHeight="1">
@@ -13729,16 +13737,16 @@
         <v>579</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C143" s="2">
         <v>4</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="24" customHeight="1">
@@ -13746,13 +13754,13 @@
         <v>586</v>
       </c>
       <c r="B144" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C144" s="2">
+        <v>1</v>
+      </c>
+      <c r="D144" s="2" t="s">
         <v>1120</v>
-      </c>
-      <c r="C144" s="2">
-        <v>1</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>1121</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>34</v>
@@ -13763,16 +13771,16 @@
         <v>586</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C145" s="2">
         <v>2</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="24" customHeight="1">
@@ -13780,16 +13788,16 @@
         <v>586</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C146" s="2">
         <v>3</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="24" customHeight="1">
@@ -13797,13 +13805,13 @@
         <v>593</v>
       </c>
       <c r="B147" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C147" s="2">
+        <v>1</v>
+      </c>
+      <c r="D147" s="2" t="s">
         <v>1126</v>
-      </c>
-      <c r="C147" s="2">
-        <v>1</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>1127</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>34</v>
@@ -13814,13 +13822,13 @@
         <v>600</v>
       </c>
       <c r="B148" s="2" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C148" s="2">
+        <v>1</v>
+      </c>
+      <c r="D148" s="2" t="s">
         <v>1128</v>
-      </c>
-      <c r="C148" s="2">
-        <v>1</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>1129</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>34</v>
@@ -13831,16 +13839,16 @@
         <v>600</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C149" s="2">
         <v>2</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="24" customHeight="1">
@@ -13848,16 +13856,16 @@
         <v>606</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C150" s="2">
         <v>2</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="24" customHeight="1">
@@ -13865,13 +13873,13 @@
         <v>606</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="C151" s="2">
         <v>1</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>34</v>
@@ -13882,13 +13890,13 @@
         <v>613</v>
       </c>
       <c r="B152" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C152" s="2">
+        <v>1</v>
+      </c>
+      <c r="D152" s="2" t="s">
         <v>1136</v>
-      </c>
-      <c r="C152" s="2">
-        <v>1</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>1137</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>34</v>
@@ -13899,16 +13907,16 @@
         <v>613</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C153" s="2">
         <v>2</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="24" customHeight="1">
@@ -13916,13 +13924,13 @@
         <v>621</v>
       </c>
       <c r="B154" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C154" s="2">
+        <v>1</v>
+      </c>
+      <c r="D154" s="2" t="s">
         <v>1140</v>
-      </c>
-      <c r="C154" s="2">
-        <v>1</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>1141</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>34</v>
@@ -13933,16 +13941,16 @@
         <v>621</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C155" s="2">
         <v>2</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="24" customHeight="1">
@@ -13950,13 +13958,13 @@
         <v>627</v>
       </c>
       <c r="B156" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C156" s="2">
+        <v>1</v>
+      </c>
+      <c r="D156" s="2" t="s">
         <v>1144</v>
-      </c>
-      <c r="C156" s="2">
-        <v>1</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>1145</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>34</v>
@@ -13967,16 +13975,16 @@
         <v>627</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C157" s="2">
         <v>2</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="24" customHeight="1">
@@ -13984,13 +13992,13 @@
         <v>634</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C158" s="2">
+        <v>1</v>
+      </c>
+      <c r="D158" s="2" t="s">
         <v>1148</v>
-      </c>
-      <c r="C158" s="2">
-        <v>1</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>1149</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>34</v>
@@ -14001,16 +14009,16 @@
         <v>634</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C159" s="2">
         <v>2</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="24" customHeight="1">
@@ -14018,16 +14026,16 @@
         <v>634</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C160" s="2">
         <v>3</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="24" customHeight="1">
@@ -14035,16 +14043,16 @@
         <v>634</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C161" s="2">
         <v>4</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="24" customHeight="1">
@@ -14052,13 +14060,13 @@
         <v>641</v>
       </c>
       <c r="B162" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C162" s="2">
+        <v>1</v>
+      </c>
+      <c r="D162" s="2" t="s">
         <v>1156</v>
-      </c>
-      <c r="C162" s="2">
-        <v>1</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>1157</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>34</v>
@@ -14069,13 +14077,13 @@
         <v>647</v>
       </c>
       <c r="B163" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C163" s="2">
+        <v>1</v>
+      </c>
+      <c r="D163" s="2" t="s">
         <v>1158</v>
-      </c>
-      <c r="C163" s="2">
-        <v>1</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>1159</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>34</v>
@@ -14086,13 +14094,13 @@
         <v>653</v>
       </c>
       <c r="B164" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C164" s="2">
+        <v>1</v>
+      </c>
+      <c r="D164" s="2" t="s">
         <v>1160</v>
-      </c>
-      <c r="C164" s="2">
-        <v>1</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>1161</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>34</v>
@@ -14103,16 +14111,16 @@
         <v>653</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="C165" s="2">
         <v>2</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="24" customHeight="1">
@@ -14120,16 +14128,16 @@
         <v>653</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C166" s="2">
         <v>3</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="24" customHeight="1">
@@ -14137,16 +14145,16 @@
         <v>653</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C167" s="2">
         <v>4</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="24" customHeight="1">
@@ -14154,16 +14162,16 @@
         <v>653</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C168" s="2">
         <v>5</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="24" customHeight="1">
@@ -14171,13 +14179,13 @@
         <v>662</v>
       </c>
       <c r="B169" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C169" s="2">
+        <v>1</v>
+      </c>
+      <c r="D169" s="2" t="s">
         <v>1170</v>
-      </c>
-      <c r="C169" s="2">
-        <v>1</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>1171</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>34</v>
@@ -14188,13 +14196,13 @@
         <v>669</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C170" s="2">
+        <v>1</v>
+      </c>
+      <c r="D170" s="2" t="s">
         <v>1172</v>
-      </c>
-      <c r="C170" s="2">
-        <v>1</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>1173</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>34</v>
@@ -14205,13 +14213,13 @@
         <v>675</v>
       </c>
       <c r="B171" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C171" s="2">
+        <v>1</v>
+      </c>
+      <c r="D171" s="2" t="s">
         <v>1174</v>
-      </c>
-      <c r="C171" s="2">
-        <v>1</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>1175</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>34</v>
@@ -14222,13 +14230,13 @@
         <v>681</v>
       </c>
       <c r="B172" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C172" s="2">
+        <v>1</v>
+      </c>
+      <c r="D172" s="2" t="s">
         <v>1176</v>
-      </c>
-      <c r="C172" s="2">
-        <v>1</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>1177</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>34</v>
@@ -14239,13 +14247,13 @@
         <v>688</v>
       </c>
       <c r="B173" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C173" s="2">
+        <v>1</v>
+      </c>
+      <c r="D173" s="2" t="s">
         <v>1178</v>
-      </c>
-      <c r="C173" s="2">
-        <v>1</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>1179</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>34</v>
@@ -14256,13 +14264,13 @@
         <v>696</v>
       </c>
       <c r="B174" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C174" s="2">
+        <v>1</v>
+      </c>
+      <c r="D174" s="2" t="s">
         <v>1180</v>
-      </c>
-      <c r="C174" s="2">
-        <v>1</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>1181</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>34</v>
@@ -14273,13 +14281,13 @@
         <v>703</v>
       </c>
       <c r="B175" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C175" s="2">
+        <v>1</v>
+      </c>
+      <c r="D175" s="2" t="s">
         <v>1182</v>
-      </c>
-      <c r="C175" s="2">
-        <v>1</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>1183</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>34</v>
@@ -14290,13 +14298,13 @@
         <v>710</v>
       </c>
       <c r="B176" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C176" s="2">
+        <v>1</v>
+      </c>
+      <c r="D176" s="2" t="s">
         <v>1184</v>
-      </c>
-      <c r="C176" s="2">
-        <v>1</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>1185</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>34</v>
@@ -14307,13 +14315,13 @@
         <v>718</v>
       </c>
       <c r="B177" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C177" s="2">
+        <v>1</v>
+      </c>
+      <c r="D177" s="2" t="s">
         <v>1186</v>
-      </c>
-      <c r="C177" s="2">
-        <v>1</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>1187</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>34</v>
@@ -14324,13 +14332,13 @@
         <v>725</v>
       </c>
       <c r="B178" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C178" s="2">
+        <v>1</v>
+      </c>
+      <c r="D178" s="2" t="s">
         <v>1188</v>
-      </c>
-      <c r="C178" s="2">
-        <v>1</v>
-      </c>
-      <c r="D178" s="2" t="s">
-        <v>1189</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>34</v>
@@ -14341,16 +14349,16 @@
         <v>725</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C179" s="2">
         <v>2</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="24" customHeight="1">
@@ -14358,13 +14366,13 @@
         <v>732</v>
       </c>
       <c r="B180" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C180" s="2">
+        <v>1</v>
+      </c>
+      <c r="D180" s="2" t="s">
         <v>1192</v>
-      </c>
-      <c r="C180" s="2">
-        <v>1</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>1193</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>34</v>
@@ -14375,16 +14383,16 @@
         <v>732</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C181" s="2">
         <v>2</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="24" customHeight="1">
@@ -14392,13 +14400,13 @@
         <v>740</v>
       </c>
       <c r="B182" s="2" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C182" s="2">
+        <v>1</v>
+      </c>
+      <c r="D182" s="2" t="s">
         <v>1196</v>
-      </c>
-      <c r="C182" s="2">
-        <v>1</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>1197</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>34</v>
@@ -14409,16 +14417,16 @@
         <v>740</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C183" s="2">
         <v>2</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="184" spans="1:5" ht="24" customHeight="1">
@@ -14426,24 +14434,24 @@
         <v>740</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C184" s="2">
         <v>3</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>1222</v>
+        <v>1241</v>
       </c>
       <c r="C185" s="2">
         <v>1</v>
@@ -14454,52 +14462,52 @@
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="C186" s="2">
         <v>2</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="C187" s="2">
         <v>3</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="C188" s="2">
         <v>4</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>1223</v>
+        <v>1245</v>
       </c>
       <c r="C189" s="2">
         <v>1</v>
@@ -14510,38 +14518,38 @@
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="C190" s="2">
         <v>2</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="C191" s="2">
         <v>3</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>1224</v>
+        <v>1248</v>
       </c>
       <c r="C192" s="2">
         <v>1</v>
@@ -14552,94 +14560,94 @@
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="C193" s="2">
         <v>2</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="C194" s="2">
         <v>3</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="C195" s="2">
         <v>4</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="C196" s="2">
         <v>5</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="C197" s="2">
         <v>6</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="C198" s="2">
         <v>7</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>1225</v>
+        <v>1255</v>
       </c>
       <c r="C199" s="2">
         <v>1</v>
@@ -14650,38 +14658,38 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>1250</v>
+        <v>1256</v>
       </c>
       <c r="C200" s="2">
         <v>2</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>1251</v>
+        <v>1257</v>
       </c>
       <c r="C201" s="2">
         <v>3</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>1226</v>
+        <v>1258</v>
       </c>
       <c r="C202" s="2">
         <v>1</v>
@@ -14692,10 +14700,10 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>1227</v>
+        <v>1259</v>
       </c>
       <c r="C203" s="2">
         <v>1</v>
@@ -14706,24 +14714,24 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
       <c r="C204" s="2">
         <v>2</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>1228</v>
+        <v>1261</v>
       </c>
       <c r="C205" s="2">
         <v>1</v>
@@ -14734,24 +14742,24 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>1253</v>
+        <v>1262</v>
       </c>
       <c r="C206" s="2">
         <v>2</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>1229</v>
+        <v>1263</v>
       </c>
       <c r="C207" s="2">
         <v>1</v>
@@ -14762,38 +14770,38 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>1255</v>
+        <v>1264</v>
       </c>
       <c r="C208" s="2">
         <v>2</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1254</v>
+        <v>1265</v>
       </c>
       <c r="C209" s="2">
         <v>3</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>1230</v>
+        <v>1266</v>
       </c>
       <c r="C210" s="2">
         <v>1</v>
@@ -14804,24 +14812,24 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>1256</v>
+        <v>1267</v>
       </c>
       <c r="C211" s="2">
         <v>2</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>1231</v>
+        <v>1268</v>
       </c>
       <c r="C212" s="2">
         <v>1</v>
@@ -14832,10 +14840,10 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>1232</v>
+        <v>1269</v>
       </c>
       <c r="C213" s="2">
         <v>1</v>
@@ -14846,10 +14854,10 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>1233</v>
+        <v>1270</v>
       </c>
       <c r="C214" s="2">
         <v>1</v>
@@ -14860,10 +14868,10 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1234</v>
+        <v>1271</v>
       </c>
       <c r="C215" s="2">
         <v>1</v>
@@ -14874,10 +14882,10 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>1235</v>
+        <v>1272</v>
       </c>
       <c r="C216" s="2">
         <v>1</v>
@@ -14888,24 +14896,24 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>1260</v>
+        <v>1273</v>
       </c>
       <c r="C217" s="2">
         <v>2</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>1263</v>
+        <v>1223</v>
       </c>
       <c r="C218" s="2">
         <v>1</v>
@@ -14916,10 +14924,10 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>1236</v>
+        <v>1274</v>
       </c>
       <c r="C219" s="2">
         <v>1</v>
@@ -14930,10 +14938,10 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>1237</v>
+        <v>1275</v>
       </c>
       <c r="C220" s="2">
         <v>1</v>
@@ -14944,52 +14952,52 @@
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>1257</v>
+        <v>1276</v>
       </c>
       <c r="C221" s="2">
         <v>2</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>1258</v>
+        <v>1277</v>
       </c>
       <c r="C222" s="2">
         <v>3</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>1259</v>
+        <v>1278</v>
       </c>
       <c r="C223" s="2">
         <v>4</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>1238</v>
+        <v>1279</v>
       </c>
       <c r="C224" s="2">
         <v>1</v>
@@ -15030,7 +15038,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="23" customHeight="1">
       <c r="A1" s="34" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -15040,7 +15048,7 @@
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="35" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B3" s="32"/>
       <c r="C3" s="32"/>
@@ -15050,7 +15058,7 @@
     </row>
     <row r="4" spans="1:6" ht="46" customHeight="1">
       <c r="A4" s="33" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B4" s="32"/>
       <c r="C4" s="32"/>
@@ -15060,7 +15068,7 @@
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="35" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B6" s="32"/>
       <c r="C6" s="32"/>
@@ -15070,7 +15078,7 @@
     </row>
     <row r="7" spans="1:6" ht="54" customHeight="1">
       <c r="A7" s="33" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B7" s="32"/>
       <c r="C7" s="32"/>
@@ -15080,7 +15088,7 @@
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
       <c r="A9" s="35" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B9" s="32"/>
       <c r="C9" s="32"/>
@@ -15090,7 +15098,7 @@
     </row>
     <row r="10" spans="1:6" ht="46" customHeight="1">
       <c r="A10" s="33" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="32"/>
@@ -15100,7 +15108,7 @@
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
       <c r="A12" s="35" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
@@ -15110,7 +15118,7 @@
     </row>
     <row r="13" spans="1:6" ht="54" customHeight="1">
       <c r="A13" s="33" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="32"/>
@@ -15120,17 +15128,17 @@
     </row>
     <row r="14" spans="1:6" ht="32" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="32" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="32" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
   </sheetData>

--- a/inventaire_mobilier.xlsx
+++ b/inventaire_mobilier.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolas.coquet/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B18DCD8-908C-B046-B76C-F6C7B8540899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF34FBC-D426-9C4A-A384-F966EFD2C58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mobilier" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2291" uniqueCount="1281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2287" uniqueCount="1279">
   <si>
     <t>Inventaire du mobilier</t>
   </si>
@@ -2553,1089 +2553,537 @@
     <t>Image principale</t>
   </si>
   <si>
-    <t>MOB-001-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du lit</t>
   </si>
   <si>
-    <t>MOB-001-02.jpeg</t>
-  </si>
-  <si>
     <t>Détail de la tête et du panneau peint</t>
   </si>
   <si>
     <t>Non</t>
   </si>
   <si>
-    <t>MOB-001-03.jpeg</t>
-  </si>
-  <si>
     <t>Vue rapprochée du pied et du décor</t>
   </si>
   <si>
-    <t>MOB-002-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de la pendule</t>
   </si>
   <si>
-    <t>MOB-002-02.jpeg</t>
-  </si>
-  <si>
     <t>Inscription manuscrite sous le socle</t>
   </si>
   <si>
-    <t>MOB-002-03.jpeg</t>
-  </si>
-  <si>
     <t>Vue du revers et du logement du mouvement</t>
   </si>
   <si>
-    <t>MOB-003-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de la lanterne-tempête</t>
   </si>
   <si>
-    <t>MOB-004-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de profil</t>
   </si>
   <si>
-    <t>MOB-004-02.jpeg</t>
-  </si>
-  <si>
     <t>Vue de trois-quarts et de la lentille</t>
   </si>
   <si>
-    <t>MOB-004-03.jpeg</t>
-  </si>
-  <si>
     <t>Vue frontale de la lentille fendue</t>
   </si>
   <si>
-    <t>MOB-005-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale avec la presse</t>
   </si>
   <si>
-    <t>MOB-005-02.jpeg</t>
-  </si>
-  <si>
     <t>Marques Persenico et Chiavenna sur le manche</t>
   </si>
   <si>
-    <t>MOB-005-03.jpeg</t>
-  </si>
-  <si>
     <t>Détail du modèle Derby et du blason</t>
   </si>
   <si>
-    <t>MOB-045-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du calorifère dans l’âtre</t>
   </si>
   <si>
-    <t>MOB-045-02.jpeg</t>
-  </si>
-  <si>
     <t>Vue frontale du réflecteur nervuré</t>
   </si>
   <si>
-    <t>MOB-006-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue latérale du mécanisme et de la manivelle</t>
   </si>
   <si>
-    <t>MOB-006-02.jpeg</t>
-  </si>
-  <si>
     <t>Détail de la poignée portant la marque FUF</t>
   </si>
   <si>
-    <t>MOB-007-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue de détail d’un globe et du corps central</t>
   </si>
   <si>
-    <t>MOB-007-02.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale depuis le dessous</t>
   </si>
   <si>
-    <t>MOB-007-03.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de trois-quarts</t>
   </si>
   <si>
-    <t>MOB-007-04.jpeg</t>
-  </si>
-  <si>
     <t>Détail des plaques ajourées et de la lanterne centrale</t>
   </si>
   <si>
-    <t>MOB-008-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du lustre</t>
   </si>
   <si>
-    <t>MOB-009-01.jpeg</t>
-  </si>
-  <si>
     <t>Détail du brûleur central et des bras</t>
   </si>
   <si>
-    <t>MOB-009-02.jpeg</t>
-  </si>
-  <si>
     <t>Vue du dessous et des montures</t>
   </si>
   <si>
-    <t>MOB-009-03.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-009-04.jpeg</t>
-  </si>
-  <si>
     <t>Détail de la suspension et d’une opaline</t>
   </si>
   <si>
-    <t>MOB-010-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue du revers et de la construction</t>
   </si>
   <si>
-    <t>MOB-010-02.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de la table</t>
   </si>
   <si>
-    <t>MOB-010-03.jpeg</t>
-  </si>
-  <si>
     <t>Vue plongeante du plateau</t>
   </si>
   <si>
-    <t>MOB-011-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de la lampe</t>
   </si>
   <si>
-    <t>MOB-011-02.jpeg</t>
-  </si>
-  <si>
     <t>Détail de la tortue minogame</t>
   </si>
   <si>
-    <t>MOB-011-03.jpeg</t>
-  </si>
-  <si>
     <t>Détail du héron et du serpent</t>
   </si>
   <si>
-    <t>MOB-012-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du meuble fermé</t>
   </si>
   <si>
-    <t>MOB-012-02.jpeg</t>
-  </si>
-  <si>
     <t>Détail de la porte et des pieds</t>
   </si>
   <si>
-    <t>MOB-012-03.jpeg</t>
-  </si>
-  <si>
     <t>Détail du tiroir et du dosseret</t>
   </si>
   <si>
-    <t>MOB-012-04.jpeg</t>
-  </si>
-  <si>
     <t>Vue du plateau de marbre</t>
   </si>
   <si>
-    <t>MOB-012-05.jpeg</t>
-  </si>
-  <si>
     <t>Vue du compartiment inférieur ouvert</t>
   </si>
   <si>
-    <t>MOB-012-06.jpeg</t>
-  </si>
-  <si>
     <t>Détail du décor marqueté de nacre</t>
   </si>
   <si>
-    <t>MOB-013-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de la composition fruitière</t>
   </si>
   <si>
-    <t>MOB-014-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du meuble à épices</t>
   </si>
   <si>
-    <t>MOB-015-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de la cuisinière ERMEC</t>
   </si>
   <si>
-    <t>MOB-016-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du plat décoratif</t>
   </si>
   <si>
-    <t>MOB-017-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du placard mural</t>
   </si>
   <si>
-    <t>MOB-017-02.jpeg</t>
-  </si>
-  <si>
     <t>Détail du motif étoilé en bois</t>
   </si>
   <si>
-    <t>MOB-018-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue d’un candélabre de la paire</t>
   </si>
   <si>
-    <t>MOB-018-02.jpeg</t>
-  </si>
-  <si>
     <t>Détail des branches et du fût</t>
   </si>
   <si>
-    <t>MOB-018-03.jpeg</t>
-  </si>
-  <si>
-    <t>Seconde vue de détail des branches</t>
-  </si>
-  <si>
-    <t>MOB-018-04.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de la paire</t>
   </si>
   <si>
-    <t>MOB-019-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du candélabre au raisin</t>
   </si>
   <si>
-    <t>MOB-019-02.jpeg</t>
-  </si>
-  <si>
     <t>Détail de la base et du départ des bras</t>
   </si>
   <si>
-    <t>MOB-019-03.jpeg</t>
-  </si>
-  <si>
     <t>Détail de la grappe de raisin</t>
   </si>
   <si>
-    <t>MOB-020-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de la corbeille de cerises</t>
   </si>
   <si>
-    <t>MOB-020-02.jpeg</t>
-  </si>
-  <si>
     <t>Revers avec inscription Deruta 88/24</t>
   </si>
   <si>
-    <t>MOB-021-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de la madia toscane</t>
   </si>
   <si>
-    <t>MOB-022-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du meuble de métier</t>
   </si>
   <si>
-    <t>MOB-023-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du grand vase</t>
   </si>
   <si>
-    <t>MOB-023-02.jpeg</t>
-  </si>
-  <si>
     <t>Détail de la base moulée</t>
   </si>
   <si>
-    <t>MOB-024-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de la travailleuse déployée</t>
   </si>
   <si>
-    <t>MOB-008-05.jpeg</t>
-  </si>
-  <si>
     <t>Détail d’une lanterne latérale et de ses baguettes de verre</t>
   </si>
   <si>
-    <t>MOB-008-06.jpeg</t>
-  </si>
-  <si>
     <t>Détail du corps central et des assemblages métalliques</t>
   </si>
   <si>
-    <t>MOB-008-07.jpeg</t>
-  </si>
-  <si>
     <t>Détail de la cascade centrale de baguettes et pampilles</t>
   </si>
   <si>
-    <t>MOB-025-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de l’ensemble d’enceintes Sony</t>
   </si>
   <si>
-    <t>MOB-026-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de l’encrier fermé</t>
   </si>
   <si>
-    <t>MOB-026-02.jpeg</t>
-  </si>
-  <si>
     <t>Vue de l’encrier ouvert et du godet</t>
   </si>
   <si>
-    <t>MOB-027-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue intérieure de la vasque opaline</t>
   </si>
   <si>
-    <t>MOB-027-02.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de la suspension en place</t>
   </si>
   <si>
-    <t>MOB-028-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du miroir octogonal</t>
   </si>
   <si>
-    <t>MOB-029-01.jpeg</t>
-  </si>
-  <si>
-    <t>Vue frontale du seggiolone paillé</t>
-  </si>
-  <si>
-    <t>MOB-029-02.jpeg</t>
-  </si>
-  <si>
-    <t>Vue de trois-quarts du siège haut</t>
-  </si>
-  <si>
-    <t>MOB-030-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du lecteur Sony et de son cordon</t>
   </si>
   <si>
-    <t>MOB-030-02.jpeg</t>
-  </si>
-  <si>
     <t>Vue de trois-quarts du lecteur Sony D-50 / D-5</t>
   </si>
   <si>
-    <t>MOB-031-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du coffret et des trois pipes</t>
   </si>
   <si>
-    <t>MOB-032-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue frontale du chauffage Campingaz</t>
   </si>
   <si>
-    <t>MOB-032-02.jpeg</t>
-  </si>
-  <si>
     <t>Vue de la commande du Campingaz 5000 IR</t>
   </si>
   <si>
-    <t>MOB-033-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue intérieure de l’abat-jour et des trois douilles</t>
   </si>
   <si>
-    <t>MOB-033-02.jpeg</t>
-  </si>
-  <si>
     <t>Détail de la base tripode aux lièvres</t>
   </si>
   <si>
-    <t>MOB-034-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de la bibliothèque vitrée</t>
   </si>
   <si>
-    <t>MOB-035-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du meuble de toilette</t>
   </si>
   <si>
-    <t>MOB-035-02.jpeg</t>
-  </si>
-  <si>
     <t>Vue plongeante du plateau, du miroir et des placards</t>
   </si>
   <si>
-    <t>MOB-036-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue de profil de la petite table fermée</t>
   </si>
   <si>
-    <t>MOB-036-02.jpeg</t>
-  </si>
-  <si>
     <t>Vue plongeante des deux panneaux fermés</t>
   </si>
   <si>
-    <t>MOB-036-03.jpeg</t>
-  </si>
-  <si>
     <t>Vue de la table déployée et du logement central</t>
   </si>
   <si>
-    <t>MOB-037-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue frontale de l’applique florale</t>
   </si>
   <si>
-    <t>MOB-037-02.jpeg</t>
-  </si>
-  <si>
     <t>Vue de profil de la branche fleurie et de la bougie</t>
   </si>
   <si>
-    <t>MOB-038-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du miroir, de la tablette et du porte-serviette</t>
   </si>
   <si>
-    <t>MOB-038-02.jpeg</t>
-  </si>
-  <si>
     <t>Détail d’une monture d’angle et du porte-serviette</t>
   </si>
   <si>
-    <t>MOB-039-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale des ornements floraux et fruitiers démontés</t>
   </si>
   <si>
-    <t>MOB-040-01.jpeg</t>
-  </si>
-  <si>
     <t>Détail du cartouche marqueté de nacre</t>
   </si>
   <si>
-    <t>MOB-040-02.jpeg</t>
-  </si>
-  <si>
     <t>Détail de la serrure et de sa plaque</t>
   </si>
   <si>
-    <t>MOB-040-03.jpeg</t>
-  </si>
-  <si>
     <t>Détail de la frise supérieure marquetée</t>
   </si>
   <si>
-    <t>MOB-040-04.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de la grande armoire</t>
   </si>
   <si>
-    <t>MOB-041-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale du meuble-classeur</t>
   </si>
   <si>
-    <t>MOB-041-02.jpeg</t>
-  </si>
-  <si>
     <t>Détail des porte-étiquettes et des languettes</t>
   </si>
   <si>
-    <t>MOB-041-03.jpeg</t>
-  </si>
-  <si>
     <t>Vue d’un abattant ouvert et des casiers</t>
   </si>
   <si>
-    <t>MOB-042-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de la bibliothèque-vitrine large, avec la vitrine étroite à droite</t>
   </si>
   <si>
-    <t>MOB-042-02.jpeg</t>
-  </si>
-  <si>
     <t>Détail des poignées des portes vitrées</t>
   </si>
   <si>
-    <t>MOB-042-03.jpeg</t>
-  </si>
-  <si>
     <t>Détail d’une poignée de tiroir</t>
   </si>
   <si>
-    <t>MOB-043-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue générale de la vitrine étroite à droite de la bibliothèque coordonnée</t>
   </si>
   <si>
-    <t>MOB-044-01.jpeg</t>
-  </si>
-  <si>
     <t>Vue frontale de la paire d’enceintes JVC</t>
   </si>
   <si>
-    <t>MOB-044-02.jpeg</t>
-  </si>
-  <si>
     <t>Vue plongeante des coffrets</t>
   </si>
   <si>
-    <t>MOB-044-03.jpeg</t>
-  </si>
-  <si>
     <t>Vue arrière, borniers et plaques signalétiques</t>
   </si>
   <si>
-    <t>MOB-046-01.jpeg</t>
-  </si>
-  <si>
     <t>Encoignure à une porte — vue 2</t>
   </si>
   <si>
-    <t>MOB-046-02.jpeg</t>
-  </si>
-  <si>
     <t>Encoignure à une porte — vue 1</t>
   </si>
   <si>
-    <t>MOB-047-01.jpeg</t>
-  </si>
-  <si>
     <t>Suspension à grand abat-jour textile fleuri — vue 1</t>
   </si>
   <si>
-    <t>MOB-047-02.jpeg</t>
-  </si>
-  <si>
     <t>Suspension à grand abat-jour textile fleuri — vue 2</t>
   </si>
   <si>
-    <t>MOB-048-01.jpeg</t>
-  </si>
-  <si>
     <t>Suspension à vasque en verre opalin bleu pâle — vue 1</t>
   </si>
   <si>
-    <t>MOB-049-01.jpeg</t>
-  </si>
-  <si>
     <t>Applique à deux lumières aux feuilles d'acanthe — vue 1</t>
   </si>
   <si>
-    <t>MOB-049-02.jpeg</t>
-  </si>
-  <si>
     <t>Applique à deux lumières aux feuilles d'acanthe — vue 2</t>
   </si>
   <si>
-    <t>MOB-049-03.jpeg</t>
-  </si>
-  <si>
     <t>Applique à deux lumières aux feuilles d'acanthe — vue 3</t>
   </si>
   <si>
-    <t>MOB-049-04.jpeg</t>
-  </si>
-  <si>
     <t>Applique à deux lumières aux feuilles d'acanthe — vue 4</t>
   </si>
   <si>
-    <t>MOB-049-05.jpeg</t>
-  </si>
-  <si>
     <t>Applique à deux lumières aux feuilles d'acanthe — vue 5</t>
   </si>
   <si>
-    <t>MOB-050-01.jpeg</t>
-  </si>
-  <si>
     <t>Lustre à pendeloques de verre — vue 1</t>
   </si>
   <si>
-    <t>MOB-050-02.jpeg</t>
-  </si>
-  <si>
     <t>Lustre à pendeloques de verre — vue 2</t>
   </si>
   <si>
-    <t>MOB-051-01.jpeg</t>
-  </si>
-  <si>
     <t>Applique à deux lumières au motif de fleur de lys — vue 1</t>
   </si>
   <si>
-    <t>MOB-052-01.jpeg</t>
-  </si>
-  <si>
     <t>Suspension à vasque festonnée jaune pâle — vue 1</t>
   </si>
   <si>
-    <t>MOB-052-02.jpeg</t>
-  </si>
-  <si>
     <t>Suspension à vasque festonnée jaune pâle — vue 2</t>
   </si>
   <si>
-    <t>MOB-053-01.jpeg</t>
-  </si>
-  <si>
     <t>Coffre en bois à façade panneautée — vue 1</t>
   </si>
   <si>
-    <t>MOB-053-02.jpeg</t>
-  </si>
-  <si>
     <t>Coffre en bois à façade panneautée — vue 2</t>
   </si>
   <si>
-    <t>MOB-054-01.jpeg</t>
-  </si>
-  <si>
     <t>Meuble de toilette à dessus de marbre et miroir triptyque — vue 1</t>
   </si>
   <si>
-    <t>MOB-054-02.jpeg</t>
-  </si>
-  <si>
     <t>Meuble de toilette à dessus de marbre et miroir triptyque — vue 2</t>
   </si>
   <si>
-    <t>MOB-054-03.jpeg</t>
-  </si>
-  <si>
     <t>Meuble de toilette à dessus de marbre et miroir triptyque — vue 3</t>
   </si>
   <si>
-    <t>MOB-055-01.jpeg</t>
-  </si>
-  <si>
     <t>Petite table noire à piètement cannelé — vue 1</t>
   </si>
   <si>
-    <t>MOB-055-02.jpeg</t>
-  </si>
-  <si>
     <t>Petite table noire à piètement cannelé — vue 2</t>
   </si>
   <si>
-    <t>MOB-056-01.jpeg</t>
-  </si>
-  <si>
     <t>Chaise en bois courbé et cannage — vue 1</t>
   </si>
   <si>
-    <t>MOB-056-02.jpeg</t>
-  </si>
-  <si>
     <t>Chaise en bois courbé et cannage — vue 2</t>
   </si>
   <si>
-    <t>MOB-056-03.jpeg</t>
-  </si>
-  <si>
     <t>Chaise en bois courbé et cannage — vue 3</t>
   </si>
   <si>
-    <t>MOB-056-04.jpeg</t>
-  </si>
-  <si>
     <t>Chaise en bois courbé et cannage — vue 4</t>
   </si>
   <si>
-    <t>MOB-057-01.jpeg</t>
-  </si>
-  <si>
     <t>Tabouret de piano pivotant — vue 1</t>
   </si>
   <si>
-    <t>MOB-057-02.jpeg</t>
-  </si>
-  <si>
     <t>Tabouret de piano pivotant — vue 2</t>
   </si>
   <si>
-    <t>MOB-058-01.jpeg</t>
-  </si>
-  <si>
     <t>Chaise à dossier sculpté et garniture jaune — vue 1</t>
   </si>
   <si>
-    <t>MOB-058-02.jpeg</t>
-  </si>
-  <si>
     <t>Chaise à dossier sculpté et garniture jaune — vue 2</t>
   </si>
   <si>
-    <t>MOB-059-01.jpeg</t>
-  </si>
-  <si>
     <t>Petit meuble haut à deux portes et un tiroir — vue 1</t>
   </si>
   <si>
-    <t>MOB-059-02.jpeg</t>
-  </si>
-  <si>
     <t>Petit meuble haut à deux portes et un tiroir — vue 2</t>
   </si>
   <si>
-    <t>MOB-060-01.jpeg</t>
-  </si>
-  <si>
     <t>Table rectangulaire à quatre pieds tournés — vue 1</t>
   </si>
   <si>
-    <t>MOB-060-02.jpeg</t>
-  </si>
-  <si>
     <t>Table rectangulaire à quatre pieds tournés — vue 2</t>
   </si>
   <si>
-    <t>MOB-060-03.jpeg</t>
-  </si>
-  <si>
     <t>Table rectangulaire à quatre pieds tournés — vue 3</t>
   </si>
   <si>
-    <t>MOB-061-01.jpeg</t>
-  </si>
-  <si>
     <t>Machine à expresso à levier Riviera Espresso — vue 1</t>
   </si>
   <si>
-    <t>MOB-061-02.jpeg</t>
-  </si>
-  <si>
     <t>Machine à expresso à levier Riviera Espresso — vue 2</t>
   </si>
   <si>
-    <t>MOB-061-03.jpeg</t>
-  </si>
-  <si>
     <t>Machine à expresso à levier Riviera Espresso — vue 3</t>
   </si>
   <si>
-    <t>MOB-061-04.jpeg</t>
-  </si>
-  <si>
     <t>Machine à expresso à levier Riviera Espresso — vue 4</t>
   </si>
   <si>
-    <t>MOB-062-01.jpeg</t>
-  </si>
-  <si>
     <t>Lampe de bureau Art déco avec pendulette — vue 1</t>
   </si>
   <si>
-    <t>MOB-062-02.jpeg</t>
-  </si>
-  <si>
     <t>Lampe de bureau Art déco avec pendulette — vue 2</t>
   </si>
   <si>
-    <t>MOB-062-03.jpeg</t>
-  </si>
-  <si>
     <t>Lampe de bureau Art déco avec pendulette — vue 3</t>
   </si>
   <si>
-    <t>MOB-063-01.jpeg</t>
-  </si>
-  <si>
     <t>Suspension en verre moulé plissé — vue 1</t>
   </si>
   <si>
-    <t>MOB-064-01.jpeg</t>
-  </si>
-  <si>
     <t>Suspension en verre opalin à décor floral orangé — vue 1</t>
   </si>
   <si>
-    <t>MOB-064-02.jpeg</t>
-  </si>
-  <si>
     <t>Suspension en verre opalin à décor floral orangé — vue 2</t>
   </si>
   <si>
-    <t>MOB-065-01.jpeg</t>
-  </si>
-  <si>
     <t>Porte-manteau mural à deux crochets grotesques — vue 1</t>
   </si>
   <si>
-    <t>MOB-065-02.jpeg</t>
-  </si>
-  <si>
     <t>Porte-manteau mural à deux crochets grotesques — vue 2</t>
   </si>
   <si>
-    <t>MOB-066-01.jpeg</t>
-  </si>
-  <si>
     <t>Lustre floral en métal peint à deux lumières — vue 1</t>
   </si>
   <si>
-    <t>MOB-066-02.jpeg</t>
-  </si>
-  <si>
     <t>Lustre floral en métal peint à deux lumières — vue 2</t>
   </si>
   <si>
-    <t>MOB-067-01.jpeg</t>
-  </si>
-  <si>
     <t>Petit meuble mural à porte vitrée verte — vue 1</t>
   </si>
   <si>
-    <t>MOB-067-02.jpeg</t>
-  </si>
-  <si>
     <t>Petit meuble mural à porte vitrée verte — vue 2</t>
   </si>
   <si>
-    <t>MOB-068-01.jpeg</t>
-  </si>
-  <si>
     <t>Meuble bas à huit tiroirs — vue 1</t>
   </si>
   <si>
-    <t>MOB-068-02.jpeg</t>
-  </si>
-  <si>
     <t>Meuble bas à huit tiroirs — vue 2</t>
   </si>
   <si>
-    <t>MOB-069-01.jpeg</t>
-  </si>
-  <si>
     <t>Horloge-calendrier avec thermomètre et sonnerie — vue 1</t>
   </si>
   <si>
-    <t>MOB-069-02.jpeg</t>
-  </si>
-  <si>
     <t>Horloge-calendrier avec thermomètre et sonnerie — vue 2</t>
   </si>
   <si>
-    <t>MOB-069-03.jpeg</t>
-  </si>
-  <si>
     <t>Horloge-calendrier avec thermomètre et sonnerie — vue 3</t>
   </si>
   <si>
-    <t>MOB-069-04.jpeg</t>
-  </si>
-  <si>
     <t>Horloge-calendrier avec thermomètre et sonnerie — vue 4</t>
   </si>
   <si>
-    <t>MOB-070-01.jpeg</t>
-  </si>
-  <si>
     <t>Lustre feuillagé en métal doré — vue 1</t>
   </si>
   <si>
-    <t>MOB-071-01.jpeg</t>
-  </si>
-  <si>
     <t>Étagère de salle de bains en verre et métal — vue 1</t>
   </si>
   <si>
-    <t>MOB-072-01.jpeg</t>
-  </si>
-  <si>
     <t>Harmonium à deux claviers Ph. J. Trayser &amp; Cie — vue 1</t>
   </si>
   <si>
-    <t>MOB-072-02.jpeg</t>
-  </si>
-  <si>
     <t>Harmonium à deux claviers Ph. J. Trayser &amp; Cie — vue 2</t>
   </si>
   <si>
-    <t>MOB-072-03.jpeg</t>
-  </si>
-  <si>
     <t>Harmonium à deux claviers Ph. J. Trayser &amp; Cie — vue 3</t>
   </si>
   <si>
-    <t>MOB-072-04.jpeg</t>
-  </si>
-  <si>
     <t>Harmonium à deux claviers Ph. J. Trayser &amp; Cie — vue 4</t>
   </si>
   <si>
-    <t>MOB-072-05.jpeg</t>
-  </si>
-  <si>
     <t>Harmonium à deux claviers Ph. J. Trayser &amp; Cie — vue 5</t>
   </si>
   <si>
-    <t>MOB-073-01.jpeg</t>
-  </si>
-  <si>
     <t>Commode sombre à quatre tiroirs — vue 1</t>
   </si>
   <si>
-    <t>MOB-074-01.jpeg</t>
-  </si>
-  <si>
     <t>Meuble haut à une porte et un tiroir — vue 1</t>
   </si>
   <si>
-    <t>MOB-075-01.jpeg</t>
-  </si>
-  <si>
     <t>Armoire à deux portes panneautées — vue 1</t>
   </si>
   <si>
-    <t>MOB-076-01.jpeg</t>
-  </si>
-  <si>
     <t>Lit double en métal à médaillons ovales — vue 1</t>
   </si>
   <si>
-    <t>MOB-077-01.jpeg</t>
-  </si>
-  <si>
     <t>Table de chevet à trois tiroirs — vue 1</t>
   </si>
   <si>
-    <t>MOB-078-01.jpeg</t>
-  </si>
-  <si>
     <t>Buffet bas à deux portes et deux tiroirs — vue 1</t>
   </si>
   <si>
-    <t>MOB-079-01.jpeg</t>
-  </si>
-  <si>
     <t>Meuble de toilette à miroir et plateau de marbre — vue 1</t>
   </si>
   <si>
-    <t>MOB-080-01.jpeg</t>
-  </si>
-  <si>
     <t>Grand miroir doré de style rocaille — vue 1</t>
   </si>
   <si>
-    <t>MOB-081-01.jpeg</t>
-  </si>
-  <si>
     <t>Fauteuil à dossier cintré et garniture noire — vue 1</t>
   </si>
   <si>
-    <t>MOB-082-01.jpeg</t>
-  </si>
-  <si>
     <t>Lampe de table en métal patiné — vue 1</t>
   </si>
   <si>
-    <t>MOB-082-02.jpeg</t>
-  </si>
-  <si>
     <t>Lampe de table en métal patiné — vue 2</t>
   </si>
   <si>
-    <t>MOB-083-01.jpeg</t>
-  </si>
-  <si>
     <t>Grand plateau de service vitré — vue 1</t>
   </si>
   <si>
-    <t>MOB-083-02.jpeg</t>
-  </si>
-  <si>
     <t>Grand plateau de service vitré — vue 2</t>
   </si>
   <si>
-    <t>MOB-084-01.jpeg</t>
-  </si>
-  <si>
     <t>Ménagère de couverts à manches clairs en coffret — vue 1</t>
   </si>
   <si>
-    <t>MOB-084-02.jpeg</t>
-  </si>
-  <si>
     <t>Ménagère de couverts à manches clairs en coffret — vue 2</t>
   </si>
   <si>
-    <t>MOB-084-03.jpeg</t>
-  </si>
-  <si>
     <t>Ménagère de couverts à manches clairs en coffret — vue 3</t>
   </si>
   <si>
@@ -3705,9 +3153,6 @@
     <t>Afrique</t>
   </si>
   <si>
-    <t>MOB-099-01.jpeg</t>
-  </si>
-  <si>
     <t>À relever</t>
   </si>
   <si>
@@ -3759,124 +3204,673 @@
     <t>France ou Italie</t>
   </si>
   <si>
-    <t>MOB-085-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-085-02.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-085-03.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-085-04.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-086-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-086-02.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-086-03.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-087-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-087-02.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-087-03.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-087-04.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-087-05.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-087-06.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-087-07.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-088-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-088-02.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-088-03.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-089-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-090-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-090-02.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-091-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-091-02.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-092-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-092-02.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-092-03.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-093-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-093-02.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-094-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-095-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-096-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-097-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-098-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-098-02.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-100-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-101-01.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-101-02.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-101-03.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-101-04.jpeg</t>
-  </si>
-  <si>
-    <t>MOB-102-01.jpeg</t>
-  </si>
-  <si>
     <t>/</t>
+  </si>
+  <si>
+    <t>MOB-001-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-001-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-001-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-002-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-002-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-002-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-003-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-004-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-004-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-004-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-005-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-005-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-005-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-045-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-045-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-006-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-006-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-007-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-007-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-007-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-007-04.webp</t>
+  </si>
+  <si>
+    <t>MOB-008-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-009-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-009-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-009-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-009-04.webp</t>
+  </si>
+  <si>
+    <t>MOB-010-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-010-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-010-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-011-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-011-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-011-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-012-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-012-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-012-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-012-04.webp</t>
+  </si>
+  <si>
+    <t>MOB-012-05.webp</t>
+  </si>
+  <si>
+    <t>MOB-012-06.webp</t>
+  </si>
+  <si>
+    <t>MOB-013-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-014-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-015-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-016-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-017-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-017-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-018-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-018-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-018-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-019-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-019-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-019-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-020-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-020-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-021-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-022-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-023-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-023-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-024-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-008-05.webp</t>
+  </si>
+  <si>
+    <t>MOB-008-06.webp</t>
+  </si>
+  <si>
+    <t>MOB-008-07.webp</t>
+  </si>
+  <si>
+    <t>MOB-025-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-026-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-026-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-027-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-027-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-028-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-029-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-029-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-030-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-030-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-031-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-032-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-032-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-033-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-033-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-034-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-035-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-035-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-036-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-036-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-036-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-037-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-037-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-038-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-038-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-039-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-040-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-040-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-040-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-040-04.webp</t>
+  </si>
+  <si>
+    <t>MOB-041-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-041-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-041-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-042-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-042-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-042-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-043-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-044-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-044-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-044-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-046-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-046-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-047-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-047-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-048-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-049-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-049-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-049-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-049-04.webp</t>
+  </si>
+  <si>
+    <t>MOB-049-05.webp</t>
+  </si>
+  <si>
+    <t>MOB-050-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-050-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-051-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-052-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-052-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-053-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-053-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-054-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-054-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-054-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-055-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-055-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-056-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-056-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-056-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-056-04.webp</t>
+  </si>
+  <si>
+    <t>MOB-057-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-057-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-058-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-058-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-059-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-059-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-060-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-060-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-060-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-061-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-061-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-061-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-061-04.webp</t>
+  </si>
+  <si>
+    <t>MOB-062-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-062-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-062-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-063-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-064-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-064-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-065-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-065-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-066-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-066-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-067-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-067-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-068-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-068-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-069-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-069-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-069-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-069-04.webp</t>
+  </si>
+  <si>
+    <t>MOB-070-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-071-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-072-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-072-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-072-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-072-04.webp</t>
+  </si>
+  <si>
+    <t>MOB-072-05.webp</t>
+  </si>
+  <si>
+    <t>MOB-073-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-074-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-075-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-076-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-077-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-078-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-079-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-080-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-081-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-082-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-082-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-083-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-083-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-084-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-084-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-084-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-085-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-085-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-085-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-085-04.webp</t>
+  </si>
+  <si>
+    <t>MOB-086-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-086-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-086-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-087-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-087-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-087-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-087-04.webp</t>
+  </si>
+  <si>
+    <t>MOB-087-05.webp</t>
+  </si>
+  <si>
+    <t>MOB-087-06.webp</t>
+  </si>
+  <si>
+    <t>MOB-087-07.webp</t>
+  </si>
+  <si>
+    <t>MOB-088-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-088-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-088-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-089-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-090-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-090-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-091-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-091-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-092-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-092-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-092-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-093-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-093-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-094-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-095-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-096-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-097-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-098-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-098-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-099-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-100-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-101-01.webp</t>
+  </si>
+  <si>
+    <t>MOB-101-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-101-03.webp</t>
+  </si>
+  <si>
+    <t>MOB-101-04.webp</t>
+  </si>
+  <si>
+    <t>MOB-102-01.webp</t>
+  </si>
+  <si>
+    <t>Vue frontale de la chaise haute</t>
+  </si>
+  <si>
+    <t>Vue de trois-quarts de la chaise haute</t>
   </si>
 </sst>
 </file>
@@ -4610,8 +4604,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PhotosTable" displayName="PhotosTable" ref="A3:E104" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A3:E104" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PhotosTable" displayName="PhotosTable" ref="A3:E103" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A3:E103" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Identifiant objet" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fichier" dataDxfId="3"/>
@@ -5028,7 +5022,7 @@
         <v>38</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1234</v>
+        <v>1049</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>39</v>
@@ -5291,7 +5285,7 @@
         <v>86</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>1216</v>
+        <v>1032</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>87</v>
@@ -5353,7 +5347,7 @@
         <v>96</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>1235</v>
+        <v>1050</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>52</v>
@@ -5418,7 +5412,7 @@
         <v>106</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1236</v>
+        <v>1051</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>52</v>
@@ -5548,7 +5542,7 @@
         <v>126</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1233</v>
+        <v>1048</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>198</v>
@@ -5678,7 +5672,7 @@
         <v>146</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1232</v>
+        <v>1047</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>198</v>
@@ -5813,7 +5807,7 @@
         <v>167</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1215</v>
+        <v>1031</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>168</v>
@@ -6463,7 +6457,7 @@
         <v>267</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1215</v>
+        <v>1031</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>268</v>
@@ -6593,13 +6587,13 @@
         <v>289</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1217</v>
+        <v>1033</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>127</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>1240</v>
+        <v>1055</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>290</v>
@@ -6785,7 +6779,7 @@
         <v>318</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>1213</v>
+        <v>1029</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>319</v>
@@ -7370,7 +7364,7 @@
         <v>410</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>1230</v>
+        <v>1045</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>309</v>
@@ -7500,7 +7494,7 @@
         <v>155</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>1231</v>
+        <v>1046</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>198</v>
@@ -8088,7 +8082,7 @@
         <v>503</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>1239</v>
+        <v>1054</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>504</v>
@@ -8445,7 +8439,7 @@
         <v>542</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>1218</v>
+        <v>1034</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>319</v>
@@ -8460,7 +8454,7 @@
         <v>544</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>1219</v>
+        <v>1035</v>
       </c>
       <c r="H58" s="12" t="s">
         <v>484</v>
@@ -8484,7 +8478,7 @@
         <v>34</v>
       </c>
       <c r="O58" s="12" t="s">
-        <v>1220</v>
+        <v>1036</v>
       </c>
       <c r="P58" s="12"/>
       <c r="Q58" s="12"/>
@@ -8515,7 +8509,7 @@
         <v>503</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>1238</v>
+        <v>1053</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>548</v>
@@ -8814,7 +8808,7 @@
         <v>580</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>1214</v>
+        <v>1030</v>
       </c>
       <c r="D64" s="12" t="s">
         <v>581</v>
@@ -8872,7 +8866,7 @@
         <v>586</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>1229</v>
+        <v>1044</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>587</v>
@@ -9058,7 +9052,7 @@
         <v>607</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>1215</v>
+        <v>1031</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>568</v>
@@ -9424,7 +9418,7 @@
         <v>648</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>1215</v>
+        <v>1031</v>
       </c>
       <c r="D74" s="12" t="s">
         <v>510</v>
@@ -9634,7 +9628,7 @@
         <v>220</v>
       </c>
       <c r="L77" s="12" t="s">
-        <v>1221</v>
+        <v>1037</v>
       </c>
       <c r="M77" s="5" t="s">
         <v>33</v>
@@ -9695,7 +9689,7 @@
         <v>450</v>
       </c>
       <c r="L78" s="12" t="s">
-        <v>1221</v>
+        <v>1037</v>
       </c>
       <c r="M78" s="5" t="s">
         <v>33</v>
@@ -9758,7 +9752,7 @@
         <v>500</v>
       </c>
       <c r="L79" s="12" t="s">
-        <v>1221</v>
+        <v>1037</v>
       </c>
       <c r="M79" s="5" t="s">
         <v>33</v>
@@ -10229,7 +10223,7 @@
         <v>554</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>1237</v>
+        <v>1052</v>
       </c>
       <c r="F87" s="12" t="s">
         <v>742</v>
@@ -10238,7 +10232,7 @@
         <v>743</v>
       </c>
       <c r="H87" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I87" s="12" t="s">
         <v>744</v>
@@ -10290,7 +10284,7 @@
         <v>748</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>1280</v>
+        <v>1056</v>
       </c>
       <c r="F88" s="14" t="s">
         <v>749</v>
@@ -10299,7 +10293,7 @@
         <v>750</v>
       </c>
       <c r="H88" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I88" s="14" t="s">
         <v>751</v>
@@ -10356,7 +10350,7 @@
         <v>755</v>
       </c>
       <c r="H89" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I89" s="14" t="s">
         <v>756</v>
@@ -10395,7 +10389,7 @@
         <v>757</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>1227</v>
+        <v>1042</v>
       </c>
       <c r="C90" s="9" t="s">
         <v>198</v>
@@ -10404,7 +10398,7 @@
         <v>758</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>1280</v>
+        <v>1056</v>
       </c>
       <c r="F90" s="14" t="s">
         <v>759</v>
@@ -10413,7 +10407,7 @@
         <v>760</v>
       </c>
       <c r="H90" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I90" s="14" t="s">
         <v>761</v>
@@ -10452,7 +10446,7 @@
         <v>762</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>1226</v>
+        <v>1041</v>
       </c>
       <c r="C91" s="9" t="s">
         <v>198</v>
@@ -10461,7 +10455,7 @@
         <v>763</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>1280</v>
+        <v>1056</v>
       </c>
       <c r="F91" s="14" t="s">
         <v>764</v>
@@ -10470,7 +10464,7 @@
         <v>765</v>
       </c>
       <c r="H91" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I91" s="14" t="s">
         <v>766</v>
@@ -10509,7 +10503,7 @@
         <v>767</v>
       </c>
       <c r="B92" s="14" t="s">
-        <v>1225</v>
+        <v>1040</v>
       </c>
       <c r="C92" s="12" t="s">
         <v>768</v>
@@ -10527,7 +10521,7 @@
         <v>770</v>
       </c>
       <c r="H92" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I92" s="14" t="s">
         <v>771</v>
@@ -10584,7 +10578,7 @@
         <v>776</v>
       </c>
       <c r="H93" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I93" s="14" t="s">
         <v>777</v>
@@ -10641,7 +10635,7 @@
         <v>781</v>
       </c>
       <c r="H94" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I94" s="14" t="s">
         <v>782</v>
@@ -10698,7 +10692,7 @@
         <v>786</v>
       </c>
       <c r="H95" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I95" s="14" t="s">
         <v>777</v>
@@ -10755,7 +10749,7 @@
         <v>790</v>
       </c>
       <c r="H96" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I96" s="14" t="s">
         <v>777</v>
@@ -10812,7 +10806,7 @@
         <v>794</v>
       </c>
       <c r="H97" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I97" s="14" t="s">
         <v>795</v>
@@ -10869,7 +10863,7 @@
         <v>799</v>
       </c>
       <c r="H98" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I98" s="14" t="s">
         <v>800</v>
@@ -10917,7 +10911,7 @@
         <v>188</v>
       </c>
       <c r="E99" s="14" t="s">
-        <v>1222</v>
+        <v>1038</v>
       </c>
       <c r="F99" s="14" t="s">
         <v>804</v>
@@ -10926,7 +10920,7 @@
         <v>805</v>
       </c>
       <c r="H99" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I99" s="14" t="s">
         <v>777</v>
@@ -10974,7 +10968,7 @@
         <v>188</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>1222</v>
+        <v>1038</v>
       </c>
       <c r="F100" s="14" t="s">
         <v>808</v>
@@ -10983,7 +10977,7 @@
         <v>809</v>
       </c>
       <c r="H100" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I100" s="14" t="s">
         <v>810</v>
@@ -11031,7 +11025,7 @@
         <v>188</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>1222</v>
+        <v>1038</v>
       </c>
       <c r="F101" s="14" t="s">
         <v>813</v>
@@ -11040,7 +11034,7 @@
         <v>814</v>
       </c>
       <c r="H101" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I101" s="14" t="s">
         <v>777</v>
@@ -11088,7 +11082,7 @@
         <v>188</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>1222</v>
+        <v>1038</v>
       </c>
       <c r="F102" s="14" t="s">
         <v>813</v>
@@ -11097,7 +11091,7 @@
         <v>817</v>
       </c>
       <c r="H102" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I102" s="14" t="s">
         <v>777</v>
@@ -11145,7 +11139,7 @@
         <v>188</v>
       </c>
       <c r="E103" s="14" t="s">
-        <v>1222</v>
+        <v>1038</v>
       </c>
       <c r="F103" s="14" t="s">
         <v>813</v>
@@ -11154,7 +11148,7 @@
         <v>820</v>
       </c>
       <c r="H103" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I103" s="14" t="s">
         <v>777</v>
@@ -11211,7 +11205,7 @@
         <v>826</v>
       </c>
       <c r="H104" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I104" s="14" t="s">
         <v>827</v>
@@ -11250,7 +11244,7 @@
         <v>828</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>1228</v>
+        <v>1043</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>52</v>
@@ -11259,7 +11253,7 @@
         <v>489</v>
       </c>
       <c r="E105" s="14" t="s">
-        <v>1280</v>
+        <v>1056</v>
       </c>
       <c r="F105" s="14" t="s">
         <v>829</v>
@@ -11268,7 +11262,7 @@
         <v>830</v>
       </c>
       <c r="H105" s="14" t="s">
-        <v>1224</v>
+        <v>1039</v>
       </c>
       <c r="I105" s="14" t="s">
         <v>831</v>
@@ -11324,7 +11318,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E224"/>
+  <dimension ref="A1:E223"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -11374,13 +11368,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="22" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C4" s="23">
+        <v>1</v>
+      </c>
+      <c r="D4" s="22" t="s">
         <v>839</v>
-      </c>
-      <c r="C4" s="23">
-        <v>1</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>840</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>34</v>
@@ -11391,16 +11385,16 @@
         <v>23</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>841</v>
+        <v>1058</v>
       </c>
       <c r="C5" s="23">
         <v>2</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
@@ -11408,16 +11402,16 @@
         <v>23</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>844</v>
+        <v>1059</v>
       </c>
       <c r="C6" s="25">
         <v>3</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
@@ -11425,13 +11419,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>846</v>
+        <v>1060</v>
       </c>
       <c r="C7" s="26">
         <v>1</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>34</v>
@@ -11442,16 +11436,16 @@
         <v>38</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>848</v>
+        <v>1061</v>
       </c>
       <c r="C8" s="26">
         <v>2</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
@@ -11459,16 +11453,16 @@
         <v>38</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>850</v>
+        <v>1062</v>
       </c>
       <c r="C9" s="26">
         <v>3</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
@@ -11476,13 +11470,13 @@
         <v>50</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>852</v>
+        <v>1063</v>
       </c>
       <c r="C10" s="26">
         <v>1</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>853</v>
+        <v>846</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>34</v>
@@ -11493,16 +11487,16 @@
         <v>62</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>854</v>
+        <v>1064</v>
       </c>
       <c r="C11" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
@@ -11510,16 +11504,16 @@
         <v>62</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>856</v>
+        <v>1065</v>
       </c>
       <c r="C12" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>857</v>
+        <v>848</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1">
@@ -11527,16 +11521,16 @@
         <v>62</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>858</v>
+        <v>1066</v>
       </c>
       <c r="C13" s="26">
         <v>3</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>859</v>
+        <v>849</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
@@ -11544,16 +11538,16 @@
         <v>73</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>860</v>
+        <v>1067</v>
       </c>
       <c r="C14" s="26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>861</v>
+        <v>850</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1">
@@ -11561,16 +11555,16 @@
         <v>73</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>862</v>
+        <v>1068</v>
       </c>
       <c r="C15" s="26">
         <v>2</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>863</v>
+        <v>851</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1">
@@ -11578,16 +11572,16 @@
         <v>73</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>864</v>
+        <v>1069</v>
       </c>
       <c r="C16" s="26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1">
@@ -11595,13 +11589,13 @@
         <v>470</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>866</v>
+        <v>1070</v>
       </c>
       <c r="C17" s="26">
         <v>1</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>867</v>
+        <v>853</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>34</v>
@@ -11612,16 +11606,16 @@
         <v>470</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>868</v>
+        <v>1071</v>
       </c>
       <c r="C18" s="26">
         <v>2</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>869</v>
+        <v>854</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1">
@@ -11629,16 +11623,16 @@
         <v>85</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>870</v>
+        <v>1072</v>
       </c>
       <c r="C19" s="26">
         <v>2</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>871</v>
+        <v>855</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1">
@@ -11646,13 +11640,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>872</v>
+        <v>1073</v>
       </c>
       <c r="C20" s="26">
         <v>1</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>873</v>
+        <v>856</v>
       </c>
       <c r="E20" s="26" t="s">
         <v>34</v>
@@ -11663,16 +11657,16 @@
         <v>96</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>874</v>
+        <v>1074</v>
       </c>
       <c r="C21" s="26">
         <v>1</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>875</v>
+        <v>857</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1">
@@ -11680,13 +11674,13 @@
         <v>96</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>876</v>
+        <v>1075</v>
       </c>
       <c r="C22" s="26">
         <v>2</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>877</v>
+        <v>858</v>
       </c>
       <c r="E22" s="26" t="s">
         <v>34</v>
@@ -11697,16 +11691,16 @@
         <v>96</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>878</v>
+        <v>1076</v>
       </c>
       <c r="C23" s="26">
         <v>3</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>879</v>
+        <v>859</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1">
@@ -11714,16 +11708,16 @@
         <v>96</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>880</v>
+        <v>1077</v>
       </c>
       <c r="C24" s="26">
         <v>4</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>881</v>
+        <v>860</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1">
@@ -11731,13 +11725,13 @@
         <v>106</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>882</v>
+        <v>1078</v>
       </c>
       <c r="C25" s="26">
         <v>1</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>883</v>
+        <v>861</v>
       </c>
       <c r="E25" s="26" t="s">
         <v>34</v>
@@ -11748,16 +11742,16 @@
         <v>114</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>884</v>
+        <v>1079</v>
       </c>
       <c r="C26" s="26">
         <v>1</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>885</v>
+        <v>862</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1">
@@ -11765,16 +11759,16 @@
         <v>114</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>886</v>
+        <v>1080</v>
       </c>
       <c r="C27" s="26">
         <v>2</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>887</v>
+        <v>863</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1">
@@ -11782,13 +11776,13 @@
         <v>114</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>888</v>
+        <v>1081</v>
       </c>
       <c r="C28" s="26">
         <v>3</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>883</v>
+        <v>861</v>
       </c>
       <c r="E28" s="26" t="s">
         <v>34</v>
@@ -11799,16 +11793,16 @@
         <v>114</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>889</v>
+        <v>1082</v>
       </c>
       <c r="C29" s="26">
         <v>4</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>890</v>
+        <v>864</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1">
@@ -11816,16 +11810,16 @@
         <v>126</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>891</v>
+        <v>1083</v>
       </c>
       <c r="C30" s="26">
         <v>1</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>892</v>
+        <v>865</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1">
@@ -11833,13 +11827,13 @@
         <v>126</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>893</v>
+        <v>1084</v>
       </c>
       <c r="C31" s="26">
         <v>2</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>894</v>
+        <v>866</v>
       </c>
       <c r="E31" s="26" t="s">
         <v>34</v>
@@ -11850,16 +11844,16 @@
         <v>126</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>895</v>
+        <v>1085</v>
       </c>
       <c r="C32" s="26">
         <v>3</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>896</v>
+        <v>867</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1">
@@ -11867,13 +11861,13 @@
         <v>136</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>897</v>
+        <v>1086</v>
       </c>
       <c r="C33" s="26">
         <v>1</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>898</v>
+        <v>868</v>
       </c>
       <c r="E33" s="26" t="s">
         <v>34</v>
@@ -11884,16 +11878,16 @@
         <v>136</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>899</v>
+        <v>1087</v>
       </c>
       <c r="C34" s="26">
         <v>2</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>900</v>
+        <v>869</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1">
@@ -11901,16 +11895,16 @@
         <v>136</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>901</v>
+        <v>1088</v>
       </c>
       <c r="C35" s="26">
         <v>3</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>902</v>
+        <v>870</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1">
@@ -11918,13 +11912,13 @@
         <v>146</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>903</v>
+        <v>1089</v>
       </c>
       <c r="C36" s="26">
         <v>1</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>904</v>
+        <v>871</v>
       </c>
       <c r="E36" s="26" t="s">
         <v>34</v>
@@ -11935,16 +11929,16 @@
         <v>146</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>905</v>
+        <v>1090</v>
       </c>
       <c r="C37" s="26">
         <v>2</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>906</v>
+        <v>872</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1">
@@ -11952,16 +11946,16 @@
         <v>146</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>907</v>
+        <v>1091</v>
       </c>
       <c r="C38" s="26">
         <v>3</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>908</v>
+        <v>873</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1">
@@ -11969,16 +11963,16 @@
         <v>146</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>909</v>
+        <v>1092</v>
       </c>
       <c r="C39" s="26">
         <v>4</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>910</v>
+        <v>874</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1">
@@ -11986,16 +11980,16 @@
         <v>146</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>911</v>
+        <v>1093</v>
       </c>
       <c r="C40" s="26">
         <v>5</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>912</v>
+        <v>875</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1">
@@ -12003,16 +11997,16 @@
         <v>146</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>913</v>
+        <v>1094</v>
       </c>
       <c r="C41" s="26">
         <v>6</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>914</v>
+        <v>876</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15" customHeight="1">
@@ -12020,13 +12014,13 @@
         <v>156</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>915</v>
+        <v>1095</v>
       </c>
       <c r="C42" s="26">
         <v>1</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>916</v>
+        <v>877</v>
       </c>
       <c r="E42" s="26" t="s">
         <v>34</v>
@@ -12037,13 +12031,13 @@
         <v>166</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>917</v>
+        <v>1096</v>
       </c>
       <c r="C43" s="26">
         <v>1</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>918</v>
+        <v>878</v>
       </c>
       <c r="E43" s="26" t="s">
         <v>34</v>
@@ -12054,13 +12048,13 @@
         <v>176</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>919</v>
+        <v>1097</v>
       </c>
       <c r="C44" s="26">
         <v>1</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>920</v>
+        <v>879</v>
       </c>
       <c r="E44" s="26" t="s">
         <v>34</v>
@@ -12071,13 +12065,13 @@
         <v>186</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>921</v>
+        <v>1098</v>
       </c>
       <c r="C45" s="26">
         <v>1</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>922</v>
+        <v>880</v>
       </c>
       <c r="E45" s="26" t="s">
         <v>34</v>
@@ -12088,13 +12082,13 @@
         <v>196</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>923</v>
+        <v>1099</v>
       </c>
       <c r="C46" s="26">
         <v>1</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>924</v>
+        <v>881</v>
       </c>
       <c r="E46" s="26" t="s">
         <v>34</v>
@@ -12105,16 +12099,16 @@
         <v>196</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>925</v>
+        <v>1100</v>
       </c>
       <c r="C47" s="26">
         <v>2</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>926</v>
+        <v>882</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" customHeight="1">
@@ -12122,16 +12116,16 @@
         <v>207</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>927</v>
+        <v>1101</v>
       </c>
       <c r="C48" s="26">
         <v>1</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>928</v>
+        <v>883</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1">
@@ -12139,16 +12133,16 @@
         <v>207</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>929</v>
+        <v>1102</v>
       </c>
       <c r="C49" s="26">
         <v>2</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>930</v>
+        <v>884</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1">
@@ -12156,30 +12150,30 @@
         <v>207</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>931</v>
+        <v>1103</v>
       </c>
       <c r="C50" s="26">
         <v>3</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>932</v>
+        <v>885</v>
       </c>
       <c r="E50" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15" customHeight="1">
       <c r="A51" s="26" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>933</v>
+        <v>1104</v>
       </c>
       <c r="C51" s="26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>934</v>
+        <v>886</v>
       </c>
       <c r="E51" s="26" t="s">
         <v>34</v>
@@ -12190,16 +12184,16 @@
         <v>216</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>935</v>
+        <v>1105</v>
       </c>
       <c r="C52" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>936</v>
+        <v>887</v>
       </c>
       <c r="E52" s="26" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15" customHeight="1">
@@ -12207,33 +12201,33 @@
         <v>216</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>937</v>
+        <v>1106</v>
       </c>
       <c r="C53" s="26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" s="26" t="s">
-        <v>938</v>
+        <v>888</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15" customHeight="1">
       <c r="A54" s="26" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>939</v>
+        <v>1107</v>
       </c>
       <c r="C54" s="26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D54" s="26" t="s">
-        <v>940</v>
+        <v>889</v>
       </c>
       <c r="E54" s="26" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15" customHeight="1">
@@ -12241,47 +12235,47 @@
         <v>226</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>941</v>
+        <v>1108</v>
       </c>
       <c r="C55" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" s="26" t="s">
-        <v>942</v>
+        <v>890</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15" customHeight="1">
       <c r="A56" s="26" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>943</v>
+        <v>1109</v>
       </c>
       <c r="C56" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>944</v>
+        <v>891</v>
       </c>
       <c r="E56" s="26" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15" customHeight="1">
       <c r="A57" s="26" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>945</v>
+        <v>1110</v>
       </c>
       <c r="C57" s="26">
         <v>1</v>
       </c>
       <c r="D57" s="26" t="s">
-        <v>946</v>
+        <v>892</v>
       </c>
       <c r="E57" s="26" t="s">
         <v>34</v>
@@ -12289,16 +12283,16 @@
     </row>
     <row r="58" spans="1:5" ht="15" customHeight="1">
       <c r="A58" s="26" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>947</v>
+        <v>1111</v>
       </c>
       <c r="C58" s="26">
         <v>1</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>948</v>
+        <v>893</v>
       </c>
       <c r="E58" s="26" t="s">
         <v>34</v>
@@ -12309,67 +12303,67 @@
         <v>255</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>949</v>
+        <v>1112</v>
       </c>
       <c r="C59" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" s="26" t="s">
-        <v>950</v>
+        <v>894</v>
       </c>
       <c r="E59" s="26" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15" customHeight="1">
       <c r="A60" s="26" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>951</v>
+        <v>1113</v>
       </c>
       <c r="C60" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" s="26" t="s">
-        <v>952</v>
+        <v>895</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="15" customHeight="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="30" customHeight="1">
       <c r="A61" s="26" t="s">
-        <v>266</v>
+        <v>106</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>953</v>
+        <v>1114</v>
       </c>
       <c r="C61" s="26">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D61" s="26" t="s">
-        <v>954</v>
+        <v>896</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="30" customHeight="1">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="15" customHeight="1">
       <c r="A62" s="26" t="s">
         <v>106</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>955</v>
+        <v>1115</v>
       </c>
       <c r="C62" s="26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>956</v>
+        <v>897</v>
       </c>
       <c r="E62" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15" customHeight="1">
@@ -12377,47 +12371,47 @@
         <v>106</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>957</v>
+        <v>1116</v>
       </c>
       <c r="C63" s="26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D63" s="26" t="s">
-        <v>958</v>
+        <v>898</v>
       </c>
       <c r="E63" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15" customHeight="1">
       <c r="A64" s="26" t="s">
-        <v>106</v>
+        <v>276</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>959</v>
+        <v>1117</v>
       </c>
       <c r="C64" s="26">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>960</v>
+        <v>899</v>
       </c>
       <c r="E64" s="26" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15" customHeight="1">
       <c r="A65" s="26" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>961</v>
+        <v>1118</v>
       </c>
       <c r="C65" s="26">
         <v>1</v>
       </c>
       <c r="D65" s="26" t="s">
-        <v>962</v>
+        <v>900</v>
       </c>
       <c r="E65" s="26" t="s">
         <v>34</v>
@@ -12428,33 +12422,33 @@
         <v>288</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>963</v>
+        <v>1119</v>
       </c>
       <c r="C66" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" s="26" t="s">
-        <v>964</v>
+        <v>901</v>
       </c>
       <c r="E66" s="26" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15" customHeight="1">
       <c r="A67" s="26" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>965</v>
+        <v>1120</v>
       </c>
       <c r="C67" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>966</v>
+        <v>902</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15" customHeight="1">
@@ -12462,30 +12456,30 @@
         <v>297</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>967</v>
+        <v>1121</v>
       </c>
       <c r="C68" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>968</v>
+        <v>903</v>
       </c>
       <c r="E68" s="26" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15" customHeight="1">
       <c r="A69" s="26" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>969</v>
+        <v>1122</v>
       </c>
       <c r="C69" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>970</v>
+        <v>904</v>
       </c>
       <c r="E69" s="26" t="s">
         <v>34</v>
@@ -12493,19 +12487,19 @@
     </row>
     <row r="70" spans="1:5" ht="15" customHeight="1">
       <c r="A70" s="26" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>971</v>
+        <v>1123</v>
       </c>
       <c r="C70" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>972</v>
+        <v>1277</v>
       </c>
       <c r="E70" s="26" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15" customHeight="1">
@@ -12513,13 +12507,13 @@
         <v>318</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>973</v>
+        <v>1124</v>
       </c>
       <c r="C71" s="26">
         <v>1</v>
       </c>
       <c r="D71" s="26" t="s">
-        <v>974</v>
+        <v>1278</v>
       </c>
       <c r="E71" s="26" t="s">
         <v>34</v>
@@ -12527,19 +12521,19 @@
     </row>
     <row r="72" spans="1:5" ht="15" customHeight="1">
       <c r="A72" s="26" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="B72" s="26" t="s">
-        <v>975</v>
+        <v>1125</v>
       </c>
       <c r="C72" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>976</v>
+        <v>905</v>
       </c>
       <c r="E72" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15" customHeight="1">
@@ -12547,30 +12541,30 @@
         <v>329</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>977</v>
+        <v>1126</v>
       </c>
       <c r="C73" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" s="26" t="s">
-        <v>978</v>
+        <v>906</v>
       </c>
       <c r="E73" s="26" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15" customHeight="1">
       <c r="A74" s="26" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>979</v>
+        <v>1127</v>
       </c>
       <c r="C74" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74" s="26" t="s">
-        <v>980</v>
+        <v>907</v>
       </c>
       <c r="E74" s="26" t="s">
         <v>34</v>
@@ -12578,16 +12572,16 @@
     </row>
     <row r="75" spans="1:5" ht="15" customHeight="1">
       <c r="A75" s="26" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>981</v>
+        <v>1128</v>
       </c>
       <c r="C75" s="26">
         <v>1</v>
       </c>
       <c r="D75" s="26" t="s">
-        <v>982</v>
+        <v>908</v>
       </c>
       <c r="E75" s="26" t="s">
         <v>34</v>
@@ -12598,33 +12592,33 @@
         <v>350</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>983</v>
+        <v>1129</v>
       </c>
       <c r="C76" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" s="26" t="s">
-        <v>984</v>
+        <v>909</v>
       </c>
       <c r="E76" s="26" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15" customHeight="1">
       <c r="A77" s="26" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>985</v>
+        <v>1130</v>
       </c>
       <c r="C77" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D77" s="26" t="s">
-        <v>986</v>
+        <v>910</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15" customHeight="1">
@@ -12632,49 +12626,49 @@
         <v>362</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>987</v>
+        <v>1131</v>
       </c>
       <c r="C78" s="26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" s="26" t="s">
-        <v>988</v>
+        <v>911</v>
       </c>
       <c r="E78" s="26" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="15" customHeight="1">
       <c r="A79" s="26" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>989</v>
+        <v>1132</v>
       </c>
       <c r="C79" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" s="26" t="s">
-        <v>990</v>
+        <v>912</v>
       </c>
       <c r="E79" s="26" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="15" customHeight="1">
-      <c r="A80" s="26" t="s">
-        <v>371</v>
-      </c>
-      <c r="B80" s="26" t="s">
-        <v>991</v>
-      </c>
-      <c r="C80" s="26">
-        <v>1</v>
-      </c>
-      <c r="D80" s="26" t="s">
-        <v>992</v>
-      </c>
-      <c r="E80" s="26" t="s">
+    <row r="80" spans="1:5">
+      <c r="A80" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C80" s="3">
+        <v>1</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>34</v>
       </c>
     </row>
@@ -12683,33 +12677,33 @@
         <v>380</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>993</v>
+        <v>1134</v>
       </c>
       <c r="C81" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>994</v>
+        <v>914</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="3" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>995</v>
+        <v>1135</v>
       </c>
       <c r="C82" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>996</v>
+        <v>915</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -12717,16 +12711,16 @@
         <v>391</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>997</v>
+        <v>1136</v>
       </c>
       <c r="C83" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>998</v>
+        <v>916</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -12734,33 +12728,33 @@
         <v>391</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>999</v>
+        <v>1137</v>
       </c>
       <c r="C84" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>1000</v>
+        <v>917</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="3" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1001</v>
+        <v>1138</v>
       </c>
       <c r="C85" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>1002</v>
+        <v>918</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -12768,33 +12762,33 @@
         <v>400</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>1003</v>
+        <v>1139</v>
       </c>
       <c r="C86" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>1004</v>
+        <v>919</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="3" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1005</v>
+        <v>1140</v>
       </c>
       <c r="C87" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>1006</v>
+        <v>920</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -12802,50 +12796,50 @@
         <v>410</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>1007</v>
+        <v>1141</v>
       </c>
       <c r="C88" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>1008</v>
+        <v>921</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="3" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1009</v>
+        <v>1142</v>
       </c>
       <c r="C89" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>1010</v>
+        <v>922</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="3" t="s">
-        <v>419</v>
+        <v>155</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>1011</v>
+        <v>1143</v>
       </c>
       <c r="C90" s="3">
         <v>1</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>1012</v>
+        <v>923</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -12853,16 +12847,16 @@
         <v>155</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>1013</v>
+        <v>1144</v>
       </c>
       <c r="C91" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>1014</v>
+        <v>924</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -12870,16 +12864,16 @@
         <v>155</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1015</v>
+        <v>1145</v>
       </c>
       <c r="C92" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>1016</v>
+        <v>925</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -12887,33 +12881,33 @@
         <v>155</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>1017</v>
+        <v>1146</v>
       </c>
       <c r="C93" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>1018</v>
+        <v>926</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="3" t="s">
-        <v>155</v>
+        <v>435</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>1019</v>
+        <v>1147</v>
       </c>
       <c r="C94" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>1020</v>
+        <v>927</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -12921,16 +12915,16 @@
         <v>435</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>1021</v>
+        <v>1148</v>
       </c>
       <c r="C95" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>1022</v>
+        <v>928</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -12938,33 +12932,33 @@
         <v>435</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>1023</v>
+        <v>1149</v>
       </c>
       <c r="C96" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>1024</v>
+        <v>929</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="3" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>1025</v>
+        <v>1150</v>
       </c>
       <c r="C97" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>1026</v>
+        <v>930</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -12972,16 +12966,16 @@
         <v>444</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>1027</v>
+        <v>1151</v>
       </c>
       <c r="C98" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>1028</v>
+        <v>931</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -12989,47 +12983,47 @@
         <v>444</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>1029</v>
+        <v>1152</v>
       </c>
       <c r="C99" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>1030</v>
+        <v>932</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="3" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>1031</v>
+        <v>1153</v>
       </c>
       <c r="C100" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>1032</v>
+        <v>933</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="3" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>1033</v>
+        <v>1154</v>
       </c>
       <c r="C101" s="3">
         <v>1</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>1034</v>
+        <v>934</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>34</v>
@@ -13040,16 +13034,16 @@
         <v>460</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>1035</v>
+        <v>1155</v>
       </c>
       <c r="C102" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>1036</v>
+        <v>935</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -13057,33 +13051,33 @@
         <v>460</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>1037</v>
+        <v>1156</v>
       </c>
       <c r="C103" s="3">
+        <v>3</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="24" customHeight="1">
+      <c r="A104" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C104" s="2">
         <v>2</v>
       </c>
-      <c r="D103" s="3" t="s">
-        <v>1038</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C104" s="3">
-        <v>3</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>1040</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>843</v>
+      <c r="D104" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="24" customHeight="1">
@@ -13091,33 +13085,33 @@
         <v>479</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1041</v>
+        <v>1158</v>
       </c>
       <c r="C105" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>1042</v>
+        <v>938</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="24" customHeight="1">
       <c r="A106" s="2" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1043</v>
+        <v>1159</v>
       </c>
       <c r="C106" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>1044</v>
+        <v>939</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="24" customHeight="1">
@@ -13125,13 +13119,13 @@
         <v>487</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1045</v>
+        <v>1160</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>1046</v>
+        <v>940</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>34</v>
@@ -13139,33 +13133,33 @@
     </row>
     <row r="108" spans="1:5" ht="24" customHeight="1">
       <c r="A108" s="2" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1047</v>
+        <v>1161</v>
       </c>
       <c r="C108" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>1048</v>
+        <v>941</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="24" customHeight="1">
       <c r="A109" s="2" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1049</v>
+        <v>1162</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>1050</v>
+        <v>942</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>34</v>
@@ -13176,16 +13170,16 @@
         <v>501</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1051</v>
+        <v>1163</v>
       </c>
       <c r="C110" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>1052</v>
+        <v>943</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="24" customHeight="1">
@@ -13193,16 +13187,16 @@
         <v>501</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1053</v>
+        <v>1164</v>
       </c>
       <c r="C111" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>1054</v>
+        <v>944</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="24" customHeight="1">
@@ -13210,16 +13204,16 @@
         <v>501</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1055</v>
+        <v>1165</v>
       </c>
       <c r="C112" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1056</v>
+        <v>945</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="24" customHeight="1">
@@ -13227,33 +13221,33 @@
         <v>501</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1057</v>
+        <v>1166</v>
       </c>
       <c r="C113" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1058</v>
+        <v>946</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="24" customHeight="1">
       <c r="A114" s="2" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1059</v>
+        <v>1167</v>
       </c>
       <c r="C114" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1060</v>
+        <v>947</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="24" customHeight="1">
@@ -13261,47 +13255,47 @@
         <v>508</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1061</v>
+        <v>1168</v>
       </c>
       <c r="C115" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>1062</v>
+        <v>948</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="24" customHeight="1">
       <c r="A116" s="2" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1063</v>
+        <v>1169</v>
       </c>
       <c r="C116" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>1064</v>
+        <v>949</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="24" customHeight="1">
       <c r="A117" s="2" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1065</v>
+        <v>1170</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>1066</v>
+        <v>950</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>34</v>
@@ -13312,33 +13306,33 @@
         <v>522</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1067</v>
+        <v>1171</v>
       </c>
       <c r="C118" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>1068</v>
+        <v>951</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="24" customHeight="1">
       <c r="A119" s="2" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1069</v>
+        <v>1172</v>
       </c>
       <c r="C119" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1070</v>
+        <v>952</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="24" customHeight="1">
@@ -13346,33 +13340,33 @@
         <v>528</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1071</v>
+        <v>1173</v>
       </c>
       <c r="C120" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1072</v>
+        <v>953</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="24" customHeight="1">
       <c r="A121" s="2" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1073</v>
+        <v>1174</v>
       </c>
       <c r="C121" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1074</v>
+        <v>954</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="24" customHeight="1">
@@ -13380,16 +13374,16 @@
         <v>536</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1075</v>
+        <v>1175</v>
       </c>
       <c r="C122" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1076</v>
+        <v>955</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="24" customHeight="1">
@@ -13397,33 +13391,33 @@
         <v>536</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1077</v>
+        <v>1176</v>
       </c>
       <c r="C123" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1078</v>
+        <v>956</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="24" customHeight="1">
       <c r="A124" s="2" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1079</v>
+        <v>1177</v>
       </c>
       <c r="C124" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1080</v>
+        <v>957</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="24" customHeight="1">
@@ -13431,33 +13425,33 @@
         <v>542</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1081</v>
+        <v>1178</v>
       </c>
       <c r="C125" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1082</v>
+        <v>958</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="24" customHeight="1">
       <c r="A126" s="2" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1083</v>
+        <v>1179</v>
       </c>
       <c r="C126" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1084</v>
+        <v>959</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="24" customHeight="1">
@@ -13465,16 +13459,16 @@
         <v>546</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1085</v>
+        <v>1180</v>
       </c>
       <c r="C127" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1086</v>
+        <v>960</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="24" customHeight="1">
@@ -13482,16 +13476,16 @@
         <v>546</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1087</v>
+        <v>1181</v>
       </c>
       <c r="C128" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1088</v>
+        <v>961</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="24" customHeight="1">
@@ -13499,33 +13493,33 @@
         <v>546</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1089</v>
+        <v>1182</v>
       </c>
       <c r="C129" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1090</v>
+        <v>962</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="24" customHeight="1">
       <c r="A130" s="2" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1091</v>
+        <v>1183</v>
       </c>
       <c r="C130" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1092</v>
+        <v>963</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="24" customHeight="1">
@@ -13533,33 +13527,33 @@
         <v>552</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1093</v>
+        <v>1184</v>
       </c>
       <c r="C131" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1094</v>
+        <v>964</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="24" customHeight="1">
       <c r="A132" s="2" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1095</v>
+        <v>1185</v>
       </c>
       <c r="C132" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1096</v>
+        <v>965</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="24" customHeight="1">
@@ -13567,33 +13561,33 @@
         <v>559</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1097</v>
+        <v>1186</v>
       </c>
       <c r="C133" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1098</v>
+        <v>966</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="24" customHeight="1">
       <c r="A134" s="2" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1099</v>
+        <v>1187</v>
       </c>
       <c r="C134" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1100</v>
+        <v>967</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="24" customHeight="1">
@@ -13601,33 +13595,33 @@
         <v>566</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1101</v>
+        <v>1188</v>
       </c>
       <c r="C135" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1102</v>
+        <v>968</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="24" customHeight="1">
       <c r="A136" s="2" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1103</v>
+        <v>1189</v>
       </c>
       <c r="C136" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1104</v>
+        <v>969</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="24" customHeight="1">
@@ -13635,16 +13629,16 @@
         <v>573</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1105</v>
+        <v>1190</v>
       </c>
       <c r="C137" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1106</v>
+        <v>970</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="24" customHeight="1">
@@ -13652,33 +13646,33 @@
         <v>573</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1107</v>
+        <v>1191</v>
       </c>
       <c r="C138" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1108</v>
+        <v>971</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="24" customHeight="1">
       <c r="A139" s="2" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1109</v>
+        <v>1192</v>
       </c>
       <c r="C139" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>1110</v>
+        <v>972</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="24" customHeight="1">
@@ -13686,16 +13680,16 @@
         <v>579</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1111</v>
+        <v>1193</v>
       </c>
       <c r="C140" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>1112</v>
+        <v>973</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="24" customHeight="1">
@@ -13703,16 +13697,16 @@
         <v>579</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1113</v>
+        <v>1194</v>
       </c>
       <c r="C141" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>1114</v>
+        <v>974</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="24" customHeight="1">
@@ -13720,33 +13714,33 @@
         <v>579</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1115</v>
+        <v>1195</v>
       </c>
       <c r="C142" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>1116</v>
+        <v>975</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="24" customHeight="1">
       <c r="A143" s="2" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1117</v>
+        <v>1196</v>
       </c>
       <c r="C143" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>1118</v>
+        <v>976</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="24" customHeight="1">
@@ -13754,16 +13748,16 @@
         <v>586</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1119</v>
+        <v>1197</v>
       </c>
       <c r="C144" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1120</v>
+        <v>977</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="24" customHeight="1">
@@ -13771,47 +13765,47 @@
         <v>586</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1121</v>
+        <v>1198</v>
       </c>
       <c r="C145" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>1122</v>
+        <v>978</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="24" customHeight="1">
       <c r="A146" s="2" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1123</v>
+        <v>1199</v>
       </c>
       <c r="C146" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>1124</v>
+        <v>979</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="24" customHeight="1">
       <c r="A147" s="2" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1125</v>
+        <v>1200</v>
       </c>
       <c r="C147" s="2">
         <v>1</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>1126</v>
+        <v>980</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>34</v>
@@ -13822,33 +13816,33 @@
         <v>600</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1127</v>
+        <v>1201</v>
       </c>
       <c r="C148" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>1128</v>
+        <v>981</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="24" customHeight="1">
       <c r="A149" s="2" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1129</v>
+        <v>1202</v>
       </c>
       <c r="C149" s="2">
         <v>2</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>1130</v>
+        <v>983</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="24" customHeight="1">
@@ -13856,30 +13850,30 @@
         <v>606</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1131</v>
+        <v>1203</v>
       </c>
       <c r="C150" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>1134</v>
+        <v>982</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="24" customHeight="1">
       <c r="A151" s="2" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1133</v>
+        <v>1204</v>
       </c>
       <c r="C151" s="2">
         <v>1</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>1132</v>
+        <v>984</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>34</v>
@@ -13890,33 +13884,33 @@
         <v>613</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1135</v>
+        <v>1205</v>
       </c>
       <c r="C152" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>1136</v>
+        <v>985</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="24" customHeight="1">
       <c r="A153" s="2" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>1137</v>
+        <v>1206</v>
       </c>
       <c r="C153" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>1138</v>
+        <v>986</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="24" customHeight="1">
@@ -13924,33 +13918,33 @@
         <v>621</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>1139</v>
+        <v>1207</v>
       </c>
       <c r="C154" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>1140</v>
+        <v>987</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="24" customHeight="1">
       <c r="A155" s="2" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>1141</v>
+        <v>1208</v>
       </c>
       <c r="C155" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>1142</v>
+        <v>988</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="24" customHeight="1">
@@ -13958,33 +13952,33 @@
         <v>627</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>1143</v>
+        <v>1209</v>
       </c>
       <c r="C156" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>1144</v>
+        <v>989</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="24" customHeight="1">
       <c r="A157" s="2" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>1145</v>
+        <v>1210</v>
       </c>
       <c r="C157" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>1146</v>
+        <v>990</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="24" customHeight="1">
@@ -13992,16 +13986,16 @@
         <v>634</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>1147</v>
+        <v>1211</v>
       </c>
       <c r="C158" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>1148</v>
+        <v>991</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="24" customHeight="1">
@@ -14009,16 +14003,16 @@
         <v>634</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>1149</v>
+        <v>1212</v>
       </c>
       <c r="C159" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>1150</v>
+        <v>992</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="24" customHeight="1">
@@ -14026,47 +14020,47 @@
         <v>634</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>1151</v>
+        <v>1213</v>
       </c>
       <c r="C160" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>1152</v>
+        <v>993</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="24" customHeight="1">
       <c r="A161" s="2" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>1153</v>
+        <v>1214</v>
       </c>
       <c r="C161" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>1154</v>
+        <v>994</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="24" customHeight="1">
       <c r="A162" s="2" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>1155</v>
+        <v>1215</v>
       </c>
       <c r="C162" s="2">
         <v>1</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>1156</v>
+        <v>995</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>34</v>
@@ -14074,16 +14068,16 @@
     </row>
     <row r="163" spans="1:5" ht="24" customHeight="1">
       <c r="A163" s="2" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>1157</v>
+        <v>1216</v>
       </c>
       <c r="C163" s="2">
         <v>1</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>1158</v>
+        <v>996</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>34</v>
@@ -14094,16 +14088,16 @@
         <v>653</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>1159</v>
+        <v>1217</v>
       </c>
       <c r="C164" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>1160</v>
+        <v>997</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="24" customHeight="1">
@@ -14111,16 +14105,16 @@
         <v>653</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>1161</v>
+        <v>1218</v>
       </c>
       <c r="C165" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>1162</v>
+        <v>998</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="24" customHeight="1">
@@ -14128,16 +14122,16 @@
         <v>653</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>1163</v>
+        <v>1219</v>
       </c>
       <c r="C166" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>1164</v>
+        <v>999</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="24" customHeight="1">
@@ -14145,47 +14139,47 @@
         <v>653</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>1165</v>
+        <v>1220</v>
       </c>
       <c r="C167" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>1166</v>
+        <v>1000</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="24" customHeight="1">
       <c r="A168" s="2" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>1167</v>
+        <v>1221</v>
       </c>
       <c r="C168" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>1168</v>
+        <v>1001</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="24" customHeight="1">
       <c r="A169" s="2" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>1169</v>
+        <v>1222</v>
       </c>
       <c r="C169" s="2">
         <v>1</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>1170</v>
+        <v>1002</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>34</v>
@@ -14193,16 +14187,16 @@
     </row>
     <row r="170" spans="1:5" ht="24" customHeight="1">
       <c r="A170" s="2" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>1171</v>
+        <v>1223</v>
       </c>
       <c r="C170" s="2">
         <v>1</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>1172</v>
+        <v>1003</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>34</v>
@@ -14210,16 +14204,16 @@
     </row>
     <row r="171" spans="1:5" ht="24" customHeight="1">
       <c r="A171" s="2" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>1173</v>
+        <v>1224</v>
       </c>
       <c r="C171" s="2">
         <v>1</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>1174</v>
+        <v>1004</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>34</v>
@@ -14227,16 +14221,16 @@
     </row>
     <row r="172" spans="1:5" ht="24" customHeight="1">
       <c r="A172" s="2" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>1175</v>
+        <v>1225</v>
       </c>
       <c r="C172" s="2">
         <v>1</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>1176</v>
+        <v>1005</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>34</v>
@@ -14244,16 +14238,16 @@
     </row>
     <row r="173" spans="1:5" ht="24" customHeight="1">
       <c r="A173" s="2" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>1177</v>
+        <v>1226</v>
       </c>
       <c r="C173" s="2">
         <v>1</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>1178</v>
+        <v>1006</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>34</v>
@@ -14261,16 +14255,16 @@
     </row>
     <row r="174" spans="1:5" ht="24" customHeight="1">
       <c r="A174" s="2" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>1179</v>
+        <v>1227</v>
       </c>
       <c r="C174" s="2">
         <v>1</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>1180</v>
+        <v>1007</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>34</v>
@@ -14278,16 +14272,16 @@
     </row>
     <row r="175" spans="1:5" ht="24" customHeight="1">
       <c r="A175" s="2" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>1181</v>
+        <v>1228</v>
       </c>
       <c r="C175" s="2">
         <v>1</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>1182</v>
+        <v>1008</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>34</v>
@@ -14295,16 +14289,16 @@
     </row>
     <row r="176" spans="1:5" ht="24" customHeight="1">
       <c r="A176" s="2" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>1183</v>
+        <v>1229</v>
       </c>
       <c r="C176" s="2">
         <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>1184</v>
+        <v>1009</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>34</v>
@@ -14312,16 +14306,16 @@
     </row>
     <row r="177" spans="1:5" ht="24" customHeight="1">
       <c r="A177" s="2" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>1185</v>
+        <v>1230</v>
       </c>
       <c r="C177" s="2">
         <v>1</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>1186</v>
+        <v>1010</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>34</v>
@@ -14332,33 +14326,33 @@
         <v>725</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>1187</v>
+        <v>1231</v>
       </c>
       <c r="C178" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>1188</v>
+        <v>1011</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="24" customHeight="1">
       <c r="A179" s="2" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>1189</v>
+        <v>1232</v>
       </c>
       <c r="C179" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>1190</v>
+        <v>1012</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="24" customHeight="1">
@@ -14366,33 +14360,33 @@
         <v>732</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>1191</v>
+        <v>1233</v>
       </c>
       <c r="C180" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>1192</v>
+        <v>1013</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="24" customHeight="1">
       <c r="A181" s="2" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>1193</v>
+        <v>1234</v>
       </c>
       <c r="C181" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>1194</v>
+        <v>1014</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="24" customHeight="1">
@@ -14400,16 +14394,16 @@
         <v>740</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>1195</v>
+        <v>1235</v>
       </c>
       <c r="C182" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>1196</v>
+        <v>1015</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1">
@@ -14417,33 +14411,30 @@
         <v>740</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>1197</v>
+        <v>1236</v>
       </c>
       <c r="C183" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>1198</v>
+        <v>1016</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" ht="24" customHeight="1">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
       <c r="A184" s="2" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>1199</v>
+        <v>1237</v>
       </c>
       <c r="C184" s="2">
-        <v>3</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -14451,13 +14442,13 @@
         <v>746</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="C185" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -14465,13 +14456,13 @@
         <v>746</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="C186" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -14479,27 +14470,27 @@
         <v>746</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="C187" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="2" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="C188" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -14507,13 +14498,13 @@
         <v>752</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="C189" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -14521,27 +14512,27 @@
         <v>752</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="C190" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="2" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="C191" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -14549,13 +14540,13 @@
         <v>757</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="C192" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -14563,13 +14554,13 @@
         <v>757</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="C193" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -14577,13 +14568,13 @@
         <v>757</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="C194" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -14591,13 +14582,13 @@
         <v>757</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="C195" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -14605,13 +14596,13 @@
         <v>757</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="C196" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -14619,27 +14610,27 @@
         <v>757</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="C197" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="C198" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -14647,13 +14638,13 @@
         <v>762</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="C199" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -14661,35 +14652,35 @@
         <v>762</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="C200" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="C201" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="C202" s="2">
         <v>1</v>
@@ -14703,27 +14694,27 @@
         <v>772</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="C203" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2" t="s">
-        <v>772</v>
+        <v>778</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="C204" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -14731,27 +14722,27 @@
         <v>778</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="C205" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="C206" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -14759,13 +14750,13 @@
         <v>783</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="C207" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -14773,27 +14764,27 @@
         <v>783</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="C208" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="C209" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -14801,35 +14792,35 @@
         <v>787</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="C210" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="C211" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="C212" s="2">
         <v>1</v>
@@ -14840,10 +14831,10 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="C213" s="2">
         <v>1</v>
@@ -14854,10 +14845,10 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="C214" s="2">
         <v>1</v>
@@ -14868,10 +14859,10 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="C215" s="2">
         <v>1</v>
@@ -14885,35 +14876,35 @@
         <v>811</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="C216" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="C217" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>843</v>
+        <v>34</v>
       </c>
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>1223</v>
+        <v>1271</v>
       </c>
       <c r="C218" s="2">
         <v>1</v>
@@ -14924,10 +14915,10 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C219" s="2">
         <v>1</v>
@@ -14941,13 +14932,13 @@
         <v>821</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="C220" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>34</v>
+        <v>841</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -14955,13 +14946,13 @@
         <v>821</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C221" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -14969,40 +14960,26 @@
         <v>821</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C222" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="C223" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5">
-      <c r="A224" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>1279</v>
-      </c>
-      <c r="C224" s="2">
-        <v>1</v>
-      </c>
-      <c r="E224" s="2" t="s">
         <v>34</v>
       </c>
     </row>
@@ -15038,7 +15015,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="23" customHeight="1">
       <c r="A1" s="34" t="s">
-        <v>1201</v>
+        <v>1017</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -15048,7 +15025,7 @@
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="35" t="s">
-        <v>1202</v>
+        <v>1018</v>
       </c>
       <c r="B3" s="32"/>
       <c r="C3" s="32"/>
@@ -15058,7 +15035,7 @@
     </row>
     <row r="4" spans="1:6" ht="46" customHeight="1">
       <c r="A4" s="33" t="s">
-        <v>1203</v>
+        <v>1019</v>
       </c>
       <c r="B4" s="32"/>
       <c r="C4" s="32"/>
@@ -15068,7 +15045,7 @@
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="35" t="s">
-        <v>1204</v>
+        <v>1020</v>
       </c>
       <c r="B6" s="32"/>
       <c r="C6" s="32"/>
@@ -15078,7 +15055,7 @@
     </row>
     <row r="7" spans="1:6" ht="54" customHeight="1">
       <c r="A7" s="33" t="s">
-        <v>1205</v>
+        <v>1021</v>
       </c>
       <c r="B7" s="32"/>
       <c r="C7" s="32"/>
@@ -15088,7 +15065,7 @@
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
       <c r="A9" s="35" t="s">
-        <v>1206</v>
+        <v>1022</v>
       </c>
       <c r="B9" s="32"/>
       <c r="C9" s="32"/>
@@ -15098,7 +15075,7 @@
     </row>
     <row r="10" spans="1:6" ht="46" customHeight="1">
       <c r="A10" s="33" t="s">
-        <v>1207</v>
+        <v>1023</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="32"/>
@@ -15108,7 +15085,7 @@
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
       <c r="A12" s="35" t="s">
-        <v>1208</v>
+        <v>1024</v>
       </c>
       <c r="B12" s="32"/>
       <c r="C12" s="32"/>
@@ -15118,7 +15095,7 @@
     </row>
     <row r="13" spans="1:6" ht="54" customHeight="1">
       <c r="A13" s="33" t="s">
-        <v>1209</v>
+        <v>1025</v>
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="32"/>
@@ -15128,17 +15105,17 @@
     </row>
     <row r="14" spans="1:6" ht="32" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>1210</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="32" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>1211</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="32" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>1212</v>
+        <v>1028</v>
       </c>
     </row>
   </sheetData>

--- a/inventaire_mobilier.xlsx
+++ b/inventaire_mobilier.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolas.coquet/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E21C7AC-4E0A-DF4D-B1BD-B2ACCA855CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5954E86-586F-9546-B552-61FD23C5C7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mobilier" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2288" uniqueCount="1280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="1286">
   <si>
     <t>Inventaire du mobilier</t>
   </si>
@@ -2289,9 +2289,6 @@
     <t>Bois sculpté, verre biseauté, vitrail au plomb, métal</t>
   </si>
   <si>
-    <t>Important buffet à corps inférieur sculpté, superstructure vitrée à vitraux au plomb et miroir central.</t>
-  </si>
-  <si>
     <t>Bon état d’usage apparent; petites usures et rayures</t>
   </si>
   <si>
@@ -3129,12 +3126,6 @@
     <t>Porte-plume avec calendrier perpétuel</t>
   </si>
   <si>
-    <t>Table de salle à manger [Art déco]</t>
-  </si>
-  <si>
-    <t>Buffet-vitrine à miroir [Art nouveau]</t>
-  </si>
-  <si>
     <t>Lampe-réveil [Art déco]</t>
   </si>
   <si>
@@ -3874,6 +3865,33 @@
   </si>
   <si>
     <t>Métal argenté , manches en celluloïd, bois, velours</t>
+  </si>
+  <si>
+    <t>MOB-110</t>
+  </si>
+  <si>
+    <t>Important buffet à corps inférieur sculpté, superstructure vitrée à vitraux au plomb.</t>
+  </si>
+  <si>
+    <t>MOB-087, MOB-088</t>
+  </si>
+  <si>
+    <t>MOB-110, MOB-088</t>
+  </si>
+  <si>
+    <t>MOB-110, MOB-087</t>
+  </si>
+  <si>
+    <t>Important buffet à corps inférieur sculpté et miroir central.</t>
+  </si>
+  <si>
+    <t>Buffet-vitrine [Art nouveau]</t>
+  </si>
+  <si>
+    <t>Table de salle à manger [Art nouveau]</t>
+  </si>
+  <si>
+    <t>MOB-110-01.webp</t>
   </si>
 </sst>
 </file>
@@ -4076,6 +4094,10 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4085,10 +4107,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4099,63 +4117,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="30">
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -4560,6 +4521,63 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4574,47 +4592,47 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MobilierTable" displayName="MobilierTable" ref="A3:U105" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
-  <autoFilter ref="A3:U105" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MobilierTable" displayName="MobilierTable" ref="A3:U106" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+  <autoFilter ref="A3:U106" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:U105">
     <sortCondition ref="A3:A105"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Identifiant" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Catégorie" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Datation" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Origine" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Matériaux" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Description" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Dimensions" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="État" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Estimation unitaire basse (€)" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Estimation unitaire haute (€)" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Localisation" dataDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Statut" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Publié" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Mots-clés" dataDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Source 1" dataDxfId="12"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Source 2" dataDxfId="11"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Quantité" dataDxfId="10"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Estimation du lot basse (€)" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Estimation du lot haute (€)" dataDxfId="8"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Associé à" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Identifiant" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Catégorie" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Datation" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Origine" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Matériaux" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Description" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Dimensions" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="État" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Estimation unitaire basse (€)" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Estimation unitaire haute (€)" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Localisation" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Statut" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Publié" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Mots-clés" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Source 1" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Source 2" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Quantité" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Estimation du lot basse (€)" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Estimation du lot haute (€)" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Associé à" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PhotosTable" displayName="PhotosTable" ref="A3:E103" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PhotosTable" displayName="PhotosTable" ref="A3:E103" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
   <autoFilter ref="A3:E103" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Identifiant objet" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fichier" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Ordre" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Légende" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Image principale" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Identifiant objet" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fichier" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Ordre" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Légende" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Image principale" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4815,7 +4833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U105"/>
+  <dimension ref="A1:U106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
@@ -4841,54 +4859,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="23">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
+      <c r="A2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
     </row>
     <row r="3" spans="1:21" s="19" customFormat="1" ht="32">
       <c r="A3" s="17" t="s">
@@ -5025,7 +5043,7 @@
         <v>38</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>39</v>
@@ -5288,7 +5306,7 @@
         <v>86</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>87</v>
@@ -5350,7 +5368,7 @@
         <v>96</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>52</v>
@@ -5415,7 +5433,7 @@
         <v>106</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>52</v>
@@ -5480,7 +5498,7 @@
         <v>114</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>52</v>
@@ -5545,7 +5563,7 @@
         <v>125</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>197</v>
@@ -5675,7 +5693,7 @@
         <v>145</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>197</v>
@@ -5810,7 +5828,7 @@
         <v>166</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>167</v>
@@ -6067,7 +6085,7 @@
         <v>206</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>52</v>
@@ -6082,7 +6100,7 @@
         <v>207</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>208</v>
@@ -6395,7 +6413,7 @@
         <v>253</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>254</v>
@@ -6460,7 +6478,7 @@
         <v>264</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>265</v>
@@ -6590,13 +6608,13 @@
         <v>286</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>126</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>287</v>
@@ -6717,7 +6735,7 @@
         <v>304</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>305</v>
@@ -6782,7 +6800,7 @@
         <v>314</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>315</v>
@@ -7042,7 +7060,7 @@
         <v>358</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>52</v>
@@ -7057,7 +7075,7 @@
         <v>359</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>360</v>
@@ -7367,7 +7385,7 @@
         <v>404</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>305</v>
@@ -7497,7 +7515,7 @@
         <v>154</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>197</v>
@@ -8085,7 +8103,7 @@
         <v>497</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>498</v>
@@ -8442,7 +8460,7 @@
         <v>536</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>315</v>
@@ -8457,7 +8475,7 @@
         <v>538</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="H58" s="12" t="s">
         <v>478</v>
@@ -8481,7 +8499,7 @@
         <v>34</v>
       </c>
       <c r="O58" s="12" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="P58" s="12"/>
       <c r="Q58" s="12"/>
@@ -8512,7 +8530,7 @@
         <v>497</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="F59" s="12" t="s">
         <v>542</v>
@@ -8811,7 +8829,7 @@
         <v>574</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="D64" s="12" t="s">
         <v>575</v>
@@ -8869,7 +8887,7 @@
         <v>580</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>581</v>
@@ -9055,7 +9073,7 @@
         <v>601</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>562</v>
@@ -9421,7 +9439,7 @@
         <v>642</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="D74" s="12" t="s">
         <v>504</v>
@@ -9631,7 +9649,7 @@
         <v>220</v>
       </c>
       <c r="L77" s="12" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M77" s="5" t="s">
         <v>33</v>
@@ -9692,7 +9710,7 @@
         <v>450</v>
       </c>
       <c r="L78" s="12" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M78" s="5" t="s">
         <v>33</v>
@@ -9755,7 +9773,7 @@
         <v>500</v>
       </c>
       <c r="L79" s="12" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="M79" s="5" t="s">
         <v>33</v>
@@ -10217,7 +10235,7 @@
         <v>734</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="C87" s="12" t="s">
         <v>728</v>
@@ -10226,16 +10244,16 @@
         <v>548</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="G87" s="12" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="H87" s="14" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="I87" s="12" t="s">
         <v>735</v>
@@ -10259,7 +10277,7 @@
         <v>736</v>
       </c>
       <c r="P87" s="12" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="Q87" s="12"/>
       <c r="R87" s="7">
@@ -10289,7 +10307,7 @@
         <v>739</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="F88" s="14" t="s">
         <v>740</v>
@@ -10298,7 +10316,7 @@
         <v>741</v>
       </c>
       <c r="H88" s="14" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="I88" s="14" t="s">
         <v>742</v>
@@ -10355,7 +10373,7 @@
         <v>746</v>
       </c>
       <c r="H89" s="14" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="I89" s="14" t="s">
         <v>747</v>
@@ -10394,7 +10412,7 @@
         <v>748</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>1032</v>
+        <v>1283</v>
       </c>
       <c r="C90" s="9" t="s">
         <v>197</v>
@@ -10403,19 +10421,19 @@
         <v>749</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="F90" s="14" t="s">
         <v>750</v>
       </c>
       <c r="G90" s="14" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H90" s="14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I90" s="14" t="s">
         <v>751</v>
-      </c>
-      <c r="H90" s="14" t="s">
-        <v>1029</v>
-      </c>
-      <c r="I90" s="14" t="s">
-        <v>752</v>
       </c>
       <c r="J90" s="27">
         <v>700</v>
@@ -10444,35 +10462,37 @@
       <c r="T90" s="27">
         <v>1500</v>
       </c>
-      <c r="U90" s="14"/>
+      <c r="U90" s="14" t="s">
+        <v>1280</v>
+      </c>
     </row>
     <row r="91" spans="1:21">
       <c r="A91" s="13" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>1031</v>
+        <v>1284</v>
       </c>
       <c r="C91" s="9" t="s">
         <v>197</v>
       </c>
       <c r="D91" s="14" t="s">
+        <v>753</v>
+      </c>
+      <c r="E91" s="14" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F91" s="14" t="s">
         <v>754</v>
       </c>
-      <c r="E91" s="14" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F91" s="14" t="s">
+      <c r="G91" s="14" t="s">
         <v>755</v>
       </c>
-      <c r="G91" s="14" t="s">
+      <c r="H91" s="14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I91" s="14" t="s">
         <v>756</v>
-      </c>
-      <c r="H91" s="14" t="s">
-        <v>1029</v>
-      </c>
-      <c r="I91" s="14" t="s">
-        <v>757</v>
       </c>
       <c r="J91" s="27">
         <v>250</v>
@@ -10501,17 +10521,19 @@
       <c r="T91" s="27">
         <v>600</v>
       </c>
-      <c r="U91" s="14"/>
+      <c r="U91" s="14" t="s">
+        <v>1281</v>
+      </c>
     </row>
     <row r="92" spans="1:21">
       <c r="A92" s="13" t="s">
+        <v>757</v>
+      </c>
+      <c r="B92" s="14" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C92" s="12" t="s">
         <v>758</v>
-      </c>
-      <c r="B92" s="14" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C92" s="12" t="s">
-        <v>759</v>
       </c>
       <c r="D92" s="14" t="s">
         <v>609</v>
@@ -10520,16 +10542,16 @@
         <v>630</v>
       </c>
       <c r="F92" s="14" t="s">
+        <v>759</v>
+      </c>
+      <c r="G92" s="14" t="s">
         <v>760</v>
       </c>
-      <c r="G92" s="14" t="s">
+      <c r="H92" s="14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I92" s="14" t="s">
         <v>761</v>
-      </c>
-      <c r="H92" s="14" t="s">
-        <v>1029</v>
-      </c>
-      <c r="I92" s="14" t="s">
-        <v>762</v>
       </c>
       <c r="J92" s="27">
         <v>20</v>
@@ -10562,13 +10584,13 @@
     </row>
     <row r="93" spans="1:21">
       <c r="A93" s="13" t="s">
+        <v>762</v>
+      </c>
+      <c r="B93" s="14" t="s">
         <v>763</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="C93" s="12" t="s">
         <v>764</v>
-      </c>
-      <c r="C93" s="12" t="s">
-        <v>765</v>
       </c>
       <c r="D93" s="14" t="s">
         <v>157</v>
@@ -10577,16 +10599,16 @@
         <v>350</v>
       </c>
       <c r="F93" s="14" t="s">
+        <v>765</v>
+      </c>
+      <c r="G93" s="14" t="s">
         <v>766</v>
       </c>
-      <c r="G93" s="14" t="s">
+      <c r="H93" s="14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I93" s="14" t="s">
         <v>767</v>
-      </c>
-      <c r="H93" s="14" t="s">
-        <v>1029</v>
-      </c>
-      <c r="I93" s="14" t="s">
-        <v>768</v>
       </c>
       <c r="J93" s="27">
         <v>30</v>
@@ -10619,13 +10641,13 @@
     </row>
     <row r="94" spans="1:21">
       <c r="A94" s="13" t="s">
+        <v>768</v>
+      </c>
+      <c r="B94" s="14" t="s">
         <v>769</v>
       </c>
-      <c r="B94" s="14" t="s">
-        <v>770</v>
-      </c>
       <c r="C94" s="12" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D94" s="14" t="s">
         <v>53</v>
@@ -10634,16 +10656,16 @@
         <v>350</v>
       </c>
       <c r="F94" s="14" t="s">
+        <v>770</v>
+      </c>
+      <c r="G94" s="14" t="s">
         <v>771</v>
       </c>
-      <c r="G94" s="14" t="s">
+      <c r="H94" s="14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I94" s="14" t="s">
         <v>772</v>
-      </c>
-      <c r="H94" s="14" t="s">
-        <v>1029</v>
-      </c>
-      <c r="I94" s="14" t="s">
-        <v>773</v>
       </c>
       <c r="J94" s="27">
         <v>30</v>
@@ -10676,13 +10698,13 @@
     </row>
     <row r="95" spans="1:21">
       <c r="A95" s="13" t="s">
+        <v>773</v>
+      </c>
+      <c r="B95" s="14" t="s">
         <v>774</v>
       </c>
-      <c r="B95" s="14" t="s">
-        <v>775</v>
-      </c>
       <c r="C95" s="12" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D95" s="14" t="s">
         <v>157</v>
@@ -10691,16 +10713,16 @@
         <v>350</v>
       </c>
       <c r="F95" s="14" t="s">
+        <v>775</v>
+      </c>
+      <c r="G95" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="G95" s="14" t="s">
-        <v>777</v>
-      </c>
       <c r="H95" s="14" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="I95" s="14" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="J95" s="27">
         <v>30</v>
@@ -10733,13 +10755,13 @@
     </row>
     <row r="96" spans="1:21">
       <c r="A96" s="13" t="s">
+        <v>777</v>
+      </c>
+      <c r="B96" s="14" t="s">
         <v>778</v>
       </c>
-      <c r="B96" s="14" t="s">
-        <v>779</v>
-      </c>
       <c r="C96" s="12" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D96" s="14" t="s">
         <v>157</v>
@@ -10748,16 +10770,16 @@
         <v>350</v>
       </c>
       <c r="F96" s="14" t="s">
+        <v>779</v>
+      </c>
+      <c r="G96" s="14" t="s">
         <v>780</v>
       </c>
-      <c r="G96" s="14" t="s">
-        <v>781</v>
-      </c>
       <c r="H96" s="14" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="I96" s="14" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="J96" s="27">
         <v>30</v>
@@ -10790,10 +10812,10 @@
     </row>
     <row r="97" spans="1:21">
       <c r="A97" s="13" t="s">
+        <v>781</v>
+      </c>
+      <c r="B97" s="14" t="s">
         <v>782</v>
-      </c>
-      <c r="B97" s="14" t="s">
-        <v>783</v>
       </c>
       <c r="C97" s="12" t="s">
         <v>75</v>
@@ -10805,16 +10827,16 @@
         <v>350</v>
       </c>
       <c r="F97" s="14" t="s">
+        <v>783</v>
+      </c>
+      <c r="G97" s="14" t="s">
         <v>784</v>
       </c>
-      <c r="G97" s="14" t="s">
+      <c r="H97" s="14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I97" s="14" t="s">
         <v>785</v>
-      </c>
-      <c r="H97" s="14" t="s">
-        <v>1029</v>
-      </c>
-      <c r="I97" s="14" t="s">
-        <v>786</v>
       </c>
       <c r="J97" s="27">
         <v>40</v>
@@ -10847,10 +10869,10 @@
     </row>
     <row r="98" spans="1:21">
       <c r="A98" s="13" t="s">
+        <v>786</v>
+      </c>
+      <c r="B98" s="14" t="s">
         <v>787</v>
-      </c>
-      <c r="B98" s="14" t="s">
-        <v>788</v>
       </c>
       <c r="C98" s="12" t="s">
         <v>728</v>
@@ -10862,16 +10884,16 @@
         <v>350</v>
       </c>
       <c r="F98" s="14" t="s">
+        <v>788</v>
+      </c>
+      <c r="G98" s="14" t="s">
         <v>789</v>
       </c>
-      <c r="G98" s="14" t="s">
+      <c r="H98" s="14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I98" s="14" t="s">
         <v>790</v>
-      </c>
-      <c r="H98" s="14" t="s">
-        <v>1029</v>
-      </c>
-      <c r="I98" s="14" t="s">
-        <v>791</v>
       </c>
       <c r="J98" s="27">
         <v>20</v>
@@ -10904,31 +10926,31 @@
     </row>
     <row r="99" spans="1:21">
       <c r="A99" s="13" t="s">
+        <v>791</v>
+      </c>
+      <c r="B99" s="14" t="s">
         <v>792</v>
       </c>
-      <c r="B99" s="14" t="s">
+      <c r="C99" s="12" t="s">
         <v>793</v>
-      </c>
-      <c r="C99" s="12" t="s">
-        <v>794</v>
       </c>
       <c r="D99" s="14" t="s">
         <v>187</v>
       </c>
       <c r="E99" s="14" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F99" s="14" t="s">
+        <v>794</v>
+      </c>
+      <c r="G99" s="14" t="s">
+        <v>795</v>
+      </c>
+      <c r="H99" s="14" t="s">
         <v>1028</v>
       </c>
-      <c r="F99" s="14" t="s">
-        <v>795</v>
-      </c>
-      <c r="G99" s="14" t="s">
-        <v>796</v>
-      </c>
-      <c r="H99" s="14" t="s">
-        <v>1029</v>
-      </c>
       <c r="I99" s="14" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="J99" s="27">
         <v>40</v>
@@ -10961,31 +10983,31 @@
     </row>
     <row r="100" spans="1:21">
       <c r="A100" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="B100" s="14" t="s">
         <v>797</v>
       </c>
-      <c r="B100" s="14" t="s">
-        <v>798</v>
-      </c>
       <c r="C100" s="12" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D100" s="14" t="s">
         <v>187</v>
       </c>
       <c r="E100" s="14" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F100" s="14" t="s">
+        <v>798</v>
+      </c>
+      <c r="G100" s="14" t="s">
+        <v>799</v>
+      </c>
+      <c r="H100" s="14" t="s">
         <v>1028</v>
       </c>
-      <c r="F100" s="14" t="s">
-        <v>799</v>
-      </c>
-      <c r="G100" s="14" t="s">
+      <c r="I100" s="14" t="s">
         <v>800</v>
-      </c>
-      <c r="H100" s="14" t="s">
-        <v>1029</v>
-      </c>
-      <c r="I100" s="14" t="s">
-        <v>801</v>
       </c>
       <c r="J100" s="27">
         <v>60</v>
@@ -11018,31 +11040,31 @@
     </row>
     <row r="101" spans="1:21">
       <c r="A101" s="13" t="s">
+        <v>801</v>
+      </c>
+      <c r="B101" s="14" t="s">
         <v>802</v>
       </c>
-      <c r="B101" s="14" t="s">
-        <v>803</v>
-      </c>
       <c r="C101" s="12" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D101" s="14" t="s">
         <v>187</v>
       </c>
       <c r="E101" s="14" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F101" s="14" t="s">
+        <v>803</v>
+      </c>
+      <c r="G101" s="14" t="s">
+        <v>804</v>
+      </c>
+      <c r="H101" s="14" t="s">
         <v>1028</v>
       </c>
-      <c r="F101" s="14" t="s">
-        <v>804</v>
-      </c>
-      <c r="G101" s="14" t="s">
-        <v>805</v>
-      </c>
-      <c r="H101" s="14" t="s">
-        <v>1029</v>
-      </c>
       <c r="I101" s="14" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="J101" s="27">
         <v>40</v>
@@ -11075,31 +11097,31 @@
     </row>
     <row r="102" spans="1:21">
       <c r="A102" s="13" t="s">
+        <v>805</v>
+      </c>
+      <c r="B102" s="14" t="s">
         <v>806</v>
       </c>
-      <c r="B102" s="14" t="s">
-        <v>807</v>
-      </c>
       <c r="C102" s="12" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D102" s="14" t="s">
         <v>187</v>
       </c>
       <c r="E102" s="14" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F102" s="14" t="s">
+        <v>803</v>
+      </c>
+      <c r="G102" s="14" t="s">
+        <v>807</v>
+      </c>
+      <c r="H102" s="14" t="s">
         <v>1028</v>
       </c>
-      <c r="F102" s="14" t="s">
-        <v>804</v>
-      </c>
-      <c r="G102" s="14" t="s">
-        <v>808</v>
-      </c>
-      <c r="H102" s="14" t="s">
-        <v>1029</v>
-      </c>
       <c r="I102" s="14" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="J102" s="27">
         <v>40</v>
@@ -11132,31 +11154,31 @@
     </row>
     <row r="103" spans="1:21">
       <c r="A103" s="13" t="s">
+        <v>808</v>
+      </c>
+      <c r="B103" s="14" t="s">
         <v>809</v>
       </c>
-      <c r="B103" s="14" t="s">
-        <v>810</v>
-      </c>
       <c r="C103" s="12" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="D103" s="14" t="s">
         <v>187</v>
       </c>
       <c r="E103" s="14" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F103" s="14" t="s">
+        <v>803</v>
+      </c>
+      <c r="G103" s="14" t="s">
+        <v>810</v>
+      </c>
+      <c r="H103" s="14" t="s">
         <v>1028</v>
       </c>
-      <c r="F103" s="14" t="s">
-        <v>804</v>
-      </c>
-      <c r="G103" s="14" t="s">
-        <v>811</v>
-      </c>
-      <c r="H103" s="14" t="s">
-        <v>1029</v>
-      </c>
       <c r="I103" s="14" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="J103" s="27">
         <v>70</v>
@@ -11189,31 +11211,31 @@
     </row>
     <row r="104" spans="1:21">
       <c r="A104" s="13" t="s">
+        <v>811</v>
+      </c>
+      <c r="B104" s="14" t="s">
         <v>812</v>
       </c>
-      <c r="B104" s="14" t="s">
+      <c r="C104" s="12" t="s">
+        <v>793</v>
+      </c>
+      <c r="D104" s="14" t="s">
         <v>813</v>
       </c>
-      <c r="C104" s="12" t="s">
-        <v>794</v>
-      </c>
-      <c r="D104" s="14" t="s">
+      <c r="E104" s="14" t="s">
         <v>814</v>
       </c>
-      <c r="E104" s="14" t="s">
+      <c r="F104" s="14" t="s">
         <v>815</v>
       </c>
-      <c r="F104" s="14" t="s">
+      <c r="G104" s="14" t="s">
         <v>816</v>
       </c>
-      <c r="G104" s="14" t="s">
+      <c r="H104" s="14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I104" s="14" t="s">
         <v>817</v>
-      </c>
-      <c r="H104" s="14" t="s">
-        <v>1029</v>
-      </c>
-      <c r="I104" s="14" t="s">
-        <v>818</v>
       </c>
       <c r="J104" s="27">
         <v>150</v>
@@ -11246,10 +11268,10 @@
     </row>
     <row r="105" spans="1:21">
       <c r="A105" s="13" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B105" s="14" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>52</v>
@@ -11258,19 +11280,19 @@
         <v>483</v>
       </c>
       <c r="E105" s="14" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="F105" s="14" t="s">
+        <v>819</v>
+      </c>
+      <c r="G105" s="14" t="s">
         <v>820</v>
       </c>
-      <c r="G105" s="14" t="s">
+      <c r="H105" s="14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I105" s="14" t="s">
         <v>821</v>
-      </c>
-      <c r="H105" s="14" t="s">
-        <v>1029</v>
-      </c>
-      <c r="I105" s="14" t="s">
-        <v>822</v>
       </c>
       <c r="J105" s="27">
         <v>120</v>
@@ -11300,6 +11322,65 @@
         <v>250</v>
       </c>
       <c r="U105" s="14"/>
+    </row>
+    <row r="106" spans="1:21">
+      <c r="A106" s="13" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B106" s="14" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D106" s="14" t="s">
+        <v>749</v>
+      </c>
+      <c r="E106" s="14" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F106" s="14" t="s">
+        <v>750</v>
+      </c>
+      <c r="G106" s="14" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H106" s="14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I106" s="14" t="s">
+        <v>751</v>
+      </c>
+      <c r="J106" s="27">
+        <v>700</v>
+      </c>
+      <c r="K106" s="27">
+        <v>1500</v>
+      </c>
+      <c r="L106" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="M106" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="N106" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="O106" s="14"/>
+      <c r="P106" s="14"/>
+      <c r="Q106" s="14"/>
+      <c r="R106" s="7">
+        <v>1</v>
+      </c>
+      <c r="S106" s="27">
+        <v>700</v>
+      </c>
+      <c r="T106" s="27">
+        <v>1500</v>
+      </c>
+      <c r="U106" s="14" t="s">
+        <v>1279</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11307,7 +11388,7 @@
     <mergeCell ref="A2:U2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="M4:M105" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="M4:M106" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"À documenter,À restaurer,À conserver,À vendre,Vendu"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="N4" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -11323,7 +11404,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E223"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -11334,38 +11415,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="3" customFormat="1" ht="34" customHeight="1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="30" t="s">
+        <v>822</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1">
+      <c r="A2" s="28" t="s">
         <v>823</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-    </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="31" t="s">
-        <v>824</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
     </row>
     <row r="3" spans="1:5" s="21" customFormat="1" ht="16" customHeight="1">
       <c r="A3" s="20" t="s">
+        <v>824</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>825</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="C3" s="20" t="s">
         <v>826</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="D3" s="20" t="s">
         <v>827</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="E3" s="20" t="s">
         <v>828</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
@@ -11373,13 +11454,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="C4" s="23">
         <v>1</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>34</v>
@@ -11390,16 +11471,16 @@
         <v>23</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="C5" s="23">
         <v>2</v>
       </c>
       <c r="D5" s="22" t="s">
+        <v>830</v>
+      </c>
+      <c r="E5" s="22" t="s">
         <v>831</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
@@ -11407,16 +11488,16 @@
         <v>23</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="C6" s="25">
         <v>3</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
@@ -11424,13 +11505,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="C7" s="26">
         <v>1</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>34</v>
@@ -11441,16 +11522,16 @@
         <v>38</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="C8" s="26">
         <v>2</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
@@ -11458,16 +11539,16 @@
         <v>38</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="C9" s="26">
         <v>3</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
@@ -11475,13 +11556,13 @@
         <v>50</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="C10" s="26">
         <v>1</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>34</v>
@@ -11492,16 +11573,16 @@
         <v>62</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="C11" s="26">
         <v>2</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
@@ -11509,13 +11590,13 @@
         <v>62</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="C12" s="26">
         <v>1</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>34</v>
@@ -11526,16 +11607,16 @@
         <v>62</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="C13" s="26">
         <v>3</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
@@ -11543,16 +11624,16 @@
         <v>73</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="C14" s="26">
         <v>3</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1">
@@ -11560,16 +11641,16 @@
         <v>73</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="C15" s="26">
         <v>2</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1">
@@ -11577,13 +11658,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="C16" s="26">
         <v>1</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E16" s="26" t="s">
         <v>34</v>
@@ -11594,13 +11675,13 @@
         <v>464</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="C17" s="26">
         <v>1</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>34</v>
@@ -11611,16 +11692,16 @@
         <v>464</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="C18" s="26">
         <v>2</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1">
@@ -11628,16 +11709,16 @@
         <v>85</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="C19" s="26">
         <v>2</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1">
@@ -11645,13 +11726,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="C20" s="26">
         <v>1</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E20" s="26" t="s">
         <v>34</v>
@@ -11662,16 +11743,16 @@
         <v>96</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="C21" s="26">
         <v>1</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1">
@@ -11679,13 +11760,13 @@
         <v>96</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="C22" s="26">
         <v>2</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E22" s="26" t="s">
         <v>34</v>
@@ -11696,16 +11777,16 @@
         <v>96</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C23" s="26">
         <v>3</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1">
@@ -11713,16 +11794,16 @@
         <v>96</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="C24" s="26">
         <v>4</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1">
@@ -11730,13 +11811,13 @@
         <v>106</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="C25" s="26">
         <v>1</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E25" s="26" t="s">
         <v>34</v>
@@ -11747,16 +11828,16 @@
         <v>114</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="C26" s="26">
         <v>1</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1">
@@ -11764,16 +11845,16 @@
         <v>114</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="C27" s="26">
         <v>2</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1">
@@ -11781,13 +11862,13 @@
         <v>114</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="C28" s="26">
         <v>3</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E28" s="26" t="s">
         <v>34</v>
@@ -11798,16 +11879,16 @@
         <v>114</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="C29" s="26">
         <v>4</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1">
@@ -11815,16 +11896,16 @@
         <v>125</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="C30" s="26">
         <v>1</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1">
@@ -11832,13 +11913,13 @@
         <v>125</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="C31" s="26">
         <v>2</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E31" s="26" t="s">
         <v>34</v>
@@ -11849,16 +11930,16 @@
         <v>125</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="C32" s="26">
         <v>3</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1">
@@ -11866,13 +11947,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="C33" s="26">
         <v>1</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="E33" s="26" t="s">
         <v>34</v>
@@ -11883,16 +11964,16 @@
         <v>135</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="C34" s="26">
         <v>2</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1">
@@ -11900,16 +11981,16 @@
         <v>135</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="C35" s="26">
         <v>3</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1">
@@ -11917,13 +11998,13 @@
         <v>145</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="C36" s="26">
         <v>1</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E36" s="26" t="s">
         <v>34</v>
@@ -11934,16 +12015,16 @@
         <v>145</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="C37" s="26">
         <v>2</v>
       </c>
       <c r="D37" s="26" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1">
@@ -11951,16 +12032,16 @@
         <v>145</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="C38" s="26">
         <v>3</v>
       </c>
       <c r="D38" s="26" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1">
@@ -11968,16 +12049,16 @@
         <v>145</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="C39" s="26">
         <v>4</v>
       </c>
       <c r="D39" s="26" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1">
@@ -11985,16 +12066,16 @@
         <v>145</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="C40" s="26">
         <v>5</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1">
@@ -12002,16 +12083,16 @@
         <v>145</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="C41" s="26">
         <v>6</v>
       </c>
       <c r="D41" s="26" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15" customHeight="1">
@@ -12019,13 +12100,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="C42" s="26">
         <v>1</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E42" s="26" t="s">
         <v>34</v>
@@ -12036,13 +12117,13 @@
         <v>165</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="C43" s="26">
         <v>1</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E43" s="26" t="s">
         <v>34</v>
@@ -12053,13 +12134,13 @@
         <v>175</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C44" s="26">
         <v>1</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E44" s="26" t="s">
         <v>34</v>
@@ -12070,13 +12151,13 @@
         <v>185</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="C45" s="26">
         <v>1</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="E45" s="26" t="s">
         <v>34</v>
@@ -12087,13 +12168,13 @@
         <v>195</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="C46" s="26">
         <v>1</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E46" s="26" t="s">
         <v>34</v>
@@ -12104,16 +12185,16 @@
         <v>195</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="C47" s="26">
         <v>2</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" customHeight="1">
@@ -12121,13 +12202,13 @@
         <v>206</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="C48" s="26">
         <v>1</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E48" s="26" t="s">
         <v>34</v>
@@ -12138,16 +12219,16 @@
         <v>206</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="C49" s="26">
         <v>2</v>
       </c>
       <c r="D49" s="26" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1">
@@ -12155,16 +12236,16 @@
         <v>206</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="C50" s="26">
         <v>3</v>
       </c>
       <c r="D50" s="26" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E50" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15" customHeight="1">
@@ -12172,13 +12253,13 @@
         <v>213</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="C51" s="26">
         <v>1</v>
       </c>
       <c r="D51" s="26" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E51" s="26" t="s">
         <v>34</v>
@@ -12189,16 +12270,16 @@
         <v>213</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="C52" s="26">
         <v>2</v>
       </c>
       <c r="D52" s="26" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E52" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15" customHeight="1">
@@ -12206,16 +12287,16 @@
         <v>213</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="C53" s="26">
         <v>3</v>
       </c>
       <c r="D53" s="26" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15" customHeight="1">
@@ -12223,13 +12304,13 @@
         <v>223</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="C54" s="26">
         <v>1</v>
       </c>
       <c r="D54" s="26" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="E54" s="26" t="s">
         <v>34</v>
@@ -12240,16 +12321,16 @@
         <v>223</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="C55" s="26">
         <v>2</v>
       </c>
       <c r="D55" s="26" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15" customHeight="1">
@@ -12257,13 +12338,13 @@
         <v>234</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="C56" s="26">
         <v>1</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E56" s="26" t="s">
         <v>34</v>
@@ -12274,13 +12355,13 @@
         <v>244</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="C57" s="26">
         <v>1</v>
       </c>
       <c r="D57" s="26" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E57" s="26" t="s">
         <v>34</v>
@@ -12291,13 +12372,13 @@
         <v>252</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="C58" s="26">
         <v>1</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E58" s="26" t="s">
         <v>34</v>
@@ -12308,16 +12389,16 @@
         <v>252</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="C59" s="26">
         <v>2</v>
       </c>
       <c r="D59" s="26" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E59" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15" customHeight="1">
@@ -12325,13 +12406,13 @@
         <v>263</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C60" s="26">
         <v>1</v>
       </c>
       <c r="D60" s="26" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="E60" s="26" t="s">
         <v>34</v>
@@ -12342,16 +12423,16 @@
         <v>106</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="C61" s="26">
         <v>5</v>
       </c>
       <c r="D61" s="26" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15" customHeight="1">
@@ -12359,16 +12440,16 @@
         <v>106</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="C62" s="26">
         <v>6</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E62" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15" customHeight="1">
@@ -12376,16 +12457,16 @@
         <v>106</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="C63" s="26">
         <v>7</v>
       </c>
       <c r="D63" s="26" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="E63" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15" customHeight="1">
@@ -12393,13 +12474,13 @@
         <v>273</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="C64" s="26">
         <v>1</v>
       </c>
       <c r="D64" s="26" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E64" s="26" t="s">
         <v>34</v>
@@ -12410,13 +12491,13 @@
         <v>285</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="C65" s="26">
         <v>1</v>
       </c>
       <c r="D65" s="26" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E65" s="26" t="s">
         <v>34</v>
@@ -12427,16 +12508,16 @@
         <v>285</v>
       </c>
       <c r="B66" s="26" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="C66" s="26">
         <v>2</v>
       </c>
       <c r="D66" s="26" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E66" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15" customHeight="1">
@@ -12444,16 +12525,16 @@
         <v>294</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="C67" s="26">
         <v>1</v>
       </c>
       <c r="D67" s="26" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15" customHeight="1">
@@ -12461,13 +12542,13 @@
         <v>294</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="C68" s="26">
         <v>2</v>
       </c>
       <c r="D68" s="26" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E68" s="26" t="s">
         <v>34</v>
@@ -12478,13 +12559,13 @@
         <v>304</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="C69" s="26">
         <v>1</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E69" s="26" t="s">
         <v>34</v>
@@ -12495,16 +12576,16 @@
         <v>314</v>
       </c>
       <c r="B70" s="26" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="C70" s="26">
         <v>2</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="E70" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15" customHeight="1">
@@ -12512,13 +12593,13 @@
         <v>314</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="C71" s="26">
         <v>1</v>
       </c>
       <c r="D71" s="26" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
       <c r="E71" s="26" t="s">
         <v>34</v>
@@ -12529,16 +12610,16 @@
         <v>325</v>
       </c>
       <c r="B72" s="26" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="C72" s="26">
         <v>1</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="E72" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15" customHeight="1">
@@ -12546,13 +12627,13 @@
         <v>325</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C73" s="26">
         <v>2</v>
       </c>
       <c r="D73" s="26" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E73" s="26" t="s">
         <v>34</v>
@@ -12563,13 +12644,13 @@
         <v>335</v>
       </c>
       <c r="B74" s="26" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="C74" s="26">
         <v>1</v>
       </c>
       <c r="D74" s="26" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E74" s="26" t="s">
         <v>34</v>
@@ -12580,13 +12661,13 @@
         <v>346</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="C75" s="26">
         <v>1</v>
       </c>
       <c r="D75" s="26" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E75" s="26" t="s">
         <v>34</v>
@@ -12597,16 +12678,16 @@
         <v>346</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="C76" s="26">
         <v>2</v>
       </c>
       <c r="D76" s="26" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E76" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15" customHeight="1">
@@ -12614,16 +12695,16 @@
         <v>358</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="C77" s="26">
         <v>1</v>
       </c>
       <c r="D77" s="26" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15" customHeight="1">
@@ -12631,13 +12712,13 @@
         <v>358</v>
       </c>
       <c r="B78" s="26" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="C78" s="26">
         <v>2</v>
       </c>
       <c r="D78" s="26" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E78" s="26" t="s">
         <v>34</v>
@@ -12648,13 +12729,13 @@
         <v>365</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="C79" s="26">
         <v>1</v>
       </c>
       <c r="D79" s="26" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E79" s="26" t="s">
         <v>34</v>
@@ -12665,13 +12746,13 @@
         <v>374</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="C80" s="3">
         <v>1</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>34</v>
@@ -12682,16 +12763,16 @@
         <v>374</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="C81" s="3">
         <v>2</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -12699,16 +12780,16 @@
         <v>385</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="C82" s="3">
         <v>1</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -12716,13 +12797,13 @@
         <v>385</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="C83" s="3">
         <v>2</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>34</v>
@@ -12733,16 +12814,16 @@
         <v>385</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="C84" s="3">
         <v>3</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -12750,13 +12831,13 @@
         <v>394</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="C85" s="3">
         <v>1</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>34</v>
@@ -12767,16 +12848,16 @@
         <v>394</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="C86" s="3">
         <v>2</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -12784,13 +12865,13 @@
         <v>404</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="C87" s="3">
         <v>1</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>34</v>
@@ -12801,16 +12882,16 @@
         <v>404</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="C88" s="3">
         <v>2</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -12818,13 +12899,13 @@
         <v>413</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="C89" s="3">
         <v>1</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>34</v>
@@ -12835,16 +12916,16 @@
         <v>154</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="C90" s="3">
         <v>1</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -12852,16 +12933,16 @@
         <v>154</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C91" s="3">
         <v>2</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -12869,16 +12950,16 @@
         <v>154</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="C92" s="3">
         <v>3</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -12886,13 +12967,13 @@
         <v>154</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="C93" s="3">
         <v>4</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>34</v>
@@ -12903,16 +12984,16 @@
         <v>429</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="C94" s="3">
         <v>3</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -12920,16 +13001,16 @@
         <v>429</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="C95" s="3">
         <v>2</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -12937,13 +13018,13 @@
         <v>429</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="C96" s="3">
         <v>1</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>34</v>
@@ -12954,13 +13035,13 @@
         <v>438</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="C97" s="3">
         <v>1</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>34</v>
@@ -12971,16 +13052,16 @@
         <v>438</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="C98" s="3">
         <v>2</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -12988,16 +13069,16 @@
         <v>438</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="C99" s="3">
         <v>3</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -13005,13 +13086,13 @@
         <v>447</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="C100" s="3">
         <v>1</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>34</v>
@@ -13022,13 +13103,13 @@
         <v>454</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="C101" s="3">
         <v>1</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>34</v>
@@ -13039,16 +13120,16 @@
         <v>454</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="C102" s="3">
         <v>2</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -13056,16 +13137,16 @@
         <v>454</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="C103" s="3">
         <v>3</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="24" customHeight="1">
@@ -13073,16 +13154,16 @@
         <v>473</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="C104" s="2">
         <v>2</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="24" customHeight="1">
@@ -13090,13 +13171,13 @@
         <v>473</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>34</v>
@@ -13107,16 +13188,16 @@
         <v>481</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="C106" s="2">
         <v>2</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="24" customHeight="1">
@@ -13124,13 +13205,13 @@
         <v>481</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>34</v>
@@ -13141,13 +13222,13 @@
         <v>489</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>34</v>
@@ -13158,13 +13239,13 @@
         <v>495</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>34</v>
@@ -13175,16 +13256,16 @@
         <v>495</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="C110" s="2">
         <v>2</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="24" customHeight="1">
@@ -13192,16 +13273,16 @@
         <v>495</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="C111" s="2">
         <v>3</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="24" customHeight="1">
@@ -13209,16 +13290,16 @@
         <v>495</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="C112" s="2">
         <v>4</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="24" customHeight="1">
@@ -13226,16 +13307,16 @@
         <v>495</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="C113" s="2">
         <v>5</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="24" customHeight="1">
@@ -13243,13 +13324,13 @@
         <v>502</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="C114" s="2">
         <v>1</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>34</v>
@@ -13260,16 +13341,16 @@
         <v>502</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="C115" s="2">
         <v>2</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="24" customHeight="1">
@@ -13277,13 +13358,13 @@
         <v>510</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="C116" s="2">
         <v>1</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>34</v>
@@ -13294,13 +13375,13 @@
         <v>516</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>34</v>
@@ -13311,16 +13392,16 @@
         <v>516</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="C118" s="2">
         <v>2</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="24" customHeight="1">
@@ -13328,13 +13409,13 @@
         <v>522</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="C119" s="2">
         <v>1</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>34</v>
@@ -13345,16 +13426,16 @@
         <v>522</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="C120" s="2">
         <v>2</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="24" customHeight="1">
@@ -13362,13 +13443,13 @@
         <v>530</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="C121" s="2">
         <v>1</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>34</v>
@@ -13379,16 +13460,16 @@
         <v>530</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="C122" s="2">
         <v>2</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="24" customHeight="1">
@@ -13396,16 +13477,16 @@
         <v>530</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="C123" s="2">
         <v>3</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="24" customHeight="1">
@@ -13413,13 +13494,13 @@
         <v>536</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="C124" s="2">
         <v>1</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>34</v>
@@ -13430,16 +13511,16 @@
         <v>536</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="C125" s="2">
         <v>2</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="24" customHeight="1">
@@ -13447,13 +13528,13 @@
         <v>540</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="C126" s="2">
         <v>1</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>34</v>
@@ -13464,16 +13545,16 @@
         <v>540</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="C127" s="2">
         <v>2</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="24" customHeight="1">
@@ -13481,16 +13562,16 @@
         <v>540</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="C128" s="2">
         <v>3</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="24" customHeight="1">
@@ -13498,16 +13579,16 @@
         <v>540</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="C129" s="2">
         <v>4</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="24" customHeight="1">
@@ -13515,13 +13596,13 @@
         <v>546</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="C130" s="2">
         <v>1</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>34</v>
@@ -13532,16 +13613,16 @@
         <v>546</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="C131" s="2">
         <v>2</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="24" customHeight="1">
@@ -13549,13 +13630,13 @@
         <v>553</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>34</v>
@@ -13566,16 +13647,16 @@
         <v>553</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="C133" s="2">
         <v>2</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="24" customHeight="1">
@@ -13583,13 +13664,13 @@
         <v>560</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="C134" s="2">
         <v>1</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>34</v>
@@ -13600,16 +13681,16 @@
         <v>560</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="C135" s="2">
         <v>2</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="24" customHeight="1">
@@ -13617,13 +13698,13 @@
         <v>567</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="C136" s="2">
         <v>1</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>34</v>
@@ -13634,16 +13715,16 @@
         <v>567</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="C137" s="2">
         <v>2</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="24" customHeight="1">
@@ -13651,16 +13732,16 @@
         <v>567</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C138" s="2">
         <v>3</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="24" customHeight="1">
@@ -13668,13 +13749,13 @@
         <v>573</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="C139" s="2">
         <v>1</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>34</v>
@@ -13685,16 +13766,16 @@
         <v>573</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="C140" s="2">
         <v>2</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="24" customHeight="1">
@@ -13702,16 +13783,16 @@
         <v>573</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="C141" s="2">
         <v>3</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="24" customHeight="1">
@@ -13719,16 +13800,16 @@
         <v>573</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="C142" s="2">
         <v>4</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="24" customHeight="1">
@@ -13736,13 +13817,13 @@
         <v>580</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="C143" s="2">
         <v>1</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>34</v>
@@ -13753,16 +13834,16 @@
         <v>580</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="C144" s="2">
         <v>2</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="24" customHeight="1">
@@ -13770,16 +13851,16 @@
         <v>580</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="C145" s="2">
         <v>3</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="24" customHeight="1">
@@ -13787,13 +13868,13 @@
         <v>587</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="C146" s="2">
         <v>1</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>34</v>
@@ -13804,13 +13885,13 @@
         <v>594</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="C147" s="2">
         <v>1</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>34</v>
@@ -13821,16 +13902,16 @@
         <v>594</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="C148" s="2">
         <v>2</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="24" customHeight="1">
@@ -13838,16 +13919,16 @@
         <v>600</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="C149" s="2">
         <v>2</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="24" customHeight="1">
@@ -13855,13 +13936,13 @@
         <v>600</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="C150" s="2">
         <v>1</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>34</v>
@@ -13872,13 +13953,13 @@
         <v>607</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="C151" s="2">
         <v>1</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>34</v>
@@ -13889,16 +13970,16 @@
         <v>607</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="C152" s="2">
         <v>2</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="24" customHeight="1">
@@ -13906,13 +13987,13 @@
         <v>615</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="C153" s="2">
         <v>1</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>34</v>
@@ -13923,16 +14004,16 @@
         <v>615</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="C154" s="2">
         <v>2</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="24" customHeight="1">
@@ -13940,13 +14021,13 @@
         <v>621</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="C155" s="2">
         <v>1</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>34</v>
@@ -13957,16 +14038,16 @@
         <v>621</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="C156" s="2">
         <v>2</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="24" customHeight="1">
@@ -13974,13 +14055,13 @@
         <v>628</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="C157" s="2">
         <v>1</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>34</v>
@@ -13991,16 +14072,16 @@
         <v>628</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="C158" s="2">
         <v>2</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="24" customHeight="1">
@@ -14008,16 +14089,16 @@
         <v>628</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="C159" s="2">
         <v>3</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="24" customHeight="1">
@@ -14025,16 +14106,16 @@
         <v>628</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="C160" s="2">
         <v>4</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="24" customHeight="1">
@@ -14042,13 +14123,13 @@
         <v>635</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="C161" s="2">
         <v>1</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>34</v>
@@ -14059,13 +14140,13 @@
         <v>641</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="C162" s="2">
         <v>1</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>34</v>
@@ -14076,16 +14157,16 @@
         <v>647</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="C163" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>34</v>
+        <v>831</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="24" customHeight="1">
@@ -14093,16 +14174,16 @@
         <v>647</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="C164" s="2">
         <v>2</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="24" customHeight="1">
@@ -14110,16 +14191,16 @@
         <v>647</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="C165" s="2">
         <v>3</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="24" customHeight="1">
@@ -14127,16 +14208,16 @@
         <v>647</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="C166" s="2">
         <v>4</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="24" customHeight="1">
@@ -14144,16 +14225,16 @@
         <v>647</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="C167" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>832</v>
+        <v>34</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="24" customHeight="1">
@@ -14161,13 +14242,13 @@
         <v>656</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="C168" s="2">
         <v>1</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>34</v>
@@ -14178,13 +14259,13 @@
         <v>663</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="C169" s="2">
         <v>1</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>34</v>
@@ -14195,13 +14276,13 @@
         <v>669</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="C170" s="2">
         <v>1</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>34</v>
@@ -14212,13 +14293,13 @@
         <v>675</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="C171" s="2">
         <v>1</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>34</v>
@@ -14229,13 +14310,13 @@
         <v>682</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="C172" s="2">
         <v>1</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>34</v>
@@ -14246,13 +14327,13 @@
         <v>690</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="C173" s="2">
         <v>1</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>34</v>
@@ -14263,13 +14344,13 @@
         <v>697</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="C174" s="2">
         <v>1</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>34</v>
@@ -14280,13 +14361,13 @@
         <v>704</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="C175" s="2">
         <v>1</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>34</v>
@@ -14297,13 +14378,13 @@
         <v>712</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="C176" s="2">
         <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>34</v>
@@ -14314,13 +14395,13 @@
         <v>719</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="C177" s="2">
         <v>1</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>34</v>
@@ -14331,16 +14412,16 @@
         <v>719</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="C178" s="2">
         <v>2</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="24" customHeight="1">
@@ -14348,16 +14429,16 @@
         <v>726</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="C179" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>1003</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>34</v>
+        <v>831</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="24" customHeight="1">
@@ -14365,16 +14446,16 @@
         <v>726</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="C180" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>832</v>
+        <v>34</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="24" customHeight="1">
@@ -14382,13 +14463,13 @@
         <v>734</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="C181" s="2">
         <v>1</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>34</v>
@@ -14399,16 +14480,16 @@
         <v>734</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="C182" s="2">
         <v>2</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1">
@@ -14416,16 +14497,16 @@
         <v>734</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="C183" s="2">
         <v>3</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -14433,7 +14514,7 @@
         <v>737</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="C184" s="2">
         <v>1</v>
@@ -14447,13 +14528,13 @@
         <v>737</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="C185" s="2">
         <v>2</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -14461,13 +14542,13 @@
         <v>737</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="C186" s="2">
         <v>3</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -14475,13 +14556,13 @@
         <v>737</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="C187" s="2">
         <v>4</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -14489,13 +14570,13 @@
         <v>743</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="C188" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>34</v>
+        <v>831</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -14503,13 +14584,13 @@
         <v>743</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="C189" s="2">
         <v>2</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -14517,13 +14598,13 @@
         <v>743</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="C190" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>832</v>
+        <v>34</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -14531,7 +14612,7 @@
         <v>748</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="C191" s="2">
         <v>1</v>
@@ -14545,13 +14626,13 @@
         <v>748</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="C192" s="2">
         <v>2</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -14559,13 +14640,13 @@
         <v>748</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="C193" s="2">
         <v>3</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -14573,13 +14654,13 @@
         <v>748</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="C194" s="2">
         <v>4</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -14587,13 +14668,13 @@
         <v>748</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="C195" s="2">
         <v>5</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -14601,13 +14682,13 @@
         <v>748</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="C196" s="2">
         <v>6</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -14615,21 +14696,21 @@
         <v>748</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="C197" s="2">
         <v>7</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="C198" s="2">
         <v>1</v>
@@ -14640,38 +14721,38 @@
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="C199" s="2">
         <v>2</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="C200" s="2">
         <v>3</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="C201" s="2">
         <v>1</v>
@@ -14682,10 +14763,10 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="C202" s="2">
         <v>1</v>
@@ -14696,24 +14777,24 @@
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="C203" s="2">
         <v>2</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="C204" s="2">
         <v>1</v>
@@ -14724,24 +14805,24 @@
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="C205" s="2">
         <v>2</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="C206" s="2">
         <v>1</v>
@@ -14752,38 +14833,38 @@
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="C207" s="2">
         <v>2</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="C208" s="2">
         <v>3</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="C209" s="2">
         <v>1</v>
@@ -14794,24 +14875,24 @@
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="C210" s="2">
         <v>2</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="C211" s="2">
         <v>1</v>
@@ -14822,10 +14903,10 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="C212" s="2">
         <v>1</v>
@@ -14836,10 +14917,10 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="C213" s="2">
         <v>1</v>
@@ -14850,10 +14931,10 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="C214" s="2">
         <v>1</v>
@@ -14864,10 +14945,10 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="C215" s="2">
         <v>1</v>
@@ -14878,24 +14959,24 @@
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
       <c r="C216" s="2">
         <v>2</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="C217" s="2">
         <v>1</v>
@@ -14906,10 +14987,10 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="C218" s="2">
         <v>1</v>
@@ -14920,10 +15001,10 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
       <c r="C219" s="2">
         <v>1</v>
@@ -14934,57 +15015,71 @@
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="C220" s="2">
         <v>2</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="C221" s="2">
         <v>3</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="C222" s="2">
         <v>4</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="C223" s="2">
         <v>1</v>
       </c>
       <c r="E223" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C224" s="2">
+        <v>1</v>
+      </c>
+      <c r="E224" s="2" t="s">
         <v>34</v>
       </c>
     </row>
@@ -15020,107 +15115,107 @@
   <sheetData>
     <row r="1" spans="1:6" ht="23" customHeight="1">
       <c r="A1" s="34" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+        <v>1007</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="35" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
+        <v>1008</v>
+      </c>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
     </row>
     <row r="4" spans="1:6" ht="46" customHeight="1">
       <c r="A4" s="33" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
+        <v>1009</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="35" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
+        <v>1010</v>
+      </c>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
     </row>
     <row r="7" spans="1:6" ht="54" customHeight="1">
       <c r="A7" s="33" t="s">
-        <v>1012</v>
-      </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
+        <v>1011</v>
+      </c>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
       <c r="A9" s="35" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
+        <v>1012</v>
+      </c>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
     </row>
     <row r="10" spans="1:6" ht="46" customHeight="1">
       <c r="A10" s="33" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
+        <v>1013</v>
+      </c>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
       <c r="A12" s="35" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
+        <v>1014</v>
+      </c>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
     </row>
     <row r="13" spans="1:6" ht="54" customHeight="1">
       <c r="A13" s="33" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
+        <v>1015</v>
+      </c>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
     </row>
     <row r="14" spans="1:6" ht="32" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="32" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="32" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
   </sheetData>

--- a/inventaire_mobilier.xlsx
+++ b/inventaire_mobilier.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolas.coquet/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1AC7F9-706F-684D-946B-48E37791C4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3678D88-D38A-CC41-82EA-BCD5B5D9E789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mobilier" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="1361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2458" uniqueCount="1362">
   <si>
     <t>Inventaire du mobilier</t>
   </si>
@@ -3933,18 +3933,6 @@
     <t>Vers 1910-1930</t>
   </si>
   <si>
-    <t>Ensemble sculptural en terre cuite : démon et scène figurée</t>
-  </si>
-  <si>
-    <t>Vue illustrée et notice de Cagliari encadrées</t>
-  </si>
-  <si>
-    <t>Porte-revues pliant en bois et cannage</t>
-  </si>
-  <si>
-    <t>Petit triptyque dévotionnel à la Vierge et aux anges</t>
-  </si>
-  <si>
     <t>Coiffe conique en fibres végétales et cuir</t>
   </si>
   <si>
@@ -4117,6 +4105,21 @@
   </si>
   <si>
     <t>MOB-105-02.webp</t>
+  </si>
+  <si>
+    <t>MOB-110-01.webp</t>
+  </si>
+  <si>
+    <t>Petit triptyque dévotionnel à la Vierge</t>
+  </si>
+  <si>
+    <t>Porte-revues en bois et cannage</t>
+  </si>
+  <si>
+    <t>Vue illustrée de Cagliari</t>
+  </si>
+  <si>
+    <t>Ensemble sculptural en terre cuite : démon et scène érotique</t>
   </si>
 </sst>
 </file>
@@ -4301,12 +4304,6 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4315,6 +4312,13 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4334,8 +4338,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4343,6 +4346,25 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="30">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -4747,25 +4769,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4905,33 +4908,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MobilierTable" displayName="MobilierTable" ref="A3:U113" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MobilierTable" displayName="MobilierTable" ref="A3:U113" totalsRowShown="0" headerRowDxfId="22" dataDxfId="0">
   <autoFilter ref="A3:U113" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:U113">
     <sortCondition ref="A3:A113"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Identifiant" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Catégorie" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Datation" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Origine" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Matériaux" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Description" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Dimensions" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="État" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Estimation unitaire basse (€)" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Estimation unitaire haute (€)" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Localisation" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Statut" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Publié" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Mots-clés" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Source 1" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Source 2" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Quantité" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Estimation du lot basse (€)" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Estimation du lot haute (€)" dataDxfId="1"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Associé à" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Identifiant" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Catégorie" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Datation" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Origine" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Matériaux" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Description" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Dimensions" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="État" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Estimation unitaire basse (€)" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Estimation unitaire haute (€)" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Localisation" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Statut" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Publié" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Mots-clés" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Source 1" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Source 2" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Quantité" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Estimation du lot basse (€)" dataDxfId="3"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Estimation du lot haute (€)" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Associé à" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5175,54 +5178,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="23">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
+      <c r="A2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
     </row>
     <row r="3" spans="1:21" s="5" customFormat="1" ht="32">
       <c r="A3" s="3" t="s">
@@ -8623,7 +8626,7 @@
         <v>120</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="M55" s="12" t="s">
         <v>33</v>
@@ -9294,7 +9297,7 @@
         <v>70</v>
       </c>
       <c r="L66" s="10" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="M66" s="12" t="s">
         <v>33</v>
@@ -11639,42 +11642,42 @@
       </c>
       <c r="U105" s="9"/>
     </row>
-    <row r="106" spans="1:21" ht="45">
+    <row r="106" spans="1:21" ht="42">
       <c r="A106" s="8" t="s">
         <v>1281</v>
       </c>
-      <c r="B106" s="22" t="s">
-        <v>1299</v>
-      </c>
-      <c r="C106" s="22" t="s">
+      <c r="B106" s="26" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C106" s="26" t="s">
         <v>790</v>
       </c>
-      <c r="D106" s="22" t="s">
+      <c r="D106" s="26" t="s">
         <v>1294</v>
       </c>
-      <c r="E106" s="22" t="s">
+      <c r="E106" s="26" t="s">
         <v>1288</v>
       </c>
-      <c r="F106" s="22" t="s">
-        <v>1307</v>
-      </c>
-      <c r="G106" s="22" t="s">
-        <v>1307</v>
+      <c r="F106" s="26" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G106" s="26" t="s">
+        <v>1303</v>
       </c>
       <c r="H106" s="9" t="s">
         <v>1025</v>
       </c>
-      <c r="I106" s="22" t="s">
-        <v>1314</v>
-      </c>
-      <c r="J106" s="23">
+      <c r="I106" s="26" t="s">
+        <v>1310</v>
+      </c>
+      <c r="J106" s="36">
         <v>120</v>
       </c>
-      <c r="K106" s="23">
+      <c r="K106" s="36">
         <v>300</v>
       </c>
       <c r="L106" s="9" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="M106" s="12" t="s">
         <v>33</v>
@@ -11688,50 +11691,50 @@
       <c r="R106" s="13">
         <v>1</v>
       </c>
-      <c r="S106" s="23">
+      <c r="S106" s="36">
         <v>120</v>
       </c>
-      <c r="T106" s="23">
+      <c r="T106" s="36">
         <v>300</v>
       </c>
       <c r="U106" s="9"/>
     </row>
-    <row r="107" spans="1:21" ht="30">
+    <row r="107" spans="1:21" ht="28">
       <c r="A107" s="8" t="s">
         <v>1282</v>
       </c>
-      <c r="B107" s="22" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C107" s="22" t="s">
-        <v>1306</v>
-      </c>
-      <c r="D107" s="22" t="s">
+      <c r="B107" s="26" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C107" s="26" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D107" s="26" t="s">
         <v>1295</v>
       </c>
-      <c r="E107" s="22" t="s">
+      <c r="E107" s="26" t="s">
         <v>627</v>
       </c>
-      <c r="F107" s="22" t="s">
-        <v>1308</v>
-      </c>
-      <c r="G107" s="22" t="s">
-        <v>1308</v>
+      <c r="F107" s="26" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G107" s="26" t="s">
+        <v>1304</v>
       </c>
       <c r="H107" s="9" t="s">
         <v>1025</v>
       </c>
-      <c r="I107" s="22" t="s">
-        <v>1315</v>
-      </c>
-      <c r="J107" s="23">
+      <c r="I107" s="26" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J107" s="36">
         <v>25</v>
       </c>
-      <c r="K107" s="23">
+      <c r="K107" s="36">
         <v>60</v>
       </c>
       <c r="L107" s="9" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="M107" s="12" t="s">
         <v>33</v>
@@ -11745,46 +11748,46 @@
       <c r="R107" s="13">
         <v>1</v>
       </c>
-      <c r="S107" s="23">
+      <c r="S107" s="36">
         <v>25</v>
       </c>
-      <c r="T107" s="23">
+      <c r="T107" s="36">
         <v>60</v>
       </c>
       <c r="U107" s="9"/>
     </row>
-    <row r="108" spans="1:21" ht="30">
+    <row r="108" spans="1:21">
       <c r="A108" s="8" t="s">
         <v>1283</v>
       </c>
-      <c r="B108" s="22" t="s">
-        <v>1301</v>
-      </c>
-      <c r="C108" s="22" t="s">
+      <c r="B108" s="26" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C108" s="26" t="s">
         <v>1017</v>
       </c>
-      <c r="D108" s="22" t="s">
+      <c r="D108" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="E108" s="22" t="s">
+      <c r="E108" s="26" t="s">
         <v>1289</v>
       </c>
-      <c r="F108" s="22" t="s">
-        <v>1309</v>
-      </c>
-      <c r="G108" s="22" t="s">
-        <v>1309</v>
+      <c r="F108" s="26" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G108" s="26" t="s">
+        <v>1305</v>
       </c>
       <c r="H108" s="9" t="s">
         <v>1025</v>
       </c>
-      <c r="I108" s="22" t="s">
-        <v>1316</v>
-      </c>
-      <c r="J108" s="23">
+      <c r="I108" s="26" t="s">
+        <v>1312</v>
+      </c>
+      <c r="J108" s="36">
         <v>60</v>
       </c>
-      <c r="K108" s="23">
+      <c r="K108" s="36">
         <v>120</v>
       </c>
       <c r="L108" s="9" t="s">
@@ -11802,46 +11805,46 @@
       <c r="R108" s="13">
         <v>1</v>
       </c>
-      <c r="S108" s="23">
+      <c r="S108" s="36">
         <v>60</v>
       </c>
-      <c r="T108" s="23">
+      <c r="T108" s="36">
         <v>120</v>
       </c>
       <c r="U108" s="9"/>
     </row>
-    <row r="109" spans="1:21" ht="30">
+    <row r="109" spans="1:21" ht="28">
       <c r="A109" s="8" t="s">
         <v>1284</v>
       </c>
-      <c r="B109" s="22" t="s">
-        <v>1302</v>
-      </c>
-      <c r="C109" s="22" t="s">
+      <c r="B109" s="26" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C109" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="D109" s="22" t="s">
+      <c r="D109" s="26" t="s">
         <v>1296</v>
       </c>
-      <c r="E109" s="22" t="s">
+      <c r="E109" s="26" t="s">
         <v>1290</v>
       </c>
-      <c r="F109" s="22" t="s">
-        <v>1310</v>
-      </c>
-      <c r="G109" s="22" t="s">
-        <v>1310</v>
+      <c r="F109" s="26" t="s">
+        <v>1306</v>
+      </c>
+      <c r="G109" s="26" t="s">
+        <v>1306</v>
       </c>
       <c r="H109" s="9" t="s">
         <v>1025</v>
       </c>
-      <c r="I109" s="22" t="s">
-        <v>1317</v>
-      </c>
-      <c r="J109" s="23">
+      <c r="I109" s="26" t="s">
+        <v>1313</v>
+      </c>
+      <c r="J109" s="36">
         <v>30</v>
       </c>
-      <c r="K109" s="23">
+      <c r="K109" s="36">
         <v>70</v>
       </c>
       <c r="L109" s="9" t="s">
@@ -11859,46 +11862,46 @@
       <c r="R109" s="13">
         <v>1</v>
       </c>
-      <c r="S109" s="23">
+      <c r="S109" s="36">
         <v>30</v>
       </c>
-      <c r="T109" s="23">
+      <c r="T109" s="36">
         <v>70</v>
       </c>
       <c r="U109" s="9"/>
     </row>
-    <row r="110" spans="1:21" ht="45">
+    <row r="110" spans="1:21" ht="42">
       <c r="A110" s="8" t="s">
         <v>1285</v>
       </c>
-      <c r="B110" s="22" t="s">
-        <v>1303</v>
-      </c>
-      <c r="C110" s="22" t="s">
+      <c r="B110" s="26" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C110" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="D110" s="22" t="s">
+      <c r="D110" s="26" t="s">
         <v>689</v>
       </c>
-      <c r="E110" s="22" t="s">
+      <c r="E110" s="26" t="s">
         <v>1291</v>
       </c>
-      <c r="F110" s="22" t="s">
-        <v>1311</v>
-      </c>
-      <c r="G110" s="22" t="s">
-        <v>1311</v>
+      <c r="F110" s="26" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G110" s="26" t="s">
+        <v>1307</v>
       </c>
       <c r="H110" s="9" t="s">
         <v>1025</v>
       </c>
-      <c r="I110" s="22" t="s">
-        <v>1318</v>
-      </c>
-      <c r="J110" s="23">
+      <c r="I110" s="26" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J110" s="36">
         <v>50</v>
       </c>
-      <c r="K110" s="23">
+      <c r="K110" s="36">
         <v>120</v>
       </c>
       <c r="L110" s="9" t="s">
@@ -11916,46 +11919,46 @@
       <c r="R110" s="13">
         <v>1</v>
       </c>
-      <c r="S110" s="23">
+      <c r="S110" s="36">
         <v>50</v>
       </c>
-      <c r="T110" s="23">
+      <c r="T110" s="36">
         <v>120</v>
       </c>
       <c r="U110" s="9"/>
     </row>
-    <row r="111" spans="1:21" ht="30">
+    <row r="111" spans="1:21" ht="28">
       <c r="A111" s="8" t="s">
         <v>1286</v>
       </c>
-      <c r="B111" s="22" t="s">
-        <v>1304</v>
-      </c>
-      <c r="C111" s="22" t="s">
+      <c r="B111" s="26" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C111" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="D111" s="22" t="s">
+      <c r="D111" s="26" t="s">
         <v>1297</v>
       </c>
-      <c r="E111" s="22" t="s">
+      <c r="E111" s="26" t="s">
         <v>1292</v>
       </c>
-      <c r="F111" s="22" t="s">
-        <v>1312</v>
-      </c>
-      <c r="G111" s="22" t="s">
-        <v>1312</v>
+      <c r="F111" s="26" t="s">
+        <v>1308</v>
+      </c>
+      <c r="G111" s="26" t="s">
+        <v>1308</v>
       </c>
       <c r="H111" s="9" t="s">
         <v>1025</v>
       </c>
-      <c r="I111" s="22" t="s">
-        <v>1319</v>
-      </c>
-      <c r="J111" s="23">
+      <c r="I111" s="26" t="s">
+        <v>1315</v>
+      </c>
+      <c r="J111" s="36">
         <v>30</v>
       </c>
-      <c r="K111" s="23">
+      <c r="K111" s="36">
         <v>80</v>
       </c>
       <c r="L111" s="9" t="s">
@@ -11973,46 +11976,46 @@
       <c r="R111" s="13">
         <v>1</v>
       </c>
-      <c r="S111" s="23">
+      <c r="S111" s="36">
         <v>30</v>
       </c>
-      <c r="T111" s="23">
+      <c r="T111" s="36">
         <v>80</v>
       </c>
       <c r="U111" s="9"/>
     </row>
-    <row r="112" spans="1:21" ht="15">
+    <row r="112" spans="1:21">
       <c r="A112" s="8" t="s">
         <v>1287</v>
       </c>
-      <c r="B112" s="22" t="s">
-        <v>1305</v>
-      </c>
-      <c r="C112" s="22" t="s">
+      <c r="B112" s="26" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C112" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="D112" s="22" t="s">
+      <c r="D112" s="26" t="s">
         <v>1298</v>
       </c>
-      <c r="E112" s="22" t="s">
+      <c r="E112" s="26" t="s">
         <v>1293</v>
       </c>
-      <c r="F112" s="22" t="s">
-        <v>1313</v>
-      </c>
-      <c r="G112" s="22" t="s">
-        <v>1313</v>
+      <c r="F112" s="26" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G112" s="26" t="s">
+        <v>1309</v>
       </c>
       <c r="H112" s="9" t="s">
         <v>1025</v>
       </c>
-      <c r="I112" s="22" t="s">
-        <v>1320</v>
-      </c>
-      <c r="J112" s="23">
+      <c r="I112" s="26" t="s">
+        <v>1316</v>
+      </c>
+      <c r="J112" s="36">
         <v>80</v>
       </c>
-      <c r="K112" s="23">
+      <c r="K112" s="36">
         <v>180</v>
       </c>
       <c r="L112" s="9" t="s">
@@ -12030,10 +12033,10 @@
       <c r="R112" s="13">
         <v>1</v>
       </c>
-      <c r="S112" s="23">
+      <c r="S112" s="36">
         <v>80</v>
       </c>
-      <c r="T112" s="23">
+      <c r="T112" s="36">
         <v>180</v>
       </c>
       <c r="U112" s="9"/>
@@ -12131,22 +12134,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" ht="34" customHeight="1">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="30" t="s">
         <v>819</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>820</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
     </row>
     <row r="3" spans="1:5" s="7" customFormat="1" ht="16" customHeight="1">
       <c r="A3" s="6" t="s">
@@ -12166,1260 +12169,1260 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="23" t="s">
         <v>1040</v>
       </c>
-      <c r="C4" s="26">
-        <v>1</v>
-      </c>
-      <c r="D4" s="25" t="s">
+      <c r="C4" s="24">
+        <v>1</v>
+      </c>
+      <c r="D4" s="23" t="s">
         <v>826</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="23" t="s">
         <v>1041</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="24">
         <v>2</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="23" t="s">
         <v>827</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="23" t="s">
         <v>1042</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="24">
         <v>3</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="23" t="s">
         <v>829</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="23" t="s">
         <v>1043</v>
       </c>
-      <c r="C7" s="25">
-        <v>1</v>
-      </c>
-      <c r="D7" s="25" t="s">
+      <c r="C7" s="23">
+        <v>1</v>
+      </c>
+      <c r="D7" s="23" t="s">
         <v>830</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="23" t="s">
         <v>1044</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="23">
         <v>2</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="23" t="s">
         <v>831</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="23" t="s">
         <v>1045</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="23">
         <v>3</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="23" t="s">
         <v>832</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="23" t="s">
         <v>1046</v>
       </c>
-      <c r="C10" s="25">
-        <v>1</v>
-      </c>
-      <c r="D10" s="25" t="s">
+      <c r="C10" s="23">
+        <v>1</v>
+      </c>
+      <c r="D10" s="23" t="s">
         <v>833</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="23" t="s">
         <v>1047</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="23">
         <v>2</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="23" t="s">
         <v>834</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="23" t="s">
         <v>1048</v>
       </c>
-      <c r="C12" s="25">
-        <v>1</v>
-      </c>
-      <c r="D12" s="25" t="s">
+      <c r="C12" s="23">
+        <v>1</v>
+      </c>
+      <c r="D12" s="23" t="s">
         <v>835</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="23" t="s">
         <v>1049</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="23">
         <v>3</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="23" t="s">
         <v>836</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="23" t="s">
         <v>1050</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="23">
         <v>3</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="23" t="s">
         <v>837</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="23" t="s">
         <v>1051</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="23">
         <v>2</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="23" t="s">
         <v>838</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="23" t="s">
         <v>1052</v>
       </c>
-      <c r="C16" s="25">
-        <v>1</v>
-      </c>
-      <c r="D16" s="25" t="s">
+      <c r="C16" s="23">
+        <v>1</v>
+      </c>
+      <c r="D16" s="23" t="s">
         <v>839</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="23" t="s">
         <v>1055</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="23">
         <v>2</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="23" t="s">
         <v>842</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="23" t="s">
         <v>1056</v>
       </c>
-      <c r="C18" s="25">
-        <v>1</v>
-      </c>
-      <c r="D18" s="25" t="s">
+      <c r="C18" s="23">
+        <v>1</v>
+      </c>
+      <c r="D18" s="23" t="s">
         <v>843</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="E18" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="23" t="s">
         <v>1057</v>
       </c>
-      <c r="C19" s="25">
-        <v>1</v>
-      </c>
-      <c r="D19" s="25" t="s">
+      <c r="C19" s="23">
+        <v>1</v>
+      </c>
+      <c r="D19" s="23" t="s">
         <v>844</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="E19" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="23" t="s">
         <v>1058</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="23">
         <v>2</v>
       </c>
-      <c r="D20" s="25" t="s">
+      <c r="D20" s="23" t="s">
         <v>845</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="E20" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="23" t="s">
         <v>1059</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="23">
         <v>3</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="23" t="s">
         <v>846</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="23" t="s">
         <v>1060</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="23">
         <v>4</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="D22" s="23" t="s">
         <v>847</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="23" t="s">
         <v>1061</v>
       </c>
-      <c r="C23" s="25">
-        <v>1</v>
-      </c>
-      <c r="D23" s="25" t="s">
+      <c r="C23" s="23">
+        <v>1</v>
+      </c>
+      <c r="D23" s="23" t="s">
         <v>848</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="E23" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="B24" s="25" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C24" s="25">
+      <c r="B24" s="23" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C24" s="23">
         <v>2</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="D24" s="23" t="s">
         <v>883</v>
       </c>
-      <c r="E24" s="25" t="s">
+      <c r="E24" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="B25" s="25" t="s">
-        <v>1358</v>
-      </c>
-      <c r="C25" s="25">
+      <c r="B25" s="23" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C25" s="23">
         <v>3</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="23" t="s">
         <v>884</v>
       </c>
-      <c r="E25" s="25" t="s">
+      <c r="E25" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="B26" s="25" t="s">
-        <v>1359</v>
-      </c>
-      <c r="C26" s="25">
+      <c r="B26" s="23" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C26" s="23">
         <v>4</v>
       </c>
-      <c r="D26" s="25" t="s">
+      <c r="D26" s="23" t="s">
         <v>885</v>
       </c>
-      <c r="E26" s="25" t="s">
+      <c r="E26" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="23" t="s">
         <v>1062</v>
       </c>
-      <c r="C27" s="25">
-        <v>1</v>
-      </c>
-      <c r="D27" s="25" t="s">
+      <c r="C27" s="23">
+        <v>1</v>
+      </c>
+      <c r="D27" s="23" t="s">
         <v>849</v>
       </c>
-      <c r="E27" s="25" t="s">
+      <c r="E27" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="23" t="s">
         <v>1063</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="23">
         <v>2</v>
       </c>
-      <c r="D28" s="25" t="s">
+      <c r="D28" s="23" t="s">
         <v>850</v>
       </c>
-      <c r="E28" s="25" t="s">
+      <c r="E28" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="23" t="s">
         <v>1064</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="23">
         <v>3</v>
       </c>
-      <c r="D29" s="25" t="s">
+      <c r="D29" s="23" t="s">
         <v>848</v>
       </c>
-      <c r="E29" s="25" t="s">
+      <c r="E29" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="23" t="s">
         <v>1065</v>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="23">
         <v>4</v>
       </c>
-      <c r="D30" s="25" t="s">
+      <c r="D30" s="23" t="s">
         <v>851</v>
       </c>
-      <c r="E30" s="25" t="s">
+      <c r="E30" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="23" t="s">
         <v>1066</v>
       </c>
-      <c r="C31" s="25">
-        <v>1</v>
-      </c>
-      <c r="D31" s="25" t="s">
+      <c r="C31" s="23">
+        <v>1</v>
+      </c>
+      <c r="D31" s="23" t="s">
         <v>852</v>
       </c>
-      <c r="E31" s="25" t="s">
+      <c r="E31" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="23" t="s">
         <v>1067</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="23">
         <v>2</v>
       </c>
-      <c r="D32" s="25" t="s">
+      <c r="D32" s="23" t="s">
         <v>853</v>
       </c>
-      <c r="E32" s="25" t="s">
+      <c r="E32" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="23" t="s">
         <v>1068</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="23">
         <v>3</v>
       </c>
-      <c r="D33" s="25" t="s">
+      <c r="D33" s="23" t="s">
         <v>854</v>
       </c>
-      <c r="E33" s="25" t="s">
+      <c r="E33" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="23" t="s">
         <v>1069</v>
       </c>
-      <c r="C34" s="25">
-        <v>1</v>
-      </c>
-      <c r="D34" s="25" t="s">
+      <c r="C34" s="23">
+        <v>1</v>
+      </c>
+      <c r="D34" s="23" t="s">
         <v>855</v>
       </c>
-      <c r="E34" s="25" t="s">
+      <c r="E34" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" customHeight="1">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="23" t="s">
         <v>1070</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="23">
         <v>2</v>
       </c>
-      <c r="D35" s="25" t="s">
+      <c r="D35" s="23" t="s">
         <v>856</v>
       </c>
-      <c r="E35" s="25" t="s">
+      <c r="E35" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1">
-      <c r="A36" s="25" t="s">
+      <c r="A36" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B36" s="23" t="s">
         <v>1071</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="23">
         <v>3</v>
       </c>
-      <c r="D36" s="25" t="s">
+      <c r="D36" s="23" t="s">
         <v>857</v>
       </c>
-      <c r="E36" s="25" t="s">
+      <c r="E36" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1">
-      <c r="A37" s="25" t="s">
+      <c r="A37" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="B37" s="25" t="s">
+      <c r="B37" s="23" t="s">
         <v>1072</v>
       </c>
-      <c r="C37" s="25">
-        <v>1</v>
-      </c>
-      <c r="D37" s="25" t="s">
+      <c r="C37" s="23">
+        <v>1</v>
+      </c>
+      <c r="D37" s="23" t="s">
         <v>858</v>
       </c>
-      <c r="E37" s="25" t="s">
+      <c r="E37" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1">
-      <c r="A38" s="25" t="s">
+      <c r="A38" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B38" s="23" t="s">
         <v>1073</v>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="23">
         <v>2</v>
       </c>
-      <c r="D38" s="25" t="s">
+      <c r="D38" s="23" t="s">
         <v>859</v>
       </c>
-      <c r="E38" s="25" t="s">
+      <c r="E38" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1">
-      <c r="A39" s="25" t="s">
+      <c r="A39" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="23" t="s">
         <v>1074</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="23">
         <v>3</v>
       </c>
-      <c r="D39" s="25" t="s">
+      <c r="D39" s="23" t="s">
         <v>860</v>
       </c>
-      <c r="E39" s="25" t="s">
+      <c r="E39" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="B40" s="25" t="s">
+      <c r="B40" s="23" t="s">
         <v>1075</v>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="23">
         <v>4</v>
       </c>
-      <c r="D40" s="25" t="s">
+      <c r="D40" s="23" t="s">
         <v>861</v>
       </c>
-      <c r="E40" s="25" t="s">
+      <c r="E40" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1">
-      <c r="A41" s="25" t="s">
+      <c r="A41" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="B41" s="25" t="s">
+      <c r="B41" s="23" t="s">
         <v>1076</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="23">
         <v>5</v>
       </c>
-      <c r="D41" s="25" t="s">
+      <c r="D41" s="23" t="s">
         <v>862</v>
       </c>
-      <c r="E41" s="25" t="s">
+      <c r="E41" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15" customHeight="1">
-      <c r="A42" s="25" t="s">
+      <c r="A42" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="B42" s="25" t="s">
+      <c r="B42" s="23" t="s">
         <v>1077</v>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="23">
         <v>6</v>
       </c>
-      <c r="D42" s="25" t="s">
+      <c r="D42" s="23" t="s">
         <v>863</v>
       </c>
-      <c r="E42" s="25" t="s">
+      <c r="E42" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15" customHeight="1">
-      <c r="A43" s="25" t="s">
+      <c r="A43" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="B43" s="25" t="s">
+      <c r="B43" s="23" t="s">
         <v>1078</v>
       </c>
-      <c r="C43" s="25">
-        <v>1</v>
-      </c>
-      <c r="D43" s="25" t="s">
+      <c r="C43" s="23">
+        <v>1</v>
+      </c>
+      <c r="D43" s="23" t="s">
         <v>864</v>
       </c>
-      <c r="E43" s="25" t="s">
+      <c r="E43" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15" customHeight="1">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B44" s="23" t="s">
         <v>1079</v>
       </c>
-      <c r="C44" s="25">
-        <v>1</v>
-      </c>
-      <c r="D44" s="25" t="s">
+      <c r="C44" s="23">
+        <v>1</v>
+      </c>
+      <c r="D44" s="23" t="s">
         <v>865</v>
       </c>
-      <c r="E44" s="25" t="s">
+      <c r="E44" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15" customHeight="1">
-      <c r="A45" s="25" t="s">
+      <c r="A45" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="B45" s="25" t="s">
+      <c r="B45" s="23" t="s">
         <v>1080</v>
       </c>
-      <c r="C45" s="25">
-        <v>1</v>
-      </c>
-      <c r="D45" s="25" t="s">
+      <c r="C45" s="23">
+        <v>1</v>
+      </c>
+      <c r="D45" s="23" t="s">
         <v>866</v>
       </c>
-      <c r="E45" s="25" t="s">
+      <c r="E45" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15" customHeight="1">
-      <c r="A46" s="25" t="s">
+      <c r="A46" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="B46" s="25" t="s">
+      <c r="B46" s="23" t="s">
         <v>1081</v>
       </c>
-      <c r="C46" s="25">
-        <v>1</v>
-      </c>
-      <c r="D46" s="25" t="s">
+      <c r="C46" s="23">
+        <v>1</v>
+      </c>
+      <c r="D46" s="23" t="s">
         <v>867</v>
       </c>
-      <c r="E46" s="25" t="s">
+      <c r="E46" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15" customHeight="1">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="B47" s="25" t="s">
+      <c r="B47" s="23" t="s">
         <v>1082</v>
       </c>
-      <c r="C47" s="25">
-        <v>1</v>
-      </c>
-      <c r="D47" s="25" t="s">
+      <c r="C47" s="23">
+        <v>1</v>
+      </c>
+      <c r="D47" s="23" t="s">
         <v>868</v>
       </c>
-      <c r="E47" s="25" t="s">
+      <c r="E47" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" customHeight="1">
-      <c r="A48" s="25" t="s">
+      <c r="A48" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B48" s="23" t="s">
         <v>1083</v>
       </c>
-      <c r="C48" s="25">
+      <c r="C48" s="23">
         <v>2</v>
       </c>
-      <c r="D48" s="25" t="s">
+      <c r="D48" s="23" t="s">
         <v>869</v>
       </c>
-      <c r="E48" s="25" t="s">
+      <c r="E48" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B49" s="23" t="s">
         <v>1084</v>
       </c>
-      <c r="C49" s="25">
-        <v>1</v>
-      </c>
-      <c r="D49" s="25" t="s">
+      <c r="C49" s="23">
+        <v>1</v>
+      </c>
+      <c r="D49" s="23" t="s">
         <v>870</v>
       </c>
-      <c r="E49" s="25" t="s">
+      <c r="E49" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15" customHeight="1">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="B50" s="25" t="s">
+      <c r="B50" s="23" t="s">
         <v>1085</v>
       </c>
-      <c r="C50" s="25">
+      <c r="C50" s="23">
         <v>2</v>
       </c>
-      <c r="D50" s="25" t="s">
+      <c r="D50" s="23" t="s">
         <v>871</v>
       </c>
-      <c r="E50" s="25" t="s">
+      <c r="E50" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15" customHeight="1">
-      <c r="A51" s="25" t="s">
+      <c r="A51" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="B51" s="25" t="s">
+      <c r="B51" s="23" t="s">
         <v>1086</v>
       </c>
-      <c r="C51" s="25">
+      <c r="C51" s="23">
         <v>3</v>
       </c>
-      <c r="D51" s="25" t="s">
+      <c r="D51" s="23" t="s">
         <v>872</v>
       </c>
-      <c r="E51" s="25" t="s">
+      <c r="E51" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15" customHeight="1">
-      <c r="A52" s="25" t="s">
+      <c r="A52" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="B52" s="25" t="s">
+      <c r="B52" s="23" t="s">
         <v>1087</v>
       </c>
-      <c r="C52" s="25">
-        <v>1</v>
-      </c>
-      <c r="D52" s="25" t="s">
+      <c r="C52" s="23">
+        <v>1</v>
+      </c>
+      <c r="D52" s="23" t="s">
         <v>873</v>
       </c>
-      <c r="E52" s="25" t="s">
+      <c r="E52" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15" customHeight="1">
-      <c r="A53" s="25" t="s">
+      <c r="A53" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="B53" s="25" t="s">
+      <c r="B53" s="23" t="s">
         <v>1088</v>
       </c>
-      <c r="C53" s="25">
+      <c r="C53" s="23">
         <v>2</v>
       </c>
-      <c r="D53" s="25" t="s">
+      <c r="D53" s="23" t="s">
         <v>874</v>
       </c>
-      <c r="E53" s="25" t="s">
+      <c r="E53" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15" customHeight="1">
-      <c r="A54" s="25" t="s">
+      <c r="A54" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="B54" s="25" t="s">
+      <c r="B54" s="23" t="s">
         <v>1089</v>
       </c>
-      <c r="C54" s="25">
+      <c r="C54" s="23">
         <v>3</v>
       </c>
-      <c r="D54" s="25" t="s">
+      <c r="D54" s="23" t="s">
         <v>875</v>
       </c>
-      <c r="E54" s="25" t="s">
+      <c r="E54" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15" customHeight="1">
-      <c r="A55" s="25" t="s">
+      <c r="A55" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="B55" s="25" t="s">
+      <c r="B55" s="23" t="s">
         <v>1090</v>
       </c>
-      <c r="C55" s="25">
-        <v>1</v>
-      </c>
-      <c r="D55" s="25" t="s">
+      <c r="C55" s="23">
+        <v>1</v>
+      </c>
+      <c r="D55" s="23" t="s">
         <v>876</v>
       </c>
-      <c r="E55" s="25" t="s">
+      <c r="E55" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15" customHeight="1">
-      <c r="A56" s="25" t="s">
+      <c r="A56" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="B56" s="25" t="s">
+      <c r="B56" s="23" t="s">
         <v>1091</v>
       </c>
-      <c r="C56" s="25">
+      <c r="C56" s="23">
         <v>2</v>
       </c>
-      <c r="D56" s="25" t="s">
+      <c r="D56" s="23" t="s">
         <v>877</v>
       </c>
-      <c r="E56" s="25" t="s">
+      <c r="E56" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15" customHeight="1">
-      <c r="A57" s="25" t="s">
+      <c r="A57" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="B57" s="25" t="s">
+      <c r="B57" s="23" t="s">
         <v>1092</v>
       </c>
-      <c r="C57" s="25">
-        <v>1</v>
-      </c>
-      <c r="D57" s="25" t="s">
+      <c r="C57" s="23">
+        <v>1</v>
+      </c>
+      <c r="D57" s="23" t="s">
         <v>878</v>
       </c>
-      <c r="E57" s="25" t="s">
+      <c r="E57" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15" customHeight="1">
-      <c r="A58" s="25" t="s">
+      <c r="A58" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="B58" s="25" t="s">
+      <c r="B58" s="23" t="s">
         <v>1093</v>
       </c>
-      <c r="C58" s="25">
-        <v>1</v>
-      </c>
-      <c r="D58" s="25" t="s">
+      <c r="C58" s="23">
+        <v>1</v>
+      </c>
+      <c r="D58" s="23" t="s">
         <v>879</v>
       </c>
-      <c r="E58" s="25" t="s">
+      <c r="E58" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15" customHeight="1">
-      <c r="A59" s="25" t="s">
+      <c r="A59" s="23" t="s">
         <v>252</v>
       </c>
-      <c r="B59" s="25" t="s">
+      <c r="B59" s="23" t="s">
         <v>1094</v>
       </c>
-      <c r="C59" s="25">
-        <v>1</v>
-      </c>
-      <c r="D59" s="25" t="s">
+      <c r="C59" s="23">
+        <v>1</v>
+      </c>
+      <c r="D59" s="23" t="s">
         <v>880</v>
       </c>
-      <c r="E59" s="25" t="s">
+      <c r="E59" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15" customHeight="1">
-      <c r="A60" s="25" t="s">
+      <c r="A60" s="23" t="s">
         <v>252</v>
       </c>
-      <c r="B60" s="25" t="s">
+      <c r="B60" s="23" t="s">
         <v>1095</v>
       </c>
-      <c r="C60" s="25">
+      <c r="C60" s="23">
         <v>2</v>
       </c>
-      <c r="D60" s="25" t="s">
+      <c r="D60" s="23" t="s">
         <v>881</v>
       </c>
-      <c r="E60" s="25" t="s">
+      <c r="E60" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="30" customHeight="1">
-      <c r="A61" s="25" t="s">
+      <c r="A61" s="23" t="s">
         <v>263</v>
       </c>
-      <c r="B61" s="25" t="s">
+      <c r="B61" s="23" t="s">
         <v>1096</v>
       </c>
-      <c r="C61" s="25">
-        <v>1</v>
-      </c>
-      <c r="D61" s="25" t="s">
+      <c r="C61" s="23">
+        <v>1</v>
+      </c>
+      <c r="D61" s="23" t="s">
         <v>882</v>
       </c>
-      <c r="E61" s="25" t="s">
+      <c r="E61" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15" customHeight="1">
-      <c r="A62" s="25" t="s">
+      <c r="A62" s="23" t="s">
         <v>273</v>
       </c>
-      <c r="B62" s="25" t="s">
+      <c r="B62" s="23" t="s">
         <v>1097</v>
       </c>
-      <c r="C62" s="25">
-        <v>1</v>
-      </c>
-      <c r="D62" s="25" t="s">
+      <c r="C62" s="23">
+        <v>1</v>
+      </c>
+      <c r="D62" s="23" t="s">
         <v>886</v>
       </c>
-      <c r="E62" s="25" t="s">
+      <c r="E62" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15" customHeight="1">
-      <c r="A63" s="25" t="s">
+      <c r="A63" s="23" t="s">
         <v>285</v>
       </c>
-      <c r="B63" s="25" t="s">
+      <c r="B63" s="23" t="s">
         <v>1098</v>
       </c>
-      <c r="C63" s="25">
-        <v>1</v>
-      </c>
-      <c r="D63" s="25" t="s">
+      <c r="C63" s="23">
+        <v>1</v>
+      </c>
+      <c r="D63" s="23" t="s">
         <v>887</v>
       </c>
-      <c r="E63" s="25" t="s">
+      <c r="E63" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15" customHeight="1">
-      <c r="A64" s="25" t="s">
+      <c r="A64" s="23" t="s">
         <v>285</v>
       </c>
-      <c r="B64" s="25" t="s">
+      <c r="B64" s="23" t="s">
         <v>1099</v>
       </c>
-      <c r="C64" s="25">
+      <c r="C64" s="23">
         <v>2</v>
       </c>
-      <c r="D64" s="25" t="s">
+      <c r="D64" s="23" t="s">
         <v>888</v>
       </c>
-      <c r="E64" s="25" t="s">
+      <c r="E64" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15" customHeight="1">
-      <c r="A65" s="25" t="s">
+      <c r="A65" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="B65" s="25" t="s">
+      <c r="B65" s="23" t="s">
         <v>1100</v>
       </c>
-      <c r="C65" s="25">
-        <v>1</v>
-      </c>
-      <c r="D65" s="25" t="s">
+      <c r="C65" s="23">
+        <v>1</v>
+      </c>
+      <c r="D65" s="23" t="s">
         <v>889</v>
       </c>
-      <c r="E65" s="25" t="s">
+      <c r="E65" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15" customHeight="1">
-      <c r="A66" s="25" t="s">
+      <c r="A66" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="B66" s="25" t="s">
+      <c r="B66" s="23" t="s">
         <v>1101</v>
       </c>
-      <c r="C66" s="25">
+      <c r="C66" s="23">
         <v>2</v>
       </c>
-      <c r="D66" s="25" t="s">
+      <c r="D66" s="23" t="s">
         <v>890</v>
       </c>
-      <c r="E66" s="25" t="s">
+      <c r="E66" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15" customHeight="1">
-      <c r="A67" s="25" t="s">
+      <c r="A67" s="23" t="s">
         <v>302</v>
       </c>
-      <c r="B67" s="25" t="s">
+      <c r="B67" s="23" t="s">
         <v>1102</v>
       </c>
-      <c r="C67" s="25">
-        <v>1</v>
-      </c>
-      <c r="D67" s="25" t="s">
+      <c r="C67" s="23">
+        <v>1</v>
+      </c>
+      <c r="D67" s="23" t="s">
         <v>891</v>
       </c>
-      <c r="E67" s="25" t="s">
+      <c r="E67" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15" customHeight="1">
-      <c r="A68" s="25" t="s">
+      <c r="A68" s="23" t="s">
         <v>312</v>
       </c>
-      <c r="B68" s="25" t="s">
+      <c r="B68" s="23" t="s">
         <v>1103</v>
       </c>
-      <c r="C68" s="25">
+      <c r="C68" s="23">
         <v>2</v>
       </c>
-      <c r="D68" s="25" t="s">
+      <c r="D68" s="23" t="s">
         <v>1257</v>
       </c>
-      <c r="E68" s="25" t="s">
+      <c r="E68" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15" customHeight="1">
-      <c r="A69" s="25" t="s">
+      <c r="A69" s="23" t="s">
         <v>312</v>
       </c>
-      <c r="B69" s="25" t="s">
+      <c r="B69" s="23" t="s">
         <v>1104</v>
       </c>
-      <c r="C69" s="25">
-        <v>1</v>
-      </c>
-      <c r="D69" s="25" t="s">
+      <c r="C69" s="23">
+        <v>1</v>
+      </c>
+      <c r="D69" s="23" t="s">
         <v>1258</v>
       </c>
-      <c r="E69" s="25" t="s">
+      <c r="E69" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15" customHeight="1">
-      <c r="A70" s="25" t="s">
+      <c r="A70" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="B70" s="25" t="s">
+      <c r="B70" s="23" t="s">
         <v>1105</v>
       </c>
-      <c r="C70" s="25">
-        <v>1</v>
-      </c>
-      <c r="D70" s="25" t="s">
+      <c r="C70" s="23">
+        <v>1</v>
+      </c>
+      <c r="D70" s="23" t="s">
         <v>892</v>
       </c>
-      <c r="E70" s="25" t="s">
+      <c r="E70" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15" customHeight="1">
-      <c r="A71" s="25" t="s">
+      <c r="A71" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="B71" s="25" t="s">
+      <c r="B71" s="23" t="s">
         <v>1106</v>
       </c>
-      <c r="C71" s="25">
+      <c r="C71" s="23">
         <v>2</v>
       </c>
-      <c r="D71" s="25" t="s">
+      <c r="D71" s="23" t="s">
         <v>893</v>
       </c>
-      <c r="E71" s="25" t="s">
+      <c r="E71" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15" customHeight="1">
-      <c r="A72" s="25" t="s">
+      <c r="A72" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="B72" s="25" t="s">
+      <c r="B72" s="23" t="s">
         <v>1107</v>
       </c>
-      <c r="C72" s="25">
-        <v>1</v>
-      </c>
-      <c r="D72" s="25" t="s">
+      <c r="C72" s="23">
+        <v>1</v>
+      </c>
+      <c r="D72" s="23" t="s">
         <v>894</v>
       </c>
-      <c r="E72" s="25" t="s">
+      <c r="E72" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15" customHeight="1">
-      <c r="A73" s="25" t="s">
+      <c r="A73" s="23" t="s">
         <v>344</v>
       </c>
-      <c r="B73" s="25" t="s">
+      <c r="B73" s="23" t="s">
         <v>1108</v>
       </c>
-      <c r="C73" s="25">
-        <v>1</v>
-      </c>
-      <c r="D73" s="25" t="s">
+      <c r="C73" s="23">
+        <v>1</v>
+      </c>
+      <c r="D73" s="23" t="s">
         <v>895</v>
       </c>
-      <c r="E73" s="25" t="s">
+      <c r="E73" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15" customHeight="1">
-      <c r="A74" s="25" t="s">
+      <c r="A74" s="23" t="s">
         <v>344</v>
       </c>
-      <c r="B74" s="25" t="s">
+      <c r="B74" s="23" t="s">
         <v>1109</v>
       </c>
-      <c r="C74" s="25">
+      <c r="C74" s="23">
         <v>2</v>
       </c>
-      <c r="D74" s="25" t="s">
+      <c r="D74" s="23" t="s">
         <v>896</v>
       </c>
-      <c r="E74" s="25" t="s">
+      <c r="E74" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="15" customHeight="1">
-      <c r="A75" s="25" t="s">
+      <c r="A75" s="23" t="s">
         <v>356</v>
       </c>
-      <c r="B75" s="25" t="s">
+      <c r="B75" s="23" t="s">
         <v>1110</v>
       </c>
-      <c r="C75" s="25">
-        <v>1</v>
-      </c>
-      <c r="D75" s="25" t="s">
+      <c r="C75" s="23">
+        <v>1</v>
+      </c>
+      <c r="D75" s="23" t="s">
         <v>897</v>
       </c>
-      <c r="E75" s="25" t="s">
+      <c r="E75" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15" customHeight="1">
-      <c r="A76" s="25" t="s">
+      <c r="A76" s="23" t="s">
         <v>356</v>
       </c>
-      <c r="B76" s="25" t="s">
+      <c r="B76" s="23" t="s">
         <v>1111</v>
       </c>
-      <c r="C76" s="25">
+      <c r="C76" s="23">
         <v>2</v>
       </c>
-      <c r="D76" s="25" t="s">
+      <c r="D76" s="23" t="s">
         <v>898</v>
       </c>
-      <c r="E76" s="25" t="s">
+      <c r="E76" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15" customHeight="1">
-      <c r="A77" s="25" t="s">
+      <c r="A77" s="23" t="s">
         <v>363</v>
       </c>
-      <c r="B77" s="25" t="s">
+      <c r="B77" s="23" t="s">
         <v>1112</v>
       </c>
-      <c r="C77" s="25">
-        <v>1</v>
-      </c>
-      <c r="D77" s="25" t="s">
+      <c r="C77" s="23">
+        <v>1</v>
+      </c>
+      <c r="D77" s="23" t="s">
         <v>899</v>
       </c>
-      <c r="E77" s="25" t="s">
+      <c r="E77" s="23" t="s">
         <v>34</v>
       </c>
     </row>
@@ -13832,2298 +13835,2299 @@
       </c>
     </row>
     <row r="102" spans="1:5" ht="15">
-      <c r="A102" s="25" t="s">
+      <c r="A102" s="23" t="s">
         <v>462</v>
       </c>
-      <c r="B102" s="25" t="s">
+      <c r="B102" s="23" t="s">
         <v>1053</v>
       </c>
-      <c r="C102" s="25">
-        <v>1</v>
-      </c>
-      <c r="D102" s="25" t="s">
+      <c r="C102" s="23">
+        <v>1</v>
+      </c>
+      <c r="D102" s="23" t="s">
         <v>840</v>
       </c>
-      <c r="E102" s="25" t="s">
+      <c r="E102" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="15">
-      <c r="A103" s="25" t="s">
+      <c r="A103" s="23" t="s">
         <v>462</v>
       </c>
-      <c r="B103" s="25" t="s">
+      <c r="B103" s="23" t="s">
         <v>1054</v>
       </c>
-      <c r="C103" s="25">
+      <c r="C103" s="23">
         <v>2</v>
       </c>
-      <c r="D103" s="25" t="s">
+      <c r="D103" s="23" t="s">
         <v>841</v>
       </c>
-      <c r="E103" s="25" t="s">
+      <c r="E103" s="23" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="24" customHeight="1">
-      <c r="A104" s="24" t="s">
+      <c r="A104" s="22" t="s">
         <v>471</v>
       </c>
-      <c r="B104" s="24" t="s">
+      <c r="B104" s="22" t="s">
         <v>1137</v>
       </c>
-      <c r="C104" s="24">
+      <c r="C104" s="22">
         <v>2</v>
       </c>
-      <c r="D104" s="24" t="s">
+      <c r="D104" s="22" t="s">
         <v>924</v>
       </c>
-      <c r="E104" s="24" t="s">
+      <c r="E104" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="24" customHeight="1">
-      <c r="A105" s="24" t="s">
+      <c r="A105" s="22" t="s">
         <v>471</v>
       </c>
-      <c r="B105" s="24" t="s">
+      <c r="B105" s="22" t="s">
         <v>1138</v>
       </c>
-      <c r="C105" s="24">
-        <v>1</v>
-      </c>
-      <c r="D105" s="24" t="s">
+      <c r="C105" s="22">
+        <v>1</v>
+      </c>
+      <c r="D105" s="22" t="s">
         <v>925</v>
       </c>
-      <c r="E105" s="24" t="s">
+      <c r="E105" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="24" customHeight="1">
-      <c r="A106" s="24" t="s">
+      <c r="A106" s="22" t="s">
         <v>478</v>
       </c>
-      <c r="B106" s="24" t="s">
+      <c r="B106" s="22" t="s">
         <v>1139</v>
       </c>
-      <c r="C106" s="24">
+      <c r="C106" s="22">
         <v>2</v>
       </c>
-      <c r="D106" s="24" t="s">
+      <c r="D106" s="22" t="s">
         <v>926</v>
       </c>
-      <c r="E106" s="24" t="s">
+      <c r="E106" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="24" customHeight="1">
-      <c r="A107" s="24" t="s">
+      <c r="A107" s="22" t="s">
         <v>478</v>
       </c>
-      <c r="B107" s="24" t="s">
+      <c r="B107" s="22" t="s">
         <v>1140</v>
       </c>
-      <c r="C107" s="24">
-        <v>1</v>
-      </c>
-      <c r="D107" s="24" t="s">
+      <c r="C107" s="22">
+        <v>1</v>
+      </c>
+      <c r="D107" s="22" t="s">
         <v>927</v>
       </c>
-      <c r="E107" s="24" t="s">
+      <c r="E107" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="24" customHeight="1">
-      <c r="A108" s="24" t="s">
+      <c r="A108" s="22" t="s">
         <v>486</v>
       </c>
-      <c r="B108" s="24" t="s">
+      <c r="B108" s="22" t="s">
         <v>1141</v>
       </c>
-      <c r="C108" s="24">
-        <v>1</v>
-      </c>
-      <c r="D108" s="24" t="s">
+      <c r="C108" s="22">
+        <v>1</v>
+      </c>
+      <c r="D108" s="22" t="s">
         <v>928</v>
       </c>
-      <c r="E108" s="24" t="s">
+      <c r="E108" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="24" customHeight="1">
-      <c r="A109" s="24" t="s">
+      <c r="A109" s="22" t="s">
         <v>492</v>
       </c>
-      <c r="B109" s="24" t="s">
+      <c r="B109" s="22" t="s">
         <v>1142</v>
       </c>
-      <c r="C109" s="24">
+      <c r="C109" s="22">
         <v>3</v>
       </c>
-      <c r="D109" s="24" t="s">
+      <c r="D109" s="22" t="s">
         <v>931</v>
       </c>
-      <c r="E109" s="24" t="s">
+      <c r="E109" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="24" customHeight="1">
-      <c r="A110" s="24" t="s">
+      <c r="A110" s="22" t="s">
         <v>492</v>
       </c>
-      <c r="B110" s="24" t="s">
+      <c r="B110" s="22" t="s">
         <v>1143</v>
       </c>
-      <c r="C110" s="24">
+      <c r="C110" s="22">
         <v>2</v>
       </c>
-      <c r="D110" s="24" t="s">
+      <c r="D110" s="22" t="s">
         <v>930</v>
       </c>
-      <c r="E110" s="24" t="s">
+      <c r="E110" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="24" customHeight="1">
-      <c r="A111" s="24" t="s">
+      <c r="A111" s="22" t="s">
         <v>492</v>
       </c>
-      <c r="B111" s="24" t="s">
+      <c r="B111" s="22" t="s">
         <v>1144</v>
       </c>
-      <c r="C111" s="24">
-        <v>1</v>
-      </c>
-      <c r="D111" s="24" t="s">
+      <c r="C111" s="22">
+        <v>1</v>
+      </c>
+      <c r="D111" s="22" t="s">
         <v>929</v>
       </c>
-      <c r="E111" s="24" t="s">
+      <c r="E111" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="24" customHeight="1">
-      <c r="A112" s="24" t="s">
+      <c r="A112" s="22" t="s">
         <v>492</v>
       </c>
-      <c r="B112" s="24" t="s">
+      <c r="B112" s="22" t="s">
         <v>1145</v>
       </c>
-      <c r="C112" s="24">
+      <c r="C112" s="22">
         <v>4</v>
       </c>
-      <c r="D112" s="24" t="s">
+      <c r="D112" s="22" t="s">
         <v>932</v>
       </c>
-      <c r="E112" s="24" t="s">
+      <c r="E112" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="24" customHeight="1">
-      <c r="A113" s="24" t="s">
+      <c r="A113" s="22" t="s">
         <v>492</v>
       </c>
-      <c r="B113" s="24" t="s">
+      <c r="B113" s="22" t="s">
         <v>1146</v>
       </c>
-      <c r="C113" s="24">
+      <c r="C113" s="22">
         <v>5</v>
       </c>
-      <c r="D113" s="24" t="s">
+      <c r="D113" s="22" t="s">
         <v>933</v>
       </c>
-      <c r="E113" s="24" t="s">
+      <c r="E113" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="24" customHeight="1">
-      <c r="A114" s="24" t="s">
+      <c r="A114" s="22" t="s">
         <v>499</v>
       </c>
-      <c r="B114" s="24" t="s">
+      <c r="B114" s="22" t="s">
         <v>1147</v>
       </c>
-      <c r="C114" s="24">
-        <v>1</v>
-      </c>
-      <c r="D114" s="24" t="s">
+      <c r="C114" s="22">
+        <v>1</v>
+      </c>
+      <c r="D114" s="22" t="s">
         <v>934</v>
       </c>
-      <c r="E114" s="24" t="s">
+      <c r="E114" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="24" customHeight="1">
-      <c r="A115" s="24" t="s">
+      <c r="A115" s="22" t="s">
         <v>499</v>
       </c>
-      <c r="B115" s="24" t="s">
+      <c r="B115" s="22" t="s">
         <v>1148</v>
       </c>
-      <c r="C115" s="24">
+      <c r="C115" s="22">
         <v>2</v>
       </c>
-      <c r="D115" s="24" t="s">
+      <c r="D115" s="22" t="s">
         <v>935</v>
       </c>
-      <c r="E115" s="24" t="s">
+      <c r="E115" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="24" customHeight="1">
-      <c r="A116" s="24" t="s">
+      <c r="A116" s="22" t="s">
         <v>507</v>
       </c>
-      <c r="B116" s="24" t="s">
+      <c r="B116" s="22" t="s">
         <v>1149</v>
       </c>
-      <c r="C116" s="24">
-        <v>1</v>
-      </c>
-      <c r="D116" s="24" t="s">
+      <c r="C116" s="22">
+        <v>1</v>
+      </c>
+      <c r="D116" s="22" t="s">
         <v>936</v>
       </c>
-      <c r="E116" s="24" t="s">
+      <c r="E116" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="24" customHeight="1">
-      <c r="A117" s="24" t="s">
+      <c r="A117" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="B117" s="24" t="s">
+      <c r="B117" s="22" t="s">
         <v>1150</v>
       </c>
-      <c r="C117" s="24">
-        <v>1</v>
-      </c>
-      <c r="D117" s="24" t="s">
+      <c r="C117" s="22">
+        <v>1</v>
+      </c>
+      <c r="D117" s="22" t="s">
         <v>937</v>
       </c>
-      <c r="E117" s="24" t="s">
+      <c r="E117" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="24" customHeight="1">
-      <c r="A118" s="24" t="s">
+      <c r="A118" s="22" t="s">
         <v>513</v>
       </c>
-      <c r="B118" s="24" t="s">
+      <c r="B118" s="22" t="s">
         <v>1151</v>
       </c>
-      <c r="C118" s="24">
+      <c r="C118" s="22">
         <v>2</v>
       </c>
-      <c r="D118" s="24" t="s">
+      <c r="D118" s="22" t="s">
         <v>938</v>
       </c>
-      <c r="E118" s="24" t="s">
+      <c r="E118" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="24" customHeight="1">
-      <c r="A119" s="24" t="s">
+      <c r="A119" s="22" t="s">
         <v>519</v>
       </c>
-      <c r="B119" s="24" t="s">
+      <c r="B119" s="22" t="s">
         <v>1152</v>
       </c>
-      <c r="C119" s="24">
-        <v>1</v>
-      </c>
-      <c r="D119" s="24" t="s">
+      <c r="C119" s="22">
+        <v>1</v>
+      </c>
+      <c r="D119" s="22" t="s">
         <v>939</v>
       </c>
-      <c r="E119" s="24" t="s">
+      <c r="E119" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="24" customHeight="1">
-      <c r="A120" s="24" t="s">
+      <c r="A120" s="22" t="s">
         <v>519</v>
       </c>
-      <c r="B120" s="24" t="s">
+      <c r="B120" s="22" t="s">
         <v>1153</v>
       </c>
-      <c r="C120" s="24">
+      <c r="C120" s="22">
         <v>2</v>
       </c>
-      <c r="D120" s="24" t="s">
+      <c r="D120" s="22" t="s">
         <v>940</v>
       </c>
-      <c r="E120" s="24" t="s">
+      <c r="E120" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="24" customHeight="1">
-      <c r="A121" s="24" t="s">
+      <c r="A121" s="22" t="s">
         <v>527</v>
       </c>
-      <c r="B121" s="24" t="s">
+      <c r="B121" s="22" t="s">
         <v>1154</v>
       </c>
-      <c r="C121" s="24">
-        <v>1</v>
-      </c>
-      <c r="D121" s="24" t="s">
+      <c r="C121" s="22">
+        <v>1</v>
+      </c>
+      <c r="D121" s="22" t="s">
         <v>941</v>
       </c>
-      <c r="E121" s="24" t="s">
+      <c r="E121" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="24" customHeight="1">
-      <c r="A122" s="24" t="s">
+      <c r="A122" s="22" t="s">
         <v>527</v>
       </c>
-      <c r="B122" s="24" t="s">
+      <c r="B122" s="22" t="s">
         <v>1155</v>
       </c>
-      <c r="C122" s="24">
+      <c r="C122" s="22">
         <v>2</v>
       </c>
-      <c r="D122" s="24" t="s">
+      <c r="D122" s="22" t="s">
         <v>942</v>
       </c>
-      <c r="E122" s="24" t="s">
+      <c r="E122" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="24" customHeight="1">
-      <c r="A123" s="24" t="s">
+      <c r="A123" s="22" t="s">
         <v>527</v>
       </c>
-      <c r="B123" s="24" t="s">
+      <c r="B123" s="22" t="s">
         <v>1156</v>
       </c>
-      <c r="C123" s="24">
+      <c r="C123" s="22">
         <v>3</v>
       </c>
-      <c r="D123" s="24" t="s">
+      <c r="D123" s="22" t="s">
         <v>943</v>
       </c>
-      <c r="E123" s="24" t="s">
+      <c r="E123" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="24" customHeight="1">
-      <c r="A124" s="24" t="s">
+      <c r="A124" s="22" t="s">
         <v>533</v>
       </c>
-      <c r="B124" s="24" t="s">
+      <c r="B124" s="22" t="s">
         <v>1157</v>
       </c>
-      <c r="C124" s="24">
-        <v>1</v>
-      </c>
-      <c r="D124" s="24" t="s">
+      <c r="C124" s="22">
+        <v>1</v>
+      </c>
+      <c r="D124" s="22" t="s">
         <v>944</v>
       </c>
-      <c r="E124" s="24" t="s">
+      <c r="E124" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="24" customHeight="1">
-      <c r="A125" s="24" t="s">
+      <c r="A125" s="22" t="s">
         <v>533</v>
       </c>
-      <c r="B125" s="24" t="s">
+      <c r="B125" s="22" t="s">
         <v>1158</v>
       </c>
-      <c r="C125" s="24">
+      <c r="C125" s="22">
         <v>2</v>
       </c>
-      <c r="D125" s="24" t="s">
+      <c r="D125" s="22" t="s">
         <v>945</v>
       </c>
-      <c r="E125" s="24" t="s">
+      <c r="E125" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="24" customHeight="1">
-      <c r="A126" s="24" t="s">
+      <c r="A126" s="22" t="s">
         <v>537</v>
       </c>
-      <c r="B126" s="24" t="s">
+      <c r="B126" s="22" t="s">
         <v>1159</v>
       </c>
-      <c r="C126" s="24">
-        <v>1</v>
-      </c>
-      <c r="D126" s="24" t="s">
+      <c r="C126" s="22">
+        <v>1</v>
+      </c>
+      <c r="D126" s="22" t="s">
         <v>946</v>
       </c>
-      <c r="E126" s="24" t="s">
+      <c r="E126" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="24" customHeight="1">
-      <c r="A127" s="24" t="s">
+      <c r="A127" s="22" t="s">
         <v>537</v>
       </c>
-      <c r="B127" s="24" t="s">
+      <c r="B127" s="22" t="s">
         <v>1160</v>
       </c>
-      <c r="C127" s="24">
+      <c r="C127" s="22">
         <v>2</v>
       </c>
-      <c r="D127" s="24" t="s">
+      <c r="D127" s="22" t="s">
         <v>947</v>
       </c>
-      <c r="E127" s="24" t="s">
+      <c r="E127" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="24" customHeight="1">
-      <c r="A128" s="24" t="s">
+      <c r="A128" s="22" t="s">
         <v>537</v>
       </c>
-      <c r="B128" s="24" t="s">
+      <c r="B128" s="22" t="s">
         <v>1161</v>
       </c>
-      <c r="C128" s="24">
+      <c r="C128" s="22">
         <v>3</v>
       </c>
-      <c r="D128" s="24" t="s">
+      <c r="D128" s="22" t="s">
         <v>948</v>
       </c>
-      <c r="E128" s="24" t="s">
+      <c r="E128" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="24" customHeight="1">
-      <c r="A129" s="24" t="s">
+      <c r="A129" s="22" t="s">
         <v>537</v>
       </c>
-      <c r="B129" s="24" t="s">
+      <c r="B129" s="22" t="s">
         <v>1162</v>
       </c>
-      <c r="C129" s="24">
+      <c r="C129" s="22">
         <v>4</v>
       </c>
-      <c r="D129" s="24" t="s">
+      <c r="D129" s="22" t="s">
         <v>949</v>
       </c>
-      <c r="E129" s="24" t="s">
+      <c r="E129" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="24" customHeight="1">
-      <c r="A130" s="24" t="s">
+      <c r="A130" s="22" t="s">
         <v>543</v>
       </c>
-      <c r="B130" s="24" t="s">
+      <c r="B130" s="22" t="s">
         <v>1163</v>
       </c>
-      <c r="C130" s="24">
-        <v>1</v>
-      </c>
-      <c r="D130" s="24" t="s">
+      <c r="C130" s="22">
+        <v>1</v>
+      </c>
+      <c r="D130" s="22" t="s">
         <v>950</v>
       </c>
-      <c r="E130" s="24" t="s">
+      <c r="E130" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="24" customHeight="1">
-      <c r="A131" s="24" t="s">
+      <c r="A131" s="22" t="s">
         <v>543</v>
       </c>
-      <c r="B131" s="24" t="s">
+      <c r="B131" s="22" t="s">
         <v>1164</v>
       </c>
-      <c r="C131" s="24">
+      <c r="C131" s="22">
         <v>2</v>
       </c>
-      <c r="D131" s="24" t="s">
+      <c r="D131" s="22" t="s">
         <v>951</v>
       </c>
-      <c r="E131" s="24" t="s">
+      <c r="E131" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="24" customHeight="1">
-      <c r="A132" s="24" t="s">
+      <c r="A132" s="22" t="s">
         <v>550</v>
       </c>
-      <c r="B132" s="24" t="s">
+      <c r="B132" s="22" t="s">
         <v>1165</v>
       </c>
-      <c r="C132" s="24">
-        <v>1</v>
-      </c>
-      <c r="D132" s="24" t="s">
+      <c r="C132" s="22">
+        <v>1</v>
+      </c>
+      <c r="D132" s="22" t="s">
         <v>952</v>
       </c>
-      <c r="E132" s="24" t="s">
+      <c r="E132" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="24" customHeight="1">
-      <c r="A133" s="24" t="s">
+      <c r="A133" s="22" t="s">
         <v>550</v>
       </c>
-      <c r="B133" s="24" t="s">
+      <c r="B133" s="22" t="s">
         <v>1166</v>
       </c>
-      <c r="C133" s="24">
+      <c r="C133" s="22">
         <v>2</v>
       </c>
-      <c r="D133" s="24" t="s">
+      <c r="D133" s="22" t="s">
         <v>953</v>
       </c>
-      <c r="E133" s="24" t="s">
+      <c r="E133" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="24" customHeight="1">
-      <c r="A134" s="24" t="s">
+      <c r="A134" s="22" t="s">
         <v>557</v>
       </c>
-      <c r="B134" s="24" t="s">
+      <c r="B134" s="22" t="s">
         <v>1167</v>
       </c>
-      <c r="C134" s="24">
-        <v>1</v>
-      </c>
-      <c r="D134" s="24" t="s">
+      <c r="C134" s="22">
+        <v>1</v>
+      </c>
+      <c r="D134" s="22" t="s">
         <v>954</v>
       </c>
-      <c r="E134" s="24" t="s">
+      <c r="E134" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="24" customHeight="1">
-      <c r="A135" s="24" t="s">
+      <c r="A135" s="22" t="s">
         <v>557</v>
       </c>
-      <c r="B135" s="24" t="s">
+      <c r="B135" s="22" t="s">
         <v>1168</v>
       </c>
-      <c r="C135" s="24">
+      <c r="C135" s="22">
         <v>2</v>
       </c>
-      <c r="D135" s="24" t="s">
+      <c r="D135" s="22" t="s">
         <v>955</v>
       </c>
-      <c r="E135" s="24" t="s">
+      <c r="E135" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="24" customHeight="1">
-      <c r="A136" s="24" t="s">
+      <c r="A136" s="22" t="s">
         <v>564</v>
       </c>
-      <c r="B136" s="24" t="s">
+      <c r="B136" s="22" t="s">
         <v>1169</v>
       </c>
-      <c r="C136" s="24">
-        <v>1</v>
-      </c>
-      <c r="D136" s="24" t="s">
+      <c r="C136" s="22">
+        <v>1</v>
+      </c>
+      <c r="D136" s="22" t="s">
         <v>956</v>
       </c>
-      <c r="E136" s="24" t="s">
+      <c r="E136" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="24" customHeight="1">
-      <c r="A137" s="24" t="s">
+      <c r="A137" s="22" t="s">
         <v>564</v>
       </c>
-      <c r="B137" s="24" t="s">
+      <c r="B137" s="22" t="s">
         <v>1170</v>
       </c>
-      <c r="C137" s="24">
+      <c r="C137" s="22">
         <v>2</v>
       </c>
-      <c r="D137" s="24" t="s">
+      <c r="D137" s="22" t="s">
         <v>957</v>
       </c>
-      <c r="E137" s="24" t="s">
+      <c r="E137" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="24" customHeight="1">
-      <c r="A138" s="24" t="s">
+      <c r="A138" s="22" t="s">
         <v>564</v>
       </c>
-      <c r="B138" s="24" t="s">
+      <c r="B138" s="22" t="s">
         <v>1171</v>
       </c>
-      <c r="C138" s="24">
+      <c r="C138" s="22">
         <v>3</v>
       </c>
-      <c r="D138" s="24" t="s">
+      <c r="D138" s="22" t="s">
         <v>958</v>
       </c>
-      <c r="E138" s="24" t="s">
+      <c r="E138" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="24" customHeight="1">
-      <c r="A139" s="24" t="s">
+      <c r="A139" s="22" t="s">
         <v>570</v>
       </c>
-      <c r="B139" s="24" t="s">
+      <c r="B139" s="22" t="s">
         <v>1172</v>
       </c>
-      <c r="C139" s="24">
-        <v>1</v>
-      </c>
-      <c r="D139" s="24" t="s">
+      <c r="C139" s="22">
+        <v>1</v>
+      </c>
+      <c r="D139" s="22" t="s">
         <v>959</v>
       </c>
-      <c r="E139" s="24" t="s">
+      <c r="E139" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="24" customHeight="1">
-      <c r="A140" s="24" t="s">
+      <c r="A140" s="22" t="s">
         <v>570</v>
       </c>
-      <c r="B140" s="24" t="s">
+      <c r="B140" s="22" t="s">
         <v>1173</v>
       </c>
-      <c r="C140" s="24">
+      <c r="C140" s="22">
         <v>2</v>
       </c>
-      <c r="D140" s="24" t="s">
+      <c r="D140" s="22" t="s">
         <v>960</v>
       </c>
-      <c r="E140" s="24" t="s">
+      <c r="E140" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="24" customHeight="1">
-      <c r="A141" s="24" t="s">
+      <c r="A141" s="22" t="s">
         <v>570</v>
       </c>
-      <c r="B141" s="24" t="s">
+      <c r="B141" s="22" t="s">
         <v>1174</v>
       </c>
-      <c r="C141" s="24">
+      <c r="C141" s="22">
         <v>3</v>
       </c>
-      <c r="D141" s="24" t="s">
+      <c r="D141" s="22" t="s">
         <v>961</v>
       </c>
-      <c r="E141" s="24" t="s">
+      <c r="E141" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="24" customHeight="1">
-      <c r="A142" s="24" t="s">
+      <c r="A142" s="22" t="s">
         <v>570</v>
       </c>
-      <c r="B142" s="24" t="s">
+      <c r="B142" s="22" t="s">
         <v>1175</v>
       </c>
-      <c r="C142" s="24">
+      <c r="C142" s="22">
         <v>4</v>
       </c>
-      <c r="D142" s="24" t="s">
+      <c r="D142" s="22" t="s">
         <v>962</v>
       </c>
-      <c r="E142" s="24" t="s">
+      <c r="E142" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="24" customHeight="1">
-      <c r="A143" s="24" t="s">
+      <c r="A143" s="22" t="s">
         <v>577</v>
       </c>
-      <c r="B143" s="24" t="s">
+      <c r="B143" s="22" t="s">
         <v>1176</v>
       </c>
-      <c r="C143" s="24">
-        <v>1</v>
-      </c>
-      <c r="D143" s="24" t="s">
+      <c r="C143" s="22">
+        <v>1</v>
+      </c>
+      <c r="D143" s="22" t="s">
         <v>963</v>
       </c>
-      <c r="E143" s="24" t="s">
+      <c r="E143" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="24" customHeight="1">
-      <c r="A144" s="24" t="s">
+      <c r="A144" s="22" t="s">
         <v>577</v>
       </c>
-      <c r="B144" s="24" t="s">
+      <c r="B144" s="22" t="s">
         <v>1177</v>
       </c>
-      <c r="C144" s="24">
+      <c r="C144" s="22">
         <v>2</v>
       </c>
-      <c r="D144" s="24" t="s">
+      <c r="D144" s="22" t="s">
         <v>964</v>
       </c>
-      <c r="E144" s="24" t="s">
+      <c r="E144" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="24" customHeight="1">
-      <c r="A145" s="24" t="s">
+      <c r="A145" s="22" t="s">
         <v>577</v>
       </c>
-      <c r="B145" s="24" t="s">
+      <c r="B145" s="22" t="s">
         <v>1178</v>
       </c>
-      <c r="C145" s="24">
+      <c r="C145" s="22">
         <v>3</v>
       </c>
-      <c r="D145" s="24" t="s">
+      <c r="D145" s="22" t="s">
         <v>965</v>
       </c>
-      <c r="E145" s="24" t="s">
+      <c r="E145" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="24" customHeight="1">
-      <c r="A146" s="24" t="s">
+      <c r="A146" s="22" t="s">
         <v>584</v>
       </c>
-      <c r="B146" s="24" t="s">
+      <c r="B146" s="22" t="s">
         <v>1179</v>
       </c>
-      <c r="C146" s="24">
-        <v>1</v>
-      </c>
-      <c r="D146" s="24" t="s">
+      <c r="C146" s="22">
+        <v>1</v>
+      </c>
+      <c r="D146" s="22" t="s">
         <v>966</v>
       </c>
-      <c r="E146" s="24" t="s">
+      <c r="E146" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="24" customHeight="1">
-      <c r="A147" s="24" t="s">
+      <c r="A147" s="22" t="s">
         <v>591</v>
       </c>
-      <c r="B147" s="24" t="s">
+      <c r="B147" s="22" t="s">
         <v>1180</v>
       </c>
-      <c r="C147" s="24">
-        <v>1</v>
-      </c>
-      <c r="D147" s="24" t="s">
+      <c r="C147" s="22">
+        <v>1</v>
+      </c>
+      <c r="D147" s="22" t="s">
         <v>967</v>
       </c>
-      <c r="E147" s="24" t="s">
+      <c r="E147" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="24" customHeight="1">
-      <c r="A148" s="24" t="s">
+      <c r="A148" s="22" t="s">
         <v>591</v>
       </c>
-      <c r="B148" s="24" t="s">
+      <c r="B148" s="22" t="s">
         <v>1181</v>
       </c>
-      <c r="C148" s="24">
+      <c r="C148" s="22">
         <v>2</v>
       </c>
-      <c r="D148" s="24" t="s">
+      <c r="D148" s="22" t="s">
         <v>968</v>
       </c>
-      <c r="E148" s="24" t="s">
+      <c r="E148" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="24" customHeight="1">
-      <c r="A149" s="24" t="s">
+      <c r="A149" s="22" t="s">
         <v>597</v>
       </c>
-      <c r="B149" s="24" t="s">
+      <c r="B149" s="22" t="s">
         <v>1182</v>
       </c>
-      <c r="C149" s="24">
+      <c r="C149" s="22">
         <v>2</v>
       </c>
-      <c r="D149" s="24" t="s">
+      <c r="D149" s="22" t="s">
         <v>970</v>
       </c>
-      <c r="E149" s="24" t="s">
+      <c r="E149" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="24" customHeight="1">
-      <c r="A150" s="24" t="s">
+      <c r="A150" s="22" t="s">
         <v>597</v>
       </c>
-      <c r="B150" s="24" t="s">
+      <c r="B150" s="22" t="s">
         <v>1183</v>
       </c>
-      <c r="C150" s="24">
-        <v>1</v>
-      </c>
-      <c r="D150" s="24" t="s">
+      <c r="C150" s="22">
+        <v>1</v>
+      </c>
+      <c r="D150" s="22" t="s">
         <v>969</v>
       </c>
-      <c r="E150" s="24" t="s">
+      <c r="E150" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="24" customHeight="1">
-      <c r="A151" s="24" t="s">
+      <c r="A151" s="22" t="s">
         <v>604</v>
       </c>
-      <c r="B151" s="24" t="s">
+      <c r="B151" s="22" t="s">
         <v>1184</v>
       </c>
-      <c r="C151" s="24">
-        <v>1</v>
-      </c>
-      <c r="D151" s="24" t="s">
+      <c r="C151" s="22">
+        <v>1</v>
+      </c>
+      <c r="D151" s="22" t="s">
         <v>971</v>
       </c>
-      <c r="E151" s="24" t="s">
+      <c r="E151" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="24" customHeight="1">
-      <c r="A152" s="24" t="s">
+      <c r="A152" s="22" t="s">
         <v>604</v>
       </c>
-      <c r="B152" s="24" t="s">
+      <c r="B152" s="22" t="s">
         <v>1185</v>
       </c>
-      <c r="C152" s="24">
+      <c r="C152" s="22">
         <v>2</v>
       </c>
-      <c r="D152" s="24" t="s">
+      <c r="D152" s="22" t="s">
         <v>972</v>
       </c>
-      <c r="E152" s="24" t="s">
+      <c r="E152" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="24" customHeight="1">
-      <c r="A153" s="24" t="s">
+      <c r="A153" s="22" t="s">
         <v>612</v>
       </c>
-      <c r="B153" s="24" t="s">
+      <c r="B153" s="22" t="s">
         <v>1186</v>
       </c>
-      <c r="C153" s="24">
-        <v>1</v>
-      </c>
-      <c r="D153" s="24" t="s">
+      <c r="C153" s="22">
+        <v>1</v>
+      </c>
+      <c r="D153" s="22" t="s">
         <v>973</v>
       </c>
-      <c r="E153" s="24" t="s">
+      <c r="E153" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="24" customHeight="1">
-      <c r="A154" s="24" t="s">
+      <c r="A154" s="22" t="s">
         <v>612</v>
       </c>
-      <c r="B154" s="24" t="s">
+      <c r="B154" s="22" t="s">
         <v>1187</v>
       </c>
-      <c r="C154" s="24">
+      <c r="C154" s="22">
         <v>2</v>
       </c>
-      <c r="D154" s="24" t="s">
+      <c r="D154" s="22" t="s">
         <v>974</v>
       </c>
-      <c r="E154" s="24" t="s">
+      <c r="E154" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="24" customHeight="1">
-      <c r="A155" s="24" t="s">
+      <c r="A155" s="22" t="s">
         <v>618</v>
       </c>
-      <c r="B155" s="24" t="s">
+      <c r="B155" s="22" t="s">
         <v>1188</v>
       </c>
-      <c r="C155" s="24">
-        <v>1</v>
-      </c>
-      <c r="D155" s="24" t="s">
+      <c r="C155" s="22">
+        <v>1</v>
+      </c>
+      <c r="D155" s="22" t="s">
         <v>975</v>
       </c>
-      <c r="E155" s="24" t="s">
+      <c r="E155" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="24" customHeight="1">
-      <c r="A156" s="24" t="s">
+      <c r="A156" s="22" t="s">
         <v>618</v>
       </c>
-      <c r="B156" s="24" t="s">
+      <c r="B156" s="22" t="s">
         <v>1189</v>
       </c>
-      <c r="C156" s="24">
+      <c r="C156" s="22">
         <v>2</v>
       </c>
-      <c r="D156" s="24" t="s">
+      <c r="D156" s="22" t="s">
         <v>976</v>
       </c>
-      <c r="E156" s="24" t="s">
+      <c r="E156" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="24" customHeight="1">
-      <c r="A157" s="24" t="s">
+      <c r="A157" s="22" t="s">
         <v>625</v>
       </c>
-      <c r="B157" s="24" t="s">
+      <c r="B157" s="22" t="s">
         <v>1190</v>
       </c>
-      <c r="C157" s="24">
-        <v>1</v>
-      </c>
-      <c r="D157" s="24" t="s">
+      <c r="C157" s="22">
+        <v>1</v>
+      </c>
+      <c r="D157" s="22" t="s">
         <v>977</v>
       </c>
-      <c r="E157" s="24" t="s">
+      <c r="E157" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="24" customHeight="1">
-      <c r="A158" s="24" t="s">
+      <c r="A158" s="22" t="s">
         <v>625</v>
       </c>
-      <c r="B158" s="24" t="s">
+      <c r="B158" s="22" t="s">
         <v>1191</v>
       </c>
-      <c r="C158" s="24">
+      <c r="C158" s="22">
         <v>2</v>
       </c>
-      <c r="D158" s="24" t="s">
+      <c r="D158" s="22" t="s">
         <v>978</v>
       </c>
-      <c r="E158" s="24" t="s">
+      <c r="E158" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="24" customHeight="1">
-      <c r="A159" s="24" t="s">
+      <c r="A159" s="22" t="s">
         <v>625</v>
       </c>
-      <c r="B159" s="24" t="s">
+      <c r="B159" s="22" t="s">
         <v>1192</v>
       </c>
-      <c r="C159" s="24">
+      <c r="C159" s="22">
         <v>3</v>
       </c>
-      <c r="D159" s="24" t="s">
+      <c r="D159" s="22" t="s">
         <v>979</v>
       </c>
-      <c r="E159" s="24" t="s">
+      <c r="E159" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="24" customHeight="1">
-      <c r="A160" s="24" t="s">
+      <c r="A160" s="22" t="s">
         <v>625</v>
       </c>
-      <c r="B160" s="24" t="s">
+      <c r="B160" s="22" t="s">
         <v>1193</v>
       </c>
-      <c r="C160" s="24">
+      <c r="C160" s="22">
         <v>4</v>
       </c>
-      <c r="D160" s="24" t="s">
+      <c r="D160" s="22" t="s">
         <v>980</v>
       </c>
-      <c r="E160" s="24" t="s">
+      <c r="E160" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="24" customHeight="1">
-      <c r="A161" s="24" t="s">
+      <c r="A161" s="22" t="s">
         <v>632</v>
       </c>
-      <c r="B161" s="24" t="s">
+      <c r="B161" s="22" t="s">
         <v>1194</v>
       </c>
-      <c r="C161" s="24">
-        <v>1</v>
-      </c>
-      <c r="D161" s="24" t="s">
+      <c r="C161" s="22">
+        <v>1</v>
+      </c>
+      <c r="D161" s="22" t="s">
         <v>981</v>
       </c>
-      <c r="E161" s="24" t="s">
+      <c r="E161" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="24" customHeight="1">
-      <c r="A162" s="24" t="s">
+      <c r="A162" s="22" t="s">
         <v>638</v>
       </c>
-      <c r="B162" s="24" t="s">
+      <c r="B162" s="22" t="s">
         <v>1195</v>
       </c>
-      <c r="C162" s="24">
-        <v>1</v>
-      </c>
-      <c r="D162" s="24" t="s">
+      <c r="C162" s="22">
+        <v>1</v>
+      </c>
+      <c r="D162" s="22" t="s">
         <v>982</v>
       </c>
-      <c r="E162" s="24" t="s">
+      <c r="E162" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="24" customHeight="1">
-      <c r="A163" s="24" t="s">
+      <c r="A163" s="22" t="s">
         <v>644</v>
       </c>
-      <c r="B163" s="24" t="s">
+      <c r="B163" s="22" t="s">
         <v>1196</v>
       </c>
-      <c r="C163" s="24">
+      <c r="C163" s="22">
         <v>5</v>
       </c>
-      <c r="D163" s="24" t="s">
+      <c r="D163" s="22" t="s">
         <v>983</v>
       </c>
-      <c r="E163" s="24" t="s">
+      <c r="E163" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="24" customHeight="1">
-      <c r="A164" s="24" t="s">
+      <c r="A164" s="22" t="s">
         <v>644</v>
       </c>
-      <c r="B164" s="24" t="s">
+      <c r="B164" s="22" t="s">
         <v>1197</v>
       </c>
-      <c r="C164" s="24">
+      <c r="C164" s="22">
         <v>2</v>
       </c>
-      <c r="D164" s="24" t="s">
+      <c r="D164" s="22" t="s">
         <v>984</v>
       </c>
-      <c r="E164" s="24" t="s">
+      <c r="E164" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="24" customHeight="1">
-      <c r="A165" s="24" t="s">
+      <c r="A165" s="22" t="s">
         <v>644</v>
       </c>
-      <c r="B165" s="24" t="s">
+      <c r="B165" s="22" t="s">
         <v>1198</v>
       </c>
-      <c r="C165" s="24">
+      <c r="C165" s="22">
         <v>3</v>
       </c>
-      <c r="D165" s="24" t="s">
+      <c r="D165" s="22" t="s">
         <v>985</v>
       </c>
-      <c r="E165" s="24" t="s">
+      <c r="E165" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="24" customHeight="1">
-      <c r="A166" s="24" t="s">
+      <c r="A166" s="22" t="s">
         <v>644</v>
       </c>
-      <c r="B166" s="24" t="s">
+      <c r="B166" s="22" t="s">
         <v>1199</v>
       </c>
-      <c r="C166" s="24">
+      <c r="C166" s="22">
         <v>4</v>
       </c>
-      <c r="D166" s="24" t="s">
+      <c r="D166" s="22" t="s">
         <v>986</v>
       </c>
-      <c r="E166" s="24" t="s">
+      <c r="E166" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="24" customHeight="1">
-      <c r="A167" s="24" t="s">
+      <c r="A167" s="22" t="s">
         <v>644</v>
       </c>
-      <c r="B167" s="24" t="s">
+      <c r="B167" s="22" t="s">
         <v>1200</v>
       </c>
-      <c r="C167" s="24">
-        <v>1</v>
-      </c>
-      <c r="D167" s="24" t="s">
+      <c r="C167" s="22">
+        <v>1</v>
+      </c>
+      <c r="D167" s="22" t="s">
         <v>987</v>
       </c>
-      <c r="E167" s="24" t="s">
+      <c r="E167" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="24" customHeight="1">
-      <c r="A168" s="24" t="s">
+      <c r="A168" s="22" t="s">
         <v>653</v>
       </c>
-      <c r="B168" s="24" t="s">
+      <c r="B168" s="22" t="s">
         <v>1201</v>
       </c>
-      <c r="C168" s="24">
-        <v>1</v>
-      </c>
-      <c r="D168" s="24" t="s">
+      <c r="C168" s="22">
+        <v>1</v>
+      </c>
+      <c r="D168" s="22" t="s">
         <v>988</v>
       </c>
-      <c r="E168" s="24" t="s">
+      <c r="E168" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="24" customHeight="1">
-      <c r="A169" s="24" t="s">
+      <c r="A169" s="22" t="s">
         <v>660</v>
       </c>
-      <c r="B169" s="24" t="s">
+      <c r="B169" s="22" t="s">
         <v>1202</v>
       </c>
-      <c r="C169" s="24">
-        <v>1</v>
-      </c>
-      <c r="D169" s="24" t="s">
+      <c r="C169" s="22">
+        <v>1</v>
+      </c>
+      <c r="D169" s="22" t="s">
         <v>989</v>
       </c>
-      <c r="E169" s="24" t="s">
+      <c r="E169" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="24" customHeight="1">
-      <c r="A170" s="24" t="s">
+      <c r="A170" s="22" t="s">
         <v>666</v>
       </c>
-      <c r="B170" s="24" t="s">
+      <c r="B170" s="22" t="s">
         <v>1203</v>
       </c>
-      <c r="C170" s="24">
-        <v>1</v>
-      </c>
-      <c r="D170" s="24" t="s">
+      <c r="C170" s="22">
+        <v>1</v>
+      </c>
+      <c r="D170" s="22" t="s">
         <v>990</v>
       </c>
-      <c r="E170" s="24" t="s">
+      <c r="E170" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="24" customHeight="1">
-      <c r="A171" s="24" t="s">
+      <c r="A171" s="22" t="s">
         <v>672</v>
       </c>
-      <c r="B171" s="24" t="s">
+      <c r="B171" s="22" t="s">
         <v>1204</v>
       </c>
-      <c r="C171" s="24">
-        <v>1</v>
-      </c>
-      <c r="D171" s="24" t="s">
+      <c r="C171" s="22">
+        <v>1</v>
+      </c>
+      <c r="D171" s="22" t="s">
         <v>991</v>
       </c>
-      <c r="E171" s="24" t="s">
+      <c r="E171" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="24" customHeight="1">
-      <c r="A172" s="24" t="s">
+      <c r="A172" s="22" t="s">
         <v>679</v>
       </c>
-      <c r="B172" s="24" t="s">
+      <c r="B172" s="22" t="s">
         <v>1205</v>
       </c>
-      <c r="C172" s="24">
-        <v>1</v>
-      </c>
-      <c r="D172" s="24" t="s">
+      <c r="C172" s="22">
+        <v>1</v>
+      </c>
+      <c r="D172" s="22" t="s">
         <v>992</v>
       </c>
-      <c r="E172" s="24" t="s">
+      <c r="E172" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="24" customHeight="1">
-      <c r="A173" s="24" t="s">
+      <c r="A173" s="22" t="s">
         <v>687</v>
       </c>
-      <c r="B173" s="24" t="s">
+      <c r="B173" s="22" t="s">
         <v>1206</v>
       </c>
-      <c r="C173" s="24">
-        <v>1</v>
-      </c>
-      <c r="D173" s="24" t="s">
+      <c r="C173" s="22">
+        <v>1</v>
+      </c>
+      <c r="D173" s="22" t="s">
         <v>993</v>
       </c>
-      <c r="E173" s="24" t="s">
+      <c r="E173" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="24" customHeight="1">
-      <c r="A174" s="24" t="s">
+      <c r="A174" s="22" t="s">
         <v>694</v>
       </c>
-      <c r="B174" s="24" t="s">
+      <c r="B174" s="22" t="s">
         <v>1207</v>
       </c>
-      <c r="C174" s="24">
-        <v>1</v>
-      </c>
-      <c r="D174" s="24" t="s">
+      <c r="C174" s="22">
+        <v>1</v>
+      </c>
+      <c r="D174" s="22" t="s">
         <v>994</v>
       </c>
-      <c r="E174" s="24" t="s">
+      <c r="E174" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="24" customHeight="1">
-      <c r="A175" s="24" t="s">
+      <c r="A175" s="22" t="s">
         <v>701</v>
       </c>
-      <c r="B175" s="24" t="s">
+      <c r="B175" s="22" t="s">
         <v>1208</v>
       </c>
-      <c r="C175" s="24">
-        <v>1</v>
-      </c>
-      <c r="D175" s="24" t="s">
+      <c r="C175" s="22">
+        <v>1</v>
+      </c>
+      <c r="D175" s="22" t="s">
         <v>995</v>
       </c>
-      <c r="E175" s="24" t="s">
+      <c r="E175" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="24" customHeight="1">
-      <c r="A176" s="24" t="s">
+      <c r="A176" s="22" t="s">
         <v>709</v>
       </c>
-      <c r="B176" s="24" t="s">
+      <c r="B176" s="22" t="s">
         <v>1209</v>
       </c>
-      <c r="C176" s="24">
-        <v>1</v>
-      </c>
-      <c r="D176" s="24" t="s">
+      <c r="C176" s="22">
+        <v>1</v>
+      </c>
+      <c r="D176" s="22" t="s">
         <v>996</v>
       </c>
-      <c r="E176" s="24" t="s">
+      <c r="E176" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="24" customHeight="1">
-      <c r="A177" s="24" t="s">
+      <c r="A177" s="22" t="s">
         <v>716</v>
       </c>
-      <c r="B177" s="24" t="s">
+      <c r="B177" s="22" t="s">
         <v>1210</v>
       </c>
-      <c r="C177" s="24">
-        <v>1</v>
-      </c>
-      <c r="D177" s="24" t="s">
+      <c r="C177" s="22">
+        <v>1</v>
+      </c>
+      <c r="D177" s="22" t="s">
         <v>997</v>
       </c>
-      <c r="E177" s="24" t="s">
+      <c r="E177" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="24" customHeight="1">
-      <c r="A178" s="24" t="s">
+      <c r="A178" s="22" t="s">
         <v>716</v>
       </c>
-      <c r="B178" s="24" t="s">
+      <c r="B178" s="22" t="s">
         <v>1211</v>
       </c>
-      <c r="C178" s="24">
+      <c r="C178" s="22">
         <v>2</v>
       </c>
-      <c r="D178" s="24" t="s">
+      <c r="D178" s="22" t="s">
         <v>998</v>
       </c>
-      <c r="E178" s="24" t="s">
+      <c r="E178" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="24" customHeight="1">
-      <c r="A179" s="24" t="s">
+      <c r="A179" s="22" t="s">
         <v>723</v>
       </c>
-      <c r="B179" s="24" t="s">
+      <c r="B179" s="22" t="s">
         <v>1212</v>
       </c>
-      <c r="C179" s="24">
+      <c r="C179" s="22">
         <v>2</v>
       </c>
-      <c r="D179" s="24" t="s">
+      <c r="D179" s="22" t="s">
         <v>1000</v>
       </c>
-      <c r="E179" s="24" t="s">
+      <c r="E179" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="24" customHeight="1">
-      <c r="A180" s="24" t="s">
+      <c r="A180" s="22" t="s">
         <v>723</v>
       </c>
-      <c r="B180" s="24" t="s">
+      <c r="B180" s="22" t="s">
         <v>1213</v>
       </c>
-      <c r="C180" s="24">
-        <v>1</v>
-      </c>
-      <c r="D180" s="24" t="s">
+      <c r="C180" s="22">
+        <v>1</v>
+      </c>
+      <c r="D180" s="22" t="s">
         <v>999</v>
       </c>
-      <c r="E180" s="24" t="s">
+      <c r="E180" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="24" customHeight="1">
-      <c r="A181" s="24" t="s">
+      <c r="A181" s="22" t="s">
         <v>731</v>
       </c>
-      <c r="B181" s="24" t="s">
+      <c r="B181" s="22" t="s">
         <v>1214</v>
       </c>
-      <c r="C181" s="24">
-        <v>1</v>
-      </c>
-      <c r="D181" s="24" t="s">
+      <c r="C181" s="22">
+        <v>1</v>
+      </c>
+      <c r="D181" s="22" t="s">
         <v>1001</v>
       </c>
-      <c r="E181" s="24" t="s">
+      <c r="E181" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="24" customHeight="1">
-      <c r="A182" s="24" t="s">
+      <c r="A182" s="22" t="s">
         <v>731</v>
       </c>
-      <c r="B182" s="24" t="s">
+      <c r="B182" s="22" t="s">
         <v>1215</v>
       </c>
-      <c r="C182" s="24">
+      <c r="C182" s="22">
         <v>2</v>
       </c>
-      <c r="D182" s="24" t="s">
+      <c r="D182" s="22" t="s">
         <v>1002</v>
       </c>
-      <c r="E182" s="24" t="s">
+      <c r="E182" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1">
-      <c r="A183" s="24" t="s">
+      <c r="A183" s="22" t="s">
         <v>731</v>
       </c>
-      <c r="B183" s="24" t="s">
+      <c r="B183" s="22" t="s">
         <v>1216</v>
       </c>
-      <c r="C183" s="24">
+      <c r="C183" s="22">
         <v>3</v>
       </c>
-      <c r="D183" s="24" t="s">
+      <c r="D183" s="22" t="s">
         <v>1003</v>
       </c>
-      <c r="E183" s="24" t="s">
+      <c r="E183" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="184" spans="1:5">
-      <c r="A184" s="24" t="s">
+      <c r="A184" s="22" t="s">
         <v>734</v>
       </c>
-      <c r="B184" s="24" t="s">
+      <c r="B184" s="22" t="s">
         <v>1217</v>
       </c>
-      <c r="C184" s="24">
-        <v>1</v>
-      </c>
-      <c r="D184" s="35"/>
-      <c r="E184" s="24" t="s">
+      <c r="C184" s="22">
+        <v>1</v>
+      </c>
+      <c r="D184" s="25"/>
+      <c r="E184" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="185" spans="1:5">
-      <c r="A185" s="24" t="s">
+      <c r="A185" s="22" t="s">
         <v>734</v>
       </c>
-      <c r="B185" s="24" t="s">
+      <c r="B185" s="22" t="s">
         <v>1218</v>
       </c>
-      <c r="C185" s="24">
+      <c r="C185" s="22">
         <v>2</v>
       </c>
-      <c r="D185" s="35"/>
-      <c r="E185" s="24" t="s">
+      <c r="D185" s="25"/>
+      <c r="E185" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="186" spans="1:5">
-      <c r="A186" s="24" t="s">
+      <c r="A186" s="22" t="s">
         <v>734</v>
       </c>
-      <c r="B186" s="24" t="s">
+      <c r="B186" s="22" t="s">
         <v>1219</v>
       </c>
-      <c r="C186" s="24">
+      <c r="C186" s="22">
         <v>3</v>
       </c>
-      <c r="D186" s="35"/>
-      <c r="E186" s="24" t="s">
+      <c r="D186" s="25"/>
+      <c r="E186" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="187" spans="1:5">
-      <c r="A187" s="24" t="s">
+      <c r="A187" s="22" t="s">
         <v>734</v>
       </c>
-      <c r="B187" s="24" t="s">
+      <c r="B187" s="22" t="s">
         <v>1220</v>
       </c>
-      <c r="C187" s="24">
+      <c r="C187" s="22">
         <v>4</v>
       </c>
-      <c r="D187" s="35"/>
-      <c r="E187" s="24" t="s">
+      <c r="D187" s="25"/>
+      <c r="E187" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="188" spans="1:5">
-      <c r="A188" s="24" t="s">
+      <c r="A188" s="22" t="s">
         <v>740</v>
       </c>
-      <c r="B188" s="24" t="s">
+      <c r="B188" s="22" t="s">
         <v>1221</v>
       </c>
-      <c r="C188" s="24">
+      <c r="C188" s="22">
         <v>3</v>
       </c>
-      <c r="D188" s="35"/>
-      <c r="E188" s="24" t="s">
+      <c r="D188" s="25"/>
+      <c r="E188" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="189" spans="1:5">
-      <c r="A189" s="24" t="s">
+      <c r="A189" s="22" t="s">
         <v>740</v>
       </c>
-      <c r="B189" s="24" t="s">
+      <c r="B189" s="22" t="s">
         <v>1222</v>
       </c>
-      <c r="C189" s="24">
+      <c r="C189" s="22">
         <v>2</v>
       </c>
-      <c r="D189" s="35"/>
-      <c r="E189" s="24" t="s">
+      <c r="D189" s="25"/>
+      <c r="E189" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="190" spans="1:5">
-      <c r="A190" s="24" t="s">
+      <c r="A190" s="22" t="s">
         <v>740</v>
       </c>
-      <c r="B190" s="24" t="s">
+      <c r="B190" s="22" t="s">
         <v>1223</v>
       </c>
-      <c r="C190" s="24">
-        <v>1</v>
-      </c>
-      <c r="D190" s="35"/>
-      <c r="E190" s="24" t="s">
+      <c r="C190" s="22">
+        <v>1</v>
+      </c>
+      <c r="D190" s="25"/>
+      <c r="E190" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="191" spans="1:5">
-      <c r="A191" s="24" t="s">
+      <c r="A191" s="22" t="s">
         <v>745</v>
       </c>
-      <c r="B191" s="24" t="s">
+      <c r="B191" s="22" t="s">
         <v>1224</v>
       </c>
-      <c r="C191" s="24">
-        <v>1</v>
-      </c>
-      <c r="D191" s="35"/>
-      <c r="E191" s="24" t="s">
+      <c r="C191" s="22">
+        <v>1</v>
+      </c>
+      <c r="D191" s="25"/>
+      <c r="E191" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="192" spans="1:5">
-      <c r="A192" s="24" t="s">
+      <c r="A192" s="22" t="s">
         <v>745</v>
       </c>
-      <c r="B192" s="24" t="s">
+      <c r="B192" s="22" t="s">
         <v>1225</v>
       </c>
-      <c r="C192" s="24">
+      <c r="C192" s="22">
         <v>2</v>
       </c>
-      <c r="D192" s="35"/>
-      <c r="E192" s="24" t="s">
+      <c r="D192" s="25"/>
+      <c r="E192" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="193" spans="1:5">
-      <c r="A193" s="24" t="s">
+      <c r="A193" s="22" t="s">
         <v>745</v>
       </c>
-      <c r="B193" s="24" t="s">
+      <c r="B193" s="22" t="s">
         <v>1226</v>
       </c>
-      <c r="C193" s="24">
+      <c r="C193" s="22">
         <v>3</v>
       </c>
-      <c r="D193" s="35"/>
-      <c r="E193" s="24" t="s">
+      <c r="D193" s="25"/>
+      <c r="E193" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="194" spans="1:5">
-      <c r="A194" s="24" t="s">
+      <c r="A194" s="22" t="s">
         <v>745</v>
       </c>
-      <c r="B194" s="24" t="s">
+      <c r="B194" s="22" t="s">
         <v>1227</v>
       </c>
-      <c r="C194" s="24">
+      <c r="C194" s="22">
         <v>4</v>
       </c>
-      <c r="D194" s="35"/>
-      <c r="E194" s="24" t="s">
+      <c r="D194" s="25"/>
+      <c r="E194" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="195" spans="1:5">
-      <c r="A195" s="24" t="s">
+      <c r="A195" s="22" t="s">
         <v>745</v>
       </c>
-      <c r="B195" s="24" t="s">
+      <c r="B195" s="22" t="s">
         <v>1228</v>
       </c>
-      <c r="C195" s="24">
+      <c r="C195" s="22">
         <v>5</v>
       </c>
-      <c r="D195" s="35"/>
-      <c r="E195" s="24" t="s">
+      <c r="D195" s="25"/>
+      <c r="E195" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="196" spans="1:5">
-      <c r="A196" s="24" t="s">
+      <c r="A196" s="22" t="s">
         <v>745</v>
       </c>
-      <c r="B196" s="24" t="s">
+      <c r="B196" s="22" t="s">
         <v>1229</v>
       </c>
-      <c r="C196" s="24">
+      <c r="C196" s="22">
         <v>6</v>
       </c>
-      <c r="D196" s="35"/>
-      <c r="E196" s="24" t="s">
+      <c r="D196" s="25"/>
+      <c r="E196" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="197" spans="1:5">
-      <c r="A197" s="24" t="s">
+      <c r="A197" s="22" t="s">
         <v>745</v>
       </c>
-      <c r="B197" s="24" t="s">
+      <c r="B197" s="22" t="s">
         <v>1230</v>
       </c>
-      <c r="C197" s="24">
+      <c r="C197" s="22">
         <v>7</v>
       </c>
-      <c r="D197" s="35"/>
-      <c r="E197" s="24" t="s">
+      <c r="D197" s="25"/>
+      <c r="E197" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="198" spans="1:5">
-      <c r="A198" s="24" t="s">
+      <c r="A198" s="22" t="s">
         <v>749</v>
       </c>
-      <c r="B198" s="24" t="s">
+      <c r="B198" s="22" t="s">
         <v>1231</v>
       </c>
-      <c r="C198" s="24">
-        <v>1</v>
-      </c>
-      <c r="D198" s="35"/>
-      <c r="E198" s="24" t="s">
+      <c r="C198" s="22">
+        <v>1</v>
+      </c>
+      <c r="D198" s="25"/>
+      <c r="E198" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="199" spans="1:5">
-      <c r="A199" s="24" t="s">
+      <c r="A199" s="22" t="s">
         <v>749</v>
       </c>
-      <c r="B199" s="24" t="s">
+      <c r="B199" s="22" t="s">
         <v>1232</v>
       </c>
-      <c r="C199" s="24">
+      <c r="C199" s="22">
         <v>2</v>
       </c>
-      <c r="D199" s="35"/>
-      <c r="E199" s="24" t="s">
+      <c r="D199" s="25"/>
+      <c r="E199" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="200" spans="1:5">
-      <c r="A200" s="24" t="s">
+      <c r="A200" s="22" t="s">
         <v>749</v>
       </c>
-      <c r="B200" s="24" t="s">
+      <c r="B200" s="22" t="s">
         <v>1233</v>
       </c>
-      <c r="C200" s="24">
+      <c r="C200" s="22">
         <v>3</v>
       </c>
-      <c r="D200" s="35"/>
-      <c r="E200" s="24" t="s">
+      <c r="D200" s="25"/>
+      <c r="E200" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="201" spans="1:5">
-      <c r="A201" s="24" t="s">
+      <c r="A201" s="22" t="s">
         <v>754</v>
       </c>
-      <c r="B201" s="24" t="s">
+      <c r="B201" s="22" t="s">
         <v>1234</v>
       </c>
-      <c r="C201" s="24">
-        <v>1</v>
-      </c>
-      <c r="D201" s="35"/>
-      <c r="E201" s="24" t="s">
+      <c r="C201" s="22">
+        <v>1</v>
+      </c>
+      <c r="D201" s="25"/>
+      <c r="E201" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="202" spans="1:5">
-      <c r="A202" s="24" t="s">
+      <c r="A202" s="22" t="s">
         <v>759</v>
       </c>
-      <c r="B202" s="24" t="s">
+      <c r="B202" s="22" t="s">
         <v>1235</v>
       </c>
-      <c r="C202" s="24">
-        <v>1</v>
-      </c>
-      <c r="D202" s="35"/>
-      <c r="E202" s="24" t="s">
+      <c r="C202" s="22">
+        <v>1</v>
+      </c>
+      <c r="D202" s="25"/>
+      <c r="E202" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="203" spans="1:5">
-      <c r="A203" s="24" t="s">
+      <c r="A203" s="22" t="s">
         <v>759</v>
       </c>
-      <c r="B203" s="24" t="s">
+      <c r="B203" s="22" t="s">
         <v>1236</v>
       </c>
-      <c r="C203" s="24">
+      <c r="C203" s="22">
         <v>2</v>
       </c>
-      <c r="D203" s="35"/>
-      <c r="E203" s="24" t="s">
+      <c r="D203" s="25"/>
+      <c r="E203" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="204" spans="1:5">
-      <c r="A204" s="24" t="s">
+      <c r="A204" s="22" t="s">
         <v>765</v>
       </c>
-      <c r="B204" s="24" t="s">
+      <c r="B204" s="22" t="s">
         <v>1237</v>
       </c>
-      <c r="C204" s="24">
-        <v>1</v>
-      </c>
-      <c r="D204" s="35"/>
-      <c r="E204" s="24" t="s">
+      <c r="C204" s="22">
+        <v>1</v>
+      </c>
+      <c r="D204" s="25"/>
+      <c r="E204" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="205" spans="1:5">
-      <c r="A205" s="24" t="s">
+      <c r="A205" s="22" t="s">
         <v>765</v>
       </c>
-      <c r="B205" s="24" t="s">
+      <c r="B205" s="22" t="s">
         <v>1238</v>
       </c>
-      <c r="C205" s="24">
+      <c r="C205" s="22">
         <v>2</v>
       </c>
-      <c r="D205" s="35"/>
-      <c r="E205" s="24" t="s">
+      <c r="D205" s="25"/>
+      <c r="E205" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="206" spans="1:5">
-      <c r="A206" s="24" t="s">
+      <c r="A206" s="22" t="s">
         <v>770</v>
       </c>
-      <c r="B206" s="24" t="s">
+      <c r="B206" s="22" t="s">
         <v>1239</v>
       </c>
-      <c r="C206" s="24">
-        <v>1</v>
-      </c>
-      <c r="D206" s="35"/>
-      <c r="E206" s="24" t="s">
+      <c r="C206" s="22">
+        <v>1</v>
+      </c>
+      <c r="D206" s="25"/>
+      <c r="E206" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="207" spans="1:5">
-      <c r="A207" s="24" t="s">
+      <c r="A207" s="22" t="s">
         <v>770</v>
       </c>
-      <c r="B207" s="24" t="s">
+      <c r="B207" s="22" t="s">
         <v>1240</v>
       </c>
-      <c r="C207" s="24">
+      <c r="C207" s="22">
         <v>2</v>
       </c>
-      <c r="D207" s="35"/>
-      <c r="E207" s="24" t="s">
+      <c r="D207" s="25"/>
+      <c r="E207" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="208" spans="1:5">
-      <c r="A208" s="24" t="s">
+      <c r="A208" s="22" t="s">
         <v>770</v>
       </c>
-      <c r="B208" s="24" t="s">
+      <c r="B208" s="22" t="s">
         <v>1241</v>
       </c>
-      <c r="C208" s="24">
+      <c r="C208" s="22">
         <v>3</v>
       </c>
-      <c r="D208" s="35"/>
-      <c r="E208" s="24" t="s">
+      <c r="D208" s="25"/>
+      <c r="E208" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="209" spans="1:5">
-      <c r="A209" s="24" t="s">
+      <c r="A209" s="22" t="s">
         <v>774</v>
       </c>
-      <c r="B209" s="24" t="s">
+      <c r="B209" s="22" t="s">
         <v>1242</v>
       </c>
-      <c r="C209" s="24">
-        <v>1</v>
-      </c>
-      <c r="D209" s="35"/>
-      <c r="E209" s="24" t="s">
+      <c r="C209" s="22">
+        <v>1</v>
+      </c>
+      <c r="D209" s="25"/>
+      <c r="E209" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="210" spans="1:5">
-      <c r="A210" s="24" t="s">
+      <c r="A210" s="22" t="s">
         <v>774</v>
       </c>
-      <c r="B210" s="24" t="s">
+      <c r="B210" s="22" t="s">
         <v>1243</v>
       </c>
-      <c r="C210" s="24">
+      <c r="C210" s="22">
         <v>2</v>
       </c>
-      <c r="D210" s="35"/>
-      <c r="E210" s="24" t="s">
+      <c r="D210" s="25"/>
+      <c r="E210" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="211" spans="1:5">
-      <c r="A211" s="24" t="s">
+      <c r="A211" s="22" t="s">
         <v>778</v>
       </c>
-      <c r="B211" s="24" t="s">
+      <c r="B211" s="22" t="s">
         <v>1244</v>
       </c>
-      <c r="C211" s="24">
-        <v>1</v>
-      </c>
-      <c r="D211" s="35"/>
-      <c r="E211" s="24" t="s">
+      <c r="C211" s="22">
+        <v>1</v>
+      </c>
+      <c r="D211" s="25"/>
+      <c r="E211" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="212" spans="1:5">
-      <c r="A212" s="24" t="s">
+      <c r="A212" s="22" t="s">
         <v>783</v>
       </c>
-      <c r="B212" s="24" t="s">
+      <c r="B212" s="22" t="s">
         <v>1245</v>
       </c>
-      <c r="C212" s="24">
-        <v>1</v>
-      </c>
-      <c r="D212" s="35"/>
-      <c r="E212" s="24" t="s">
+      <c r="C212" s="22">
+        <v>1</v>
+      </c>
+      <c r="D212" s="25"/>
+      <c r="E212" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="213" spans="1:5">
-      <c r="A213" s="24" t="s">
+      <c r="A213" s="22" t="s">
         <v>788</v>
       </c>
-      <c r="B213" s="24" t="s">
+      <c r="B213" s="22" t="s">
         <v>1246</v>
       </c>
-      <c r="C213" s="24">
-        <v>1</v>
-      </c>
-      <c r="D213" s="35"/>
-      <c r="E213" s="24" t="s">
+      <c r="C213" s="22">
+        <v>1</v>
+      </c>
+      <c r="D213" s="25"/>
+      <c r="E213" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="214" spans="1:5">
-      <c r="A214" s="24" t="s">
+      <c r="A214" s="22" t="s">
         <v>793</v>
       </c>
-      <c r="B214" s="24" t="s">
+      <c r="B214" s="22" t="s">
         <v>1247</v>
       </c>
-      <c r="C214" s="24">
-        <v>1</v>
-      </c>
-      <c r="D214" s="35"/>
-      <c r="E214" s="24" t="s">
+      <c r="C214" s="22">
+        <v>1</v>
+      </c>
+      <c r="D214" s="25"/>
+      <c r="E214" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="215" spans="1:5">
-      <c r="A215" s="24" t="s">
+      <c r="A215" s="22" t="s">
         <v>798</v>
       </c>
-      <c r="B215" s="24" t="s">
+      <c r="B215" s="22" t="s">
         <v>1248</v>
       </c>
-      <c r="C215" s="24">
-        <v>1</v>
-      </c>
-      <c r="D215" s="35"/>
-      <c r="E215" s="24" t="s">
+      <c r="C215" s="22">
+        <v>1</v>
+      </c>
+      <c r="D215" s="25"/>
+      <c r="E215" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="216" spans="1:5">
-      <c r="A216" s="24" t="s">
+      <c r="A216" s="22" t="s">
         <v>798</v>
       </c>
-      <c r="B216" s="24" t="s">
+      <c r="B216" s="22" t="s">
         <v>1249</v>
       </c>
-      <c r="C216" s="24">
+      <c r="C216" s="22">
         <v>2</v>
       </c>
-      <c r="D216" s="35"/>
-      <c r="E216" s="24" t="s">
+      <c r="D216" s="25"/>
+      <c r="E216" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="217" spans="1:5">
-      <c r="A217" s="24" t="s">
+      <c r="A217" s="22" t="s">
         <v>802</v>
       </c>
-      <c r="B217" s="24" t="s">
+      <c r="B217" s="22" t="s">
         <v>1250</v>
       </c>
-      <c r="C217" s="24">
-        <v>1</v>
-      </c>
-      <c r="D217" s="35"/>
-      <c r="E217" s="24" t="s">
+      <c r="C217" s="22">
+        <v>1</v>
+      </c>
+      <c r="D217" s="25"/>
+      <c r="E217" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="218" spans="1:5">
-      <c r="A218" s="24" t="s">
+      <c r="A218" s="22" t="s">
         <v>805</v>
       </c>
-      <c r="B218" s="24" t="s">
+      <c r="B218" s="22" t="s">
         <v>1251</v>
       </c>
-      <c r="C218" s="24">
-        <v>1</v>
-      </c>
-      <c r="D218" s="35"/>
-      <c r="E218" s="24" t="s">
+      <c r="C218" s="22">
+        <v>1</v>
+      </c>
+      <c r="D218" s="25"/>
+      <c r="E218" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="219" spans="1:5">
-      <c r="A219" s="24" t="s">
+      <c r="A219" s="22" t="s">
         <v>808</v>
       </c>
-      <c r="B219" s="24" t="s">
+      <c r="B219" s="22" t="s">
         <v>1252</v>
       </c>
-      <c r="C219" s="24">
-        <v>1</v>
-      </c>
-      <c r="D219" s="35"/>
-      <c r="E219" s="24" t="s">
+      <c r="C219" s="22">
+        <v>1</v>
+      </c>
+      <c r="D219" s="25"/>
+      <c r="E219" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="220" spans="1:5">
-      <c r="A220" s="24" t="s">
+      <c r="A220" s="22" t="s">
         <v>808</v>
       </c>
-      <c r="B220" s="24" t="s">
+      <c r="B220" s="22" t="s">
         <v>1253</v>
       </c>
-      <c r="C220" s="24">
+      <c r="C220" s="22">
         <v>2</v>
       </c>
-      <c r="D220" s="35"/>
-      <c r="E220" s="24" t="s">
+      <c r="D220" s="25"/>
+      <c r="E220" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="221" spans="1:5">
-      <c r="A221" s="24" t="s">
+      <c r="A221" s="22" t="s">
         <v>808</v>
       </c>
-      <c r="B221" s="24" t="s">
+      <c r="B221" s="22" t="s">
         <v>1254</v>
       </c>
-      <c r="C221" s="24">
+      <c r="C221" s="22">
         <v>3</v>
       </c>
-      <c r="D221" s="35"/>
-      <c r="E221" s="24" t="s">
+      <c r="D221" s="25"/>
+      <c r="E221" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="222" spans="1:5">
-      <c r="A222" s="24" t="s">
+      <c r="A222" s="22" t="s">
         <v>808</v>
       </c>
-      <c r="B222" s="24" t="s">
+      <c r="B222" s="22" t="s">
         <v>1255</v>
       </c>
-      <c r="C222" s="24">
+      <c r="C222" s="22">
         <v>4</v>
       </c>
-      <c r="D222" s="35"/>
-      <c r="E222" s="24" t="s">
+      <c r="D222" s="25"/>
+      <c r="E222" s="22" t="s">
         <v>828</v>
       </c>
     </row>
     <row r="223" spans="1:5">
-      <c r="A223" s="24" t="s">
+      <c r="A223" s="22" t="s">
         <v>815</v>
       </c>
-      <c r="B223" s="24" t="s">
+      <c r="B223" s="22" t="s">
         <v>1256</v>
       </c>
-      <c r="C223" s="24">
-        <v>1</v>
-      </c>
-      <c r="D223" s="35"/>
-      <c r="E223" s="24" t="s">
+      <c r="C223" s="22">
+        <v>1</v>
+      </c>
+      <c r="D223" s="25"/>
+      <c r="E223" s="22" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="224" spans="1:5">
-      <c r="A224" s="24" t="s">
+      <c r="A224" s="22" t="s">
         <v>1271</v>
       </c>
-      <c r="B224" s="24"/>
-      <c r="C224" s="24">
-        <v>1</v>
-      </c>
-      <c r="D224" s="35"/>
-      <c r="E224" s="24" t="s">
+      <c r="B224" s="25" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C224" s="22">
+        <v>1</v>
+      </c>
+      <c r="E224" s="27" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="225" spans="1:5" ht="28">
-      <c r="A225" s="36" t="s">
+      <c r="A225" s="26" t="s">
         <v>1281</v>
       </c>
-      <c r="B225" s="35" t="s">
+      <c r="B225" s="25" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C225" s="22">
+        <v>1</v>
+      </c>
+      <c r="D225" s="26" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E225" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" ht="28">
+      <c r="A226" s="26" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B226" s="25" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C226" s="22">
+        <v>2</v>
+      </c>
+      <c r="D226" s="26" t="s">
+        <v>1319</v>
+      </c>
+      <c r="E226" s="26" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" ht="28">
+      <c r="A227" s="26" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B227" s="25" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C227" s="22">
+        <v>3</v>
+      </c>
+      <c r="D227" s="26" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E227" s="26" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" ht="28">
+      <c r="A228" s="26" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B228" s="25" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C228" s="22">
+        <v>4</v>
+      </c>
+      <c r="D228" s="26" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E228" s="26" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" ht="28">
+      <c r="A229" s="26" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B229" s="25" t="s">
         <v>1339</v>
       </c>
-      <c r="C225" s="24">
-        <v>1</v>
-      </c>
-      <c r="D225" s="36" t="s">
+      <c r="C229" s="22">
+        <v>5</v>
+      </c>
+      <c r="D229" s="26" t="s">
         <v>1322</v>
       </c>
-      <c r="E225" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" ht="28">
-      <c r="A226" s="36" t="s">
+      <c r="E229" s="26" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" ht="28">
+      <c r="A230" s="26" t="s">
         <v>1281</v>
       </c>
-      <c r="B226" s="35" t="s">
+      <c r="B230" s="25" t="s">
         <v>1340</v>
       </c>
-      <c r="C226" s="24">
+      <c r="C230" s="22">
+        <v>6</v>
+      </c>
+      <c r="D230" s="26" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E230" s="26" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="26" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B231" s="25" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C231" s="22">
         <v>2</v>
       </c>
-      <c r="D226" s="36" t="s">
-        <v>1323</v>
-      </c>
-      <c r="E226" s="36" t="s">
+      <c r="D231" s="26" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E231" s="26" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="28">
-      <c r="A227" s="36" t="s">
-        <v>1281</v>
-      </c>
-      <c r="B227" s="35" t="s">
-        <v>1341</v>
-      </c>
-      <c r="C227" s="24">
-        <v>3</v>
-      </c>
-      <c r="D227" s="36" t="s">
+    <row r="232" spans="1:5">
+      <c r="A232" s="26" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B232" s="25" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C232" s="22">
+        <v>1</v>
+      </c>
+      <c r="D232" s="26" t="s">
         <v>1324</v>
       </c>
-      <c r="E227" s="36" t="s">
+      <c r="E232" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="26" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B233" s="25" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C233" s="22">
+        <v>1</v>
+      </c>
+      <c r="D233" s="26" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E233" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="26" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B234" s="25" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C234" s="22">
+        <v>2</v>
+      </c>
+      <c r="D234" s="26" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E234" s="26" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="228" spans="1:5" ht="28">
-      <c r="A228" s="36" t="s">
-        <v>1281</v>
-      </c>
-      <c r="B228" s="35" t="s">
-        <v>1342</v>
-      </c>
-      <c r="C228" s="24">
-        <v>4</v>
-      </c>
-      <c r="D228" s="36" t="s">
-        <v>1325</v>
-      </c>
-      <c r="E228" s="36" t="s">
+    <row r="235" spans="1:5">
+      <c r="A235" s="26" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B235" s="25" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C235" s="22">
+        <v>1</v>
+      </c>
+      <c r="D235" s="26" t="s">
+        <v>1328</v>
+      </c>
+      <c r="E235" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="26" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B236" s="25" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C236" s="22">
+        <v>2</v>
+      </c>
+      <c r="D236" s="26" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E236" s="26" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="28">
-      <c r="A229" s="36" t="s">
-        <v>1281</v>
-      </c>
-      <c r="B229" s="35" t="s">
-        <v>1343</v>
-      </c>
-      <c r="C229" s="24">
-        <v>5</v>
-      </c>
-      <c r="D229" s="36" t="s">
-        <v>1326</v>
-      </c>
-      <c r="E229" s="36" t="s">
+    <row r="237" spans="1:5">
+      <c r="A237" s="26" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B237" s="25" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C237" s="22">
+        <v>1</v>
+      </c>
+      <c r="D237" s="26" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E237" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="26" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B238" s="25" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C238" s="22">
+        <v>2</v>
+      </c>
+      <c r="D238" s="26" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E238" s="26" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="28">
-      <c r="A230" s="36" t="s">
-        <v>1281</v>
-      </c>
-      <c r="B230" s="35" t="s">
-        <v>1344</v>
-      </c>
-      <c r="C230" s="24">
-        <v>6</v>
-      </c>
-      <c r="D230" s="36" t="s">
-        <v>1327</v>
-      </c>
-      <c r="E230" s="36" t="s">
+    <row r="239" spans="1:5">
+      <c r="A239" s="26" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B239" s="25" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C239" s="22">
+        <v>1</v>
+      </c>
+      <c r="D239" s="26" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E239" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="26" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B240" s="25" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C240" s="22">
+        <v>2</v>
+      </c>
+      <c r="D240" s="26" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E240" s="26" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="231" spans="1:5">
-      <c r="A231" s="36" t="s">
-        <v>1282</v>
-      </c>
-      <c r="B231" s="35" t="s">
-        <v>1345</v>
-      </c>
-      <c r="C231" s="24">
-        <v>2</v>
-      </c>
-      <c r="D231" s="36" t="s">
-        <v>1329</v>
-      </c>
-      <c r="E231" s="36" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5">
-      <c r="A232" s="36" t="s">
-        <v>1282</v>
-      </c>
-      <c r="B232" s="35" t="s">
-        <v>1346</v>
-      </c>
-      <c r="C232" s="24">
-        <v>1</v>
-      </c>
-      <c r="D232" s="36" t="s">
-        <v>1328</v>
-      </c>
-      <c r="E232" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="233" spans="1:5">
-      <c r="A233" s="36" t="s">
-        <v>1283</v>
-      </c>
-      <c r="B233" s="35" t="s">
-        <v>1347</v>
-      </c>
-      <c r="C233" s="24">
-        <v>1</v>
-      </c>
-      <c r="D233" s="36" t="s">
-        <v>1330</v>
-      </c>
-      <c r="E233" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5">
-      <c r="A234" s="36" t="s">
-        <v>1283</v>
-      </c>
-      <c r="B234" s="35" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C234" s="24">
-        <v>2</v>
-      </c>
-      <c r="D234" s="36" t="s">
-        <v>1331</v>
-      </c>
-      <c r="E234" s="36" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="235" spans="1:5">
-      <c r="A235" s="36" t="s">
-        <v>1284</v>
-      </c>
-      <c r="B235" s="35" t="s">
-        <v>1348</v>
-      </c>
-      <c r="C235" s="24">
-        <v>1</v>
-      </c>
-      <c r="D235" s="36" t="s">
-        <v>1332</v>
-      </c>
-      <c r="E235" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="236" spans="1:5">
-      <c r="A236" s="36" t="s">
-        <v>1284</v>
-      </c>
-      <c r="B236" s="35" t="s">
-        <v>1349</v>
-      </c>
-      <c r="C236" s="24">
-        <v>2</v>
-      </c>
-      <c r="D236" s="36" t="s">
-        <v>1333</v>
-      </c>
-      <c r="E236" s="36" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5">
-      <c r="A237" s="36" t="s">
-        <v>1285</v>
-      </c>
-      <c r="B237" s="35" t="s">
+    <row r="241" spans="1:5">
+      <c r="A241" s="26" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B241" s="25" t="s">
         <v>1350</v>
       </c>
-      <c r="C237" s="24">
-        <v>1</v>
-      </c>
-      <c r="D237" s="36" t="s">
+      <c r="C241" s="22">
+        <v>1</v>
+      </c>
+      <c r="D241" s="26" t="s">
         <v>1334</v>
       </c>
-      <c r="E237" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5">
-      <c r="A238" s="36" t="s">
-        <v>1285</v>
-      </c>
-      <c r="B238" s="35" t="s">
-        <v>1351</v>
-      </c>
-      <c r="C238" s="24">
-        <v>2</v>
-      </c>
-      <c r="D238" s="36" t="s">
-        <v>1335</v>
-      </c>
-      <c r="E238" s="36" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5">
-      <c r="A239" s="36" t="s">
-        <v>1286</v>
-      </c>
-      <c r="B239" s="35" t="s">
-        <v>1352</v>
-      </c>
-      <c r="C239" s="24">
-        <v>1</v>
-      </c>
-      <c r="D239" s="36" t="s">
-        <v>1336</v>
-      </c>
-      <c r="E239" s="36" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5">
-      <c r="A240" s="36" t="s">
-        <v>1286</v>
-      </c>
-      <c r="B240" s="35" t="s">
-        <v>1353</v>
-      </c>
-      <c r="C240" s="24">
-        <v>2</v>
-      </c>
-      <c r="D240" s="36" t="s">
-        <v>1337</v>
-      </c>
-      <c r="E240" s="36" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5">
-      <c r="A241" s="36" t="s">
-        <v>1287</v>
-      </c>
-      <c r="B241" s="35" t="s">
-        <v>1354</v>
-      </c>
-      <c r="C241" s="24">
-        <v>1</v>
-      </c>
-      <c r="D241" s="36" t="s">
-        <v>1338</v>
-      </c>
-      <c r="E241" s="36" t="s">
+      <c r="E241" s="26" t="s">
         <v>34</v>
       </c>
     </row>
@@ -16158,94 +16162,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>1004</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="35" t="s">
         <v>1005</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
     </row>
     <row r="4" spans="1:6" ht="46" customHeight="1">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="33" t="s">
         <v>1006</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="35" t="s">
         <v>1007</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
     </row>
     <row r="7" spans="1:6" ht="54" customHeight="1">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="33" t="s">
         <v>1008</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="35" t="s">
         <v>1009</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
     </row>
     <row r="10" spans="1:6" ht="46" customHeight="1">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="33" t="s">
         <v>1010</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="35" t="s">
         <v>1011</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
     </row>
     <row r="13" spans="1:6" ht="54" customHeight="1">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="33" t="s">
         <v>1012</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
     </row>
     <row r="14" spans="1:6" ht="32" customHeight="1">
       <c r="A14" s="1" t="s">

--- a/inventaire_mobilier.xlsx
+++ b/inventaire_mobilier.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolas.coquet/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolas.coquet/Documents/PERSONNEL/Emeleta/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3678D88-D38A-CC41-82EA-BCD5B5D9E789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F5A6D9-E1E0-0646-89A2-9A752801FBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mobilier" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2458" uniqueCount="1362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2455" uniqueCount="1361">
   <si>
     <t>Inventaire du mobilier</t>
   </si>
@@ -3724,9 +3724,6 @@
   </si>
   <si>
     <t>MOB-087-06.webp</t>
-  </si>
-  <si>
-    <t>MOB-087-07.webp</t>
   </si>
   <si>
     <t>MOB-088-01.webp</t>
@@ -4320,10 +4317,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4333,14 +4329,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4353,7 +4350,8 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <sz val="11"/>
+        <color auto="1"/>
         <name val="Carlito"/>
         <scheme val="none"/>
       </font>
@@ -4364,6 +4362,109 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4769,17 +4870,13 @@
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
+        <sz val="10"/>
         <name val="Carlito"/>
         <scheme val="none"/>
       </font>
@@ -4792,107 +4889,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4908,50 +4905,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MobilierTable" displayName="MobilierTable" ref="A3:U113" totalsRowShown="0" headerRowDxfId="22" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MobilierTable" displayName="MobilierTable" ref="A3:U113" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
   <autoFilter ref="A3:U113" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:U113">
     <sortCondition ref="A3:A113"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Identifiant" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Catégorie" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Datation" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Origine" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Matériaux" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Description" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Dimensions" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="État" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Estimation unitaire basse (€)" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Estimation unitaire haute (€)" dataDxfId="11"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Localisation" dataDxfId="10"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Statut" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Publié" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Mots-clés" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Source 1" dataDxfId="6"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Source 2" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Quantité" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Estimation du lot basse (€)" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Estimation du lot haute (€)" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Associé à" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Identifiant" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Catégorie" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Datation" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Origine" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Matériaux" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Description" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Dimensions" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="État" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Estimation unitaire basse (€)" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Estimation unitaire haute (€)" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Localisation" dataDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Statut" dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Publié" dataDxfId="14"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Mots-clés" dataDxfId="13"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Source 1" dataDxfId="12"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Source 2" dataDxfId="11"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Quantité" dataDxfId="10"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Estimation du lot basse (€)" dataDxfId="9"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Estimation du lot haute (€)" dataDxfId="8"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Associé à" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PhotosTable" displayName="PhotosTable" ref="A3:E103" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PhotosTable" displayName="PhotosTable" ref="A3:E103" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A3:E103" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:E103">
     <sortCondition ref="A3:A103"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Identifiant objet" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fichier" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Ordre" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Légende" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Image principale" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Identifiant objet" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fichier" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Ordre" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Légende" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Image principale" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5178,54 +5175,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="23">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
-      <c r="T2" s="31"/>
-      <c r="U2" s="31"/>
+      <c r="A2" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
     </row>
     <row r="3" spans="1:21" s="5" customFormat="1" ht="32">
       <c r="A3" s="3" t="s">
@@ -5817,7 +5814,7 @@
         <v>114</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>52</v>
@@ -6404,7 +6401,7 @@
         <v>206</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>52</v>
@@ -6419,7 +6416,7 @@
         <v>207</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>208</v>
@@ -6924,7 +6921,7 @@
         <v>285</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>1019</v>
@@ -7054,7 +7051,7 @@
         <v>302</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>303</v>
@@ -7119,7 +7116,7 @@
         <v>312</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>313</v>
@@ -7379,7 +7376,7 @@
         <v>356</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>52</v>
@@ -7394,7 +7391,7 @@
         <v>357</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>358</v>
@@ -8230,7 +8227,7 @@
         <v>471</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>197</v>
@@ -8626,7 +8623,7 @@
         <v>120</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="M55" s="12" t="s">
         <v>33</v>
@@ -9297,7 +9294,7 @@
         <v>70</v>
       </c>
       <c r="L66" s="10" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="M66" s="12" t="s">
         <v>33</v>
@@ -10554,7 +10551,7 @@
         <v>731</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C87" s="10" t="s">
         <v>725</v>
@@ -10563,13 +10560,13 @@
         <v>545</v>
       </c>
       <c r="E87" s="10" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>1269</v>
+      </c>
+      <c r="G87" s="10" t="s">
         <v>1268</v>
-      </c>
-      <c r="F87" s="10" t="s">
-        <v>1270</v>
-      </c>
-      <c r="G87" s="10" t="s">
-        <v>1269</v>
       </c>
       <c r="H87" s="9" t="s">
         <v>1025</v>
@@ -10596,7 +10593,7 @@
         <v>733</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="13">
@@ -10731,7 +10728,7 @@
         <v>745</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C90" s="17" t="s">
         <v>197</v>
@@ -10746,7 +10743,7 @@
         <v>747</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="H90" s="9" t="s">
         <v>1025</v>
@@ -10782,7 +10779,7 @@
         <v>1500</v>
       </c>
       <c r="U90" s="9" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="91" spans="1:21">
@@ -10790,7 +10787,7 @@
         <v>749</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C91" s="17" t="s">
         <v>197</v>
@@ -10841,7 +10838,7 @@
         <v>600</v>
       </c>
       <c r="U91" s="9" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="92" spans="1:21">
@@ -11644,40 +11641,40 @@
     </row>
     <row r="106" spans="1:21" ht="42">
       <c r="A106" s="8" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B106" s="26" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C106" s="26" t="s">
         <v>790</v>
       </c>
       <c r="D106" s="26" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="E106" s="26" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="G106" s="26" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H106" s="9" t="s">
         <v>1025</v>
       </c>
       <c r="I106" s="26" t="s">
-        <v>1310</v>
-      </c>
-      <c r="J106" s="36">
+        <v>1309</v>
+      </c>
+      <c r="J106" s="28">
         <v>120</v>
       </c>
-      <c r="K106" s="36">
+      <c r="K106" s="28">
         <v>300</v>
       </c>
       <c r="L106" s="9" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M106" s="12" t="s">
         <v>33</v>
@@ -11691,50 +11688,50 @@
       <c r="R106" s="13">
         <v>1</v>
       </c>
-      <c r="S106" s="36">
+      <c r="S106" s="28">
         <v>120</v>
       </c>
-      <c r="T106" s="36">
+      <c r="T106" s="28">
         <v>300</v>
       </c>
       <c r="U106" s="9"/>
     </row>
     <row r="107" spans="1:21" ht="28">
       <c r="A107" s="8" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B107" s="26" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C107" s="26" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D107" s="26" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="E107" s="26" t="s">
         <v>627</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="G107" s="26" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H107" s="9" t="s">
         <v>1025</v>
       </c>
       <c r="I107" s="26" t="s">
-        <v>1311</v>
-      </c>
-      <c r="J107" s="36">
+        <v>1310</v>
+      </c>
+      <c r="J107" s="28">
         <v>25</v>
       </c>
-      <c r="K107" s="36">
+      <c r="K107" s="28">
         <v>60</v>
       </c>
       <c r="L107" s="9" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="M107" s="12" t="s">
         <v>33</v>
@@ -11748,20 +11745,20 @@
       <c r="R107" s="13">
         <v>1</v>
       </c>
-      <c r="S107" s="36">
+      <c r="S107" s="28">
         <v>25</v>
       </c>
-      <c r="T107" s="36">
+      <c r="T107" s="28">
         <v>60</v>
       </c>
       <c r="U107" s="9"/>
     </row>
     <row r="108" spans="1:21">
       <c r="A108" s="8" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B108" s="26" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="C108" s="26" t="s">
         <v>1017</v>
@@ -11770,24 +11767,24 @@
         <v>167</v>
       </c>
       <c r="E108" s="26" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="G108" s="26" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H108" s="9" t="s">
         <v>1025</v>
       </c>
       <c r="I108" s="26" t="s">
-        <v>1312</v>
-      </c>
-      <c r="J108" s="36">
+        <v>1311</v>
+      </c>
+      <c r="J108" s="28">
         <v>60</v>
       </c>
-      <c r="K108" s="36">
+      <c r="K108" s="28">
         <v>120</v>
       </c>
       <c r="L108" s="9" t="s">
@@ -11805,46 +11802,46 @@
       <c r="R108" s="13">
         <v>1</v>
       </c>
-      <c r="S108" s="36">
+      <c r="S108" s="28">
         <v>60</v>
       </c>
-      <c r="T108" s="36">
+      <c r="T108" s="28">
         <v>120</v>
       </c>
       <c r="U108" s="9"/>
     </row>
     <row r="109" spans="1:21" ht="28">
       <c r="A109" s="8" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B109" s="26" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="C109" s="26" t="s">
         <v>75</v>
       </c>
       <c r="D109" s="26" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="E109" s="26" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="G109" s="26" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H109" s="9" t="s">
         <v>1025</v>
       </c>
       <c r="I109" s="26" t="s">
-        <v>1313</v>
-      </c>
-      <c r="J109" s="36">
+        <v>1312</v>
+      </c>
+      <c r="J109" s="28">
         <v>30</v>
       </c>
-      <c r="K109" s="36">
+      <c r="K109" s="28">
         <v>70</v>
       </c>
       <c r="L109" s="9" t="s">
@@ -11862,20 +11859,20 @@
       <c r="R109" s="13">
         <v>1</v>
       </c>
-      <c r="S109" s="36">
+      <c r="S109" s="28">
         <v>30</v>
       </c>
-      <c r="T109" s="36">
+      <c r="T109" s="28">
         <v>70</v>
       </c>
       <c r="U109" s="9"/>
     </row>
     <row r="110" spans="1:21" ht="42">
       <c r="A110" s="8" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B110" s="26" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C110" s="26" t="s">
         <v>75</v>
@@ -11884,24 +11881,24 @@
         <v>689</v>
       </c>
       <c r="E110" s="26" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="F110" s="26" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="G110" s="26" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H110" s="9" t="s">
         <v>1025</v>
       </c>
       <c r="I110" s="26" t="s">
-        <v>1314</v>
-      </c>
-      <c r="J110" s="36">
+        <v>1313</v>
+      </c>
+      <c r="J110" s="28">
         <v>50</v>
       </c>
-      <c r="K110" s="36">
+      <c r="K110" s="28">
         <v>120</v>
       </c>
       <c r="L110" s="9" t="s">
@@ -11919,46 +11916,46 @@
       <c r="R110" s="13">
         <v>1</v>
       </c>
-      <c r="S110" s="36">
+      <c r="S110" s="28">
         <v>50</v>
       </c>
-      <c r="T110" s="36">
+      <c r="T110" s="28">
         <v>120</v>
       </c>
       <c r="U110" s="9"/>
     </row>
     <row r="111" spans="1:21" ht="28">
       <c r="A111" s="8" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B111" s="26" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C111" s="26" t="s">
         <v>75</v>
       </c>
       <c r="D111" s="26" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="E111" s="26" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="F111" s="26" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="G111" s="26" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H111" s="9" t="s">
         <v>1025</v>
       </c>
       <c r="I111" s="26" t="s">
-        <v>1315</v>
-      </c>
-      <c r="J111" s="36">
+        <v>1314</v>
+      </c>
+      <c r="J111" s="28">
         <v>30</v>
       </c>
-      <c r="K111" s="36">
+      <c r="K111" s="28">
         <v>80</v>
       </c>
       <c r="L111" s="9" t="s">
@@ -11976,46 +11973,46 @@
       <c r="R111" s="13">
         <v>1</v>
       </c>
-      <c r="S111" s="36">
+      <c r="S111" s="28">
         <v>30</v>
       </c>
-      <c r="T111" s="36">
+      <c r="T111" s="28">
         <v>80</v>
       </c>
       <c r="U111" s="9"/>
     </row>
     <row r="112" spans="1:21">
       <c r="A112" s="8" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B112" s="26" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C112" s="26" t="s">
         <v>197</v>
       </c>
       <c r="D112" s="26" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="E112" s="26" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="G112" s="26" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H112" s="9" t="s">
         <v>1025</v>
       </c>
       <c r="I112" s="26" t="s">
-        <v>1316</v>
-      </c>
-      <c r="J112" s="36">
+        <v>1315</v>
+      </c>
+      <c r="J112" s="28">
         <v>80</v>
       </c>
-      <c r="K112" s="36">
+      <c r="K112" s="28">
         <v>180</v>
       </c>
       <c r="L112" s="9" t="s">
@@ -12033,20 +12030,20 @@
       <c r="R112" s="13">
         <v>1</v>
       </c>
-      <c r="S112" s="36">
+      <c r="S112" s="28">
         <v>80</v>
       </c>
-      <c r="T112" s="36">
+      <c r="T112" s="28">
         <v>180</v>
       </c>
       <c r="U112" s="9"/>
     </row>
     <row r="113" spans="1:21">
       <c r="A113" s="8" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C113" s="17" t="s">
         <v>197</v>
@@ -12061,7 +12058,7 @@
         <v>747</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="H113" s="9" t="s">
         <v>1025</v>
@@ -12097,7 +12094,7 @@
         <v>1500</v>
       </c>
       <c r="U113" s="9" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
   </sheetData>
@@ -12123,7 +12120,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E241"/>
+  <dimension ref="A1:E240"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -12134,22 +12131,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" ht="34" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>819</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="32" t="s">
         <v>820</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
     </row>
     <row r="3" spans="1:5" s="7" customFormat="1" ht="16" customHeight="1">
       <c r="A3" s="6" t="s">
@@ -12513,7 +12510,7 @@
         <v>106</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C24" s="23">
         <v>2</v>
@@ -12530,7 +12527,7 @@
         <v>106</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="C25" s="23">
         <v>3</v>
@@ -12547,7 +12544,7 @@
         <v>106</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C26" s="23">
         <v>4</v>
@@ -13267,7 +13264,7 @@
         <v>2</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="E68" s="23" t="s">
         <v>828</v>
@@ -13284,7 +13281,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="E69" s="23" t="s">
         <v>34</v>
@@ -15425,17 +15422,17 @@
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="22" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B197" s="22" t="s">
         <v>1230</v>
       </c>
       <c r="C197" s="22">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D197" s="25"/>
       <c r="E197" s="22" t="s">
-        <v>828</v>
+        <v>34</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -15446,11 +15443,11 @@
         <v>1231</v>
       </c>
       <c r="C198" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D198" s="25"/>
       <c r="E198" s="22" t="s">
-        <v>34</v>
+        <v>828</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -15461,7 +15458,7 @@
         <v>1232</v>
       </c>
       <c r="C199" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D199" s="25"/>
       <c r="E199" s="22" t="s">
@@ -15470,22 +15467,22 @@
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="22" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="B200" s="22" t="s">
         <v>1233</v>
       </c>
       <c r="C200" s="22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D200" s="25"/>
       <c r="E200" s="22" t="s">
-        <v>828</v>
+        <v>34</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="22" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="B201" s="22" t="s">
         <v>1234</v>
@@ -15506,26 +15503,26 @@
         <v>1235</v>
       </c>
       <c r="C202" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D202" s="25"/>
       <c r="E202" s="22" t="s">
-        <v>34</v>
+        <v>828</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="22" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="B203" s="22" t="s">
         <v>1236</v>
       </c>
       <c r="C203" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D203" s="25"/>
       <c r="E203" s="22" t="s">
-        <v>828</v>
+        <v>34</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -15536,26 +15533,26 @@
         <v>1237</v>
       </c>
       <c r="C204" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D204" s="25"/>
       <c r="E204" s="22" t="s">
-        <v>34</v>
+        <v>828</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="22" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="B205" s="22" t="s">
         <v>1238</v>
       </c>
       <c r="C205" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D205" s="25"/>
       <c r="E205" s="22" t="s">
-        <v>828</v>
+        <v>34</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -15566,11 +15563,11 @@
         <v>1239</v>
       </c>
       <c r="C206" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D206" s="25"/>
       <c r="E206" s="22" t="s">
-        <v>34</v>
+        <v>828</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -15581,7 +15578,7 @@
         <v>1240</v>
       </c>
       <c r="C207" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D207" s="25"/>
       <c r="E207" s="22" t="s">
@@ -15590,17 +15587,17 @@
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="22" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="B208" s="22" t="s">
         <v>1241</v>
       </c>
       <c r="C208" s="22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D208" s="25"/>
       <c r="E208" s="22" t="s">
-        <v>828</v>
+        <v>34</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -15611,31 +15608,31 @@
         <v>1242</v>
       </c>
       <c r="C209" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D209" s="25"/>
       <c r="E209" s="22" t="s">
-        <v>34</v>
+        <v>828</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="22" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B210" s="22" t="s">
         <v>1243</v>
       </c>
       <c r="C210" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D210" s="25"/>
       <c r="E210" s="22" t="s">
-        <v>828</v>
+        <v>34</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="22" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="B211" s="22" t="s">
         <v>1244</v>
@@ -15650,7 +15647,7 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="22" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="B212" s="22" t="s">
         <v>1245</v>
@@ -15665,7 +15662,7 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="22" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="B213" s="22" t="s">
         <v>1246</v>
@@ -15680,7 +15677,7 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="22" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="B214" s="22" t="s">
         <v>1247</v>
@@ -15701,31 +15698,31 @@
         <v>1248</v>
       </c>
       <c r="C215" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D215" s="25"/>
       <c r="E215" s="22" t="s">
-        <v>34</v>
+        <v>828</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="22" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="B216" s="22" t="s">
         <v>1249</v>
       </c>
       <c r="C216" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D216" s="25"/>
       <c r="E216" s="22" t="s">
-        <v>828</v>
+        <v>34</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="22" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B217" s="22" t="s">
         <v>1250</v>
@@ -15740,7 +15737,7 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="22" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B218" s="22" t="s">
         <v>1251</v>
@@ -15761,11 +15758,11 @@
         <v>1252</v>
       </c>
       <c r="C219" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D219" s="25"/>
       <c r="E219" s="22" t="s">
-        <v>34</v>
+        <v>828</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -15776,7 +15773,7 @@
         <v>1253</v>
       </c>
       <c r="C220" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D220" s="25"/>
       <c r="E220" s="22" t="s">
@@ -15791,7 +15788,7 @@
         <v>1254</v>
       </c>
       <c r="C221" s="22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D221" s="25"/>
       <c r="E221" s="22" t="s">
@@ -15800,74 +15797,76 @@
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="22" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="B222" s="22" t="s">
         <v>1255</v>
       </c>
       <c r="C222" s="22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D222" s="25"/>
       <c r="E222" s="22" t="s">
-        <v>828</v>
+        <v>34</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="22" t="s">
-        <v>815</v>
-      </c>
-      <c r="B223" s="22" t="s">
-        <v>1256</v>
+        <v>1270</v>
+      </c>
+      <c r="B223" s="25" t="s">
+        <v>1356</v>
       </c>
       <c r="C223" s="22">
         <v>1</v>
       </c>
-      <c r="D223" s="25"/>
-      <c r="E223" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5">
-      <c r="A224" s="22" t="s">
-        <v>1271</v>
+      <c r="E223" s="27" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" ht="28">
+      <c r="A224" s="26" t="s">
+        <v>1280</v>
       </c>
       <c r="B224" s="25" t="s">
-        <v>1357</v>
+        <v>1334</v>
       </c>
       <c r="C224" s="22">
         <v>1</v>
       </c>
-      <c r="E224" s="27" t="s">
+      <c r="D224" s="26" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E224" s="26" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="225" spans="1:5" ht="28">
       <c r="A225" s="26" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B225" s="25" t="s">
         <v>1335</v>
       </c>
       <c r="C225" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D225" s="26" t="s">
         <v>1318</v>
       </c>
       <c r="E225" s="26" t="s">
-        <v>34</v>
+        <v>828</v>
       </c>
     </row>
     <row r="226" spans="1:5" ht="28">
       <c r="A226" s="26" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B226" s="25" t="s">
         <v>1336</v>
       </c>
       <c r="C226" s="22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D226" s="26" t="s">
         <v>1319</v>
@@ -15878,13 +15877,13 @@
     </row>
     <row r="227" spans="1:5" ht="28">
       <c r="A227" s="26" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B227" s="25" t="s">
         <v>1337</v>
       </c>
       <c r="C227" s="22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D227" s="26" t="s">
         <v>1320</v>
@@ -15895,13 +15894,13 @@
     </row>
     <row r="228" spans="1:5" ht="28">
       <c r="A228" s="26" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B228" s="25" t="s">
         <v>1338</v>
       </c>
       <c r="C228" s="22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D228" s="26" t="s">
         <v>1321</v>
@@ -15912,13 +15911,13 @@
     </row>
     <row r="229" spans="1:5" ht="28">
       <c r="A229" s="26" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B229" s="25" t="s">
         <v>1339</v>
       </c>
       <c r="C229" s="22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D229" s="26" t="s">
         <v>1322</v>
@@ -15927,7 +15926,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="28">
+    <row r="230" spans="1:5">
       <c r="A230" s="26" t="s">
         <v>1281</v>
       </c>
@@ -15935,10 +15934,10 @@
         <v>1340</v>
       </c>
       <c r="C230" s="22">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D230" s="26" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="E230" s="26" t="s">
         <v>828</v>
@@ -15946,19 +15945,19 @@
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="26" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B231" s="25" t="s">
         <v>1341</v>
       </c>
       <c r="C231" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D231" s="26" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="E231" s="26" t="s">
-        <v>828</v>
+        <v>34</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -15972,7 +15971,7 @@
         <v>1</v>
       </c>
       <c r="D232" s="26" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="E232" s="26" t="s">
         <v>34</v>
@@ -15980,19 +15979,19 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="26" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B233" s="25" t="s">
-        <v>1343</v>
+        <v>1355</v>
       </c>
       <c r="C233" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D233" s="26" t="s">
         <v>1326</v>
       </c>
       <c r="E233" s="26" t="s">
-        <v>34</v>
+        <v>828</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -16000,33 +15999,33 @@
         <v>1283</v>
       </c>
       <c r="B234" s="25" t="s">
-        <v>1356</v>
+        <v>1343</v>
       </c>
       <c r="C234" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D234" s="26" t="s">
         <v>1327</v>
       </c>
       <c r="E234" s="26" t="s">
-        <v>828</v>
+        <v>34</v>
       </c>
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="26" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B235" s="25" t="s">
         <v>1344</v>
       </c>
       <c r="C235" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D235" s="26" t="s">
         <v>1328</v>
       </c>
       <c r="E235" s="26" t="s">
-        <v>34</v>
+        <v>828</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -16037,30 +16036,30 @@
         <v>1345</v>
       </c>
       <c r="C236" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D236" s="26" t="s">
         <v>1329</v>
       </c>
       <c r="E236" s="26" t="s">
-        <v>828</v>
+        <v>34</v>
       </c>
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="26" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B237" s="25" t="s">
         <v>1346</v>
       </c>
       <c r="C237" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D237" s="26" t="s">
         <v>1330</v>
       </c>
       <c r="E237" s="26" t="s">
-        <v>34</v>
+        <v>828</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -16071,30 +16070,30 @@
         <v>1347</v>
       </c>
       <c r="C238" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D238" s="26" t="s">
         <v>1331</v>
       </c>
       <c r="E238" s="26" t="s">
-        <v>828</v>
+        <v>34</v>
       </c>
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="26" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B239" s="25" t="s">
         <v>1348</v>
       </c>
       <c r="C239" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D239" s="26" t="s">
         <v>1332</v>
       </c>
       <c r="E239" s="26" t="s">
-        <v>34</v>
+        <v>828</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -16105,29 +16104,12 @@
         <v>1349</v>
       </c>
       <c r="C240" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D240" s="26" t="s">
         <v>1333</v>
       </c>
       <c r="E240" s="26" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5">
-      <c r="A241" s="26" t="s">
-        <v>1287</v>
-      </c>
-      <c r="B241" s="25" t="s">
-        <v>1350</v>
-      </c>
-      <c r="C241" s="22">
-        <v>1</v>
-      </c>
-      <c r="D241" s="26" t="s">
-        <v>1334</v>
-      </c>
-      <c r="E241" s="26" t="s">
         <v>34</v>
       </c>
     </row>
@@ -16162,94 +16144,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="35" t="s">
         <v>1004</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="36" t="s">
         <v>1005</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
     </row>
     <row r="4" spans="1:6" ht="46" customHeight="1">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="34" t="s">
         <v>1006</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="36" t="s">
         <v>1007</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
     </row>
     <row r="7" spans="1:6" ht="54" customHeight="1">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="34" t="s">
         <v>1008</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="36" t="s">
         <v>1009</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
     </row>
     <row r="10" spans="1:6" ht="46" customHeight="1">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="34" t="s">
         <v>1010</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="36" t="s">
         <v>1011</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
     </row>
     <row r="13" spans="1:6" ht="54" customHeight="1">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="34" t="s">
         <v>1012</v>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
     </row>
     <row r="14" spans="1:6" ht="32" customHeight="1">
       <c r="A14" s="1" t="s">

--- a/inventaire_mobilier.xlsx
+++ b/inventaire_mobilier.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolas.coquet/Documents/PERSONNEL/Emeleta/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F5A6D9-E1E0-0646-89A2-9A752801FBFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{096A49BF-22BA-EC4C-AB1C-B59C0F270D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mobilier" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2455" uniqueCount="1361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="1363">
   <si>
     <t>Inventaire du mobilier</t>
   </si>
@@ -1935,15 +1935,9 @@
     <t>MOB-070</t>
   </si>
   <si>
-    <t>Lustre feuillagé en métal doré</t>
-  </si>
-  <si>
     <t>Métal doré</t>
   </si>
   <si>
-    <t>Lustre décoratif en forme de bouquet de branches et feuilles, à plusieurs lumières.</t>
-  </si>
-  <si>
     <t>Patine et oxydation; photographie peu détaillée; électrification à réviser</t>
   </si>
   <si>
@@ -4117,6 +4111,18 @@
   </si>
   <si>
     <t>Ensemble sculptural en terre cuite : démon et scène érotique</t>
+  </si>
+  <si>
+    <t>Applique à deux lumières de type "Fern" en métal doré</t>
+  </si>
+  <si>
+    <t>Applique murale en forme de bouquet de branches et feuilles, à deux lumières.</t>
+  </si>
+  <si>
+    <t>https://www.1stdibs.com/fr/meubles/luminaires/appliques/une-applique-murale-italienne-exceptionnelle-de-style-fern-du-milieu-du-si%C3%A8cle-en-m%C3%A9tal-dor%C3%A9/id-f_51098232/</t>
+  </si>
+  <si>
+    <t>https://www.leboncoin.fr/ad/decoration/3207338508</t>
   </si>
 </sst>
 </file>
@@ -4128,7 +4134,7 @@
     <numFmt numFmtId="165" formatCode="#,##0\ &quot;€&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0\ [$€-40C]"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -4191,6 +4197,12 @@
       <sz val="10"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -4233,10 +4245,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4320,6 +4333,10 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4329,143 +4346,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="30">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -4891,6 +4785,129 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4905,50 +4922,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MobilierTable" displayName="MobilierTable" ref="A3:U113" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MobilierTable" displayName="MobilierTable" ref="A3:U113" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="A3:U113" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:U113">
     <sortCondition ref="A3:A113"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Identifiant" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Catégorie" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Datation" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Origine" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Matériaux" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Description" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Dimensions" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="État" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Estimation unitaire basse (€)" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Estimation unitaire haute (€)" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Localisation" dataDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Statut" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Publié" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Mots-clés" dataDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Source 1" dataDxfId="12"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Source 2" dataDxfId="11"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Quantité" dataDxfId="10"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Estimation du lot basse (€)" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Estimation du lot haute (€)" dataDxfId="8"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Associé à" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Identifiant" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Catégorie" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Datation" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Origine" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Matériaux" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Description" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Dimensions" dataDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="État" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Estimation unitaire basse (€)" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Estimation unitaire haute (€)" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Localisation" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Statut" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Publié" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Mots-clés" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Source 1" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Source 2" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Quantité" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Estimation du lot basse (€)" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Estimation du lot haute (€)" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Associé à" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PhotosTable" displayName="PhotosTable" ref="A3:E103" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="PhotosTable" displayName="PhotosTable" ref="A3:E103" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
   <autoFilter ref="A3:E103" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:E103">
     <sortCondition ref="A3:A103"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Identifiant objet" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fichier" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Ordre" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Légende" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Image principale" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Identifiant objet" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fichier" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Ordre" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Légende" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Image principale" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5175,54 +5192,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="23">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
+      <c r="A2" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
     </row>
     <row r="3" spans="1:21" s="5" customFormat="1" ht="32">
       <c r="A3" s="3" t="s">
@@ -5359,7 +5376,7 @@
         <v>38</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>39</v>
@@ -5622,7 +5639,7 @@
         <v>86</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>87</v>
@@ -5684,7 +5701,7 @@
         <v>96</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>52</v>
@@ -5749,7 +5766,7 @@
         <v>106</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>52</v>
@@ -5814,7 +5831,7 @@
         <v>114</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>52</v>
@@ -5879,7 +5896,7 @@
         <v>125</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>197</v>
@@ -6009,7 +6026,7 @@
         <v>145</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>197</v>
@@ -6144,7 +6161,7 @@
         <v>166</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>167</v>
@@ -6401,7 +6418,7 @@
         <v>206</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>52</v>
@@ -6416,7 +6433,7 @@
         <v>207</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="H21" s="17" t="s">
         <v>208</v>
@@ -6729,7 +6746,7 @@
         <v>253</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>254</v>
@@ -6794,7 +6811,7 @@
         <v>264</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>265</v>
@@ -6921,16 +6938,16 @@
         <v>285</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D29" s="17" t="s">
         <v>126</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="F29" s="17" t="s">
         <v>286</v>
@@ -7016,7 +7033,7 @@
         <v>140</v>
       </c>
       <c r="L30" s="17" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="M30" s="12" t="s">
         <v>33</v>
@@ -7051,7 +7068,7 @@
         <v>302</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>303</v>
@@ -7116,7 +7133,7 @@
         <v>312</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>313</v>
@@ -7376,7 +7393,7 @@
         <v>356</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>52</v>
@@ -7391,7 +7408,7 @@
         <v>357</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>358</v>
@@ -7701,7 +7718,7 @@
         <v>402</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>303</v>
@@ -7831,7 +7848,7 @@
         <v>154</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>197</v>
@@ -8227,7 +8244,7 @@
         <v>471</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>197</v>
@@ -8318,7 +8335,7 @@
         <v>100</v>
       </c>
       <c r="L50" s="10" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="M50" s="12" t="s">
         <v>33</v>
@@ -8379,7 +8396,7 @@
         <v>90</v>
       </c>
       <c r="L51" s="10" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="M51" s="12" t="s">
         <v>33</v>
@@ -8419,7 +8436,7 @@
         <v>494</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="F52" s="10" t="s">
         <v>495</v>
@@ -8623,7 +8640,7 @@
         <v>120</v>
       </c>
       <c r="L55" s="10" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="M55" s="12" t="s">
         <v>33</v>
@@ -8776,7 +8793,7 @@
         <v>533</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>313</v>
@@ -8791,7 +8808,7 @@
         <v>535</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="H58" s="10" t="s">
         <v>475</v>
@@ -8815,7 +8832,7 @@
         <v>34</v>
       </c>
       <c r="O58" s="10" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="P58" s="10"/>
       <c r="Q58" s="10"/>
@@ -8846,7 +8863,7 @@
         <v>494</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>539</v>
@@ -9145,7 +9162,7 @@
         <v>571</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>572</v>
@@ -9203,7 +9220,7 @@
         <v>577</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>578</v>
@@ -9294,7 +9311,7 @@
         <v>70</v>
       </c>
       <c r="L66" s="10" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="M66" s="12" t="s">
         <v>33</v>
@@ -9355,7 +9372,7 @@
         <v>100</v>
       </c>
       <c r="L67" s="10" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="M67" s="12" t="s">
         <v>33</v>
@@ -9389,7 +9406,7 @@
         <v>598</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>559</v>
@@ -9686,12 +9703,12 @@
       </c>
       <c r="U72" s="17"/>
     </row>
-    <row r="73" spans="1:21">
+    <row r="73" spans="1:21" ht="75">
       <c r="A73" s="20" t="s">
         <v>632</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>633</v>
+        <v>1359</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>52</v>
@@ -9700,19 +9717,19 @@
         <v>606</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>635</v>
+        <v>1360</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>504</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="J73" s="21">
         <v>80</v>
@@ -9721,7 +9738,7 @@
         <v>180</v>
       </c>
       <c r="L73" s="10" t="s">
-        <v>308</v>
+        <v>1349</v>
       </c>
       <c r="M73" s="12" t="s">
         <v>33</v>
@@ -9730,10 +9747,14 @@
         <v>34</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>637</v>
-      </c>
-      <c r="P73" s="10"/>
-      <c r="Q73" s="10"/>
+        <v>635</v>
+      </c>
+      <c r="P73" s="10" t="s">
+        <v>1362</v>
+      </c>
+      <c r="Q73" s="37" t="s">
+        <v>1361</v>
+      </c>
       <c r="R73" s="13">
         <v>1</v>
       </c>
@@ -9749,13 +9770,13 @@
     </row>
     <row r="74" spans="1:21">
       <c r="A74" s="20" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>501</v>
@@ -9764,16 +9785,16 @@
         <v>348</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H74" s="10" t="s">
         <v>475</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="J74" s="21">
         <v>30</v>
@@ -9791,7 +9812,7 @@
         <v>34</v>
       </c>
       <c r="O74" s="10" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="P74" s="10"/>
       <c r="Q74" s="10"/>
@@ -9810,31 +9831,31 @@
     </row>
     <row r="75" spans="1:21" ht="28">
       <c r="A75" s="20" t="s">
+        <v>642</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="C75" s="10" t="s">
         <v>644</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="D75" s="10" t="s">
         <v>645</v>
       </c>
-      <c r="C75" s="10" t="s">
+      <c r="E75" s="10" t="s">
         <v>646</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="F75" s="10" t="s">
         <v>647</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="G75" s="10" t="s">
         <v>648</v>
-      </c>
-      <c r="F75" s="10" t="s">
-        <v>649</v>
-      </c>
-      <c r="G75" s="10" t="s">
-        <v>650</v>
       </c>
       <c r="H75" s="10" t="s">
         <v>475</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="J75" s="21">
         <v>250</v>
@@ -9852,7 +9873,7 @@
         <v>34</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="P75" s="10"/>
       <c r="Q75" s="10"/>
@@ -9871,31 +9892,31 @@
     </row>
     <row r="76" spans="1:21">
       <c r="A76" s="20" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>197</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E76" s="10" t="s">
         <v>348</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="H76" s="10" t="s">
         <v>475</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="J76" s="21">
         <v>120</v>
@@ -9913,7 +9934,7 @@
         <v>34</v>
       </c>
       <c r="O76" s="10" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="P76" s="10"/>
       <c r="Q76" s="10"/>
@@ -9932,10 +9953,10 @@
     </row>
     <row r="77" spans="1:21">
       <c r="A77" s="20" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>197</v>
@@ -9947,16 +9968,16 @@
         <v>348</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="H77" s="10" t="s">
         <v>475</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="J77" s="21">
         <v>100</v>
@@ -9965,7 +9986,7 @@
         <v>220</v>
       </c>
       <c r="L77" s="10" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="M77" s="12" t="s">
         <v>33</v>
@@ -9974,7 +9995,7 @@
         <v>34</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="P77" s="10"/>
       <c r="Q77" s="10"/>
@@ -9993,10 +10014,10 @@
     </row>
     <row r="78" spans="1:21">
       <c r="A78" s="20" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C78" s="10" t="s">
         <v>197</v>
@@ -10008,16 +10029,16 @@
         <v>348</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="H78" s="10" t="s">
         <v>475</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="J78" s="21">
         <v>200</v>
@@ -10026,7 +10047,7 @@
         <v>450</v>
       </c>
       <c r="L78" s="10" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="M78" s="12" t="s">
         <v>33</v>
@@ -10035,7 +10056,7 @@
         <v>34</v>
       </c>
       <c r="O78" s="10" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="P78" s="10"/>
       <c r="Q78" s="10"/>
@@ -10051,15 +10072,15 @@
         <v>450</v>
       </c>
       <c r="U78" s="17" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79" s="20" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>25</v>
@@ -10071,16 +10092,16 @@
         <v>348</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="H79" s="10" t="s">
         <v>475</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="J79" s="21">
         <v>200</v>
@@ -10089,7 +10110,7 @@
         <v>500</v>
       </c>
       <c r="L79" s="10" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="M79" s="12" t="s">
         <v>33</v>
@@ -10098,7 +10119,7 @@
         <v>34</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="P79" s="10"/>
       <c r="Q79" s="10"/>
@@ -10114,36 +10135,36 @@
         <v>500</v>
       </c>
       <c r="U79" s="17" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="80" spans="1:21">
       <c r="A80" s="20" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C80" s="10" t="s">
         <v>197</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>348</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H80" s="10" t="s">
         <v>475</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="J80" s="21">
         <v>40</v>
@@ -10161,7 +10182,7 @@
         <v>34</v>
       </c>
       <c r="O80" s="10" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="P80" s="10"/>
       <c r="Q80" s="10"/>
@@ -10177,36 +10198,36 @@
         <v>80</v>
       </c>
       <c r="U80" s="17" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="81" spans="1:21">
       <c r="A81" s="20" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>197</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>348</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H81" s="10" t="s">
         <v>475</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="J81" s="21">
         <v>80</v>
@@ -10224,7 +10245,7 @@
         <v>34</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="P81" s="10"/>
       <c r="Q81" s="10"/>
@@ -10243,10 +10264,10 @@
     </row>
     <row r="82" spans="1:21">
       <c r="A82" s="20" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>197</v>
@@ -10258,16 +10279,16 @@
         <v>348</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H82" s="10" t="s">
         <v>475</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="J82" s="21">
         <v>100</v>
@@ -10276,7 +10297,7 @@
         <v>250</v>
       </c>
       <c r="L82" s="10" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="M82" s="12" t="s">
         <v>33</v>
@@ -10285,7 +10306,7 @@
         <v>34</v>
       </c>
       <c r="O82" s="10" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="P82" s="10"/>
       <c r="Q82" s="10"/>
@@ -10304,31 +10325,31 @@
     </row>
     <row r="83" spans="1:21">
       <c r="A83" s="20" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>303</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>348</v>
       </c>
       <c r="F83" s="10" t="s">
+        <v>702</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>704</v>
       </c>
-      <c r="G83" s="10" t="s">
+      <c r="I83" s="10" t="s">
         <v>705</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>706</v>
-      </c>
-      <c r="I83" s="10" t="s">
-        <v>707</v>
       </c>
       <c r="J83" s="21">
         <v>100</v>
@@ -10337,7 +10358,7 @@
         <v>250</v>
       </c>
       <c r="L83" s="10" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="M83" s="12" t="s">
         <v>240</v>
@@ -10346,7 +10367,7 @@
         <v>34</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="P83" s="10"/>
       <c r="Q83" s="10"/>
@@ -10365,31 +10386,31 @@
     </row>
     <row r="84" spans="1:21" ht="28">
       <c r="A84" s="20" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>313</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>348</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H84" s="10" t="s">
         <v>475</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="J84" s="21">
         <v>100</v>
@@ -10407,7 +10428,7 @@
         <v>34</v>
       </c>
       <c r="O84" s="10" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="P84" s="10"/>
       <c r="Q84" s="10"/>
@@ -10426,31 +10447,31 @@
     </row>
     <row r="85" spans="1:21" ht="28">
       <c r="A85" s="20" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>348</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="H85" s="10" t="s">
         <v>504</v>
       </c>
       <c r="I85" s="10" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="J85" s="21">
         <v>50</v>
@@ -10468,7 +10489,7 @@
         <v>34</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="P85" s="10"/>
       <c r="Q85" s="10"/>
@@ -10487,13 +10508,13 @@
     </row>
     <row r="86" spans="1:21">
       <c r="A86" s="20" t="s">
+        <v>721</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>722</v>
+      </c>
+      <c r="C86" s="10" t="s">
         <v>723</v>
-      </c>
-      <c r="B86" s="10" t="s">
-        <v>724</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>725</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>534</v>
@@ -10502,16 +10523,16 @@
         <v>348</v>
       </c>
       <c r="F86" s="10" t="s">
+        <v>724</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>725</v>
+      </c>
+      <c r="H86" s="10" t="s">
         <v>726</v>
       </c>
-      <c r="G86" s="10" t="s">
+      <c r="I86" s="10" t="s">
         <v>727</v>
-      </c>
-      <c r="H86" s="10" t="s">
-        <v>728</v>
-      </c>
-      <c r="I86" s="10" t="s">
-        <v>729</v>
       </c>
       <c r="J86" s="21">
         <v>60</v>
@@ -10529,7 +10550,7 @@
         <v>34</v>
       </c>
       <c r="O86" s="10" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="P86" s="10"/>
       <c r="Q86" s="10"/>
@@ -10548,31 +10569,31 @@
     </row>
     <row r="87" spans="1:21" ht="56">
       <c r="A87" s="20" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>545</v>
       </c>
       <c r="E87" s="10" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F87" s="10" t="s">
         <v>1267</v>
       </c>
-      <c r="F87" s="10" t="s">
-        <v>1269</v>
-      </c>
       <c r="G87" s="10" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I87" s="10" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="J87" s="21">
         <v>80</v>
@@ -10590,10 +10611,10 @@
         <v>34</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="13">
@@ -10611,31 +10632,31 @@
     </row>
     <row r="88" spans="1:21">
       <c r="A88" s="8" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C88" s="10" t="s">
         <v>52</v>
       </c>
       <c r="D88" s="9" t="s">
+        <v>734</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="G88" s="9" t="s">
         <v>736</v>
       </c>
-      <c r="E88" s="9" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F88" s="9" t="s">
+      <c r="H88" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I88" s="9" t="s">
         <v>737</v>
-      </c>
-      <c r="G88" s="9" t="s">
-        <v>738</v>
-      </c>
-      <c r="H88" s="9" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I88" s="9" t="s">
-        <v>739</v>
       </c>
       <c r="J88" s="11">
         <v>80</v>
@@ -10668,13 +10689,13 @@
     </row>
     <row r="89" spans="1:21">
       <c r="A89" s="8" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>157</v>
@@ -10683,16 +10704,16 @@
         <v>627</v>
       </c>
       <c r="F89" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I89" s="9" t="s">
         <v>742</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>743</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I89" s="9" t="s">
-        <v>744</v>
       </c>
       <c r="J89" s="11">
         <v>20</v>
@@ -10725,31 +10746,31 @@
     </row>
     <row r="90" spans="1:21">
       <c r="A90" s="8" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C90" s="17" t="s">
         <v>197</v>
       </c>
       <c r="D90" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="E90" s="9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I90" s="9" t="s">
         <v>746</v>
-      </c>
-      <c r="E90" s="9" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>747</v>
-      </c>
-      <c r="G90" s="9" t="s">
-        <v>1271</v>
-      </c>
-      <c r="H90" s="9" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I90" s="9" t="s">
-        <v>748</v>
       </c>
       <c r="J90" s="11">
         <v>700</v>
@@ -10779,36 +10800,36 @@
         <v>1500</v>
       </c>
       <c r="U90" s="9" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="91" spans="1:21">
       <c r="A91" s="8" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C91" s="17" t="s">
         <v>197</v>
       </c>
       <c r="D91" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="G91" s="9" t="s">
         <v>750</v>
       </c>
-      <c r="E91" s="9" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F91" s="9" t="s">
+      <c r="H91" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I91" s="9" t="s">
         <v>751</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>752</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I91" s="9" t="s">
-        <v>753</v>
       </c>
       <c r="J91" s="11">
         <v>250</v>
@@ -10838,18 +10859,18 @@
         <v>600</v>
       </c>
       <c r="U91" s="9" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="92" spans="1:21">
       <c r="A92" s="8" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D92" s="9" t="s">
         <v>606</v>
@@ -10858,16 +10879,16 @@
         <v>627</v>
       </c>
       <c r="F92" s="9" t="s">
+        <v>754</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>755</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I92" s="9" t="s">
         <v>756</v>
-      </c>
-      <c r="G92" s="9" t="s">
-        <v>757</v>
-      </c>
-      <c r="H92" s="9" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I92" s="9" t="s">
-        <v>758</v>
       </c>
       <c r="J92" s="11">
         <v>20</v>
@@ -10900,13 +10921,13 @@
     </row>
     <row r="93" spans="1:21">
       <c r="A93" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="C93" s="10" t="s">
         <v>759</v>
-      </c>
-      <c r="B93" s="9" t="s">
-        <v>760</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>761</v>
       </c>
       <c r="D93" s="9" t="s">
         <v>157</v>
@@ -10915,16 +10936,16 @@
         <v>348</v>
       </c>
       <c r="F93" s="9" t="s">
+        <v>760</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I93" s="9" t="s">
         <v>762</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>763</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I93" s="9" t="s">
-        <v>764</v>
       </c>
       <c r="J93" s="11">
         <v>30</v>
@@ -10957,13 +10978,13 @@
     </row>
     <row r="94" spans="1:21">
       <c r="A94" s="8" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D94" s="9" t="s">
         <v>53</v>
@@ -10972,16 +10993,16 @@
         <v>348</v>
       </c>
       <c r="F94" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>766</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I94" s="9" t="s">
         <v>767</v>
-      </c>
-      <c r="G94" s="9" t="s">
-        <v>768</v>
-      </c>
-      <c r="H94" s="9" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I94" s="9" t="s">
-        <v>769</v>
       </c>
       <c r="J94" s="11">
         <v>30</v>
@@ -11014,13 +11035,13 @@
     </row>
     <row r="95" spans="1:21">
       <c r="A95" s="8" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D95" s="9" t="s">
         <v>157</v>
@@ -11029,16 +11050,16 @@
         <v>348</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I95" s="9" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="J95" s="11">
         <v>30</v>
@@ -11071,13 +11092,13 @@
     </row>
     <row r="96" spans="1:21">
       <c r="A96" s="8" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D96" s="9" t="s">
         <v>157</v>
@@ -11086,16 +11107,16 @@
         <v>348</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="J96" s="11">
         <v>30</v>
@@ -11128,31 +11149,31 @@
     </row>
     <row r="97" spans="1:21">
       <c r="A97" s="8" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C97" s="10" t="s">
         <v>75</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>348</v>
       </c>
       <c r="F97" s="9" t="s">
+        <v>778</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>779</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I97" s="9" t="s">
         <v>780</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>781</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I97" s="9" t="s">
-        <v>782</v>
       </c>
       <c r="J97" s="11">
         <v>40</v>
@@ -11185,13 +11206,13 @@
     </row>
     <row r="98" spans="1:21">
       <c r="A98" s="8" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D98" s="9" t="s">
         <v>157</v>
@@ -11200,16 +11221,16 @@
         <v>348</v>
       </c>
       <c r="F98" s="9" t="s">
+        <v>783</v>
+      </c>
+      <c r="G98" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I98" s="9" t="s">
         <v>785</v>
-      </c>
-      <c r="G98" s="9" t="s">
-        <v>786</v>
-      </c>
-      <c r="H98" s="9" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I98" s="9" t="s">
-        <v>787</v>
       </c>
       <c r="J98" s="11">
         <v>20</v>
@@ -11242,31 +11263,31 @@
     </row>
     <row r="99" spans="1:21">
       <c r="A99" s="8" t="s">
+        <v>786</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>787</v>
+      </c>
+      <c r="C99" s="10" t="s">
         <v>788</v>
-      </c>
-      <c r="B99" s="9" t="s">
-        <v>789</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>790</v>
       </c>
       <c r="D99" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="J99" s="11">
         <v>40</v>
@@ -11299,31 +11320,31 @@
     </row>
     <row r="100" spans="1:21">
       <c r="A100" s="8" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D100" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="F100" s="9" t="s">
+        <v>793</v>
+      </c>
+      <c r="G100" s="9" t="s">
+        <v>794</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I100" s="9" t="s">
         <v>795</v>
-      </c>
-      <c r="G100" s="9" t="s">
-        <v>796</v>
-      </c>
-      <c r="H100" s="9" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I100" s="9" t="s">
-        <v>797</v>
       </c>
       <c r="J100" s="11">
         <v>60</v>
@@ -11356,31 +11377,31 @@
     </row>
     <row r="101" spans="1:21">
       <c r="A101" s="8" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D101" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="F101" s="9" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="J101" s="11">
         <v>40</v>
@@ -11413,31 +11434,31 @@
     </row>
     <row r="102" spans="1:21">
       <c r="A102" s="8" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D102" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="J102" s="11">
         <v>40</v>
@@ -11470,31 +11491,31 @@
     </row>
     <row r="103" spans="1:21">
       <c r="A103" s="8" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D103" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="F103" s="9" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="J103" s="11">
         <v>70</v>
@@ -11527,31 +11548,31 @@
     </row>
     <row r="104" spans="1:21">
       <c r="A104" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>807</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>788</v>
+      </c>
+      <c r="D104" s="9" t="s">
         <v>808</v>
       </c>
-      <c r="B104" s="9" t="s">
+      <c r="E104" s="9" t="s">
         <v>809</v>
       </c>
-      <c r="C104" s="10" t="s">
-        <v>790</v>
-      </c>
-      <c r="D104" s="9" t="s">
+      <c r="F104" s="9" t="s">
         <v>810</v>
       </c>
-      <c r="E104" s="9" t="s">
+      <c r="G104" s="9" t="s">
         <v>811</v>
       </c>
-      <c r="F104" s="9" t="s">
+      <c r="H104" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I104" s="9" t="s">
         <v>812</v>
-      </c>
-      <c r="G104" s="9" t="s">
-        <v>813</v>
-      </c>
-      <c r="H104" s="9" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I104" s="9" t="s">
-        <v>814</v>
       </c>
       <c r="J104" s="11">
         <v>150</v>
@@ -11584,10 +11605,10 @@
     </row>
     <row r="105" spans="1:21">
       <c r="A105" s="8" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C105" s="10" t="s">
         <v>52</v>
@@ -11596,19 +11617,19 @@
         <v>480</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="F105" s="9" t="s">
+        <v>814</v>
+      </c>
+      <c r="G105" s="9" t="s">
+        <v>815</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I105" s="9" t="s">
         <v>816</v>
-      </c>
-      <c r="G105" s="9" t="s">
-        <v>817</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I105" s="9" t="s">
-        <v>818</v>
       </c>
       <c r="J105" s="11">
         <v>120</v>
@@ -11641,31 +11662,31 @@
     </row>
     <row r="106" spans="1:21" ht="42">
       <c r="A106" s="8" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B106" s="26" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="C106" s="26" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D106" s="26" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="E106" s="26" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="G106" s="26" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="H106" s="9" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I106" s="26" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="J106" s="28">
         <v>120</v>
@@ -11674,7 +11695,7 @@
         <v>300</v>
       </c>
       <c r="L106" s="9" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="M106" s="12" t="s">
         <v>33</v>
@@ -11698,31 +11719,31 @@
     </row>
     <row r="107" spans="1:21" ht="28">
       <c r="A107" s="8" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B107" s="26" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="C107" s="26" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D107" s="26" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="E107" s="26" t="s">
         <v>627</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="G107" s="26" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I107" s="26" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="J107" s="28">
         <v>25</v>
@@ -11731,7 +11752,7 @@
         <v>60</v>
       </c>
       <c r="L107" s="9" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="M107" s="12" t="s">
         <v>33</v>
@@ -11755,31 +11776,31 @@
     </row>
     <row r="108" spans="1:21">
       <c r="A108" s="8" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="B108" s="26" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="C108" s="26" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="D108" s="26" t="s">
         <v>167</v>
       </c>
       <c r="E108" s="26" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="G108" s="26" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="H108" s="9" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I108" s="26" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="J108" s="28">
         <v>60</v>
@@ -11812,31 +11833,31 @@
     </row>
     <row r="109" spans="1:21" ht="28">
       <c r="A109" s="8" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="B109" s="26" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="C109" s="26" t="s">
         <v>75</v>
       </c>
       <c r="D109" s="26" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E109" s="26" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="G109" s="26" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I109" s="26" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="J109" s="28">
         <v>30</v>
@@ -11869,31 +11890,31 @@
     </row>
     <row r="110" spans="1:21" ht="42">
       <c r="A110" s="8" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="B110" s="26" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="C110" s="26" t="s">
         <v>75</v>
       </c>
       <c r="D110" s="26" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E110" s="26" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="F110" s="26" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="G110" s="26" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="H110" s="9" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I110" s="26" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="J110" s="28">
         <v>50</v>
@@ -11926,31 +11947,31 @@
     </row>
     <row r="111" spans="1:21" ht="28">
       <c r="A111" s="8" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B111" s="26" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="C111" s="26" t="s">
         <v>75</v>
       </c>
       <c r="D111" s="26" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="E111" s="26" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="F111" s="26" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="G111" s="26" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I111" s="26" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="J111" s="28">
         <v>30</v>
@@ -11983,31 +12004,31 @@
     </row>
     <row r="112" spans="1:21">
       <c r="A112" s="8" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B112" s="26" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="C112" s="26" t="s">
         <v>197</v>
       </c>
       <c r="D112" s="26" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="E112" s="26" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="G112" s="26" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="H112" s="9" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I112" s="26" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="J112" s="28">
         <v>80</v>
@@ -12040,31 +12061,31 @@
     </row>
     <row r="113" spans="1:21">
       <c r="A113" s="8" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C113" s="17" t="s">
         <v>197</v>
       </c>
       <c r="D113" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="E113" s="9" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="G113" s="9" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I113" s="9" t="s">
         <v>746</v>
-      </c>
-      <c r="E113" s="9" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F113" s="9" t="s">
-        <v>747</v>
-      </c>
-      <c r="G113" s="9" t="s">
-        <v>1275</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>1025</v>
-      </c>
-      <c r="I113" s="9" t="s">
-        <v>748</v>
       </c>
       <c r="J113" s="11">
         <v>700</v>
@@ -12094,7 +12115,7 @@
         <v>1500</v>
       </c>
       <c r="U113" s="9" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
   </sheetData>
@@ -12111,9 +12132,12 @@
       <formula1>"Oui,Non"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="Q73" r:id="rId1" xr:uid="{CF2548D7-7BFC-ED42-8E5E-0BFE92EF85C0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -12131,38 +12155,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" ht="34" customHeight="1">
-      <c r="A1" s="29" t="s">
-        <v>819</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
+      <c r="A1" s="31" t="s">
+        <v>817</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
     </row>
     <row r="2" spans="1:5" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
-        <v>820</v>
-      </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
+      <c r="A2" s="29" t="s">
+        <v>818</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
     </row>
     <row r="3" spans="1:5" s="7" customFormat="1" ht="16" customHeight="1">
       <c r="A3" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>820</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>821</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>822</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>823</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>824</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
@@ -12170,13 +12194,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C4" s="24">
         <v>1</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>34</v>
@@ -12187,16 +12211,16 @@
         <v>23</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C5" s="24">
         <v>2</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1">
@@ -12204,16 +12228,16 @@
         <v>23</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C6" s="24">
         <v>3</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
@@ -12221,13 +12245,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C7" s="23">
         <v>1</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E7" s="23" t="s">
         <v>34</v>
@@ -12238,16 +12262,16 @@
         <v>38</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C8" s="23">
         <v>2</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
@@ -12255,16 +12279,16 @@
         <v>38</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C9" s="23">
         <v>3</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1">
@@ -12272,13 +12296,13 @@
         <v>50</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C10" s="23">
         <v>1</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="E10" s="23" t="s">
         <v>34</v>
@@ -12289,16 +12313,16 @@
         <v>62</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C11" s="23">
         <v>2</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1">
@@ -12306,13 +12330,13 @@
         <v>62</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C12" s="23">
         <v>1</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E12" s="23" t="s">
         <v>34</v>
@@ -12323,16 +12347,16 @@
         <v>62</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C13" s="23">
         <v>3</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1">
@@ -12340,16 +12364,16 @@
         <v>73</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C14" s="23">
         <v>3</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1">
@@ -12357,16 +12381,16 @@
         <v>73</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="C15" s="23">
         <v>2</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1">
@@ -12374,13 +12398,13 @@
         <v>73</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C16" s="23">
         <v>1</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E16" s="23" t="s">
         <v>34</v>
@@ -12391,16 +12415,16 @@
         <v>85</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C17" s="23">
         <v>2</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1">
@@ -12408,13 +12432,13 @@
         <v>85</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C18" s="23">
         <v>1</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="E18" s="23" t="s">
         <v>34</v>
@@ -12425,16 +12449,16 @@
         <v>96</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C19" s="23">
         <v>1</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1">
@@ -12442,13 +12466,13 @@
         <v>96</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C20" s="23">
         <v>2</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="E20" s="23" t="s">
         <v>34</v>
@@ -12459,16 +12483,16 @@
         <v>96</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C21" s="23">
         <v>3</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1">
@@ -12476,16 +12500,16 @@
         <v>96</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="C22" s="23">
         <v>4</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1">
@@ -12493,13 +12517,13 @@
         <v>106</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C23" s="23">
         <v>1</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="E23" s="23" t="s">
         <v>34</v>
@@ -12510,16 +12534,16 @@
         <v>106</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="C24" s="23">
         <v>2</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1">
@@ -12527,16 +12551,16 @@
         <v>106</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="C25" s="23">
         <v>3</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1">
@@ -12544,16 +12568,16 @@
         <v>106</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="C26" s="23">
         <v>4</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1">
@@ -12561,16 +12585,16 @@
         <v>114</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="C27" s="23">
         <v>1</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1">
@@ -12578,16 +12602,16 @@
         <v>114</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="C28" s="23">
         <v>2</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1">
@@ -12595,13 +12619,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C29" s="23">
         <v>3</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="E29" s="23" t="s">
         <v>34</v>
@@ -12612,16 +12636,16 @@
         <v>114</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="C30" s="23">
         <v>4</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1">
@@ -12629,16 +12653,16 @@
         <v>125</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C31" s="23">
         <v>1</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1">
@@ -12646,13 +12670,13 @@
         <v>125</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="C32" s="23">
         <v>2</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="E32" s="23" t="s">
         <v>34</v>
@@ -12663,16 +12687,16 @@
         <v>125</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C33" s="23">
         <v>3</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1">
@@ -12680,13 +12704,13 @@
         <v>135</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="C34" s="23">
         <v>1</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="E34" s="23" t="s">
         <v>34</v>
@@ -12697,16 +12721,16 @@
         <v>135</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C35" s="23">
         <v>2</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1">
@@ -12714,16 +12738,16 @@
         <v>135</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C36" s="23">
         <v>3</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1">
@@ -12731,13 +12755,13 @@
         <v>145</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="C37" s="23">
         <v>1</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="E37" s="23" t="s">
         <v>34</v>
@@ -12748,16 +12772,16 @@
         <v>145</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C38" s="23">
         <v>2</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" customHeight="1">
@@ -12765,16 +12789,16 @@
         <v>145</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C39" s="23">
         <v>3</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" customHeight="1">
@@ -12782,16 +12806,16 @@
         <v>145</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="C40" s="23">
         <v>4</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" customHeight="1">
@@ -12799,16 +12823,16 @@
         <v>145</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="C41" s="23">
         <v>5</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15" customHeight="1">
@@ -12816,16 +12840,16 @@
         <v>145</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="C42" s="23">
         <v>6</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15" customHeight="1">
@@ -12833,13 +12857,13 @@
         <v>155</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="C43" s="23">
         <v>1</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="E43" s="23" t="s">
         <v>34</v>
@@ -12850,13 +12874,13 @@
         <v>165</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="C44" s="23">
         <v>1</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="E44" s="23" t="s">
         <v>34</v>
@@ -12867,13 +12891,13 @@
         <v>175</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C45" s="23">
         <v>1</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="E45" s="23" t="s">
         <v>34</v>
@@ -12884,13 +12908,13 @@
         <v>185</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="C46" s="23">
         <v>1</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="E46" s="23" t="s">
         <v>34</v>
@@ -12901,13 +12925,13 @@
         <v>195</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C47" s="23">
         <v>1</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="E47" s="23" t="s">
         <v>34</v>
@@ -12918,16 +12942,16 @@
         <v>195</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="C48" s="23">
         <v>2</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" customHeight="1">
@@ -12935,13 +12959,13 @@
         <v>206</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C49" s="23">
         <v>1</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="E49" s="23" t="s">
         <v>34</v>
@@ -12952,16 +12976,16 @@
         <v>206</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="C50" s="23">
         <v>2</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15" customHeight="1">
@@ -12969,16 +12993,16 @@
         <v>206</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="C51" s="23">
         <v>3</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15" customHeight="1">
@@ -12986,13 +13010,13 @@
         <v>213</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="C52" s="23">
         <v>1</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="E52" s="23" t="s">
         <v>34</v>
@@ -13003,16 +13027,16 @@
         <v>213</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="C53" s="23">
         <v>2</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="E53" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15" customHeight="1">
@@ -13020,16 +13044,16 @@
         <v>213</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="C54" s="23">
         <v>3</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="E54" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15" customHeight="1">
@@ -13037,13 +13061,13 @@
         <v>223</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="C55" s="23">
         <v>1</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="E55" s="23" t="s">
         <v>34</v>
@@ -13054,16 +13078,16 @@
         <v>223</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="C56" s="23">
         <v>2</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15" customHeight="1">
@@ -13071,13 +13095,13 @@
         <v>234</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="C57" s="23">
         <v>1</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="E57" s="23" t="s">
         <v>34</v>
@@ -13088,13 +13112,13 @@
         <v>244</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C58" s="23">
         <v>1</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="E58" s="23" t="s">
         <v>34</v>
@@ -13105,13 +13129,13 @@
         <v>252</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C59" s="23">
         <v>1</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="E59" s="23" t="s">
         <v>34</v>
@@ -13122,16 +13146,16 @@
         <v>252</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C60" s="23">
         <v>2</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="30" customHeight="1">
@@ -13139,13 +13163,13 @@
         <v>263</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="C61" s="23">
         <v>1</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="E61" s="23" t="s">
         <v>34</v>
@@ -13156,13 +13180,13 @@
         <v>273</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="C62" s="23">
         <v>1</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E62" s="23" t="s">
         <v>34</v>
@@ -13173,13 +13197,13 @@
         <v>285</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="C63" s="23">
         <v>1</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="E63" s="23" t="s">
         <v>34</v>
@@ -13190,16 +13214,16 @@
         <v>285</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C64" s="23">
         <v>2</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15" customHeight="1">
@@ -13207,16 +13231,16 @@
         <v>293</v>
       </c>
       <c r="B65" s="23" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="C65" s="23">
         <v>1</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="E65" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15" customHeight="1">
@@ -13224,13 +13248,13 @@
         <v>293</v>
       </c>
       <c r="B66" s="23" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="C66" s="23">
         <v>2</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="E66" s="23" t="s">
         <v>34</v>
@@ -13241,13 +13265,13 @@
         <v>302</v>
       </c>
       <c r="B67" s="23" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="C67" s="23">
         <v>1</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="E67" s="23" t="s">
         <v>34</v>
@@ -13258,16 +13282,16 @@
         <v>312</v>
       </c>
       <c r="B68" s="23" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C68" s="23">
         <v>2</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="E68" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15" customHeight="1">
@@ -13275,13 +13299,13 @@
         <v>312</v>
       </c>
       <c r="B69" s="23" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="C69" s="23">
         <v>1</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="E69" s="23" t="s">
         <v>34</v>
@@ -13292,16 +13316,16 @@
         <v>323</v>
       </c>
       <c r="B70" s="23" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C70" s="23">
         <v>1</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="E70" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15" customHeight="1">
@@ -13309,13 +13333,13 @@
         <v>323</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="C71" s="23">
         <v>2</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E71" s="23" t="s">
         <v>34</v>
@@ -13326,13 +13350,13 @@
         <v>333</v>
       </c>
       <c r="B72" s="23" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="C72" s="23">
         <v>1</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="E72" s="23" t="s">
         <v>34</v>
@@ -13343,13 +13367,13 @@
         <v>344</v>
       </c>
       <c r="B73" s="23" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="C73" s="23">
         <v>1</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="E73" s="23" t="s">
         <v>34</v>
@@ -13360,16 +13384,16 @@
         <v>344</v>
       </c>
       <c r="B74" s="23" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="C74" s="23">
         <v>2</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E74" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="15" customHeight="1">
@@ -13377,16 +13401,16 @@
         <v>356</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="C75" s="23">
         <v>1</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15" customHeight="1">
@@ -13394,13 +13418,13 @@
         <v>356</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="C76" s="23">
         <v>2</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="E76" s="23" t="s">
         <v>34</v>
@@ -13411,13 +13435,13 @@
         <v>363</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="C77" s="23">
         <v>1</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="E77" s="23" t="s">
         <v>34</v>
@@ -13428,13 +13452,13 @@
         <v>372</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>34</v>
@@ -13445,16 +13469,16 @@
         <v>372</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="C79" s="2">
         <v>2</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -13462,16 +13486,16 @@
         <v>383</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -13479,13 +13503,13 @@
         <v>383</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="C81" s="2">
         <v>2</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>34</v>
@@ -13496,16 +13520,16 @@
         <v>383</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="C82" s="2">
         <v>3</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -13513,13 +13537,13 @@
         <v>392</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>34</v>
@@ -13530,16 +13554,16 @@
         <v>392</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="C84" s="2">
         <v>2</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -13547,13 +13571,13 @@
         <v>402</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>34</v>
@@ -13564,16 +13588,16 @@
         <v>402</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="C86" s="2">
         <v>2</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -13581,13 +13605,13 @@
         <v>411</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="C87" s="2">
         <v>1</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>34</v>
@@ -13598,16 +13622,16 @@
         <v>154</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -13615,16 +13639,16 @@
         <v>154</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="C89" s="2">
         <v>2</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -13632,16 +13656,16 @@
         <v>154</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="C90" s="2">
         <v>3</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -13649,13 +13673,13 @@
         <v>154</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="C91" s="2">
         <v>4</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>34</v>
@@ -13666,16 +13690,16 @@
         <v>427</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C92" s="2">
         <v>3</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -13683,16 +13707,16 @@
         <v>427</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="C93" s="2">
         <v>2</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -13700,13 +13724,13 @@
         <v>427</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="C94" s="2">
         <v>1</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>34</v>
@@ -13717,13 +13741,13 @@
         <v>436</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="C95" s="2">
         <v>1</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>34</v>
@@ -13734,16 +13758,16 @@
         <v>436</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="C96" s="2">
         <v>2</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -13751,16 +13775,16 @@
         <v>436</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="C97" s="2">
         <v>3</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -13768,13 +13792,13 @@
         <v>445</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>34</v>
@@ -13785,13 +13809,13 @@
         <v>452</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>34</v>
@@ -13802,16 +13826,16 @@
         <v>452</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="C100" s="2">
         <v>2</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -13819,16 +13843,16 @@
         <v>452</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="C101" s="2">
         <v>3</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="15">
@@ -13836,13 +13860,13 @@
         <v>462</v>
       </c>
       <c r="B102" s="23" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="C102" s="23">
         <v>1</v>
       </c>
       <c r="D102" s="23" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="E102" s="23" t="s">
         <v>34</v>
@@ -13853,16 +13877,16 @@
         <v>462</v>
       </c>
       <c r="B103" s="23" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C103" s="23">
         <v>2</v>
       </c>
       <c r="D103" s="23" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="E103" s="23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="24" customHeight="1">
@@ -13870,16 +13894,16 @@
         <v>471</v>
       </c>
       <c r="B104" s="22" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="C104" s="22">
         <v>2</v>
       </c>
       <c r="D104" s="22" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="E104" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="24" customHeight="1">
@@ -13887,13 +13911,13 @@
         <v>471</v>
       </c>
       <c r="B105" s="22" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="C105" s="22">
         <v>1</v>
       </c>
       <c r="D105" s="22" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="E105" s="22" t="s">
         <v>34</v>
@@ -13904,16 +13928,16 @@
         <v>478</v>
       </c>
       <c r="B106" s="22" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="C106" s="22">
         <v>2</v>
       </c>
       <c r="D106" s="22" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="E106" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="24" customHeight="1">
@@ -13921,13 +13945,13 @@
         <v>478</v>
       </c>
       <c r="B107" s="22" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="C107" s="22">
         <v>1</v>
       </c>
       <c r="D107" s="22" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E107" s="22" t="s">
         <v>34</v>
@@ -13938,13 +13962,13 @@
         <v>486</v>
       </c>
       <c r="B108" s="22" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="C108" s="22">
         <v>1</v>
       </c>
       <c r="D108" s="22" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="E108" s="22" t="s">
         <v>34</v>
@@ -13955,16 +13979,16 @@
         <v>492</v>
       </c>
       <c r="B109" s="22" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="C109" s="22">
         <v>3</v>
       </c>
       <c r="D109" s="22" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="E109" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="24" customHeight="1">
@@ -13972,16 +13996,16 @@
         <v>492</v>
       </c>
       <c r="B110" s="22" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C110" s="22">
         <v>2</v>
       </c>
       <c r="D110" s="22" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E110" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="24" customHeight="1">
@@ -13989,13 +14013,13 @@
         <v>492</v>
       </c>
       <c r="B111" s="22" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="C111" s="22">
         <v>1</v>
       </c>
       <c r="D111" s="22" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="E111" s="22" t="s">
         <v>34</v>
@@ -14006,16 +14030,16 @@
         <v>492</v>
       </c>
       <c r="B112" s="22" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C112" s="22">
         <v>4</v>
       </c>
       <c r="D112" s="22" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="E112" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="24" customHeight="1">
@@ -14023,16 +14047,16 @@
         <v>492</v>
       </c>
       <c r="B113" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="C113" s="22">
         <v>5</v>
       </c>
       <c r="D113" s="22" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="E113" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="24" customHeight="1">
@@ -14040,13 +14064,13 @@
         <v>499</v>
       </c>
       <c r="B114" s="22" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="C114" s="22">
         <v>1</v>
       </c>
       <c r="D114" s="22" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="E114" s="22" t="s">
         <v>34</v>
@@ -14057,16 +14081,16 @@
         <v>499</v>
       </c>
       <c r="B115" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="C115" s="22">
         <v>2</v>
       </c>
       <c r="D115" s="22" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="E115" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="24" customHeight="1">
@@ -14074,13 +14098,13 @@
         <v>507</v>
       </c>
       <c r="B116" s="22" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="C116" s="22">
         <v>1</v>
       </c>
       <c r="D116" s="22" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="E116" s="22" t="s">
         <v>34</v>
@@ -14091,13 +14115,13 @@
         <v>513</v>
       </c>
       <c r="B117" s="22" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C117" s="22">
         <v>1</v>
       </c>
       <c r="D117" s="22" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="E117" s="22" t="s">
         <v>34</v>
@@ -14108,16 +14132,16 @@
         <v>513</v>
       </c>
       <c r="B118" s="22" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="C118" s="22">
         <v>2</v>
       </c>
       <c r="D118" s="22" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="E118" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="24" customHeight="1">
@@ -14125,13 +14149,13 @@
         <v>519</v>
       </c>
       <c r="B119" s="22" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="C119" s="22">
         <v>1</v>
       </c>
       <c r="D119" s="22" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="E119" s="22" t="s">
         <v>34</v>
@@ -14142,16 +14166,16 @@
         <v>519</v>
       </c>
       <c r="B120" s="22" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="C120" s="22">
         <v>2</v>
       </c>
       <c r="D120" s="22" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="E120" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="24" customHeight="1">
@@ -14159,13 +14183,13 @@
         <v>527</v>
       </c>
       <c r="B121" s="22" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="C121" s="22">
         <v>1</v>
       </c>
       <c r="D121" s="22" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="E121" s="22" t="s">
         <v>34</v>
@@ -14176,16 +14200,16 @@
         <v>527</v>
       </c>
       <c r="B122" s="22" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="C122" s="22">
         <v>2</v>
       </c>
       <c r="D122" s="22" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="E122" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="24" customHeight="1">
@@ -14193,16 +14217,16 @@
         <v>527</v>
       </c>
       <c r="B123" s="22" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C123" s="22">
         <v>3</v>
       </c>
       <c r="D123" s="22" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="E123" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="24" customHeight="1">
@@ -14210,13 +14234,13 @@
         <v>533</v>
       </c>
       <c r="B124" s="22" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="C124" s="22">
         <v>1</v>
       </c>
       <c r="D124" s="22" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="E124" s="22" t="s">
         <v>34</v>
@@ -14227,16 +14251,16 @@
         <v>533</v>
       </c>
       <c r="B125" s="22" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C125" s="22">
         <v>2</v>
       </c>
       <c r="D125" s="22" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="E125" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="24" customHeight="1">
@@ -14244,13 +14268,13 @@
         <v>537</v>
       </c>
       <c r="B126" s="22" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C126" s="22">
         <v>1</v>
       </c>
       <c r="D126" s="22" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="E126" s="22" t="s">
         <v>34</v>
@@ -14261,16 +14285,16 @@
         <v>537</v>
       </c>
       <c r="B127" s="22" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="C127" s="22">
         <v>2</v>
       </c>
       <c r="D127" s="22" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="E127" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="24" customHeight="1">
@@ -14278,16 +14302,16 @@
         <v>537</v>
       </c>
       <c r="B128" s="22" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="C128" s="22">
         <v>3</v>
       </c>
       <c r="D128" s="22" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="E128" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="24" customHeight="1">
@@ -14295,16 +14319,16 @@
         <v>537</v>
       </c>
       <c r="B129" s="22" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="C129" s="22">
         <v>4</v>
       </c>
       <c r="D129" s="22" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="E129" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="24" customHeight="1">
@@ -14312,13 +14336,13 @@
         <v>543</v>
       </c>
       <c r="B130" s="22" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="C130" s="22">
         <v>1</v>
       </c>
       <c r="D130" s="22" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="E130" s="22" t="s">
         <v>34</v>
@@ -14329,16 +14353,16 @@
         <v>543</v>
       </c>
       <c r="B131" s="22" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="C131" s="22">
         <v>2</v>
       </c>
       <c r="D131" s="22" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E131" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="24" customHeight="1">
@@ -14346,13 +14370,13 @@
         <v>550</v>
       </c>
       <c r="B132" s="22" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C132" s="22">
         <v>1</v>
       </c>
       <c r="D132" s="22" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="E132" s="22" t="s">
         <v>34</v>
@@ -14363,16 +14387,16 @@
         <v>550</v>
       </c>
       <c r="B133" s="22" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C133" s="22">
         <v>2</v>
       </c>
       <c r="D133" s="22" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="E133" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="24" customHeight="1">
@@ -14380,13 +14404,13 @@
         <v>557</v>
       </c>
       <c r="B134" s="22" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="C134" s="22">
         <v>1</v>
       </c>
       <c r="D134" s="22" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="E134" s="22" t="s">
         <v>34</v>
@@ -14397,16 +14421,16 @@
         <v>557</v>
       </c>
       <c r="B135" s="22" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="C135" s="22">
         <v>2</v>
       </c>
       <c r="D135" s="22" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="E135" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="24" customHeight="1">
@@ -14414,13 +14438,13 @@
         <v>564</v>
       </c>
       <c r="B136" s="22" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="C136" s="22">
         <v>1</v>
       </c>
       <c r="D136" s="22" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E136" s="22" t="s">
         <v>34</v>
@@ -14431,16 +14455,16 @@
         <v>564</v>
       </c>
       <c r="B137" s="22" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="C137" s="22">
         <v>2</v>
       </c>
       <c r="D137" s="22" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="E137" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="24" customHeight="1">
@@ -14448,16 +14472,16 @@
         <v>564</v>
       </c>
       <c r="B138" s="22" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="C138" s="22">
         <v>3</v>
       </c>
       <c r="D138" s="22" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="E138" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="24" customHeight="1">
@@ -14465,13 +14489,13 @@
         <v>570</v>
       </c>
       <c r="B139" s="22" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C139" s="22">
         <v>1</v>
       </c>
       <c r="D139" s="22" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="E139" s="22" t="s">
         <v>34</v>
@@ -14482,16 +14506,16 @@
         <v>570</v>
       </c>
       <c r="B140" s="22" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="C140" s="22">
         <v>2</v>
       </c>
       <c r="D140" s="22" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="E140" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="24" customHeight="1">
@@ -14499,16 +14523,16 @@
         <v>570</v>
       </c>
       <c r="B141" s="22" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="C141" s="22">
         <v>3</v>
       </c>
       <c r="D141" s="22" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E141" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="24" customHeight="1">
@@ -14516,16 +14540,16 @@
         <v>570</v>
       </c>
       <c r="B142" s="22" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C142" s="22">
         <v>4</v>
       </c>
       <c r="D142" s="22" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="E142" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="24" customHeight="1">
@@ -14533,13 +14557,13 @@
         <v>577</v>
       </c>
       <c r="B143" s="22" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="C143" s="22">
         <v>1</v>
       </c>
       <c r="D143" s="22" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="E143" s="22" t="s">
         <v>34</v>
@@ -14550,16 +14574,16 @@
         <v>577</v>
       </c>
       <c r="B144" s="22" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="C144" s="22">
         <v>2</v>
       </c>
       <c r="D144" s="22" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="E144" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="24" customHeight="1">
@@ -14567,16 +14591,16 @@
         <v>577</v>
       </c>
       <c r="B145" s="22" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C145" s="22">
         <v>3</v>
       </c>
       <c r="D145" s="22" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="E145" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="24" customHeight="1">
@@ -14584,13 +14608,13 @@
         <v>584</v>
       </c>
       <c r="B146" s="22" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="C146" s="22">
         <v>1</v>
       </c>
       <c r="D146" s="22" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="E146" s="22" t="s">
         <v>34</v>
@@ -14601,13 +14625,13 @@
         <v>591</v>
       </c>
       <c r="B147" s="22" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C147" s="22">
         <v>1</v>
       </c>
       <c r="D147" s="22" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="E147" s="22" t="s">
         <v>34</v>
@@ -14618,16 +14642,16 @@
         <v>591</v>
       </c>
       <c r="B148" s="22" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="C148" s="22">
         <v>2</v>
       </c>
       <c r="D148" s="22" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="E148" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="24" customHeight="1">
@@ -14635,16 +14659,16 @@
         <v>597</v>
       </c>
       <c r="B149" s="22" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C149" s="22">
         <v>2</v>
       </c>
       <c r="D149" s="22" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="E149" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="24" customHeight="1">
@@ -14652,13 +14676,13 @@
         <v>597</v>
       </c>
       <c r="B150" s="22" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C150" s="22">
         <v>1</v>
       </c>
       <c r="D150" s="22" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="E150" s="22" t="s">
         <v>34</v>
@@ -14669,13 +14693,13 @@
         <v>604</v>
       </c>
       <c r="B151" s="22" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C151" s="22">
         <v>1</v>
       </c>
       <c r="D151" s="22" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="E151" s="22" t="s">
         <v>34</v>
@@ -14686,16 +14710,16 @@
         <v>604</v>
       </c>
       <c r="B152" s="22" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="C152" s="22">
         <v>2</v>
       </c>
       <c r="D152" s="22" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="E152" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="24" customHeight="1">
@@ -14703,13 +14727,13 @@
         <v>612</v>
       </c>
       <c r="B153" s="22" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C153" s="22">
         <v>1</v>
       </c>
       <c r="D153" s="22" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="E153" s="22" t="s">
         <v>34</v>
@@ -14720,16 +14744,16 @@
         <v>612</v>
       </c>
       <c r="B154" s="22" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C154" s="22">
         <v>2</v>
       </c>
       <c r="D154" s="22" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="E154" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="24" customHeight="1">
@@ -14737,13 +14761,13 @@
         <v>618</v>
       </c>
       <c r="B155" s="22" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C155" s="22">
         <v>1</v>
       </c>
       <c r="D155" s="22" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="E155" s="22" t="s">
         <v>34</v>
@@ -14754,16 +14778,16 @@
         <v>618</v>
       </c>
       <c r="B156" s="22" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C156" s="22">
         <v>2</v>
       </c>
       <c r="D156" s="22" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="E156" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="24" customHeight="1">
@@ -14771,13 +14795,13 @@
         <v>625</v>
       </c>
       <c r="B157" s="22" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C157" s="22">
         <v>1</v>
       </c>
       <c r="D157" s="22" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="E157" s="22" t="s">
         <v>34</v>
@@ -14788,16 +14812,16 @@
         <v>625</v>
       </c>
       <c r="B158" s="22" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C158" s="22">
         <v>2</v>
       </c>
       <c r="D158" s="22" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="E158" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="24" customHeight="1">
@@ -14805,16 +14829,16 @@
         <v>625</v>
       </c>
       <c r="B159" s="22" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C159" s="22">
         <v>3</v>
       </c>
       <c r="D159" s="22" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="E159" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="24" customHeight="1">
@@ -14822,16 +14846,16 @@
         <v>625</v>
       </c>
       <c r="B160" s="22" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C160" s="22">
         <v>4</v>
       </c>
       <c r="D160" s="22" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="E160" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="24" customHeight="1">
@@ -14839,13 +14863,13 @@
         <v>632</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="C161" s="22">
         <v>1</v>
       </c>
       <c r="D161" s="22" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="E161" s="22" t="s">
         <v>34</v>
@@ -14853,16 +14877,16 @@
     </row>
     <row r="162" spans="1:5" ht="24" customHeight="1">
       <c r="A162" s="22" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B162" s="22" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="C162" s="22">
         <v>1</v>
       </c>
       <c r="D162" s="22" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E162" s="22" t="s">
         <v>34</v>
@@ -14870,84 +14894,84 @@
     </row>
     <row r="163" spans="1:5" ht="24" customHeight="1">
       <c r="A163" s="22" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B163" s="22" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="C163" s="22">
         <v>5</v>
       </c>
       <c r="D163" s="22" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="E163" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="24" customHeight="1">
       <c r="A164" s="22" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B164" s="22" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="C164" s="22">
         <v>2</v>
       </c>
       <c r="D164" s="22" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="E164" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="24" customHeight="1">
       <c r="A165" s="22" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="C165" s="22">
         <v>3</v>
       </c>
       <c r="D165" s="22" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="E165" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="24" customHeight="1">
       <c r="A166" s="22" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B166" s="22" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="C166" s="22">
         <v>4</v>
       </c>
       <c r="D166" s="22" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="E166" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="24" customHeight="1">
       <c r="A167" s="22" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B167" s="22" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="C167" s="22">
         <v>1</v>
       </c>
       <c r="D167" s="22" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E167" s="22" t="s">
         <v>34</v>
@@ -14955,16 +14979,16 @@
     </row>
     <row r="168" spans="1:5" ht="24" customHeight="1">
       <c r="A168" s="22" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B168" s="22" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="C168" s="22">
         <v>1</v>
       </c>
       <c r="D168" s="22" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="E168" s="22" t="s">
         <v>34</v>
@@ -14972,16 +14996,16 @@
     </row>
     <row r="169" spans="1:5" ht="24" customHeight="1">
       <c r="A169" s="22" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B169" s="22" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="C169" s="22">
         <v>1</v>
       </c>
       <c r="D169" s="22" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="E169" s="22" t="s">
         <v>34</v>
@@ -14989,16 +15013,16 @@
     </row>
     <row r="170" spans="1:5" ht="24" customHeight="1">
       <c r="A170" s="22" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B170" s="22" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="C170" s="22">
         <v>1</v>
       </c>
       <c r="D170" s="22" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="E170" s="22" t="s">
         <v>34</v>
@@ -15006,16 +15030,16 @@
     </row>
     <row r="171" spans="1:5" ht="24" customHeight="1">
       <c r="A171" s="22" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B171" s="22" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="C171" s="22">
         <v>1</v>
       </c>
       <c r="D171" s="22" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="E171" s="22" t="s">
         <v>34</v>
@@ -15023,16 +15047,16 @@
     </row>
     <row r="172" spans="1:5" ht="24" customHeight="1">
       <c r="A172" s="22" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B172" s="22" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="C172" s="22">
         <v>1</v>
       </c>
       <c r="D172" s="22" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E172" s="22" t="s">
         <v>34</v>
@@ -15040,16 +15064,16 @@
     </row>
     <row r="173" spans="1:5" ht="24" customHeight="1">
       <c r="A173" s="22" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B173" s="22" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="C173" s="22">
         <v>1</v>
       </c>
       <c r="D173" s="22" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="E173" s="22" t="s">
         <v>34</v>
@@ -15057,16 +15081,16 @@
     </row>
     <row r="174" spans="1:5" ht="24" customHeight="1">
       <c r="A174" s="22" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B174" s="22" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C174" s="22">
         <v>1</v>
       </c>
       <c r="D174" s="22" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="E174" s="22" t="s">
         <v>34</v>
@@ -15074,16 +15098,16 @@
     </row>
     <row r="175" spans="1:5" ht="24" customHeight="1">
       <c r="A175" s="22" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B175" s="22" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="C175" s="22">
         <v>1</v>
       </c>
       <c r="D175" s="22" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="E175" s="22" t="s">
         <v>34</v>
@@ -15091,16 +15115,16 @@
     </row>
     <row r="176" spans="1:5" ht="24" customHeight="1">
       <c r="A176" s="22" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B176" s="22" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C176" s="22">
         <v>1</v>
       </c>
       <c r="D176" s="22" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="E176" s="22" t="s">
         <v>34</v>
@@ -15108,16 +15132,16 @@
     </row>
     <row r="177" spans="1:5" ht="24" customHeight="1">
       <c r="A177" s="22" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B177" s="22" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="C177" s="22">
         <v>1</v>
       </c>
       <c r="D177" s="22" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E177" s="22" t="s">
         <v>34</v>
@@ -15125,50 +15149,50 @@
     </row>
     <row r="178" spans="1:5" ht="24" customHeight="1">
       <c r="A178" s="22" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B178" s="22" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C178" s="22">
         <v>2</v>
       </c>
       <c r="D178" s="22" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="E178" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="24" customHeight="1">
       <c r="A179" s="22" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B179" s="22" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="C179" s="22">
         <v>2</v>
       </c>
       <c r="D179" s="22" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="E179" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="24" customHeight="1">
       <c r="A180" s="22" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B180" s="22" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="C180" s="22">
         <v>1</v>
       </c>
       <c r="D180" s="22" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="E180" s="22" t="s">
         <v>34</v>
@@ -15176,16 +15200,16 @@
     </row>
     <row r="181" spans="1:5" ht="24" customHeight="1">
       <c r="A181" s="22" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B181" s="22" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="C181" s="22">
         <v>1</v>
       </c>
       <c r="D181" s="22" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="E181" s="22" t="s">
         <v>34</v>
@@ -15193,44 +15217,44 @@
     </row>
     <row r="182" spans="1:5" ht="24" customHeight="1">
       <c r="A182" s="22" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B182" s="22" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C182" s="22">
         <v>2</v>
       </c>
       <c r="D182" s="22" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="E182" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="24" customHeight="1">
       <c r="A183" s="22" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B183" s="22" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="C183" s="22">
         <v>3</v>
       </c>
       <c r="D183" s="22" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E183" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="22" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B184" s="22" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C184" s="22">
         <v>1</v>
@@ -15242,85 +15266,85 @@
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="22" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B185" s="22" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="C185" s="22">
         <v>2</v>
       </c>
       <c r="D185" s="25"/>
       <c r="E185" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="22" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B186" s="22" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C186" s="22">
         <v>3</v>
       </c>
       <c r="D186" s="25"/>
       <c r="E186" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="22" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B187" s="22" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="C187" s="22">
         <v>4</v>
       </c>
       <c r="D187" s="25"/>
       <c r="E187" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="22" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B188" s="22" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C188" s="22">
         <v>3</v>
       </c>
       <c r="D188" s="25"/>
       <c r="E188" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="22" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B189" s="22" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C189" s="22">
         <v>2</v>
       </c>
       <c r="D189" s="25"/>
       <c r="E189" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="22" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B190" s="22" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C190" s="22">
         <v>1</v>
@@ -15332,10 +15356,10 @@
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="22" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B191" s="22" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="C191" s="22">
         <v>1</v>
@@ -15347,85 +15371,85 @@
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="22" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B192" s="22" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="C192" s="22">
         <v>2</v>
       </c>
       <c r="D192" s="25"/>
       <c r="E192" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="22" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B193" s="22" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="C193" s="22">
         <v>3</v>
       </c>
       <c r="D193" s="25"/>
       <c r="E193" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="22" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B194" s="22" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="C194" s="22">
         <v>4</v>
       </c>
       <c r="D194" s="25"/>
       <c r="E194" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="22" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B195" s="22" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="C195" s="22">
         <v>5</v>
       </c>
       <c r="D195" s="25"/>
       <c r="E195" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="22" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B196" s="22" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C196" s="22">
         <v>6</v>
       </c>
       <c r="D196" s="25"/>
       <c r="E196" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="22" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B197" s="22" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="C197" s="22">
         <v>1</v>
@@ -15437,40 +15461,40 @@
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="22" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B198" s="22" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="C198" s="22">
         <v>2</v>
       </c>
       <c r="D198" s="25"/>
       <c r="E198" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="22" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B199" s="22" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="C199" s="22">
         <v>3</v>
       </c>
       <c r="D199" s="25"/>
       <c r="E199" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="22" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B200" s="22" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="C200" s="22">
         <v>1</v>
@@ -15482,10 +15506,10 @@
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="22" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B201" s="22" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="C201" s="22">
         <v>1</v>
@@ -15497,25 +15521,25 @@
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="22" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B202" s="22" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="C202" s="22">
         <v>2</v>
       </c>
       <c r="D202" s="25"/>
       <c r="E202" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="22" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B203" s="22" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="C203" s="22">
         <v>1</v>
@@ -15527,25 +15551,25 @@
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="22" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B204" s="22" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="C204" s="22">
         <v>2</v>
       </c>
       <c r="D204" s="25"/>
       <c r="E204" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="22" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B205" s="22" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="C205" s="22">
         <v>1</v>
@@ -15557,40 +15581,40 @@
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="22" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B206" s="22" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="C206" s="22">
         <v>2</v>
       </c>
       <c r="D206" s="25"/>
       <c r="E206" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="22" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B207" s="22" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="C207" s="22">
         <v>3</v>
       </c>
       <c r="D207" s="25"/>
       <c r="E207" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="22" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B208" s="22" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="C208" s="22">
         <v>1</v>
@@ -15602,25 +15626,25 @@
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="22" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B209" s="22" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="C209" s="22">
         <v>2</v>
       </c>
       <c r="D209" s="25"/>
       <c r="E209" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="22" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B210" s="22" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="C210" s="22">
         <v>1</v>
@@ -15632,10 +15656,10 @@
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="22" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B211" s="22" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="C211" s="22">
         <v>1</v>
@@ -15647,10 +15671,10 @@
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="22" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B212" s="22" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="C212" s="22">
         <v>1</v>
@@ -15662,10 +15686,10 @@
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="22" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B213" s="22" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="C213" s="22">
         <v>1</v>
@@ -15677,10 +15701,10 @@
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="22" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B214" s="22" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="C214" s="22">
         <v>1</v>
@@ -15692,25 +15716,25 @@
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="22" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B215" s="22" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="C215" s="22">
         <v>2</v>
       </c>
       <c r="D215" s="25"/>
       <c r="E215" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="22" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B216" s="22" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="C216" s="22">
         <v>1</v>
@@ -15722,10 +15746,10 @@
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="22" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B217" s="22" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="C217" s="22">
         <v>1</v>
@@ -15737,10 +15761,10 @@
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="22" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B218" s="22" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="C218" s="22">
         <v>1</v>
@@ -15752,55 +15776,55 @@
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="22" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B219" s="22" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C219" s="22">
         <v>2</v>
       </c>
       <c r="D219" s="25"/>
       <c r="E219" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="22" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B220" s="22" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="C220" s="22">
         <v>3</v>
       </c>
       <c r="D220" s="25"/>
       <c r="E220" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="22" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B221" s="22" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="C221" s="22">
         <v>4</v>
       </c>
       <c r="D221" s="25"/>
       <c r="E221" s="22" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="22" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B222" s="22" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="C222" s="22">
         <v>1</v>
@@ -15812,10 +15836,10 @@
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="22" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="B223" s="25" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="C223" s="22">
         <v>1</v>
@@ -15826,16 +15850,16 @@
     </row>
     <row r="224" spans="1:5" ht="28">
       <c r="A224" s="26" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B224" s="25" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="C224" s="22">
         <v>1</v>
       </c>
       <c r="D224" s="26" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="E224" s="26" t="s">
         <v>34</v>
@@ -15843,118 +15867,118 @@
     </row>
     <row r="225" spans="1:5" ht="28">
       <c r="A225" s="26" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B225" s="25" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="C225" s="22">
         <v>2</v>
       </c>
       <c r="D225" s="26" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="E225" s="26" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="226" spans="1:5" ht="28">
       <c r="A226" s="26" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B226" s="25" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="C226" s="22">
         <v>3</v>
       </c>
       <c r="D226" s="26" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="E226" s="26" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="227" spans="1:5" ht="28">
       <c r="A227" s="26" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B227" s="25" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="C227" s="22">
         <v>4</v>
       </c>
       <c r="D227" s="26" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="E227" s="26" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="228" spans="1:5" ht="28">
       <c r="A228" s="26" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B228" s="25" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="C228" s="22">
         <v>5</v>
       </c>
       <c r="D228" s="26" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="E228" s="26" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="229" spans="1:5" ht="28">
       <c r="A229" s="26" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B229" s="25" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="C229" s="22">
         <v>6</v>
       </c>
       <c r="D229" s="26" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="E229" s="26" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="26" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B230" s="25" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="C230" s="22">
         <v>2</v>
       </c>
       <c r="D230" s="26" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="E230" s="26" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="26" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B231" s="25" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="C231" s="22">
         <v>1</v>
       </c>
       <c r="D231" s="26" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="E231" s="26" t="s">
         <v>34</v>
@@ -15962,16 +15986,16 @@
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="26" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="B232" s="25" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="C232" s="22">
         <v>1</v>
       </c>
       <c r="D232" s="26" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="E232" s="26" t="s">
         <v>34</v>
@@ -15979,33 +16003,33 @@
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="26" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="B233" s="25" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="C233" s="22">
         <v>2</v>
       </c>
       <c r="D233" s="26" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="E233" s="26" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="26" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="B234" s="25" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="C234" s="22">
         <v>1</v>
       </c>
       <c r="D234" s="26" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E234" s="26" t="s">
         <v>34</v>
@@ -16013,33 +16037,33 @@
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="26" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="B235" s="25" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="C235" s="22">
         <v>2</v>
       </c>
       <c r="D235" s="26" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="E235" s="26" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="26" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="B236" s="25" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="C236" s="22">
         <v>1</v>
       </c>
       <c r="D236" s="26" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="E236" s="26" t="s">
         <v>34</v>
@@ -16047,33 +16071,33 @@
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="26" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="B237" s="25" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="C237" s="22">
         <v>2</v>
       </c>
       <c r="D237" s="26" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="E237" s="26" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="26" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B238" s="25" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="C238" s="22">
         <v>1</v>
       </c>
       <c r="D238" s="26" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E238" s="26" t="s">
         <v>34</v>
@@ -16081,33 +16105,33 @@
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="26" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B239" s="25" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="C239" s="22">
         <v>2</v>
       </c>
       <c r="D239" s="26" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="E239" s="26" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="26" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B240" s="25" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="C240" s="22">
         <v>1</v>
       </c>
       <c r="D240" s="26" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="E240" s="26" t="s">
         <v>34</v>
@@ -16145,107 +16169,107 @@
   <sheetData>
     <row r="1" spans="1:6" ht="23" customHeight="1">
       <c r="A1" s="35" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+        <v>1002</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1">
       <c r="A3" s="36" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
+        <v>1003</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
     </row>
     <row r="4" spans="1:6" ht="46" customHeight="1">
       <c r="A4" s="34" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
+        <v>1004</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1">
       <c r="A6" s="36" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
+        <v>1005</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
     </row>
     <row r="7" spans="1:6" ht="54" customHeight="1">
       <c r="A7" s="34" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
+        <v>1006</v>
+      </c>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1">
       <c r="A9" s="36" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
+        <v>1007</v>
+      </c>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
     </row>
     <row r="10" spans="1:6" ht="46" customHeight="1">
       <c r="A10" s="34" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
+        <v>1008</v>
+      </c>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1">
       <c r="A12" s="36" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
+        <v>1009</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
     </row>
     <row r="13" spans="1:6" ht="54" customHeight="1">
       <c r="A13" s="34" t="s">
-        <v>1012</v>
-      </c>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
+        <v>1010</v>
+      </c>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
     </row>
     <row r="14" spans="1:6" ht="32" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="32" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="32" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
   </sheetData>
